--- a/NL2SPARQL_Evaluation_Results.xlsx
+++ b/NL2SPARQL_Evaluation_Results.xlsx
@@ -16785,7 +16785,7 @@
         <v>0</v>
       </c>
       <c r="N260" s="5" t="n">
-        <v>41.85</v>
+        <v>34.35</v>
       </c>
     </row>
     <row r="261">
@@ -16839,13 +16839,13 @@
         </is>
       </c>
       <c r="L261" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M261" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N261" s="5" t="n">
-        <v>22.83</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="262">
@@ -16905,7 +16905,7 @@
         <v>0</v>
       </c>
       <c r="N262" s="5" t="n">
-        <v>19.11</v>
+        <v>18.83</v>
       </c>
     </row>
     <row r="263">
@@ -16965,7 +16965,7 @@
         <v>0</v>
       </c>
       <c r="N263" s="5" t="n">
-        <v>17.71</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="264">
@@ -17004,11 +17004,11 @@
       </c>
       <c r="H264" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I264" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J264" s="5" t="b">
         <v>1</v>
@@ -17025,7 +17025,7 @@
         <v>0</v>
       </c>
       <c r="N264" s="5" t="n">
-        <v>21.88</v>
+        <v>44.76</v>
       </c>
     </row>
     <row r="265">
@@ -17085,7 +17085,7 @@
         <v>0</v>
       </c>
       <c r="N265" s="5" t="n">
-        <v>19.26</v>
+        <v>18.67</v>
       </c>
     </row>
     <row r="266">
@@ -17124,24 +17124,24 @@
       </c>
       <c r="H266" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I266" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J266" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K266" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L266" s="5" t="n"/>
       <c r="M266" s="5" t="n"/>
       <c r="N266" s="5" t="n">
-        <v>30.12</v>
+        <v>29.63</v>
       </c>
     </row>
     <row r="267">
@@ -17180,11 +17180,11 @@
       </c>
       <c r="H267" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I267" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J267" s="5" t="b">
         <v>1</v>
@@ -17197,7 +17197,7 @@
       <c r="L267" s="5" t="n"/>
       <c r="M267" s="5" t="n"/>
       <c r="N267" s="5" t="n">
-        <v>24.6</v>
+        <v>28.54</v>
       </c>
     </row>
     <row r="268">
@@ -17236,24 +17236,24 @@
       </c>
       <c r="H268" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I268" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J268" s="5" t="b">
         <v>1</v>
       </c>
       <c r="K268" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L268" s="5" t="n"/>
       <c r="M268" s="5" t="n"/>
       <c r="N268" s="5" t="n">
-        <v>36.11</v>
+        <v>25.66</v>
       </c>
     </row>
     <row r="269">
@@ -17292,24 +17292,24 @@
       </c>
       <c r="H269" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I269" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J269" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K269" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L269" s="5" t="n"/>
       <c r="M269" s="5" t="n"/>
       <c r="N269" s="5" t="n">
-        <v>14.57</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="270">
@@ -17348,24 +17348,24 @@
       </c>
       <c r="H270" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I270" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J270" s="5" t="b">
         <v>1</v>
       </c>
       <c r="K270" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L270" s="5" t="n"/>
       <c r="M270" s="5" t="n"/>
       <c r="N270" s="5" t="n">
-        <v>24.34</v>
+        <v>28.52</v>
       </c>
     </row>
     <row r="271">
@@ -17404,24 +17404,24 @@
       </c>
       <c r="H271" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I271" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J271" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K271" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>generation_failure</t>
         </is>
       </c>
       <c r="L271" s="5" t="n"/>
       <c r="M271" s="5" t="n"/>
       <c r="N271" s="5" t="n">
-        <v>23.67</v>
+        <v>26.41</v>
       </c>
     </row>
     <row r="272">
@@ -17481,7 +17481,7 @@
         <v>0.2222</v>
       </c>
       <c r="N272" s="5" t="n">
-        <v>19.44</v>
+        <v>19.22</v>
       </c>
     </row>
     <row r="273">
@@ -17541,7 +17541,7 @@
         <v>0.2667</v>
       </c>
       <c r="N273" s="5" t="n">
-        <v>15.3</v>
+        <v>18.63</v>
       </c>
     </row>
     <row r="274">
@@ -17601,7 +17601,7 @@
         <v>0.2667</v>
       </c>
       <c r="N274" s="5" t="n">
-        <v>21.1</v>
+        <v>19.48</v>
       </c>
     </row>
     <row r="275">
@@ -17661,7 +17661,7 @@
         <v>0.2222</v>
       </c>
       <c r="N275" s="5" t="n">
-        <v>19.01</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="276">
@@ -17721,7 +17721,7 @@
         <v>0.2222</v>
       </c>
       <c r="N276" s="5" t="n">
-        <v>14.68</v>
+        <v>19.21</v>
       </c>
     </row>
     <row r="277">
@@ -17767,21 +17767,21 @@
         <v>1</v>
       </c>
       <c r="J277" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K277" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>sparql_build_failure</t>
         </is>
       </c>
       <c r="L277" s="5" t="b">
         <v>0</v>
       </c>
       <c r="M277" s="5" t="n">
-        <v>0.2222</v>
+        <v>0</v>
       </c>
       <c r="N277" s="5" t="n">
-        <v>13.68</v>
+        <v>18.31</v>
       </c>
     </row>
     <row r="278">
@@ -17841,7 +17841,7 @@
         <v>0.3077</v>
       </c>
       <c r="N278" s="5" t="n">
-        <v>15.66</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="279">
@@ -17901,7 +17901,7 @@
         <v>0.3077</v>
       </c>
       <c r="N279" s="5" t="n">
-        <v>15.02</v>
+        <v>21.77</v>
       </c>
     </row>
     <row r="280">
@@ -17961,7 +17961,7 @@
         <v>0.3077</v>
       </c>
       <c r="N280" s="5" t="n">
-        <v>14.68</v>
+        <v>14.83</v>
       </c>
     </row>
     <row r="281">
@@ -17998,7 +17998,7 @@
       </c>
       <c r="H281" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I281" s="5" t="b">
@@ -18015,7 +18015,7 @@
       <c r="L281" s="5" t="n"/>
       <c r="M281" s="5" t="n"/>
       <c r="N281" s="5" t="n">
-        <v>10.43</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="282">
@@ -18069,7 +18069,7 @@
       <c r="L282" s="5" t="n"/>
       <c r="M282" s="5" t="n"/>
       <c r="N282" s="5" t="n">
-        <v>25.87</v>
+        <v>32.02</v>
       </c>
     </row>
     <row r="283">
@@ -18123,7 +18123,7 @@
       <c r="L283" s="5" t="n"/>
       <c r="M283" s="5" t="n"/>
       <c r="N283" s="5" t="n">
-        <v>4.37</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="284">
@@ -18183,7 +18183,7 @@
         <v>0</v>
       </c>
       <c r="N284" s="5" t="n">
-        <v>4.57</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="285">
@@ -18243,7 +18243,7 @@
         <v>0</v>
       </c>
       <c r="N285" s="5" t="n">
-        <v>16.48</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="286">
@@ -18303,7 +18303,7 @@
         <v>0</v>
       </c>
       <c r="N286" s="5" t="n">
-        <v>4.78</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="287">
@@ -18363,7 +18363,7 @@
         <v>0</v>
       </c>
       <c r="N287" s="5" t="n">
-        <v>4.27</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="288">
@@ -18423,7 +18423,7 @@
         <v>0</v>
       </c>
       <c r="N288" s="5" t="n">
-        <v>20.26</v>
+        <v>18.68</v>
       </c>
     </row>
     <row r="289">
@@ -18483,7 +18483,7 @@
         <v>0</v>
       </c>
       <c r="N289" s="5" t="n">
-        <v>4.85</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="290">
@@ -18543,7 +18543,7 @@
         <v>1</v>
       </c>
       <c r="N290" s="5" t="n">
-        <v>4.8</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="291">
@@ -18603,7 +18603,7 @@
         <v>0</v>
       </c>
       <c r="N291" s="5" t="n">
-        <v>23.19</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="292">
@@ -18663,7 +18663,7 @@
         <v>0</v>
       </c>
       <c r="N292" s="5" t="n">
-        <v>6.06</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="293">
@@ -18723,7 +18723,7 @@
         <v>1</v>
       </c>
       <c r="N293" s="5" t="n">
-        <v>15.89</v>
+        <v>14.42</v>
       </c>
     </row>
     <row r="294">
@@ -18783,7 +18783,7 @@
         <v>1</v>
       </c>
       <c r="N294" s="5" t="n">
-        <v>16.31</v>
+        <v>16.02</v>
       </c>
     </row>
     <row r="295">
@@ -18843,7 +18843,7 @@
         <v>1</v>
       </c>
       <c r="N295" s="5" t="n">
-        <v>16.23</v>
+        <v>16.86</v>
       </c>
     </row>
     <row r="296">
@@ -18903,7 +18903,7 @@
         <v>1</v>
       </c>
       <c r="N296" s="5" t="n">
-        <v>27.19</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="297">
@@ -18963,7 +18963,7 @@
         <v>0.2</v>
       </c>
       <c r="N297" s="5" t="n">
-        <v>17.95</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="298">
@@ -19023,7 +19023,7 @@
         <v>0.2</v>
       </c>
       <c r="N298" s="5" t="n">
-        <v>23.28</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="299">
@@ -19083,7 +19083,7 @@
         <v>1</v>
       </c>
       <c r="N299" s="5" t="n">
-        <v>22.71</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="300">
@@ -19143,7 +19143,7 @@
         <v>1</v>
       </c>
       <c r="N300" s="5" t="n">
-        <v>22.14</v>
+        <v>21.68</v>
       </c>
     </row>
     <row r="301">
@@ -19203,7 +19203,7 @@
         <v>1</v>
       </c>
       <c r="N301" s="5" t="n">
-        <v>20.34</v>
+        <v>19.29</v>
       </c>
     </row>
     <row r="302">
@@ -19263,7 +19263,7 @@
         <v>1</v>
       </c>
       <c r="N302" s="5" t="n">
-        <v>16.41</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="303">
@@ -19323,7 +19323,7 @@
         <v>1</v>
       </c>
       <c r="N303" s="5" t="n">
-        <v>15.42</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="304">
@@ -19383,7 +19383,7 @@
         <v>1</v>
       </c>
       <c r="N304" s="5" t="n">
-        <v>15.65</v>
+        <v>15.37</v>
       </c>
     </row>
     <row r="305">
@@ -19443,7 +19443,7 @@
         <v>1</v>
       </c>
       <c r="N305" s="5" t="n">
-        <v>15.29</v>
+        <v>13.91</v>
       </c>
     </row>
     <row r="306">
@@ -19503,7 +19503,7 @@
         <v>1</v>
       </c>
       <c r="N306" s="5" t="n">
-        <v>16.23</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="307">
@@ -19563,7 +19563,7 @@
         <v>1</v>
       </c>
       <c r="N307" s="5" t="n">
-        <v>15.69</v>
+        <v>15.59</v>
       </c>
     </row>
     <row r="308">
@@ -19623,7 +19623,7 @@
         <v>0</v>
       </c>
       <c r="N308" s="5" t="n">
-        <v>3.95</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="309">
@@ -19669,11 +19669,11 @@
         <v>1</v>
       </c>
       <c r="J309" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K309" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L309" s="5" t="b">
@@ -19683,7 +19683,7 @@
         <v>0</v>
       </c>
       <c r="N309" s="5" t="n">
-        <v>3.07</v>
+        <v>19.71</v>
       </c>
     </row>
     <row r="310">
@@ -19743,7 +19743,7 @@
         <v>0</v>
       </c>
       <c r="N310" s="5" t="n">
-        <v>5.5</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="311">
@@ -19803,7 +19803,7 @@
         <v>1</v>
       </c>
       <c r="N311" s="5" t="n">
-        <v>15.77</v>
+        <v>15.09</v>
       </c>
     </row>
     <row r="312">
@@ -19863,7 +19863,7 @@
         <v>1</v>
       </c>
       <c r="N312" s="5" t="n">
-        <v>17.23</v>
+        <v>16.61</v>
       </c>
     </row>
     <row r="313">
@@ -19923,7 +19923,7 @@
         <v>1</v>
       </c>
       <c r="N313" s="5" t="n">
-        <v>17.31</v>
+        <v>15.26</v>
       </c>
     </row>
     <row r="314">
@@ -19979,7 +19979,7 @@
       <c r="L314" s="5" t="n"/>
       <c r="M314" s="5" t="n"/>
       <c r="N314" s="5" t="n">
-        <v>12.18</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="315">
@@ -20035,7 +20035,7 @@
       <c r="L315" s="5" t="n"/>
       <c r="M315" s="5" t="n"/>
       <c r="N315" s="5" t="n">
-        <v>12.88</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="316">
@@ -20091,7 +20091,7 @@
       <c r="L316" s="5" t="n"/>
       <c r="M316" s="5" t="n"/>
       <c r="N316" s="5" t="n">
-        <v>14.07</v>
+        <v>13.17</v>
       </c>
     </row>
     <row r="317">
@@ -20151,7 +20151,7 @@
         <v>0.5</v>
       </c>
       <c r="N317" s="5" t="n">
-        <v>13.23</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="318">
@@ -20211,7 +20211,7 @@
         <v>0.5</v>
       </c>
       <c r="N318" s="5" t="n">
-        <v>14.15</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="319">
@@ -20271,7 +20271,7 @@
         <v>0.5</v>
       </c>
       <c r="N319" s="5" t="n">
-        <v>13.18</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="320">
@@ -20383,7 +20383,7 @@
       <c r="L321" s="5" t="n"/>
       <c r="M321" s="5" t="n"/>
       <c r="N321" s="5" t="n">
-        <v>12.78</v>
+        <v>11.82</v>
       </c>
     </row>
     <row r="322">
@@ -20439,7 +20439,7 @@
       <c r="L322" s="5" t="n"/>
       <c r="M322" s="5" t="n"/>
       <c r="N322" s="5" t="n">
-        <v>13.62</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="323">
@@ -20495,7 +20495,7 @@
       <c r="L323" s="5" t="n"/>
       <c r="M323" s="5" t="n"/>
       <c r="N323" s="5" t="n">
-        <v>12.18</v>
+        <v>11.83</v>
       </c>
     </row>
     <row r="324">
@@ -20551,7 +20551,7 @@
       <c r="L324" s="5" t="n"/>
       <c r="M324" s="5" t="n"/>
       <c r="N324" s="5" t="n">
-        <v>13.04</v>
+        <v>12.11</v>
       </c>
     </row>
     <row r="325">
@@ -20607,7 +20607,7 @@
       <c r="L325" s="5" t="n"/>
       <c r="M325" s="5" t="n"/>
       <c r="N325" s="5" t="n">
-        <v>12.73</v>
+        <v>11.46</v>
       </c>
     </row>
   </sheetData>

--- a/NL2SPARQL_Evaluation_Results.xlsx
+++ b/NL2SPARQL_Evaluation_Results.xlsx
@@ -17427,7 +17427,7 @@
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B272" s="5" t="n">
@@ -17478,16 +17478,16 @@
         <v>0</v>
       </c>
       <c r="M272" s="5" t="n">
-        <v>0.2222</v>
+        <v>0.3077</v>
       </c>
       <c r="N272" s="5" t="n">
-        <v>19.22</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B273" s="5" t="n">
@@ -17538,16 +17538,16 @@
         <v>0</v>
       </c>
       <c r="M273" s="5" t="n">
-        <v>0.2667</v>
+        <v>0.3077</v>
       </c>
       <c r="N273" s="5" t="n">
-        <v>18.63</v>
+        <v>21.77</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B274" s="5" t="n">
@@ -17598,30 +17598,28 @@
         <v>0</v>
       </c>
       <c r="M274" s="5" t="n">
-        <v>0.2667</v>
+        <v>0.3077</v>
       </c>
       <c r="N274" s="5" t="n">
-        <v>19.48</v>
+        <v>14.83</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B275" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D275" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D275" s="5" t="n">
+        <v/>
       </c>
       <c r="E275" s="5" t="inlineStr">
         <is>
@@ -17635,53 +17633,47 @@
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H275" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I275" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J275" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K275" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L275" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M275" s="5" t="n">
-        <v>0.2222</v>
-      </c>
+          <t>mapping_failure</t>
+        </is>
+      </c>
+      <c r="L275" s="5" t="n"/>
+      <c r="M275" s="5" t="n"/>
       <c r="N275" s="5" t="n">
-        <v>19.1</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B276" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D276" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D276" s="5" t="n">
+        <v/>
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
@@ -17695,16 +17687,16 @@
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H276" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I276" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J276" s="5" t="b">
         <v>1</v>
@@ -17714,34 +17706,28 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L276" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M276" s="5" t="n">
-        <v>0.2222</v>
-      </c>
+      <c r="L276" s="5" t="n"/>
+      <c r="M276" s="5" t="n"/>
       <c r="N276" s="5" t="n">
-        <v>19.21</v>
+        <v>32.02</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B277" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C277" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D277" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D277" s="5" t="n">
+        <v/>
       </c>
       <c r="E277" s="5" t="inlineStr">
         <is>
@@ -17755,52 +17741,48 @@
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H277" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I277" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J277" s="5" t="b">
         <v>0</v>
       </c>
       <c r="K277" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L277" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M277" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>mapping_failure</t>
+        </is>
+      </c>
+      <c r="L277" s="5" t="n"/>
+      <c r="M277" s="5" t="n"/>
       <c r="N277" s="5" t="n">
-        <v>18.31</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B278" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E278" s="5" t="inlineStr">
@@ -17815,12 +17797,12 @@
       </c>
       <c r="G278" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H278" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I278" s="5" t="b">
@@ -17838,29 +17820,29 @@
         <v>0</v>
       </c>
       <c r="M278" s="5" t="n">
-        <v>0.3077</v>
+        <v>0</v>
       </c>
       <c r="N278" s="5" t="n">
-        <v>14.76</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B279" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E279" s="5" t="inlineStr">
@@ -17875,16 +17857,16 @@
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H279" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I279" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J279" s="5" t="b">
         <v>1</v>
@@ -17898,29 +17880,29 @@
         <v>0</v>
       </c>
       <c r="M279" s="5" t="n">
-        <v>0.3077</v>
+        <v>0</v>
       </c>
       <c r="N279" s="5" t="n">
-        <v>21.77</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B280" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E280" s="5" t="inlineStr">
@@ -17935,12 +17917,12 @@
       </c>
       <c r="G280" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H280" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I280" s="5" t="b">
@@ -17958,16 +17940,16 @@
         <v>0</v>
       </c>
       <c r="M280" s="5" t="n">
-        <v>0.3077</v>
+        <v>0</v>
       </c>
       <c r="N280" s="5" t="n">
-        <v>14.83</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B281" s="5" t="n">
@@ -17975,11 +17957,13 @@
       </c>
       <c r="C281" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D281" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D281" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E281" s="5" t="inlineStr">
         <is>
@@ -17993,35 +17977,39 @@
       </c>
       <c r="G281" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H281" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I281" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J281" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K281" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L281" s="5" t="n"/>
-      <c r="M281" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L281" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M281" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N281" s="5" t="n">
-        <v>14.29</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B282" s="5" t="n">
@@ -18029,11 +18017,13 @@
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D282" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D282" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E282" s="5" t="inlineStr">
         <is>
@@ -18047,12 +18037,12 @@
       </c>
       <c r="G282" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H282" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I282" s="5" t="b">
@@ -18066,16 +18056,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L282" s="5" t="n"/>
-      <c r="M282" s="5" t="n"/>
+      <c r="L282" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M282" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N282" s="5" t="n">
-        <v>32.02</v>
+        <v>18.68</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B283" s="5" t="n">
@@ -18083,11 +18077,13 @@
       </c>
       <c r="C283" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D283" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D283" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E283" s="5" t="inlineStr">
         <is>
@@ -18101,7 +18097,7 @@
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H283" s="5" t="inlineStr">
@@ -18110,7 +18106,7 @@
         </is>
       </c>
       <c r="I283" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J283" s="5" t="b">
         <v>0</v>
@@ -18120,16 +18116,20 @@
           <t>mapping_failure</t>
         </is>
       </c>
-      <c r="L283" s="5" t="n"/>
-      <c r="M283" s="5" t="n"/>
+      <c r="L283" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M283" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N283" s="5" t="n">
-        <v>5.66</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B284" s="5" t="n">
@@ -18177,19 +18177,19 @@
         </is>
       </c>
       <c r="L284" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M284" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N284" s="5" t="n">
-        <v>4.77</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B285" s="5" t="n">
@@ -18222,7 +18222,7 @@
       </c>
       <c r="H285" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I285" s="5" t="b">
@@ -18243,13 +18243,13 @@
         <v>0</v>
       </c>
       <c r="N285" s="5" t="n">
-        <v>16.99</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B286" s="5" t="n">
@@ -18289,11 +18289,11 @@
         <v>1</v>
       </c>
       <c r="J286" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K286" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L286" s="5" t="b">
@@ -18303,13 +18303,13 @@
         <v>0</v>
       </c>
       <c r="N286" s="5" t="n">
-        <v>5.74</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B287" s="5" t="n">
@@ -18317,7 +18317,7 @@
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D287" s="5" t="inlineStr">
@@ -18337,12 +18337,12 @@
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H287" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I287" s="5" t="b">
@@ -18357,19 +18357,19 @@
         </is>
       </c>
       <c r="L287" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M287" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N287" s="5" t="n">
-        <v>4.75</v>
+        <v>14.42</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B288" s="5" t="n">
@@ -18377,7 +18377,7 @@
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D288" s="5" t="inlineStr">
@@ -18397,7 +18397,7 @@
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H288" s="5" t="inlineStr">
@@ -18406,7 +18406,7 @@
         </is>
       </c>
       <c r="I288" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J288" s="5" t="b">
         <v>1</v>
@@ -18417,19 +18417,19 @@
         </is>
       </c>
       <c r="L288" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M288" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N288" s="5" t="n">
-        <v>18.68</v>
+        <v>16.02</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B289" s="5" t="n">
@@ -18437,7 +18437,7 @@
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D289" s="5" t="inlineStr">
@@ -18457,39 +18457,39 @@
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H289" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I289" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J289" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K289" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L289" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M289" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N289" s="5" t="n">
-        <v>4.1</v>
+        <v>16.86</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B290" s="5" t="n">
@@ -18497,7 +18497,7 @@
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D290" s="5" t="inlineStr">
@@ -18517,12 +18517,12 @@
       </c>
       <c r="G290" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H290" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I290" s="5" t="b">
@@ -18543,13 +18543,13 @@
         <v>1</v>
       </c>
       <c r="N290" s="5" t="n">
-        <v>4.43</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B291" s="5" t="n">
@@ -18557,7 +18557,7 @@
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
@@ -18577,16 +18577,16 @@
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H291" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I291" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J291" s="5" t="b">
         <v>1</v>
@@ -18600,16 +18600,16 @@
         <v>0</v>
       </c>
       <c r="M291" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N291" s="5" t="n">
-        <v>19.7</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B292" s="5" t="n">
@@ -18617,7 +18617,7 @@
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
@@ -18637,39 +18637,39 @@
       </c>
       <c r="G292" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H292" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I292" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J292" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K292" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L292" s="5" t="b">
         <v>0</v>
       </c>
       <c r="M292" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N292" s="5" t="n">
-        <v>5.07</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B293" s="5" t="n">
@@ -18723,13 +18723,13 @@
         <v>1</v>
       </c>
       <c r="N293" s="5" t="n">
-        <v>14.42</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B294" s="5" t="n">
@@ -18783,13 +18783,13 @@
         <v>1</v>
       </c>
       <c r="N294" s="5" t="n">
-        <v>16.02</v>
+        <v>21.68</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B295" s="5" t="n">
@@ -18843,13 +18843,13 @@
         <v>1</v>
       </c>
       <c r="N295" s="5" t="n">
-        <v>16.86</v>
+        <v>19.29</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B296" s="5" t="n">
@@ -18857,7 +18857,7 @@
       </c>
       <c r="C296" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D296" s="5" t="inlineStr">
@@ -18882,7 +18882,7 @@
       </c>
       <c r="H296" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I296" s="5" t="b">
@@ -18903,13 +18903,13 @@
         <v>1</v>
       </c>
       <c r="N296" s="5" t="n">
-        <v>23.7</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B297" s="5" t="n">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="C297" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D297" s="5" t="inlineStr">
@@ -18942,7 +18942,7 @@
       </c>
       <c r="H297" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I297" s="5" t="b">
@@ -18957,19 +18957,19 @@
         </is>
       </c>
       <c r="L297" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M297" s="5" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="N297" s="5" t="n">
-        <v>15.77</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B298" s="5" t="n">
@@ -18977,7 +18977,7 @@
       </c>
       <c r="C298" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D298" s="5" t="inlineStr">
@@ -19002,7 +19002,7 @@
       </c>
       <c r="H298" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I298" s="5" t="b">
@@ -19017,19 +19017,19 @@
         </is>
       </c>
       <c r="L298" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M298" s="5" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="N298" s="5" t="n">
-        <v>20.83</v>
+        <v>15.37</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B299" s="5" t="n">
@@ -19037,7 +19037,7 @@
       </c>
       <c r="C299" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D299" s="5" t="inlineStr">
@@ -19083,13 +19083,13 @@
         <v>1</v>
       </c>
       <c r="N299" s="5" t="n">
-        <v>18.2</v>
+        <v>13.91</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B300" s="5" t="n">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="C300" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D300" s="5" t="inlineStr">
@@ -19143,13 +19143,13 @@
         <v>1</v>
       </c>
       <c r="N300" s="5" t="n">
-        <v>21.68</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B301" s="5" t="n">
@@ -19157,7 +19157,7 @@
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D301" s="5" t="inlineStr">
@@ -19203,13 +19203,13 @@
         <v>1</v>
       </c>
       <c r="N301" s="5" t="n">
-        <v>19.29</v>
+        <v>15.59</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B302" s="5" t="n">
@@ -19242,7 +19242,7 @@
       </c>
       <c r="H302" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I302" s="5" t="b">
@@ -19257,19 +19257,19 @@
         </is>
       </c>
       <c r="L302" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M302" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N302" s="5" t="n">
-        <v>15.77</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B303" s="5" t="n">
@@ -19317,19 +19317,19 @@
         </is>
       </c>
       <c r="L303" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M303" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N303" s="5" t="n">
-        <v>14.59</v>
+        <v>19.71</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B304" s="5" t="n">
@@ -19362,34 +19362,34 @@
       </c>
       <c r="H304" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I304" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J304" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K304" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L304" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M304" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N304" s="5" t="n">
-        <v>15.37</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B305" s="5" t="n">
@@ -19443,13 +19443,13 @@
         <v>1</v>
       </c>
       <c r="N305" s="5" t="n">
-        <v>13.91</v>
+        <v>15.09</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B306" s="5" t="n">
@@ -19503,13 +19503,13 @@
         <v>1</v>
       </c>
       <c r="N306" s="5" t="n">
-        <v>15.93</v>
+        <v>16.61</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B307" s="5" t="n">
@@ -19563,13 +19563,13 @@
         <v>1</v>
       </c>
       <c r="N307" s="5" t="n">
-        <v>15.59</v>
+        <v>15.26</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B308" s="5" t="n">
@@ -19577,7 +19577,7 @@
       </c>
       <c r="C308" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D308" s="5" t="inlineStr">
@@ -19602,7 +19602,7 @@
       </c>
       <c r="H308" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I308" s="5" t="b">
@@ -19613,23 +19613,19 @@
       </c>
       <c r="K308" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L308" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M308" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>execution_failure</t>
+        </is>
+      </c>
+      <c r="L308" s="5" t="n"/>
+      <c r="M308" s="5" t="n"/>
       <c r="N308" s="5" t="n">
-        <v>3.34</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B309" s="5" t="n">
@@ -19637,7 +19633,7 @@
       </c>
       <c r="C309" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D309" s="5" t="inlineStr">
@@ -19662,7 +19658,7 @@
       </c>
       <c r="H309" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I309" s="5" t="b">
@@ -19673,23 +19669,19 @@
       </c>
       <c r="K309" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L309" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M309" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>execution_failure</t>
+        </is>
+      </c>
+      <c r="L309" s="5" t="n"/>
+      <c r="M309" s="5" t="n"/>
       <c r="N309" s="5" t="n">
-        <v>19.71</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B310" s="5" t="n">
@@ -19697,7 +19689,7 @@
       </c>
       <c r="C310" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D310" s="5" t="inlineStr">
@@ -19722,34 +19714,30 @@
       </c>
       <c r="H310" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I310" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J310" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K310" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L310" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M310" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>execution_failure</t>
+        </is>
+      </c>
+      <c r="L310" s="5" t="n"/>
+      <c r="M310" s="5" t="n"/>
       <c r="N310" s="5" t="n">
-        <v>4.48</v>
+        <v>13.17</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B311" s="5" t="n">
@@ -19757,7 +19745,7 @@
       </c>
       <c r="C311" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D311" s="5" t="inlineStr">
@@ -19782,7 +19770,7 @@
       </c>
       <c r="H311" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I311" s="5" t="b">
@@ -19797,19 +19785,19 @@
         </is>
       </c>
       <c r="L311" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M311" s="5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N311" s="5" t="n">
-        <v>15.09</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B312" s="5" t="n">
@@ -19817,7 +19805,7 @@
       </c>
       <c r="C312" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D312" s="5" t="inlineStr">
@@ -19842,7 +19830,7 @@
       </c>
       <c r="H312" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I312" s="5" t="b">
@@ -19857,19 +19845,19 @@
         </is>
       </c>
       <c r="L312" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M312" s="5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N312" s="5" t="n">
-        <v>16.61</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B313" s="5" t="n">
@@ -19877,7 +19865,7 @@
       </c>
       <c r="C313" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D313" s="5" t="inlineStr">
@@ -19902,7 +19890,7 @@
       </c>
       <c r="H313" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I313" s="5" t="b">
@@ -19917,19 +19905,19 @@
         </is>
       </c>
       <c r="L313" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M313" s="5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N313" s="5" t="n">
-        <v>15.26</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B314" s="5" t="n">
@@ -19973,19 +19961,19 @@
       </c>
       <c r="K314" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L314" s="5" t="n"/>
       <c r="M314" s="5" t="n"/>
       <c r="N314" s="5" t="n">
-        <v>10.62</v>
+        <v>12.42</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B315" s="5" t="n">
@@ -20029,19 +20017,19 @@
       </c>
       <c r="K315" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L315" s="5" t="n"/>
       <c r="M315" s="5" t="n"/>
       <c r="N315" s="5" t="n">
-        <v>13.14</v>
+        <v>11.82</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B316" s="5" t="n">
@@ -20085,19 +20073,19 @@
       </c>
       <c r="K316" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L316" s="5" t="n"/>
       <c r="M316" s="5" t="n"/>
       <c r="N316" s="5" t="n">
-        <v>13.17</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B317" s="5" t="n">
@@ -20144,20 +20132,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L317" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M317" s="5" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="L317" s="5" t="n"/>
+      <c r="M317" s="5" t="n"/>
       <c r="N317" s="5" t="n">
-        <v>11.73</v>
+        <v>11.83</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B318" s="5" t="n">
@@ -20204,20 +20188,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L318" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M318" s="5" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="L318" s="5" t="n"/>
+      <c r="M318" s="5" t="n"/>
       <c r="N318" s="5" t="n">
-        <v>12.16</v>
+        <v>12.11</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B319" s="5" t="n">
@@ -20264,33 +20244,29 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L319" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M319" s="5" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="L319" s="5" t="n"/>
+      <c r="M319" s="5" t="n"/>
       <c r="N319" s="5" t="n">
-        <v>11.92</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B320" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C320" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D320" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E320" s="5" t="inlineStr">
@@ -20305,12 +20281,12 @@
       </c>
       <c r="G320" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H320" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I320" s="5" t="b">
@@ -20324,29 +20300,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L320" s="5" t="n"/>
-      <c r="M320" s="5" t="n"/>
+      <c r="L320" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M320" s="5" t="n">
+        <v>0.2667</v>
+      </c>
       <c r="N320" s="5" t="n">
-        <v>12.42</v>
+        <v>32.16</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B321" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C321" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D321" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E321" s="5" t="inlineStr">
@@ -20361,12 +20341,12 @@
       </c>
       <c r="G321" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H321" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I321" s="5" t="b">
@@ -20380,29 +20360,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L321" s="5" t="n"/>
-      <c r="M321" s="5" t="n"/>
+      <c r="L321" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M321" s="5" t="n">
+        <v>0.2667</v>
+      </c>
       <c r="N321" s="5" t="n">
-        <v>11.82</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B322" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C322" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D322" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E322" s="5" t="inlineStr">
@@ -20417,12 +20401,12 @@
       </c>
       <c r="G322" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H322" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I322" s="5" t="b">
@@ -20436,29 +20420,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L322" s="5" t="n"/>
-      <c r="M322" s="5" t="n"/>
+      <c r="L322" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M322" s="5" t="n">
+        <v>0.2667</v>
+      </c>
       <c r="N322" s="5" t="n">
-        <v>13.05</v>
+        <v>12.18</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B323" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C323" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E323" s="5" t="inlineStr">
@@ -20473,12 +20461,12 @@
       </c>
       <c r="G323" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H323" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I323" s="5" t="b">
@@ -20492,29 +20480,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L323" s="5" t="n"/>
-      <c r="M323" s="5" t="n"/>
+      <c r="L323" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M323" s="5" t="n">
+        <v>0.2222</v>
+      </c>
       <c r="N323" s="5" t="n">
-        <v>11.83</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B324" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C324" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D324" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E324" s="5" t="inlineStr">
@@ -20529,12 +20521,12 @@
       </c>
       <c r="G324" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H324" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I324" s="5" t="b">
@@ -20548,29 +20540,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L324" s="5" t="n"/>
-      <c r="M324" s="5" t="n"/>
+      <c r="L324" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M324" s="5" t="n">
+        <v>0.2222</v>
+      </c>
       <c r="N324" s="5" t="n">
-        <v>12.11</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B325" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C325" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E325" s="5" t="inlineStr">
@@ -20585,12 +20581,12 @@
       </c>
       <c r="G325" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H325" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I325" s="5" t="b">
@@ -20604,10 +20600,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L325" s="5" t="n"/>
-      <c r="M325" s="5" t="n"/>
+      <c r="L325" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M325" s="5" t="n">
+        <v>0.2222</v>
+      </c>
       <c r="N325" s="5" t="n">
-        <v>11.46</v>
+        <v>12.02</v>
       </c>
     </row>
   </sheetData>

--- a/NL2SPARQL_Evaluation_Results.xlsx
+++ b/NL2SPARQL_Evaluation_Results.xlsx
@@ -16785,7 +16785,7 @@
         <v>0</v>
       </c>
       <c r="N260" s="5" t="n">
-        <v>34.35</v>
+        <v>17.78</v>
       </c>
     </row>
     <row r="261">
@@ -16845,7 +16845,7 @@
         <v>1</v>
       </c>
       <c r="N261" s="5" t="n">
-        <v>32.8</v>
+        <v>21.82</v>
       </c>
     </row>
     <row r="262">
@@ -16905,7 +16905,7 @@
         <v>0</v>
       </c>
       <c r="N262" s="5" t="n">
-        <v>18.83</v>
+        <v>18.98</v>
       </c>
     </row>
     <row r="263">
@@ -16965,7 +16965,7 @@
         <v>0</v>
       </c>
       <c r="N263" s="5" t="n">
-        <v>18.18</v>
+        <v>18.26</v>
       </c>
     </row>
     <row r="264">
@@ -17004,11 +17004,11 @@
       </c>
       <c r="H264" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I264" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J264" s="5" t="b">
         <v>1</v>
@@ -17019,13 +17019,13 @@
         </is>
       </c>
       <c r="L264" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M264" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N264" s="5" t="n">
-        <v>44.76</v>
+        <v>22.52</v>
       </c>
     </row>
     <row r="265">
@@ -17085,7 +17085,7 @@
         <v>0</v>
       </c>
       <c r="N265" s="5" t="n">
-        <v>18.67</v>
+        <v>18.51</v>
       </c>
     </row>
     <row r="266">
@@ -17141,7 +17141,7 @@
       <c r="L266" s="5" t="n"/>
       <c r="M266" s="5" t="n"/>
       <c r="N266" s="5" t="n">
-        <v>29.63</v>
+        <v>24.16</v>
       </c>
     </row>
     <row r="267">
@@ -17197,7 +17197,7 @@
       <c r="L267" s="5" t="n"/>
       <c r="M267" s="5" t="n"/>
       <c r="N267" s="5" t="n">
-        <v>28.54</v>
+        <v>23.64</v>
       </c>
     </row>
     <row r="268">
@@ -17247,13 +17247,13 @@
       </c>
       <c r="K268" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L268" s="5" t="n"/>
       <c r="M268" s="5" t="n"/>
       <c r="N268" s="5" t="n">
-        <v>25.66</v>
+        <v>23.49</v>
       </c>
     </row>
     <row r="269">
@@ -17303,13 +17303,13 @@
       </c>
       <c r="K269" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L269" s="5" t="n"/>
       <c r="M269" s="5" t="n"/>
       <c r="N269" s="5" t="n">
-        <v>26.09</v>
+        <v>24.41</v>
       </c>
     </row>
     <row r="270">
@@ -17359,13 +17359,13 @@
       </c>
       <c r="K270" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L270" s="5" t="n"/>
       <c r="M270" s="5" t="n"/>
       <c r="N270" s="5" t="n">
-        <v>28.52</v>
+        <v>24.78</v>
       </c>
     </row>
     <row r="271">
@@ -17411,23 +17411,23 @@
         <v>1</v>
       </c>
       <c r="J271" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K271" s="5" t="inlineStr">
         <is>
-          <t>generation_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L271" s="5" t="n"/>
       <c r="M271" s="5" t="n"/>
       <c r="N271" s="5" t="n">
-        <v>26.41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B272" s="5" t="n">
@@ -17478,16 +17478,16 @@
         <v>0</v>
       </c>
       <c r="M272" s="5" t="n">
-        <v>0.3077</v>
+        <v>0.2667</v>
       </c>
       <c r="N272" s="5" t="n">
-        <v>14.76</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B273" s="5" t="n">
@@ -17538,16 +17538,16 @@
         <v>0</v>
       </c>
       <c r="M273" s="5" t="n">
-        <v>0.3077</v>
+        <v>0.2667</v>
       </c>
       <c r="N273" s="5" t="n">
-        <v>21.77</v>
+        <v>13.74</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B274" s="5" t="n">
@@ -17598,28 +17598,30 @@
         <v>0</v>
       </c>
       <c r="M274" s="5" t="n">
-        <v>0.3077</v>
+        <v>0.2667</v>
       </c>
       <c r="N274" s="5" t="n">
-        <v>14.83</v>
+        <v>13.66</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B275" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D275" s="5" t="n">
-        <v/>
+          <t>compare_two_airports</t>
+        </is>
+      </c>
+      <c r="D275" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
       </c>
       <c r="E275" s="5" t="inlineStr">
         <is>
@@ -17633,47 +17635,53 @@
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H275" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I275" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J275" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K275" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L275" s="5" t="n"/>
-      <c r="M275" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L275" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M275" s="5" t="n">
+        <v>0.2222</v>
+      </c>
       <c r="N275" s="5" t="n">
-        <v>14.29</v>
+        <v>13.37</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B276" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D276" s="5" t="n">
-        <v/>
+          <t>compare_two_airports</t>
+        </is>
+      </c>
+      <c r="D276" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
@@ -17687,16 +17695,16 @@
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H276" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I276" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J276" s="5" t="b">
         <v>1</v>
@@ -17706,28 +17714,34 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L276" s="5" t="n"/>
-      <c r="M276" s="5" t="n"/>
+      <c r="L276" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M276" s="5" t="n">
+        <v>0.2222</v>
+      </c>
       <c r="N276" s="5" t="n">
-        <v>32.02</v>
+        <v>13.26</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B277" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C277" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D277" s="5" t="n">
-        <v/>
+          <t>compare_two_airports</t>
+        </is>
+      </c>
+      <c r="D277" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
       </c>
       <c r="E277" s="5" t="inlineStr">
         <is>
@@ -17741,48 +17755,52 @@
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H277" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I277" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J277" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K277" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L277" s="5" t="n"/>
-      <c r="M277" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L277" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M277" s="5" t="n">
+        <v>0.2222</v>
+      </c>
       <c r="N277" s="5" t="n">
-        <v>5.66</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B278" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E278" s="5" t="inlineStr">
@@ -17797,12 +17815,12 @@
       </c>
       <c r="G278" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H278" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I278" s="5" t="b">
@@ -17820,29 +17838,29 @@
         <v>0</v>
       </c>
       <c r="M278" s="5" t="n">
-        <v>0</v>
+        <v>0.3077</v>
       </c>
       <c r="N278" s="5" t="n">
-        <v>4.77</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B279" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E279" s="5" t="inlineStr">
@@ -17857,16 +17875,16 @@
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H279" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I279" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J279" s="5" t="b">
         <v>1</v>
@@ -17880,29 +17898,29 @@
         <v>0</v>
       </c>
       <c r="M279" s="5" t="n">
-        <v>0</v>
+        <v>0.3077</v>
       </c>
       <c r="N279" s="5" t="n">
-        <v>16.99</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B280" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E280" s="5" t="inlineStr">
@@ -17917,12 +17935,12 @@
       </c>
       <c r="G280" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H280" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I280" s="5" t="b">
@@ -17940,16 +17958,16 @@
         <v>0</v>
       </c>
       <c r="M280" s="5" t="n">
-        <v>0</v>
+        <v>0.3077</v>
       </c>
       <c r="N280" s="5" t="n">
-        <v>5.74</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B281" s="5" t="n">
@@ -17957,13 +17975,11 @@
       </c>
       <c r="C281" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
-        </is>
-      </c>
-      <c r="D281" s="5" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D281" s="5" t="n">
+        <v/>
       </c>
       <c r="E281" s="5" t="inlineStr">
         <is>
@@ -17977,39 +17993,35 @@
       </c>
       <c r="G281" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H281" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I281" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J281" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K281" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L281" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M281" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>mapping_failure</t>
+        </is>
+      </c>
+      <c r="L281" s="5" t="n"/>
+      <c r="M281" s="5" t="n"/>
       <c r="N281" s="5" t="n">
-        <v>4.75</v>
+        <v>23.98</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B282" s="5" t="n">
@@ -18017,13 +18029,11 @@
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
-        </is>
-      </c>
-      <c r="D282" s="5" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D282" s="5" t="n">
+        <v/>
       </c>
       <c r="E282" s="5" t="inlineStr">
         <is>
@@ -18037,12 +18047,12 @@
       </c>
       <c r="G282" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H282" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I282" s="5" t="b">
@@ -18056,20 +18066,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L282" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M282" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L282" s="5" t="n"/>
+      <c r="M282" s="5" t="n"/>
       <c r="N282" s="5" t="n">
-        <v>18.68</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B283" s="5" t="n">
@@ -18077,59 +18083,53 @@
       </c>
       <c r="C283" s="5" t="inlineStr">
         <is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D283" s="5" t="n">
+        <v/>
+      </c>
+      <c r="E283" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F283" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G283" s="5" t="inlineStr">
+        <is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="H283" s="5" t="inlineStr">
+        <is>
           <t>ask_query</t>
         </is>
       </c>
-      <c r="D283" s="5" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="E283" s="5" t="inlineStr">
-        <is>
-          <t>ar</t>
-        </is>
-      </c>
-      <c r="F283" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G283" s="5" t="inlineStr">
-        <is>
-          <t>ask_query</t>
-        </is>
-      </c>
-      <c r="H283" s="5" t="inlineStr">
-        <is>
-          <t>ask_query</t>
-        </is>
-      </c>
       <c r="I283" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J283" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K283" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L283" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M283" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L283" s="5" t="n"/>
+      <c r="M283" s="5" t="n"/>
       <c r="N283" s="5" t="n">
-        <v>4.1</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B284" s="5" t="n">
@@ -18177,19 +18177,19 @@
         </is>
       </c>
       <c r="L284" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M284" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N284" s="5" t="n">
-        <v>4.43</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B285" s="5" t="n">
@@ -18222,7 +18222,7 @@
       </c>
       <c r="H285" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I285" s="5" t="b">
@@ -18243,13 +18243,13 @@
         <v>0</v>
       </c>
       <c r="N285" s="5" t="n">
-        <v>19.7</v>
+        <v>17.02</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B286" s="5" t="n">
@@ -18289,11 +18289,11 @@
         <v>1</v>
       </c>
       <c r="J286" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K286" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L286" s="5" t="b">
@@ -18303,13 +18303,13 @@
         <v>0</v>
       </c>
       <c r="N286" s="5" t="n">
-        <v>5.07</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B287" s="5" t="n">
@@ -18317,7 +18317,7 @@
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D287" s="5" t="inlineStr">
@@ -18337,12 +18337,12 @@
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H287" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I287" s="5" t="b">
@@ -18357,19 +18357,19 @@
         </is>
       </c>
       <c r="L287" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M287" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N287" s="5" t="n">
-        <v>14.42</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B288" s="5" t="n">
@@ -18377,7 +18377,7 @@
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D288" s="5" t="inlineStr">
@@ -18397,7 +18397,7 @@
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H288" s="5" t="inlineStr">
@@ -18406,7 +18406,7 @@
         </is>
       </c>
       <c r="I288" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J288" s="5" t="b">
         <v>1</v>
@@ -18417,19 +18417,19 @@
         </is>
       </c>
       <c r="L288" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M288" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N288" s="5" t="n">
-        <v>16.02</v>
+        <v>19.83</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B289" s="5" t="n">
@@ -18437,7 +18437,7 @@
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D289" s="5" t="inlineStr">
@@ -18457,39 +18457,39 @@
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H289" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I289" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J289" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K289" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L289" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M289" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N289" s="5" t="n">
-        <v>16.86</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B290" s="5" t="n">
@@ -18497,7 +18497,7 @@
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D290" s="5" t="inlineStr">
@@ -18517,12 +18517,12 @@
       </c>
       <c r="G290" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H290" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I290" s="5" t="b">
@@ -18543,13 +18543,13 @@
         <v>1</v>
       </c>
       <c r="N290" s="5" t="n">
-        <v>23.7</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B291" s="5" t="n">
@@ -18557,7 +18557,7 @@
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
@@ -18577,16 +18577,16 @@
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H291" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I291" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J291" s="5" t="b">
         <v>1</v>
@@ -18600,16 +18600,16 @@
         <v>0</v>
       </c>
       <c r="M291" s="5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N291" s="5" t="n">
-        <v>15.77</v>
+        <v>21.12</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B292" s="5" t="n">
@@ -18617,7 +18617,7 @@
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
@@ -18637,39 +18637,39 @@
       </c>
       <c r="G292" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H292" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I292" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J292" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K292" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L292" s="5" t="b">
         <v>0</v>
       </c>
       <c r="M292" s="5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N292" s="5" t="n">
-        <v>20.83</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B293" s="5" t="n">
@@ -18723,13 +18723,13 @@
         <v>1</v>
       </c>
       <c r="N293" s="5" t="n">
-        <v>18.2</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B294" s="5" t="n">
@@ -18783,13 +18783,13 @@
         <v>1</v>
       </c>
       <c r="N294" s="5" t="n">
-        <v>21.68</v>
+        <v>16.43</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B295" s="5" t="n">
@@ -18843,13 +18843,13 @@
         <v>1</v>
       </c>
       <c r="N295" s="5" t="n">
-        <v>19.29</v>
+        <v>15.84</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B296" s="5" t="n">
@@ -18857,7 +18857,7 @@
       </c>
       <c r="C296" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D296" s="5" t="inlineStr">
@@ -18882,7 +18882,7 @@
       </c>
       <c r="H296" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I296" s="5" t="b">
@@ -18903,13 +18903,13 @@
         <v>1</v>
       </c>
       <c r="N296" s="5" t="n">
-        <v>15.77</v>
+        <v>30.83</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B297" s="5" t="n">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="C297" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D297" s="5" t="inlineStr">
@@ -18942,7 +18942,7 @@
       </c>
       <c r="H297" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I297" s="5" t="b">
@@ -18957,19 +18957,19 @@
         </is>
       </c>
       <c r="L297" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M297" s="5" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="N297" s="5" t="n">
-        <v>14.59</v>
+        <v>17.77</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B298" s="5" t="n">
@@ -18977,7 +18977,7 @@
       </c>
       <c r="C298" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D298" s="5" t="inlineStr">
@@ -19002,7 +19002,7 @@
       </c>
       <c r="H298" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I298" s="5" t="b">
@@ -19017,19 +19017,19 @@
         </is>
       </c>
       <c r="L298" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M298" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N298" s="5" t="n">
-        <v>15.37</v>
+        <v>18.24</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B299" s="5" t="n">
@@ -19037,7 +19037,7 @@
       </c>
       <c r="C299" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D299" s="5" t="inlineStr">
@@ -19083,13 +19083,13 @@
         <v>1</v>
       </c>
       <c r="N299" s="5" t="n">
-        <v>13.91</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B300" s="5" t="n">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="C300" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D300" s="5" t="inlineStr">
@@ -19143,13 +19143,13 @@
         <v>1</v>
       </c>
       <c r="N300" s="5" t="n">
-        <v>15.93</v>
+        <v>23.03</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B301" s="5" t="n">
@@ -19157,7 +19157,7 @@
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D301" s="5" t="inlineStr">
@@ -19203,13 +19203,13 @@
         <v>1</v>
       </c>
       <c r="N301" s="5" t="n">
-        <v>15.59</v>
+        <v>22.92</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B302" s="5" t="n">
@@ -19242,7 +19242,7 @@
       </c>
       <c r="H302" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I302" s="5" t="b">
@@ -19257,19 +19257,19 @@
         </is>
       </c>
       <c r="L302" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M302" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N302" s="5" t="n">
-        <v>3.34</v>
+        <v>16.06</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B303" s="5" t="n">
@@ -19317,19 +19317,19 @@
         </is>
       </c>
       <c r="L303" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M303" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N303" s="5" t="n">
-        <v>19.71</v>
+        <v>16.26</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B304" s="5" t="n">
@@ -19362,34 +19362,34 @@
       </c>
       <c r="H304" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I304" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J304" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K304" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L304" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M304" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N304" s="5" t="n">
-        <v>4.48</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B305" s="5" t="n">
@@ -19443,13 +19443,13 @@
         <v>1</v>
       </c>
       <c r="N305" s="5" t="n">
-        <v>15.09</v>
+        <v>15.61</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B306" s="5" t="n">
@@ -19503,13 +19503,13 @@
         <v>1</v>
       </c>
       <c r="N306" s="5" t="n">
-        <v>16.61</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B307" s="5" t="n">
@@ -19563,13 +19563,13 @@
         <v>1</v>
       </c>
       <c r="N307" s="5" t="n">
-        <v>15.26</v>
+        <v>16.14</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B308" s="5" t="n">
@@ -19577,7 +19577,7 @@
       </c>
       <c r="C308" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D308" s="5" t="inlineStr">
@@ -19602,7 +19602,7 @@
       </c>
       <c r="H308" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I308" s="5" t="b">
@@ -19613,19 +19613,23 @@
       </c>
       <c r="K308" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L308" s="5" t="n"/>
-      <c r="M308" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L308" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M308" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N308" s="5" t="n">
-        <v>10.62</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B309" s="5" t="n">
@@ -19633,7 +19637,7 @@
       </c>
       <c r="C309" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D309" s="5" t="inlineStr">
@@ -19658,7 +19662,7 @@
       </c>
       <c r="H309" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I309" s="5" t="b">
@@ -19669,19 +19673,23 @@
       </c>
       <c r="K309" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L309" s="5" t="n"/>
-      <c r="M309" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L309" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M309" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N309" s="5" t="n">
-        <v>13.14</v>
+        <v>16.38</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B310" s="5" t="n">
@@ -19689,7 +19697,7 @@
       </c>
       <c r="C310" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D310" s="5" t="inlineStr">
@@ -19714,30 +19722,34 @@
       </c>
       <c r="H310" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I310" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J310" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K310" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L310" s="5" t="n"/>
-      <c r="M310" s="5" t="n"/>
+          <t>mapping_failure</t>
+        </is>
+      </c>
+      <c r="L310" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M310" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N310" s="5" t="n">
-        <v>13.17</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B311" s="5" t="n">
@@ -19745,7 +19757,7 @@
       </c>
       <c r="C311" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D311" s="5" t="inlineStr">
@@ -19770,7 +19782,7 @@
       </c>
       <c r="H311" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I311" s="5" t="b">
@@ -19785,19 +19797,19 @@
         </is>
       </c>
       <c r="L311" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M311" s="5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N311" s="5" t="n">
-        <v>11.73</v>
+        <v>15.46</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B312" s="5" t="n">
@@ -19805,7 +19817,7 @@
       </c>
       <c r="C312" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D312" s="5" t="inlineStr">
@@ -19830,7 +19842,7 @@
       </c>
       <c r="H312" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I312" s="5" t="b">
@@ -19845,19 +19857,19 @@
         </is>
       </c>
       <c r="L312" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M312" s="5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N312" s="5" t="n">
-        <v>12.16</v>
+        <v>17.33</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B313" s="5" t="n">
@@ -19865,7 +19877,7 @@
       </c>
       <c r="C313" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D313" s="5" t="inlineStr">
@@ -19890,7 +19902,7 @@
       </c>
       <c r="H313" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I313" s="5" t="b">
@@ -19905,19 +19917,19 @@
         </is>
       </c>
       <c r="L313" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M313" s="5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N313" s="5" t="n">
-        <v>11.92</v>
+        <v>16.73</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B314" s="5" t="n">
@@ -19967,13 +19979,13 @@
       <c r="L314" s="5" t="n"/>
       <c r="M314" s="5" t="n"/>
       <c r="N314" s="5" t="n">
-        <v>12.42</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B315" s="5" t="n">
@@ -20023,13 +20035,13 @@
       <c r="L315" s="5" t="n"/>
       <c r="M315" s="5" t="n"/>
       <c r="N315" s="5" t="n">
-        <v>11.82</v>
+        <v>14</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B316" s="5" t="n">
@@ -20079,13 +20091,13 @@
       <c r="L316" s="5" t="n"/>
       <c r="M316" s="5" t="n"/>
       <c r="N316" s="5" t="n">
-        <v>13.05</v>
+        <v>14.22</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B317" s="5" t="n">
@@ -20132,16 +20144,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L317" s="5" t="n"/>
-      <c r="M317" s="5" t="n"/>
+      <c r="L317" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M317" s="5" t="n">
+        <v>0.5</v>
+      </c>
       <c r="N317" s="5" t="n">
-        <v>11.83</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B318" s="5" t="n">
@@ -20188,16 +20204,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L318" s="5" t="n"/>
-      <c r="M318" s="5" t="n"/>
+      <c r="L318" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M318" s="5" t="n">
+        <v>0.5</v>
+      </c>
       <c r="N318" s="5" t="n">
-        <v>12.11</v>
+        <v>12.97</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B319" s="5" t="n">
@@ -20244,29 +20264,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L319" s="5" t="n"/>
-      <c r="M319" s="5" t="n"/>
+      <c r="L319" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M319" s="5" t="n">
+        <v>0.5</v>
+      </c>
       <c r="N319" s="5" t="n">
-        <v>11.46</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B320" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C320" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D320" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E320" s="5" t="inlineStr">
@@ -20281,12 +20305,12 @@
       </c>
       <c r="G320" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H320" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I320" s="5" t="b">
@@ -20300,33 +20324,29 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L320" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M320" s="5" t="n">
-        <v>0.2667</v>
-      </c>
+      <c r="L320" s="5" t="n"/>
+      <c r="M320" s="5" t="n"/>
       <c r="N320" s="5" t="n">
-        <v>32.16</v>
+        <v>12.83</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B321" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C321" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D321" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E321" s="5" t="inlineStr">
@@ -20341,12 +20361,12 @@
       </c>
       <c r="G321" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H321" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I321" s="5" t="b">
@@ -20360,33 +20380,29 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L321" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M321" s="5" t="n">
-        <v>0.2667</v>
-      </c>
+      <c r="L321" s="5" t="n"/>
+      <c r="M321" s="5" t="n"/>
       <c r="N321" s="5" t="n">
-        <v>12.5</v>
+        <v>12.57</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B322" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C322" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D322" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E322" s="5" t="inlineStr">
@@ -20401,12 +20417,12 @@
       </c>
       <c r="G322" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H322" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I322" s="5" t="b">
@@ -20420,33 +20436,29 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L322" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M322" s="5" t="n">
-        <v>0.2667</v>
-      </c>
+      <c r="L322" s="5" t="n"/>
+      <c r="M322" s="5" t="n"/>
       <c r="N322" s="5" t="n">
-        <v>12.18</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B323" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C323" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E323" s="5" t="inlineStr">
@@ -20461,12 +20473,12 @@
       </c>
       <c r="G323" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H323" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I323" s="5" t="b">
@@ -20480,33 +20492,29 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L323" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M323" s="5" t="n">
-        <v>0.2222</v>
-      </c>
+      <c r="L323" s="5" t="n"/>
+      <c r="M323" s="5" t="n"/>
       <c r="N323" s="5" t="n">
-        <v>11.92</v>
+        <v>12.38</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B324" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C324" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D324" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E324" s="5" t="inlineStr">
@@ -20521,12 +20529,12 @@
       </c>
       <c r="G324" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H324" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I324" s="5" t="b">
@@ -20540,33 +20548,29 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L324" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M324" s="5" t="n">
-        <v>0.2222</v>
-      </c>
+      <c r="L324" s="5" t="n"/>
+      <c r="M324" s="5" t="n"/>
       <c r="N324" s="5" t="n">
-        <v>11.92</v>
+        <v>13.58</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B325" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C325" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E325" s="5" t="inlineStr">
@@ -20581,12 +20585,12 @@
       </c>
       <c r="G325" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H325" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I325" s="5" t="b">
@@ -20600,14 +20604,10 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L325" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M325" s="5" t="n">
-        <v>0.2222</v>
-      </c>
+      <c r="L325" s="5" t="n"/>
+      <c r="M325" s="5" t="n"/>
       <c r="N325" s="5" t="n">
-        <v>12.02</v>
+        <v>14.61</v>
       </c>
     </row>
   </sheetData>

--- a/NL2SPARQL_Evaluation_Results.xlsx
+++ b/NL2SPARQL_Evaluation_Results.xlsx
@@ -13879,7 +13879,7 @@
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_002</t>
+          <t>filter_numeric_kg1_001</t>
         </is>
       </c>
       <c r="B209" s="5" t="n">
@@ -13887,7 +13887,7 @@
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D209" s="5" t="inlineStr">
@@ -13912,30 +13912,30 @@
       </c>
       <c r="H209" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I209" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J209" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K209" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L209" s="5" t="n"/>
       <c r="M209" s="5" t="n"/>
       <c r="N209" s="5" t="n">
-        <v>3.92</v>
+        <v>14.93</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_002</t>
+          <t>filter_numeric_kg1_001</t>
         </is>
       </c>
       <c r="B210" s="5" t="n">
@@ -13943,7 +13943,7 @@
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
@@ -13968,30 +13968,30 @@
       </c>
       <c r="H210" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I210" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J210" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K210" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L210" s="5" t="n"/>
       <c r="M210" s="5" t="n"/>
       <c r="N210" s="5" t="n">
-        <v>3.78</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_002</t>
+          <t>filter_numeric_kg1_001</t>
         </is>
       </c>
       <c r="B211" s="5" t="n">
@@ -13999,7 +13999,7 @@
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D211" s="5" t="inlineStr">
@@ -14024,30 +14024,30 @@
       </c>
       <c r="H211" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I211" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J211" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K211" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L211" s="5" t="n"/>
       <c r="M211" s="5" t="n"/>
       <c r="N211" s="5" t="n">
-        <v>3.76</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_003</t>
+          <t>filter_numeric_kg1_002</t>
         </is>
       </c>
       <c r="B212" s="5" t="n">
@@ -14055,7 +14055,7 @@
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D212" s="5" t="inlineStr">
@@ -14080,30 +14080,30 @@
       </c>
       <c r="H212" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I212" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J212" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K212" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L212" s="5" t="n"/>
       <c r="M212" s="5" t="n"/>
       <c r="N212" s="5" t="n">
-        <v>3.81</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_003</t>
+          <t>filter_numeric_kg1_002</t>
         </is>
       </c>
       <c r="B213" s="5" t="n">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D213" s="5" t="inlineStr">
@@ -14136,30 +14136,30 @@
       </c>
       <c r="H213" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I213" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J213" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K213" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L213" s="5" t="n"/>
       <c r="M213" s="5" t="n"/>
       <c r="N213" s="5" t="n">
-        <v>3.64</v>
+        <v>27.37</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_003</t>
+          <t>filter_numeric_kg1_002</t>
         </is>
       </c>
       <c r="B214" s="5" t="n">
@@ -14167,7 +14167,7 @@
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D214" s="5" t="inlineStr">
@@ -14192,30 +14192,30 @@
       </c>
       <c r="H214" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I214" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J214" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K214" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L214" s="5" t="n"/>
       <c r="M214" s="5" t="n"/>
       <c r="N214" s="5" t="n">
-        <v>3.22</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_001</t>
+          <t>filter_numeric_kg1_003</t>
         </is>
       </c>
       <c r="B215" s="5" t="n">
@@ -14265,13 +14265,13 @@
       <c r="L215" s="5" t="n"/>
       <c r="M215" s="5" t="n"/>
       <c r="N215" s="5" t="n">
-        <v>14.93</v>
+        <v>13.67</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_001</t>
+          <t>filter_numeric_kg1_003</t>
         </is>
       </c>
       <c r="B216" s="5" t="n">
@@ -14321,13 +14321,13 @@
       <c r="L216" s="5" t="n"/>
       <c r="M216" s="5" t="n"/>
       <c r="N216" s="5" t="n">
-        <v>15.05</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_001</t>
+          <t>filter_numeric_kg1_003</t>
         </is>
       </c>
       <c r="B217" s="5" t="n">
@@ -14377,13 +14377,13 @@
       <c r="L217" s="5" t="n"/>
       <c r="M217" s="5" t="n"/>
       <c r="N217" s="5" t="n">
-        <v>14.84</v>
+        <v>14.15</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_002</t>
+          <t>filter_numeric_kg2_001</t>
         </is>
       </c>
       <c r="B218" s="5" t="n">
@@ -14391,12 +14391,12 @@
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
@@ -14423,23 +14423,23 @@
         <v>1</v>
       </c>
       <c r="J218" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K218" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>sparql_build_failure</t>
         </is>
       </c>
       <c r="L218" s="5" t="n"/>
       <c r="M218" s="5" t="n"/>
       <c r="N218" s="5" t="n">
-        <v>15.15</v>
+        <v>14.77</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_002</t>
+          <t>filter_numeric_kg2_001</t>
         </is>
       </c>
       <c r="B219" s="5" t="n">
@@ -14447,12 +14447,12 @@
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E219" s="5" t="inlineStr">
@@ -14489,13 +14489,13 @@
       <c r="L219" s="5" t="n"/>
       <c r="M219" s="5" t="n"/>
       <c r="N219" s="5" t="n">
-        <v>27.37</v>
+        <v>15.68</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_002</t>
+          <t>filter_numeric_kg2_001</t>
         </is>
       </c>
       <c r="B220" s="5" t="n">
@@ -14503,12 +14503,12 @@
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
@@ -14526,32 +14526,28 @@
           <t>template</t>
         </is>
       </c>
-      <c r="H220" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
+      <c r="H220" s="5" t="n"/>
       <c r="I220" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J220" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K220" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>exception: int() argument must be a string, a bytes-like object or a real number, not 'NoneType'</t>
         </is>
       </c>
       <c r="L220" s="5" t="n"/>
       <c r="M220" s="5" t="n"/>
       <c r="N220" s="5" t="n">
-        <v>19.23</v>
+        <v>21.08</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_003</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B221" s="5" t="n">
@@ -14559,12 +14555,12 @@
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E221" s="5" t="inlineStr">
@@ -14601,13 +14597,13 @@
       <c r="L221" s="5" t="n"/>
       <c r="M221" s="5" t="n"/>
       <c r="N221" s="5" t="n">
-        <v>13.67</v>
+        <v>16.11</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_003</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B222" s="5" t="n">
@@ -14615,12 +14611,12 @@
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
@@ -14657,13 +14653,13 @@
       <c r="L222" s="5" t="n"/>
       <c r="M222" s="5" t="n"/>
       <c r="N222" s="5" t="n">
-        <v>13.76</v>
+        <v>15.32</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_003</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B223" s="5" t="n">
@@ -14671,12 +14667,12 @@
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E223" s="5" t="inlineStr">
@@ -14713,13 +14709,13 @@
       <c r="L223" s="5" t="n"/>
       <c r="M223" s="5" t="n"/>
       <c r="N223" s="5" t="n">
-        <v>14.15</v>
+        <v>15.59</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_001</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B224" s="5" t="n">
@@ -14759,23 +14755,23 @@
         <v>1</v>
       </c>
       <c r="J224" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K224" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L224" s="5" t="n"/>
       <c r="M224" s="5" t="n"/>
       <c r="N224" s="5" t="n">
-        <v>14.77</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_001</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B225" s="5" t="n">
@@ -14825,13 +14821,13 @@
       <c r="L225" s="5" t="n"/>
       <c r="M225" s="5" t="n"/>
       <c r="N225" s="5" t="n">
-        <v>15.68</v>
+        <v>15.76</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_001</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B226" s="5" t="n">
@@ -14862,28 +14858,32 @@
           <t>template</t>
         </is>
       </c>
-      <c r="H226" s="5" t="n"/>
+      <c r="H226" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
       <c r="I226" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J226" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K226" s="5" t="inlineStr">
         <is>
-          <t>exception: int() argument must be a string, a bytes-like object or a real number, not 'NoneType'</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L226" s="5" t="n"/>
       <c r="M226" s="5" t="n"/>
       <c r="N226" s="5" t="n">
-        <v>21.08</v>
+        <v>18.69</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>ranking_kg2_001</t>
         </is>
       </c>
       <c r="B227" s="5" t="n">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D227" s="5" t="inlineStr">
@@ -14933,13 +14933,13 @@
       <c r="L227" s="5" t="n"/>
       <c r="M227" s="5" t="n"/>
       <c r="N227" s="5" t="n">
-        <v>16.11</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>ranking_kg2_001</t>
         </is>
       </c>
       <c r="B228" s="5" t="n">
@@ -14947,7 +14947,7 @@
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D228" s="5" t="inlineStr">
@@ -14989,13 +14989,13 @@
       <c r="L228" s="5" t="n"/>
       <c r="M228" s="5" t="n"/>
       <c r="N228" s="5" t="n">
-        <v>15.32</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>ranking_kg2_001</t>
         </is>
       </c>
       <c r="B229" s="5" t="n">
@@ -15003,7 +15003,7 @@
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D229" s="5" t="inlineStr">
@@ -15045,13 +15045,13 @@
       <c r="L229" s="5" t="n"/>
       <c r="M229" s="5" t="n"/>
       <c r="N229" s="5" t="n">
-        <v>15.59</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>ranking_kg2_002</t>
         </is>
       </c>
       <c r="B230" s="5" t="n">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="C230" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D230" s="5" t="inlineStr">
@@ -15101,13 +15101,13 @@
       <c r="L230" s="5" t="n"/>
       <c r="M230" s="5" t="n"/>
       <c r="N230" s="5" t="n">
-        <v>16.67</v>
+        <v>13.56</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>ranking_kg2_002</t>
         </is>
       </c>
       <c r="B231" s="5" t="n">
@@ -15115,7 +15115,7 @@
       </c>
       <c r="C231" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D231" s="5" t="inlineStr">
@@ -15157,13 +15157,13 @@
       <c r="L231" s="5" t="n"/>
       <c r="M231" s="5" t="n"/>
       <c r="N231" s="5" t="n">
-        <v>15.76</v>
+        <v>13.72</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>ranking_kg2_002</t>
         </is>
       </c>
       <c r="B232" s="5" t="n">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D232" s="5" t="inlineStr">
@@ -15213,13 +15213,13 @@
       <c r="L232" s="5" t="n"/>
       <c r="M232" s="5" t="n"/>
       <c r="N232" s="5" t="n">
-        <v>18.69</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_001</t>
+          <t>ranking_kg2_003</t>
         </is>
       </c>
       <c r="B233" s="5" t="n">
@@ -15227,7 +15227,7 @@
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D233" s="5" t="inlineStr">
@@ -15269,13 +15269,13 @@
       <c r="L233" s="5" t="n"/>
       <c r="M233" s="5" t="n"/>
       <c r="N233" s="5" t="n">
-        <v>17.13</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_001</t>
+          <t>ranking_kg2_003</t>
         </is>
       </c>
       <c r="B234" s="5" t="n">
@@ -15283,7 +15283,7 @@
       </c>
       <c r="C234" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D234" s="5" t="inlineStr">
@@ -15315,23 +15315,23 @@
         <v>1</v>
       </c>
       <c r="J234" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K234" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L234" s="5" t="n"/>
       <c r="M234" s="5" t="n"/>
       <c r="N234" s="5" t="n">
-        <v>13.7</v>
+        <v>22.08</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_001</t>
+          <t>ranking_kg2_003</t>
         </is>
       </c>
       <c r="B235" s="5" t="n">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D235" s="5" t="inlineStr">
@@ -15371,37 +15371,35 @@
         <v>1</v>
       </c>
       <c r="J235" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K235" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L235" s="5" t="n"/>
       <c r="M235" s="5" t="n"/>
       <c r="N235" s="5" t="n">
-        <v>13.52</v>
+        <v>15.17</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_002</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B236" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C236" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
-        </is>
-      </c>
-      <c r="D236" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D236" s="5" t="n">
+        <v/>
       </c>
       <c r="E236" s="5" t="inlineStr">
         <is>
@@ -15415,49 +15413,47 @@
       </c>
       <c r="G236" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H236" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I236" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J236" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K236" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L236" s="5" t="n"/>
       <c r="M236" s="5" t="n"/>
       <c r="N236" s="5" t="n">
-        <v>17.73</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_002</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B237" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
-        </is>
-      </c>
-      <c r="D237" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D237" s="5" t="n">
+        <v/>
       </c>
       <c r="E237" s="5" t="inlineStr">
         <is>
@@ -15471,49 +15467,47 @@
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H237" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I237" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J237" s="5" t="b">
         <v>0</v>
       </c>
       <c r="K237" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L237" s="5" t="n"/>
       <c r="M237" s="5" t="n"/>
       <c r="N237" s="5" t="n">
-        <v>16.24</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_002</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B238" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C238" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
-        </is>
-      </c>
-      <c r="D238" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D238" s="5" t="n">
+        <v/>
       </c>
       <c r="E238" s="5" t="inlineStr">
         <is>
@@ -15527,49 +15521,47 @@
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H238" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I238" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J238" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K238" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L238" s="5" t="n"/>
       <c r="M238" s="5" t="n"/>
       <c r="N238" s="5" t="n">
-        <v>16.98</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B239" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
-        </is>
-      </c>
-      <c r="D239" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D239" s="5" t="n">
+        <v/>
       </c>
       <c r="E239" s="5" t="inlineStr">
         <is>
@@ -15583,16 +15575,16 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I239" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J239" s="5" t="b">
         <v>1</v>
@@ -15605,27 +15597,25 @@
       <c r="L239" s="5" t="n"/>
       <c r="M239" s="5" t="n"/>
       <c r="N239" s="5" t="n">
-        <v>15.25</v>
+        <v>21.12</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B240" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C240" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
-        </is>
-      </c>
-      <c r="D240" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D240" s="5" t="n">
+        <v/>
       </c>
       <c r="E240" s="5" t="inlineStr">
         <is>
@@ -15639,19 +15629,19 @@
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H240" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I240" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J240" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K240" s="5" t="inlineStr">
         <is>
@@ -15661,27 +15651,25 @@
       <c r="L240" s="5" t="n"/>
       <c r="M240" s="5" t="n"/>
       <c r="N240" s="5" t="n">
-        <v>16.44</v>
+        <v>44.56</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B241" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
-        </is>
-      </c>
-      <c r="D241" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D241" s="5" t="n">
+        <v/>
       </c>
       <c r="E241" s="5" t="inlineStr">
         <is>
@@ -15695,48 +15683,48 @@
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="H241" s="5" t="inlineStr">
+        <is>
           <t>template</t>
         </is>
       </c>
-      <c r="H241" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
       <c r="I241" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J241" s="5" t="b">
         <v>0</v>
       </c>
       <c r="K241" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>sparql_build_failure</t>
         </is>
       </c>
       <c r="L241" s="5" t="n"/>
       <c r="M241" s="5" t="n"/>
       <c r="N241" s="5" t="n">
-        <v>14.11</v>
+        <v>12.53</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_001</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B242" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E242" s="5" t="inlineStr">
@@ -15751,12 +15739,12 @@
       </c>
       <c r="G242" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H242" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I242" s="5" t="b">
@@ -15770,29 +15758,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L242" s="5" t="n"/>
-      <c r="M242" s="5" t="n"/>
+      <c r="L242" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M242" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N242" s="5" t="n">
-        <v>14.2</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_001</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B243" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E243" s="5" t="inlineStr">
@@ -15807,48 +15799,52 @@
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H243" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I243" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J243" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K243" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L243" s="5" t="n"/>
-      <c r="M243" s="5" t="n"/>
+          <t>mapping_failure</t>
+        </is>
+      </c>
+      <c r="L243" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M243" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N243" s="5" t="n">
-        <v>14.37</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_001</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B244" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E244" s="5" t="inlineStr">
@@ -15863,35 +15859,39 @@
       </c>
       <c r="G244" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H244" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I244" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J244" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K244" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L244" s="5" t="n"/>
-      <c r="M244" s="5" t="n"/>
+          <t>mapping_failure</t>
+        </is>
+      </c>
+      <c r="L244" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M244" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N244" s="5" t="n">
-        <v>15.89</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_002</t>
+          <t>filter_string_kg2_001</t>
         </is>
       </c>
       <c r="B245" s="5" t="n">
@@ -15899,7 +15899,7 @@
       </c>
       <c r="C245" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D245" s="5" t="inlineStr">
@@ -15914,7 +15914,7 @@
       </c>
       <c r="F245" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr">
@@ -15941,13 +15941,13 @@
       <c r="L245" s="5" t="n"/>
       <c r="M245" s="5" t="n"/>
       <c r="N245" s="5" t="n">
-        <v>13.56</v>
+        <v>35.74</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_002</t>
+          <t>filter_string_kg2_001</t>
         </is>
       </c>
       <c r="B246" s="5" t="n">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="C246" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D246" s="5" t="inlineStr">
@@ -15970,7 +15970,7 @@
       </c>
       <c r="F246" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
@@ -15997,13 +15997,13 @@
       <c r="L246" s="5" t="n"/>
       <c r="M246" s="5" t="n"/>
       <c r="N246" s="5" t="n">
-        <v>13.72</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_002</t>
+          <t>filter_string_kg2_001</t>
         </is>
       </c>
       <c r="B247" s="5" t="n">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="C247" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D247" s="5" t="inlineStr">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
@@ -16053,13 +16053,13 @@
       <c r="L247" s="5" t="n"/>
       <c r="M247" s="5" t="n"/>
       <c r="N247" s="5" t="n">
-        <v>13.77</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_003</t>
+          <t>filter_string_kg2_002</t>
         </is>
       </c>
       <c r="B248" s="5" t="n">
@@ -16067,7 +16067,7 @@
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D248" s="5" t="inlineStr">
@@ -16082,7 +16082,7 @@
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
@@ -16109,13 +16109,13 @@
       <c r="L248" s="5" t="n"/>
       <c r="M248" s="5" t="n"/>
       <c r="N248" s="5" t="n">
-        <v>13.92</v>
+        <v>13.46</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_003</t>
+          <t>filter_string_kg2_002</t>
         </is>
       </c>
       <c r="B249" s="5" t="n">
@@ -16123,7 +16123,7 @@
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D249" s="5" t="inlineStr">
@@ -16138,7 +16138,7 @@
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
@@ -16165,13 +16165,13 @@
       <c r="L249" s="5" t="n"/>
       <c r="M249" s="5" t="n"/>
       <c r="N249" s="5" t="n">
-        <v>22.08</v>
+        <v>13.03</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_003</t>
+          <t>filter_string_kg2_002</t>
         </is>
       </c>
       <c r="B250" s="5" t="n">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D250" s="5" t="inlineStr">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
@@ -16221,25 +16221,27 @@
       <c r="L250" s="5" t="n"/>
       <c r="M250" s="5" t="n"/>
       <c r="N250" s="5" t="n">
-        <v>15.17</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B251" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C251" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D251" s="5" t="n">
-        <v/>
+          <t>filter_string_kg2</t>
+        </is>
+      </c>
+      <c r="D251" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
@@ -16248,52 +16250,54 @@
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H251" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I251" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J251" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K251" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L251" s="5" t="n"/>
       <c r="M251" s="5" t="n"/>
       <c r="N251" s="5" t="n">
-        <v>4.09</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B252" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C252" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D252" s="5" t="n">
-        <v/>
+          <t>filter_string_kg2</t>
+        </is>
+      </c>
+      <c r="D252" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
@@ -16302,52 +16306,54 @@
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H252" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I252" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J252" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K252" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L252" s="5" t="n"/>
       <c r="M252" s="5" t="n"/>
       <c r="N252" s="5" t="n">
-        <v>3.9</v>
+        <v>9.619999999999999</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B253" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D253" s="5" t="n">
-        <v/>
+          <t>filter_string_kg2</t>
+        </is>
+      </c>
+      <c r="D253" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
       </c>
       <c r="E253" s="5" t="inlineStr">
         <is>
@@ -16356,52 +16362,54 @@
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I253" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J253" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K253" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L253" s="5" t="n"/>
       <c r="M253" s="5" t="n"/>
       <c r="N253" s="5" t="n">
-        <v>4.26</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>count_kg1_002</t>
         </is>
       </c>
       <c r="B254" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D254" s="5" t="n">
-        <v/>
+          <t>count_kg1</t>
+        </is>
+      </c>
+      <c r="D254" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
@@ -16410,21 +16418,21 @@
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H254" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I254" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J254" s="5" t="b">
         <v>1</v>
@@ -16437,25 +16445,27 @@
       <c r="L254" s="5" t="n"/>
       <c r="M254" s="5" t="n"/>
       <c r="N254" s="5" t="n">
-        <v>21.12</v>
+        <v>17.01</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>count_kg1_002</t>
         </is>
       </c>
       <c r="B255" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D255" s="5" t="n">
-        <v/>
+          <t>count_kg1</t>
+        </is>
+      </c>
+      <c r="D255" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
       </c>
       <c r="E255" s="5" t="inlineStr">
         <is>
@@ -16464,52 +16474,54 @@
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I255" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J255" s="5" t="b">
         <v>1</v>
       </c>
       <c r="K255" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L255" s="5" t="n"/>
       <c r="M255" s="5" t="n"/>
       <c r="N255" s="5" t="n">
-        <v>44.56</v>
+        <v>14.33</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>count_kg1_002</t>
         </is>
       </c>
       <c r="B256" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C256" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D256" s="5" t="n">
-        <v/>
+          <t>count_kg1</t>
+        </is>
+      </c>
+      <c r="D256" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
       </c>
       <c r="E256" s="5" t="inlineStr">
         <is>
@@ -16518,12 +16530,12 @@
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H256" s="5" t="inlineStr">
@@ -16532,39 +16544,39 @@
         </is>
       </c>
       <c r="I256" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J256" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K256" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L256" s="5" t="n"/>
       <c r="M256" s="5" t="n"/>
       <c r="N256" s="5" t="n">
-        <v>12.53</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>count_kg1_003</t>
         </is>
       </c>
       <c r="B257" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E257" s="5" t="inlineStr">
@@ -16574,17 +16586,17 @@
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I257" s="5" t="b">
@@ -16598,33 +16610,29 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L257" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M257" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L257" s="5" t="n"/>
+      <c r="M257" s="5" t="n"/>
       <c r="N257" s="5" t="n">
-        <v>4.41</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>count_kg1_003</t>
         </is>
       </c>
       <c r="B258" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E258" s="5" t="inlineStr">
@@ -16634,57 +16642,53 @@
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H258" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I258" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J258" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K258" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L258" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M258" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L258" s="5" t="n"/>
+      <c r="M258" s="5" t="n"/>
       <c r="N258" s="5" t="n">
-        <v>3.66</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>count_kg1_003</t>
         </is>
       </c>
       <c r="B259" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C259" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E259" s="5" t="inlineStr">
@@ -16694,38 +16698,34 @@
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H259" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I259" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J259" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K259" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L259" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M259" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L259" s="5" t="n"/>
+      <c r="M259" s="5" t="n"/>
       <c r="N259" s="5" t="n">
-        <v>4.99</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="260">
@@ -16785,7 +16785,7 @@
         <v>0</v>
       </c>
       <c r="N260" s="5" t="n">
-        <v>17.78</v>
+        <v>28.93</v>
       </c>
     </row>
     <row r="261">
@@ -16845,7 +16845,7 @@
         <v>1</v>
       </c>
       <c r="N261" s="5" t="n">
-        <v>21.82</v>
+        <v>19.93</v>
       </c>
     </row>
     <row r="262">
@@ -16905,7 +16905,7 @@
         <v>0</v>
       </c>
       <c r="N262" s="5" t="n">
-        <v>18.98</v>
+        <v>16.47</v>
       </c>
     </row>
     <row r="263">
@@ -16965,7 +16965,7 @@
         <v>0</v>
       </c>
       <c r="N263" s="5" t="n">
-        <v>18.26</v>
+        <v>18.45</v>
       </c>
     </row>
     <row r="264">
@@ -17025,7 +17025,7 @@
         <v>1</v>
       </c>
       <c r="N264" s="5" t="n">
-        <v>22.52</v>
+        <v>24.79</v>
       </c>
     </row>
     <row r="265">
@@ -17085,7 +17085,7 @@
         <v>0</v>
       </c>
       <c r="N265" s="5" t="n">
-        <v>18.51</v>
+        <v>17.84</v>
       </c>
     </row>
     <row r="266">
@@ -17141,7 +17141,7 @@
       <c r="L266" s="5" t="n"/>
       <c r="M266" s="5" t="n"/>
       <c r="N266" s="5" t="n">
-        <v>24.16</v>
+        <v>23.17</v>
       </c>
     </row>
     <row r="267">
@@ -17197,7 +17197,7 @@
       <c r="L267" s="5" t="n"/>
       <c r="M267" s="5" t="n"/>
       <c r="N267" s="5" t="n">
-        <v>23.64</v>
+        <v>22.38</v>
       </c>
     </row>
     <row r="268">
@@ -17253,7 +17253,7 @@
       <c r="L268" s="5" t="n"/>
       <c r="M268" s="5" t="n"/>
       <c r="N268" s="5" t="n">
-        <v>23.49</v>
+        <v>23.04</v>
       </c>
     </row>
     <row r="269">
@@ -17309,7 +17309,7 @@
       <c r="L269" s="5" t="n"/>
       <c r="M269" s="5" t="n"/>
       <c r="N269" s="5" t="n">
-        <v>24.41</v>
+        <v>24.88</v>
       </c>
     </row>
     <row r="270">
@@ -17365,7 +17365,7 @@
       <c r="L270" s="5" t="n"/>
       <c r="M270" s="5" t="n"/>
       <c r="N270" s="5" t="n">
-        <v>24.78</v>
+        <v>24.77</v>
       </c>
     </row>
     <row r="271">
@@ -17421,7 +17421,7 @@
       <c r="L271" s="5" t="n"/>
       <c r="M271" s="5" t="n"/>
       <c r="N271" s="5" t="n">
-        <v>24</v>
+        <v>23.62</v>
       </c>
     </row>
     <row r="272">
@@ -17481,7 +17481,7 @@
         <v>0.2667</v>
       </c>
       <c r="N272" s="5" t="n">
-        <v>14.19</v>
+        <v>13.54</v>
       </c>
     </row>
     <row r="273">
@@ -17541,7 +17541,7 @@
         <v>0.2667</v>
       </c>
       <c r="N273" s="5" t="n">
-        <v>13.74</v>
+        <v>12.56</v>
       </c>
     </row>
     <row r="274">
@@ -17601,7 +17601,7 @@
         <v>0.2667</v>
       </c>
       <c r="N274" s="5" t="n">
-        <v>13.66</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="275">
@@ -17661,7 +17661,7 @@
         <v>0.2222</v>
       </c>
       <c r="N275" s="5" t="n">
-        <v>13.37</v>
+        <v>11.89</v>
       </c>
     </row>
     <row r="276">
@@ -17721,7 +17721,7 @@
         <v>0.2222</v>
       </c>
       <c r="N276" s="5" t="n">
-        <v>13.26</v>
+        <v>11.82</v>
       </c>
     </row>
     <row r="277">
@@ -17760,14 +17760,14 @@
       </c>
       <c r="H277" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I277" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J277" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K277" s="5" t="inlineStr">
         <is>
@@ -17778,10 +17778,10 @@
         <v>0</v>
       </c>
       <c r="M277" s="5" t="n">
-        <v>0.2222</v>
+        <v>0</v>
       </c>
       <c r="N277" s="5" t="n">
-        <v>13.43</v>
+        <v>20.53</v>
       </c>
     </row>
     <row r="278">
@@ -17841,7 +17841,7 @@
         <v>0.3077</v>
       </c>
       <c r="N278" s="5" t="n">
-        <v>10.02</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="279">
@@ -17901,7 +17901,7 @@
         <v>0.3077</v>
       </c>
       <c r="N279" s="5" t="n">
-        <v>9.91</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="280">
@@ -17961,7 +17961,7 @@
         <v>0.3077</v>
       </c>
       <c r="N280" s="5" t="n">
-        <v>10.07</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="281">
@@ -18015,7 +18015,7 @@
       <c r="L281" s="5" t="n"/>
       <c r="M281" s="5" t="n"/>
       <c r="N281" s="5" t="n">
-        <v>23.98</v>
+        <v>21.08</v>
       </c>
     </row>
     <row r="282">
@@ -18069,7 +18069,7 @@
       <c r="L282" s="5" t="n"/>
       <c r="M282" s="5" t="n"/>
       <c r="N282" s="5" t="n">
-        <v>32.68</v>
+        <v>34.21</v>
       </c>
     </row>
     <row r="283">
@@ -18123,7 +18123,7 @@
       <c r="L283" s="5" t="n"/>
       <c r="M283" s="5" t="n"/>
       <c r="N283" s="5" t="n">
-        <v>5.09</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="284">
@@ -18183,7 +18183,7 @@
         <v>0</v>
       </c>
       <c r="N284" s="5" t="n">
-        <v>4.7</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="285">
@@ -18243,7 +18243,7 @@
         <v>0</v>
       </c>
       <c r="N285" s="5" t="n">
-        <v>17.02</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="286">
@@ -18303,7 +18303,7 @@
         <v>0</v>
       </c>
       <c r="N286" s="5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="287">
@@ -18363,7 +18363,7 @@
         <v>0</v>
       </c>
       <c r="N287" s="5" t="n">
-        <v>4.53</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="288">
@@ -18423,7 +18423,7 @@
         <v>0</v>
       </c>
       <c r="N288" s="5" t="n">
-        <v>19.83</v>
+        <v>15.32</v>
       </c>
     </row>
     <row r="289">
@@ -18483,7 +18483,7 @@
         <v>0</v>
       </c>
       <c r="N289" s="5" t="n">
-        <v>5.14</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="290">
@@ -18543,7 +18543,7 @@
         <v>1</v>
       </c>
       <c r="N290" s="5" t="n">
-        <v>4.68</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="291">
@@ -18603,7 +18603,7 @@
         <v>0</v>
       </c>
       <c r="N291" s="5" t="n">
-        <v>21.12</v>
+        <v>21.18</v>
       </c>
     </row>
     <row r="292">
@@ -18663,7 +18663,7 @@
         <v>0</v>
       </c>
       <c r="N292" s="5" t="n">
-        <v>6.03</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="293">
@@ -18723,7 +18723,7 @@
         <v>1</v>
       </c>
       <c r="N293" s="5" t="n">
-        <v>15.94</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="294">
@@ -18783,7 +18783,7 @@
         <v>1</v>
       </c>
       <c r="N294" s="5" t="n">
-        <v>16.43</v>
+        <v>15.44</v>
       </c>
     </row>
     <row r="295">
@@ -18843,7 +18843,7 @@
         <v>1</v>
       </c>
       <c r="N295" s="5" t="n">
-        <v>15.84</v>
+        <v>15.16</v>
       </c>
     </row>
     <row r="296">
@@ -18903,7 +18903,7 @@
         <v>1</v>
       </c>
       <c r="N296" s="5" t="n">
-        <v>30.83</v>
+        <v>29.89</v>
       </c>
     </row>
     <row r="297">
@@ -18963,7 +18963,7 @@
         <v>0.2</v>
       </c>
       <c r="N297" s="5" t="n">
-        <v>17.77</v>
+        <v>16.52</v>
       </c>
     </row>
     <row r="298">
@@ -19002,7 +19002,7 @@
       </c>
       <c r="H298" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I298" s="5" t="b">
@@ -19020,10 +19020,10 @@
         <v>0</v>
       </c>
       <c r="M298" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N298" s="5" t="n">
-        <v>18.24</v>
+        <v>22.66</v>
       </c>
     </row>
     <row r="299">
@@ -19083,7 +19083,7 @@
         <v>1</v>
       </c>
       <c r="N299" s="5" t="n">
-        <v>20.3</v>
+        <v>19.57</v>
       </c>
     </row>
     <row r="300">
@@ -19143,7 +19143,7 @@
         <v>1</v>
       </c>
       <c r="N300" s="5" t="n">
-        <v>23.03</v>
+        <v>21.27</v>
       </c>
     </row>
     <row r="301">
@@ -19203,7 +19203,7 @@
         <v>1</v>
       </c>
       <c r="N301" s="5" t="n">
-        <v>22.92</v>
+        <v>21.57</v>
       </c>
     </row>
     <row r="302">
@@ -19263,7 +19263,7 @@
         <v>1</v>
       </c>
       <c r="N302" s="5" t="n">
-        <v>16.06</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="303">
@@ -19323,7 +19323,7 @@
         <v>1</v>
       </c>
       <c r="N303" s="5" t="n">
-        <v>16.26</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="304">
@@ -19383,7 +19383,7 @@
         <v>1</v>
       </c>
       <c r="N304" s="5" t="n">
-        <v>15.75</v>
+        <v>16.23</v>
       </c>
     </row>
     <row r="305">
@@ -19443,7 +19443,7 @@
         <v>1</v>
       </c>
       <c r="N305" s="5" t="n">
-        <v>15.61</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="306">
@@ -19503,7 +19503,7 @@
         <v>1</v>
       </c>
       <c r="N306" s="5" t="n">
-        <v>16.6</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="307">
@@ -19542,28 +19542,28 @@
       </c>
       <c r="H307" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I307" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J307" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K307" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L307" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M307" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N307" s="5" t="n">
-        <v>16.14</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="308">
@@ -19623,7 +19623,7 @@
         <v>0</v>
       </c>
       <c r="N308" s="5" t="n">
-        <v>4.34</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="309">
@@ -19669,11 +19669,11 @@
         <v>1</v>
       </c>
       <c r="J309" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K309" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L309" s="5" t="b">
@@ -19683,7 +19683,7 @@
         <v>0</v>
       </c>
       <c r="N309" s="5" t="n">
-        <v>16.38</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="310">
@@ -19743,7 +19743,7 @@
         <v>0</v>
       </c>
       <c r="N310" s="5" t="n">
-        <v>5.54</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="311">
@@ -19803,7 +19803,7 @@
         <v>1</v>
       </c>
       <c r="N311" s="5" t="n">
-        <v>15.46</v>
+        <v>14.06</v>
       </c>
     </row>
     <row r="312">
@@ -19863,7 +19863,7 @@
         <v>1</v>
       </c>
       <c r="N312" s="5" t="n">
-        <v>17.33</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="313">
@@ -19923,7 +19923,7 @@
         <v>1</v>
       </c>
       <c r="N313" s="5" t="n">
-        <v>16.73</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="314">
@@ -19979,7 +19979,7 @@
       <c r="L314" s="5" t="n"/>
       <c r="M314" s="5" t="n"/>
       <c r="N314" s="5" t="n">
-        <v>12.31</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="315">
@@ -20035,7 +20035,7 @@
       <c r="L315" s="5" t="n"/>
       <c r="M315" s="5" t="n"/>
       <c r="N315" s="5" t="n">
-        <v>14</v>
+        <v>13.26</v>
       </c>
     </row>
     <row r="316">
@@ -20091,7 +20091,7 @@
       <c r="L316" s="5" t="n"/>
       <c r="M316" s="5" t="n"/>
       <c r="N316" s="5" t="n">
-        <v>14.22</v>
+        <v>13.13</v>
       </c>
     </row>
     <row r="317">
@@ -20151,7 +20151,7 @@
         <v>0.5</v>
       </c>
       <c r="N317" s="5" t="n">
-        <v>12.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="318">
@@ -20211,7 +20211,7 @@
         <v>0.5</v>
       </c>
       <c r="N318" s="5" t="n">
-        <v>12.97</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="319">
@@ -20271,7 +20271,7 @@
         <v>0.5</v>
       </c>
       <c r="N319" s="5" t="n">
-        <v>12.6</v>
+        <v>12.68</v>
       </c>
     </row>
     <row r="320">
@@ -20327,7 +20327,7 @@
       <c r="L320" s="5" t="n"/>
       <c r="M320" s="5" t="n"/>
       <c r="N320" s="5" t="n">
-        <v>12.83</v>
+        <v>11.94</v>
       </c>
     </row>
     <row r="321">
@@ -20383,7 +20383,7 @@
       <c r="L321" s="5" t="n"/>
       <c r="M321" s="5" t="n"/>
       <c r="N321" s="5" t="n">
-        <v>12.57</v>
+        <v>11.78</v>
       </c>
     </row>
     <row r="322">
@@ -20439,7 +20439,7 @@
       <c r="L322" s="5" t="n"/>
       <c r="M322" s="5" t="n"/>
       <c r="N322" s="5" t="n">
-        <v>12.84</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="323">
@@ -20495,7 +20495,7 @@
       <c r="L323" s="5" t="n"/>
       <c r="M323" s="5" t="n"/>
       <c r="N323" s="5" t="n">
-        <v>12.38</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="324">
@@ -20551,7 +20551,7 @@
       <c r="L324" s="5" t="n"/>
       <c r="M324" s="5" t="n"/>
       <c r="N324" s="5" t="n">
-        <v>13.58</v>
+        <v>12.43</v>
       </c>
     </row>
     <row r="325">
@@ -20607,7 +20607,7 @@
       <c r="L325" s="5" t="n"/>
       <c r="M325" s="5" t="n"/>
       <c r="N325" s="5" t="n">
-        <v>14.61</v>
+        <v>11.56</v>
       </c>
     </row>
   </sheetData>

--- a/NL2SPARQL_Evaluation_Results.xlsx
+++ b/NL2SPARQL_Evaluation_Results.xlsx
@@ -1552,11 +1552,11 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I2" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="5" t="b">
         <v>1</v>
@@ -1573,7 +1573,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>34.74</v>
+        <v>34.84</v>
       </c>
     </row>
     <row r="3">
@@ -1612,11 +1612,11 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I3" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5" t="b">
         <v>1</v>
@@ -1633,7 +1633,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>16.11</v>
+        <v>15.42</v>
       </c>
     </row>
     <row r="4">
@@ -1672,11 +1672,11 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I4" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5" t="b">
         <v>1</v>
@@ -1693,7 +1693,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>15.71</v>
+        <v>15.29</v>
       </c>
     </row>
     <row r="5">
@@ -1732,11 +1732,11 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I5" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5" t="b">
         <v>1</v>
@@ -1753,7 +1753,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>20.86</v>
+        <v>16.93</v>
       </c>
     </row>
     <row r="6">
@@ -1792,11 +1792,11 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I6" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="5" t="b">
         <v>1</v>
@@ -1813,7 +1813,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>15.74</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -1852,11 +1852,11 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I7" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="5" t="b">
         <v>1</v>
@@ -1873,7 +1873,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>16.01</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="8">
@@ -1912,11 +1912,11 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I8" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="5" t="b">
         <v>1</v>
@@ -1933,7 +1933,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>27.53</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="9">
@@ -1972,11 +1972,11 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I9" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="5" t="b">
         <v>1</v>
@@ -1993,7 +1993,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>16.67</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -2032,11 +2032,11 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I10" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="5" t="b">
         <v>1</v>
@@ -2053,7 +2053,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>17.23</v>
+        <v>16.44</v>
       </c>
     </row>
     <row r="11">
@@ -2113,7 +2113,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>14.35</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="12">
@@ -2173,7 +2173,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>13.98</v>
+        <v>13.87</v>
       </c>
     </row>
     <row r="13">
@@ -2233,7 +2233,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>14.32</v>
+        <v>14.62</v>
       </c>
     </row>
     <row r="14">
@@ -2293,7 +2293,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>16.47</v>
+        <v>15.87</v>
       </c>
     </row>
     <row r="15">
@@ -2353,7 +2353,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>14.85</v>
+        <v>15.33</v>
       </c>
     </row>
     <row r="16">
@@ -2413,7 +2413,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>15.45</v>
+        <v>15.07</v>
       </c>
     </row>
     <row r="17">
@@ -2473,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>16.84</v>
+        <v>30.02</v>
       </c>
     </row>
     <row r="18">
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>16.03</v>
+        <v>15.85</v>
       </c>
     </row>
     <row r="19">
@@ -2593,7 +2593,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>16.34</v>
+        <v>16.53</v>
       </c>
     </row>
     <row r="20">
@@ -2653,7 +2653,7 @@
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>16.96</v>
+        <v>16.38</v>
       </c>
     </row>
     <row r="21">
@@ -2713,7 +2713,7 @@
         <v>1</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>15.15</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="22">
@@ -2773,7 +2773,7 @@
         <v>1</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>15.73</v>
+        <v>15.11</v>
       </c>
     </row>
     <row r="23">
@@ -2833,7 +2833,7 @@
         <v>1</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>16.87</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="24">
@@ -2893,7 +2893,7 @@
         <v>1</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>16.33</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="25">
@@ -2953,7 +2953,7 @@
         <v>1</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>17.02</v>
+        <v>16.46</v>
       </c>
     </row>
     <row r="26">
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>18.61</v>
+        <v>17.56</v>
       </c>
     </row>
     <row r="27">
@@ -3052,18 +3052,18 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I27" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L27" s="5" t="b">
@@ -3073,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>14.07</v>
+        <v>20.62</v>
       </c>
     </row>
     <row r="28">
@@ -3133,7 +3133,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>12.82</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="29">
@@ -3187,13 +3187,13 @@
         </is>
       </c>
       <c r="L29" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>21.76</v>
+        <v>20.02</v>
       </c>
     </row>
     <row r="30">
@@ -3247,13 +3247,13 @@
         </is>
       </c>
       <c r="L30" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>21.35</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="31">
@@ -3307,13 +3307,13 @@
         </is>
       </c>
       <c r="L31" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>20.25</v>
+        <v>18.96</v>
       </c>
     </row>
     <row r="32">
@@ -3370,10 +3370,10 @@
         <v>0</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>18.92</v>
+        <v>16.49</v>
       </c>
     </row>
     <row r="33">
@@ -3430,10 +3430,10 @@
         <v>0</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>15.84</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="34">
@@ -3490,10 +3490,10 @@
         <v>0</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>15.96</v>
+        <v>14.93</v>
       </c>
     </row>
     <row r="35">
@@ -3532,11 +3532,11 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I35" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" s="5" t="b">
         <v>1</v>
@@ -3550,10 +3550,10 @@
         <v>0</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N35" s="5" t="n">
-        <v>26.33</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="36">
@@ -3592,11 +3592,11 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I36" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="5" t="b">
         <v>1</v>
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>18.27</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="37">
@@ -3652,18 +3652,18 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I37" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L37" s="5" t="b">
@@ -3673,7 +3673,7 @@
         <v>0</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>14.7</v>
+        <v>20.39</v>
       </c>
     </row>
     <row r="38">
@@ -3733,7 +3733,7 @@
         <v>1</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>23.68</v>
+        <v>19.32</v>
       </c>
     </row>
     <row r="39">
@@ -3793,7 +3793,7 @@
         <v>1</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>22.97</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="40">
@@ -3853,7 +3853,7 @@
         <v>1</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>21.71</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="41">
@@ -3913,7 +3913,7 @@
         <v>0.2</v>
       </c>
       <c r="N41" s="5" t="n">
-        <v>18.18</v>
+        <v>18.54</v>
       </c>
     </row>
     <row r="42">
@@ -3973,7 +3973,7 @@
         <v>0.2</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>17.01</v>
+        <v>16.81</v>
       </c>
     </row>
     <row r="43">
@@ -4033,7 +4033,7 @@
         <v>0.2</v>
       </c>
       <c r="N43" s="5" t="n">
-        <v>17.45</v>
+        <v>16.98</v>
       </c>
     </row>
     <row r="44">
@@ -4093,7 +4093,7 @@
         <v>0</v>
       </c>
       <c r="N44" s="5" t="n">
-        <v>17.73</v>
+        <v>17.23</v>
       </c>
     </row>
     <row r="45">
@@ -4139,11 +4139,11 @@
         <v>0</v>
       </c>
       <c r="J45" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L45" s="5" t="b">
@@ -4153,7 +4153,7 @@
         <v>0</v>
       </c>
       <c r="N45" s="5" t="n">
-        <v>17.89</v>
+        <v>12.83</v>
       </c>
     </row>
     <row r="46">
@@ -4213,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>18.04</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="47">
@@ -4252,11 +4252,11 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I47" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" s="5" t="b">
         <v>1</v>
@@ -4267,13 +4267,13 @@
         </is>
       </c>
       <c r="L47" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N47" s="5" t="n">
-        <v>27.51</v>
+        <v>20.39</v>
       </c>
     </row>
     <row r="48">
@@ -4327,13 +4327,13 @@
         </is>
       </c>
       <c r="L48" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N48" s="5" t="n">
-        <v>25.5</v>
+        <v>23.54</v>
       </c>
     </row>
     <row r="49">
@@ -4393,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="N49" s="5" t="n">
-        <v>18.25</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="50">
@@ -4453,7 +4453,7 @@
         <v>0</v>
       </c>
       <c r="N50" s="5" t="n">
-        <v>20.28</v>
+        <v>18.83</v>
       </c>
     </row>
     <row r="51">
@@ -4513,7 +4513,7 @@
         <v>0</v>
       </c>
       <c r="N51" s="5" t="n">
-        <v>20.24</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="52">
@@ -4573,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="N52" s="5" t="n">
-        <v>17.92</v>
+        <v>18.72</v>
       </c>
     </row>
     <row r="53">
@@ -4612,11 +4612,11 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I53" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" s="5" t="b">
         <v>1</v>
@@ -4627,13 +4627,13 @@
         </is>
       </c>
       <c r="L53" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>44.86</v>
+        <v>21.49</v>
       </c>
     </row>
     <row r="54">
@@ -4693,7 +4693,7 @@
         <v>0</v>
       </c>
       <c r="N54" s="5" t="n">
-        <v>20.27</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="55">
@@ -4739,11 +4739,11 @@
         <v>0</v>
       </c>
       <c r="J55" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L55" s="5" t="b">
@@ -4753,7 +4753,7 @@
         <v>0</v>
       </c>
       <c r="N55" s="5" t="n">
-        <v>14.53</v>
+        <v>16.24</v>
       </c>
     </row>
     <row r="56">
@@ -4792,11 +4792,11 @@
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I56" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="5" t="b">
         <v>1</v>
@@ -4813,7 +4813,7 @@
         <v>1</v>
       </c>
       <c r="N56" s="5" t="n">
-        <v>21.39</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="57">
@@ -4852,11 +4852,11 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I57" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" s="5" t="b">
         <v>1</v>
@@ -4873,7 +4873,7 @@
         <v>1</v>
       </c>
       <c r="N57" s="5" t="n">
-        <v>16.86</v>
+        <v>13.54</v>
       </c>
     </row>
     <row r="58">
@@ -4912,11 +4912,11 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I58" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" s="5" t="b">
         <v>1</v>
@@ -4933,7 +4933,7 @@
         <v>1</v>
       </c>
       <c r="N58" s="5" t="n">
-        <v>18.46</v>
+        <v>14.14</v>
       </c>
     </row>
     <row r="59">
@@ -4972,11 +4972,11 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I59" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" s="5" t="b">
         <v>1</v>
@@ -4993,7 +4993,7 @@
         <v>1</v>
       </c>
       <c r="N59" s="5" t="n">
-        <v>22.78</v>
+        <v>16.03</v>
       </c>
     </row>
     <row r="60">
@@ -5032,11 +5032,11 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I60" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" s="5" t="b">
         <v>1</v>
@@ -5053,7 +5053,7 @@
         <v>1</v>
       </c>
       <c r="N60" s="5" t="n">
-        <v>16.74</v>
+        <v>14.82</v>
       </c>
     </row>
     <row r="61">
@@ -5092,11 +5092,11 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I61" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" s="5" t="b">
         <v>1</v>
@@ -5113,7 +5113,7 @@
         <v>1</v>
       </c>
       <c r="N61" s="5" t="n">
-        <v>16.57</v>
+        <v>16.53</v>
       </c>
     </row>
     <row r="62">
@@ -5152,11 +5152,11 @@
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I62" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" s="5" t="b">
         <v>1</v>
@@ -5167,13 +5167,13 @@
         </is>
       </c>
       <c r="L62" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N62" s="5" t="n">
-        <v>18.83</v>
+        <v>17.01</v>
       </c>
     </row>
     <row r="63">
@@ -5212,11 +5212,11 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I63" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" s="5" t="b">
         <v>1</v>
@@ -5227,13 +5227,13 @@
         </is>
       </c>
       <c r="L63" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N63" s="5" t="n">
-        <v>18.92</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="64">
@@ -5272,11 +5272,11 @@
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I64" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" s="5" t="b">
         <v>1</v>
@@ -5287,13 +5287,13 @@
         </is>
       </c>
       <c r="L64" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N64" s="5" t="n">
-        <v>18.01</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="65">
@@ -5332,11 +5332,11 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I65" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" s="5" t="b">
         <v>1</v>
@@ -5347,13 +5347,13 @@
         </is>
       </c>
       <c r="L65" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N65" s="5" t="n">
-        <v>17.15</v>
+        <v>15.32</v>
       </c>
     </row>
     <row r="66">
@@ -5392,11 +5392,11 @@
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I66" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" s="5" t="b">
         <v>1</v>
@@ -5407,13 +5407,13 @@
         </is>
       </c>
       <c r="L66" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N66" s="5" t="n">
-        <v>16.05</v>
+        <v>13.47</v>
       </c>
     </row>
     <row r="67">
@@ -5452,11 +5452,11 @@
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I67" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" s="5" t="b">
         <v>1</v>
@@ -5467,13 +5467,13 @@
         </is>
       </c>
       <c r="L67" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N67" s="5" t="n">
-        <v>16.73</v>
+        <v>14.26</v>
       </c>
     </row>
     <row r="68">
@@ -5512,11 +5512,11 @@
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I68" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" s="5" t="b">
         <v>1</v>
@@ -5527,13 +5527,13 @@
         </is>
       </c>
       <c r="L68" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N68" s="5" t="n">
-        <v>18.12</v>
+        <v>15.78</v>
       </c>
     </row>
     <row r="69">
@@ -5572,11 +5572,11 @@
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I69" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" s="5" t="b">
         <v>1</v>
@@ -5587,13 +5587,13 @@
         </is>
       </c>
       <c r="L69" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N69" s="5" t="n">
-        <v>16.79</v>
+        <v>15.02</v>
       </c>
     </row>
     <row r="70">
@@ -5632,11 +5632,11 @@
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I70" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="5" t="b">
         <v>1</v>
@@ -5647,13 +5647,13 @@
         </is>
       </c>
       <c r="L70" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N70" s="5" t="n">
-        <v>16.77</v>
+        <v>15.85</v>
       </c>
     </row>
     <row r="71">
@@ -5692,11 +5692,11 @@
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I71" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" s="5" t="b">
         <v>1</v>
@@ -5713,7 +5713,7 @@
         <v>1</v>
       </c>
       <c r="N71" s="5" t="n">
-        <v>20.4</v>
+        <v>15.87</v>
       </c>
     </row>
     <row r="72">
@@ -5752,11 +5752,11 @@
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I72" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" s="5" t="b">
         <v>1</v>
@@ -5773,7 +5773,7 @@
         <v>1</v>
       </c>
       <c r="N72" s="5" t="n">
-        <v>17.65</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="73">
@@ -5812,11 +5812,11 @@
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I73" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" s="5" t="b">
         <v>1</v>
@@ -5833,7 +5833,7 @@
         <v>1</v>
       </c>
       <c r="N73" s="5" t="n">
-        <v>17.28</v>
+        <v>16.21</v>
       </c>
     </row>
     <row r="74">
@@ -5893,7 +5893,7 @@
         <v>1</v>
       </c>
       <c r="N74" s="5" t="n">
-        <v>16.64</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="75">
@@ -5953,7 +5953,7 @@
         <v>1</v>
       </c>
       <c r="N75" s="5" t="n">
-        <v>15.02</v>
+        <v>13.37</v>
       </c>
     </row>
     <row r="76">
@@ -6013,7 +6013,7 @@
         <v>1</v>
       </c>
       <c r="N76" s="5" t="n">
-        <v>15.58</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="77">
@@ -6073,7 +6073,7 @@
         <v>1</v>
       </c>
       <c r="N77" s="5" t="n">
-        <v>18</v>
+        <v>15.16</v>
       </c>
     </row>
     <row r="78">
@@ -6133,7 +6133,7 @@
         <v>1</v>
       </c>
       <c r="N78" s="5" t="n">
-        <v>15.46</v>
+        <v>14.52</v>
       </c>
     </row>
     <row r="79">
@@ -6193,7 +6193,7 @@
         <v>1</v>
       </c>
       <c r="N79" s="5" t="n">
-        <v>15.83</v>
+        <v>15.28</v>
       </c>
     </row>
     <row r="80">
@@ -6253,7 +6253,7 @@
         <v>1</v>
       </c>
       <c r="N80" s="5" t="n">
-        <v>16.95</v>
+        <v>15.16</v>
       </c>
     </row>
     <row r="81">
@@ -6313,7 +6313,7 @@
         <v>1</v>
       </c>
       <c r="N81" s="5" t="n">
-        <v>15.99</v>
+        <v>14.32</v>
       </c>
     </row>
     <row r="82">
@@ -6373,7 +6373,7 @@
         <v>1</v>
       </c>
       <c r="N82" s="5" t="n">
-        <v>15.66</v>
+        <v>15.52</v>
       </c>
     </row>
     <row r="83">
@@ -6433,7 +6433,7 @@
         <v>1</v>
       </c>
       <c r="N83" s="5" t="n">
-        <v>15.41</v>
+        <v>14</v>
       </c>
     </row>
     <row r="84">
@@ -6493,7 +6493,7 @@
         <v>1</v>
       </c>
       <c r="N84" s="5" t="n">
-        <v>13.36</v>
+        <v>12.13</v>
       </c>
     </row>
     <row r="85">
@@ -6553,7 +6553,7 @@
         <v>1</v>
       </c>
       <c r="N85" s="5" t="n">
-        <v>15.27</v>
+        <v>12.88</v>
       </c>
     </row>
     <row r="86">
@@ -6613,7 +6613,7 @@
         <v>1</v>
       </c>
       <c r="N86" s="5" t="n">
-        <v>16.02</v>
+        <v>14.34</v>
       </c>
     </row>
     <row r="87">
@@ -6673,7 +6673,7 @@
         <v>1</v>
       </c>
       <c r="N87" s="5" t="n">
-        <v>14.47</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="88">
@@ -6733,7 +6733,7 @@
         <v>1</v>
       </c>
       <c r="N88" s="5" t="n">
-        <v>14.96</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="89">
@@ -6793,7 +6793,7 @@
         <v>1</v>
       </c>
       <c r="N89" s="5" t="n">
-        <v>15.38</v>
+        <v>14.12</v>
       </c>
     </row>
     <row r="90">
@@ -6853,7 +6853,7 @@
         <v>1</v>
       </c>
       <c r="N90" s="5" t="n">
-        <v>14.5</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="91">
@@ -6913,7 +6913,7 @@
         <v>1</v>
       </c>
       <c r="N91" s="5" t="n">
-        <v>14.56</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="92">
@@ -6973,7 +6973,7 @@
         <v>1</v>
       </c>
       <c r="N92" s="5" t="n">
-        <v>16.31</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="93">
@@ -7033,7 +7033,7 @@
         <v>1</v>
       </c>
       <c r="N93" s="5" t="n">
-        <v>13.7</v>
+        <v>12.38</v>
       </c>
     </row>
     <row r="94">
@@ -7093,7 +7093,7 @@
         <v>1</v>
       </c>
       <c r="N94" s="5" t="n">
-        <v>14.35</v>
+        <v>13.21</v>
       </c>
     </row>
     <row r="95">
@@ -7153,7 +7153,7 @@
         <v>1</v>
       </c>
       <c r="N95" s="5" t="n">
-        <v>16.96</v>
+        <v>16.14</v>
       </c>
     </row>
     <row r="96">
@@ -7213,7 +7213,7 @@
         <v>1</v>
       </c>
       <c r="N96" s="5" t="n">
-        <v>15.6</v>
+        <v>14.17</v>
       </c>
     </row>
     <row r="97">
@@ -7273,7 +7273,7 @@
         <v>1</v>
       </c>
       <c r="N97" s="5" t="n">
-        <v>15.17</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="98">
@@ -7333,7 +7333,7 @@
         <v>1</v>
       </c>
       <c r="N98" s="5" t="n">
-        <v>16.33</v>
+        <v>14.34</v>
       </c>
     </row>
     <row r="99">
@@ -7393,7 +7393,7 @@
         <v>1</v>
       </c>
       <c r="N99" s="5" t="n">
-        <v>14.6</v>
+        <v>13.45</v>
       </c>
     </row>
     <row r="100">
@@ -7453,7 +7453,7 @@
         <v>1</v>
       </c>
       <c r="N100" s="5" t="n">
-        <v>15.98</v>
+        <v>14.69</v>
       </c>
     </row>
     <row r="101">
@@ -7492,28 +7492,28 @@
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I101" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J101" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K101" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L101" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M101" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N101" s="5" t="n">
-        <v>19.92</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="102">
@@ -7552,28 +7552,28 @@
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I102" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J102" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K102" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L102" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N102" s="5" t="n">
-        <v>18.96</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="103">
@@ -7612,28 +7612,28 @@
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I103" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J103" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K103" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L103" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M103" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N103" s="5" t="n">
-        <v>19</v>
+        <v>17.27</v>
       </c>
     </row>
     <row r="104">
@@ -7693,7 +7693,7 @@
         <v>1</v>
       </c>
       <c r="N104" s="5" t="n">
-        <v>20.18</v>
+        <v>17.72</v>
       </c>
     </row>
     <row r="105">
@@ -7753,7 +7753,7 @@
         <v>1</v>
       </c>
       <c r="N105" s="5" t="n">
-        <v>20.09</v>
+        <v>16.24</v>
       </c>
     </row>
     <row r="106">
@@ -7813,7 +7813,7 @@
         <v>1</v>
       </c>
       <c r="N106" s="5" t="n">
-        <v>21.36</v>
+        <v>18.65</v>
       </c>
     </row>
     <row r="107">
@@ -7873,7 +7873,7 @@
         <v>1</v>
       </c>
       <c r="N107" s="5" t="n">
-        <v>21.58</v>
+        <v>20.01</v>
       </c>
     </row>
     <row r="108">
@@ -7933,7 +7933,7 @@
         <v>1</v>
       </c>
       <c r="N108" s="5" t="n">
-        <v>20.41</v>
+        <v>18.67</v>
       </c>
     </row>
     <row r="109">
@@ -7993,7 +7993,7 @@
         <v>1</v>
       </c>
       <c r="N109" s="5" t="n">
-        <v>21</v>
+        <v>20.32</v>
       </c>
     </row>
     <row r="110">
@@ -8053,7 +8053,7 @@
         <v>1</v>
       </c>
       <c r="N110" s="5" t="n">
-        <v>15.2</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="111">
@@ -8113,7 +8113,7 @@
         <v>1</v>
       </c>
       <c r="N111" s="5" t="n">
-        <v>13.07</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="112">
@@ -8173,7 +8173,7 @@
         <v>1</v>
       </c>
       <c r="N112" s="5" t="n">
-        <v>14.14</v>
+        <v>13.47</v>
       </c>
     </row>
     <row r="113">
@@ -8233,7 +8233,7 @@
         <v>1</v>
       </c>
       <c r="N113" s="5" t="n">
-        <v>16.24</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="114">
@@ -8293,7 +8293,7 @@
         <v>1</v>
       </c>
       <c r="N114" s="5" t="n">
-        <v>16.45</v>
+        <v>14.87</v>
       </c>
     </row>
     <row r="115">
@@ -8353,7 +8353,7 @@
         <v>1</v>
       </c>
       <c r="N115" s="5" t="n">
-        <v>15.49</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="116">
@@ -8399,21 +8399,21 @@
         <v>1</v>
       </c>
       <c r="J116" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K116" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L116" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N116" s="5" t="n">
-        <v>17.09</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="117">
@@ -8459,11 +8459,11 @@
         <v>1</v>
       </c>
       <c r="J117" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K117" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L117" s="5" t="b">
@@ -8473,7 +8473,7 @@
         <v>0</v>
       </c>
       <c r="N117" s="5" t="n">
-        <v>18.71</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="118">
@@ -8519,21 +8519,21 @@
         <v>1</v>
       </c>
       <c r="J118" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K118" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L118" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N118" s="5" t="n">
-        <v>1.75</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="119">
@@ -8593,7 +8593,7 @@
         <v>1</v>
       </c>
       <c r="N119" s="5" t="n">
-        <v>22.47</v>
+        <v>18.94</v>
       </c>
     </row>
     <row r="120">
@@ -8653,7 +8653,7 @@
         <v>1</v>
       </c>
       <c r="N120" s="5" t="n">
-        <v>18.94</v>
+        <v>17.51</v>
       </c>
     </row>
     <row r="121">
@@ -8713,7 +8713,7 @@
         <v>1</v>
       </c>
       <c r="N121" s="5" t="n">
-        <v>20.94</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="122">
@@ -8773,7 +8773,7 @@
         <v>1</v>
       </c>
       <c r="N122" s="5" t="n">
-        <v>21.27</v>
+        <v>19.97</v>
       </c>
     </row>
     <row r="123">
@@ -8833,7 +8833,7 @@
         <v>1</v>
       </c>
       <c r="N123" s="5" t="n">
-        <v>20.51</v>
+        <v>19.28</v>
       </c>
     </row>
     <row r="124">
@@ -8893,7 +8893,7 @@
         <v>1</v>
       </c>
       <c r="N124" s="5" t="n">
-        <v>20.97</v>
+        <v>20.08</v>
       </c>
     </row>
     <row r="125">
@@ -8953,7 +8953,7 @@
         <v>1</v>
       </c>
       <c r="N125" s="5" t="n">
-        <v>20.57</v>
+        <v>18.68</v>
       </c>
     </row>
     <row r="126">
@@ -9013,7 +9013,7 @@
         <v>1</v>
       </c>
       <c r="N126" s="5" t="n">
-        <v>19.52</v>
+        <v>18.06</v>
       </c>
     </row>
     <row r="127">
@@ -9073,7 +9073,7 @@
         <v>1</v>
       </c>
       <c r="N127" s="5" t="n">
-        <v>21.25</v>
+        <v>19.67</v>
       </c>
     </row>
     <row r="128">
@@ -9127,13 +9127,13 @@
         </is>
       </c>
       <c r="L128" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M128" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N128" s="5" t="n">
-        <v>19.89</v>
+        <v>17.84</v>
       </c>
     </row>
     <row r="129">
@@ -9187,13 +9187,13 @@
         </is>
       </c>
       <c r="L129" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M129" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N129" s="5" t="n">
-        <v>18.13</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="130">
@@ -9247,13 +9247,13 @@
         </is>
       </c>
       <c r="L130" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M130" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N130" s="5" t="n">
-        <v>19.3</v>
+        <v>17.56</v>
       </c>
     </row>
     <row r="131">
@@ -9307,13 +9307,13 @@
         </is>
       </c>
       <c r="L131" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M131" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N131" s="5" t="n">
-        <v>22.26</v>
+        <v>18.55</v>
       </c>
     </row>
     <row r="132">
@@ -9367,13 +9367,13 @@
         </is>
       </c>
       <c r="L132" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M132" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N132" s="5" t="n">
-        <v>19.87</v>
+        <v>18.13</v>
       </c>
     </row>
     <row r="133">
@@ -9427,13 +9427,13 @@
         </is>
       </c>
       <c r="L133" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M133" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N133" s="5" t="n">
-        <v>19.71</v>
+        <v>19.48</v>
       </c>
     </row>
     <row r="134">
@@ -9487,13 +9487,13 @@
         </is>
       </c>
       <c r="L134" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M134" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N134" s="5" t="n">
-        <v>21.51</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="135">
@@ -9547,13 +9547,13 @@
         </is>
       </c>
       <c r="L135" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M135" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N135" s="5" t="n">
-        <v>20.54</v>
+        <v>18.82</v>
       </c>
     </row>
     <row r="136">
@@ -9607,13 +9607,13 @@
         </is>
       </c>
       <c r="L136" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M136" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N136" s="5" t="n">
-        <v>21.13</v>
+        <v>19.56</v>
       </c>
     </row>
     <row r="137">
@@ -9673,7 +9673,7 @@
         <v>1</v>
       </c>
       <c r="N137" s="5" t="n">
-        <v>14.48</v>
+        <v>13.35</v>
       </c>
     </row>
     <row r="138">
@@ -9733,7 +9733,7 @@
         <v>1</v>
       </c>
       <c r="N138" s="5" t="n">
-        <v>12.53</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="139">
@@ -9793,7 +9793,7 @@
         <v>1</v>
       </c>
       <c r="N139" s="5" t="n">
-        <v>13.28</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="140">
@@ -9853,7 +9853,7 @@
         <v>1</v>
       </c>
       <c r="N140" s="5" t="n">
-        <v>15.94</v>
+        <v>14.93</v>
       </c>
     </row>
     <row r="141">
@@ -9913,7 +9913,7 @@
         <v>1</v>
       </c>
       <c r="N141" s="5" t="n">
-        <v>14.75</v>
+        <v>15.16</v>
       </c>
     </row>
     <row r="142">
@@ -9973,7 +9973,7 @@
         <v>1</v>
       </c>
       <c r="N142" s="5" t="n">
-        <v>15.54</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="143">
@@ -10033,7 +10033,7 @@
         <v>1</v>
       </c>
       <c r="N143" s="5" t="n">
-        <v>15.79</v>
+        <v>14.18</v>
       </c>
     </row>
     <row r="144">
@@ -10087,13 +10087,13 @@
         </is>
       </c>
       <c r="L144" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M144" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N144" s="5" t="n">
-        <v>18.27</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="145">
@@ -10153,7 +10153,7 @@
         <v>1</v>
       </c>
       <c r="N145" s="5" t="n">
-        <v>14.32</v>
+        <v>13.48</v>
       </c>
     </row>
     <row r="146">
@@ -10192,28 +10192,28 @@
       </c>
       <c r="H146" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I146" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J146" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K146" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L146" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M146" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N146" s="5" t="n">
-        <v>18.76</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="147">
@@ -10252,11 +10252,11 @@
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I147" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J147" s="5" t="b">
         <v>1</v>
@@ -10267,13 +10267,13 @@
         </is>
       </c>
       <c r="L147" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M147" s="5" t="n">
-        <v>1</v>
+        <v>0.3333</v>
       </c>
       <c r="N147" s="5" t="n">
-        <v>17.89</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="148">
@@ -10312,28 +10312,28 @@
       </c>
       <c r="H148" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I148" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J148" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K148" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L148" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M148" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N148" s="5" t="n">
-        <v>18.89</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="149">
@@ -10393,7 +10393,7 @@
         <v>1</v>
       </c>
       <c r="N149" s="5" t="n">
-        <v>19.65</v>
+        <v>17.78</v>
       </c>
     </row>
     <row r="150">
@@ -10453,7 +10453,7 @@
         <v>1</v>
       </c>
       <c r="N150" s="5" t="n">
-        <v>19.18</v>
+        <v>16.38</v>
       </c>
     </row>
     <row r="151">
@@ -10513,7 +10513,7 @@
         <v>1</v>
       </c>
       <c r="N151" s="5" t="n">
-        <v>20.2</v>
+        <v>18.04</v>
       </c>
     </row>
     <row r="152">
@@ -10573,7 +10573,7 @@
         <v>1</v>
       </c>
       <c r="N152" s="5" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="153">
@@ -10633,7 +10633,7 @@
         <v>1</v>
       </c>
       <c r="N153" s="5" t="n">
-        <v>19.57</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="154">
@@ -10753,7 +10753,7 @@
         <v>1</v>
       </c>
       <c r="N155" s="5" t="n">
-        <v>14.97</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="156">
@@ -10813,7 +10813,7 @@
         <v>1</v>
       </c>
       <c r="N156" s="5" t="n">
-        <v>13.01</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="157">
@@ -10873,7 +10873,7 @@
         <v>1</v>
       </c>
       <c r="N157" s="5" t="n">
-        <v>14.96</v>
+        <v>12.44</v>
       </c>
     </row>
     <row r="158">
@@ -10933,7 +10933,7 @@
         <v>1</v>
       </c>
       <c r="N158" s="5" t="n">
-        <v>16.9</v>
+        <v>15.09</v>
       </c>
     </row>
     <row r="159">
@@ -10993,7 +10993,7 @@
         <v>1</v>
       </c>
       <c r="N159" s="5" t="n">
-        <v>15.91</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="160">
@@ -11053,7 +11053,7 @@
         <v>1</v>
       </c>
       <c r="N160" s="5" t="n">
-        <v>16.71</v>
+        <v>15.11</v>
       </c>
     </row>
     <row r="161">
@@ -11113,7 +11113,7 @@
         <v>1</v>
       </c>
       <c r="N161" s="5" t="n">
-        <v>16.17</v>
+        <v>17.29</v>
       </c>
     </row>
     <row r="162">
@@ -11159,11 +11159,11 @@
         <v>1</v>
       </c>
       <c r="J162" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K162" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L162" s="5" t="b">
@@ -11173,7 +11173,7 @@
         <v>0</v>
       </c>
       <c r="N162" s="5" t="n">
-        <v>2.27</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="163">
@@ -11219,21 +11219,21 @@
         <v>1</v>
       </c>
       <c r="J163" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K163" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L163" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M163" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N163" s="5" t="n">
-        <v>2.15</v>
+        <v>13.91</v>
       </c>
     </row>
     <row r="164">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
@@ -11287,13 +11287,13 @@
         </is>
       </c>
       <c r="L164" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M164" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N164" s="5" t="n">
-        <v>21.9</v>
+        <v>18.48</v>
       </c>
     </row>
     <row r="165">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
@@ -11347,13 +11347,13 @@
         </is>
       </c>
       <c r="L165" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M165" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N165" s="5" t="n">
-        <v>20.33</v>
+        <v>17.27</v>
       </c>
     </row>
     <row r="166">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
@@ -11407,13 +11407,13 @@
         </is>
       </c>
       <c r="L166" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M166" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N166" s="5" t="n">
-        <v>18.63</v>
+        <v>18.74</v>
       </c>
     </row>
     <row r="167">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
@@ -11473,7 +11473,7 @@
         <v>1</v>
       </c>
       <c r="N167" s="5" t="n">
-        <v>16.79</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="168">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
@@ -11533,7 +11533,7 @@
         <v>1</v>
       </c>
       <c r="N168" s="5" t="n">
-        <v>17.42</v>
+        <v>15.16</v>
       </c>
     </row>
     <row r="169">
@@ -11562,7 +11562,7 @@
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
@@ -11593,7 +11593,7 @@
         <v>1</v>
       </c>
       <c r="N169" s="5" t="n">
-        <v>17.91</v>
+        <v>15.86</v>
       </c>
     </row>
     <row r="170">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
@@ -11653,7 +11653,7 @@
         <v>1</v>
       </c>
       <c r="N170" s="5" t="n">
-        <v>18.28</v>
+        <v>16.42</v>
       </c>
     </row>
     <row r="171">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
@@ -11713,7 +11713,7 @@
         <v>1</v>
       </c>
       <c r="N171" s="5" t="n">
-        <v>23.87</v>
+        <v>20.32</v>
       </c>
     </row>
     <row r="172">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
@@ -11773,7 +11773,7 @@
         <v>1</v>
       </c>
       <c r="N172" s="5" t="n">
-        <v>18.54</v>
+        <v>16.27</v>
       </c>
     </row>
     <row r="173">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
@@ -11833,7 +11833,7 @@
         <v>1</v>
       </c>
       <c r="N173" s="5" t="n">
-        <v>18.57</v>
+        <v>19.56</v>
       </c>
     </row>
     <row r="174">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
@@ -11893,7 +11893,7 @@
         <v>1</v>
       </c>
       <c r="N174" s="5" t="n">
-        <v>20.89</v>
+        <v>17.42</v>
       </c>
     </row>
     <row r="175">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
@@ -11953,13 +11953,13 @@
         <v>1</v>
       </c>
       <c r="N175" s="5" t="n">
-        <v>19.34</v>
+        <v>16.53</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_006</t>
+          <t>cross_kg_005</t>
         </is>
       </c>
       <c r="B176" s="5" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
@@ -11992,11 +11992,11 @@
       </c>
       <c r="H176" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I176" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J176" s="5" t="b">
         <v>1</v>
@@ -12007,19 +12007,19 @@
         </is>
       </c>
       <c r="L176" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M176" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N176" s="5" t="n">
-        <v>17.49</v>
+        <v>16.81</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_006</t>
+          <t>cross_kg_005</t>
         </is>
       </c>
       <c r="B177" s="5" t="n">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
@@ -12073,13 +12073,13 @@
         <v>1</v>
       </c>
       <c r="N177" s="5" t="n">
-        <v>17.45</v>
+        <v>21.94</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_006</t>
+          <t>cross_kg_005</t>
         </is>
       </c>
       <c r="B178" s="5" t="n">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
@@ -12112,11 +12112,11 @@
       </c>
       <c r="H178" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I178" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J178" s="5" t="b">
         <v>1</v>
@@ -12127,19 +12127,19 @@
         </is>
       </c>
       <c r="L178" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M178" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N178" s="5" t="n">
-        <v>21.16</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_007</t>
+          <t>cross_kg_006</t>
         </is>
       </c>
       <c r="B179" s="5" t="n">
@@ -12162,7 +12162,7 @@
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
@@ -12193,13 +12193,13 @@
         <v>1</v>
       </c>
       <c r="N179" s="5" t="n">
-        <v>18.92</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_007</t>
+          <t>cross_kg_006</t>
         </is>
       </c>
       <c r="B180" s="5" t="n">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
@@ -12253,13 +12253,13 @@
         <v>1</v>
       </c>
       <c r="N180" s="5" t="n">
-        <v>24.28</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_007</t>
+          <t>cross_kg_006</t>
         </is>
       </c>
       <c r="B181" s="5" t="n">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
@@ -12313,13 +12313,13 @@
         <v>1</v>
       </c>
       <c r="N181" s="5" t="n">
-        <v>18.96</v>
+        <v>17.54</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_008</t>
+          <t>cross_kg_007</t>
         </is>
       </c>
       <c r="B182" s="5" t="n">
@@ -12342,7 +12342,7 @@
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
@@ -12373,13 +12373,13 @@
         <v>1</v>
       </c>
       <c r="N182" s="5" t="n">
-        <v>19.89</v>
+        <v>16.58</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_008</t>
+          <t>cross_kg_007</t>
         </is>
       </c>
       <c r="B183" s="5" t="n">
@@ -12402,7 +12402,7 @@
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
@@ -12433,13 +12433,13 @@
         <v>1</v>
       </c>
       <c r="N183" s="5" t="n">
-        <v>19.67</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_008</t>
+          <t>cross_kg_007</t>
         </is>
       </c>
       <c r="B184" s="5" t="n">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
@@ -12493,13 +12493,13 @@
         <v>1</v>
       </c>
       <c r="N184" s="5" t="n">
-        <v>17.52</v>
+        <v>16.66</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_010</t>
+          <t>cross_kg_008</t>
         </is>
       </c>
       <c r="B185" s="5" t="n">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr">
@@ -12553,13 +12553,13 @@
         <v>1</v>
       </c>
       <c r="N185" s="5" t="n">
-        <v>16.8</v>
+        <v>19.28</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_010</t>
+          <t>cross_kg_008</t>
         </is>
       </c>
       <c r="B186" s="5" t="n">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
@@ -12613,13 +12613,13 @@
         <v>1</v>
       </c>
       <c r="N186" s="5" t="n">
-        <v>17.95</v>
+        <v>18.17</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_010</t>
+          <t>cross_kg_008</t>
         </is>
       </c>
       <c r="B187" s="5" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
@@ -12673,13 +12673,13 @@
         <v>1</v>
       </c>
       <c r="N187" s="5" t="n">
-        <v>18.18</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_011</t>
+          <t>cross_kg_009</t>
         </is>
       </c>
       <c r="B188" s="5" t="n">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="F188" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
@@ -12712,11 +12712,11 @@
       </c>
       <c r="H188" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I188" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J188" s="5" t="b">
         <v>1</v>
@@ -12727,19 +12727,19 @@
         </is>
       </c>
       <c r="L188" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M188" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N188" s="5" t="n">
-        <v>18.26</v>
+        <v>15.45</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_011</t>
+          <t>cross_kg_009</t>
         </is>
       </c>
       <c r="B189" s="5" t="n">
@@ -12762,7 +12762,7 @@
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
@@ -12772,11 +12772,11 @@
       </c>
       <c r="H189" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I189" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J189" s="5" t="b">
         <v>1</v>
@@ -12787,19 +12787,19 @@
         </is>
       </c>
       <c r="L189" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M189" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N189" s="5" t="n">
-        <v>20.59</v>
+        <v>38.59</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_011</t>
+          <t>cross_kg_009</t>
         </is>
       </c>
       <c r="B190" s="5" t="n">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="F190" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
@@ -12832,11 +12832,11 @@
       </c>
       <c r="H190" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I190" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J190" s="5" t="b">
         <v>1</v>
@@ -12847,19 +12847,19 @@
         </is>
       </c>
       <c r="L190" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M190" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N190" s="5" t="n">
-        <v>18.78</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_012</t>
+          <t>cross_kg_010</t>
         </is>
       </c>
       <c r="B191" s="5" t="n">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="F191" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G191" s="5" t="inlineStr">
@@ -12913,13 +12913,13 @@
         <v>1</v>
       </c>
       <c r="N191" s="5" t="n">
-        <v>17.39</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_012</t>
+          <t>cross_kg_010</t>
         </is>
       </c>
       <c r="B192" s="5" t="n">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="F192" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
@@ -12973,13 +12973,13 @@
         <v>1</v>
       </c>
       <c r="N192" s="5" t="n">
-        <v>18.28</v>
+        <v>16.24</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_012</t>
+          <t>cross_kg_010</t>
         </is>
       </c>
       <c r="B193" s="5" t="n">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
@@ -13033,13 +13033,13 @@
         <v>1</v>
       </c>
       <c r="N193" s="5" t="n">
-        <v>18.02</v>
+        <v>15.53</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
         <is>
-          <t>open_kg_002</t>
+          <t>cross_kg_011</t>
         </is>
       </c>
       <c r="B194" s="5" t="n">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D194" s="5" t="inlineStr">
@@ -13062,17 +13062,17 @@
       </c>
       <c r="F194" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I194" s="5" t="b">
@@ -13086,16 +13086,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L194" s="5" t="n"/>
-      <c r="M194" s="5" t="n"/>
+      <c r="L194" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M194" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N194" s="5" t="n">
-        <v>28.3</v>
+        <v>16.23</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>open_kg_002</t>
+          <t>cross_kg_011</t>
         </is>
       </c>
       <c r="B195" s="5" t="n">
@@ -13103,7 +13107,7 @@
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D195" s="5" t="inlineStr">
@@ -13118,40 +13122,44 @@
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I195" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J195" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K195" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L195" s="5" t="n"/>
-      <c r="M195" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L195" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M195" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N195" s="5" t="n">
-        <v>12.92</v>
+        <v>17.96</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
         <is>
-          <t>open_kg_002</t>
+          <t>cross_kg_011</t>
         </is>
       </c>
       <c r="B196" s="5" t="n">
@@ -13159,7 +13167,7 @@
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D196" s="5" t="inlineStr">
@@ -13174,40 +13182,44 @@
       </c>
       <c r="F196" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H196" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I196" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J196" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K196" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L196" s="5" t="n"/>
-      <c r="M196" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L196" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M196" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N196" s="5" t="n">
-        <v>12.83</v>
+        <v>16.55</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>open_kg_003</t>
+          <t>cross_kg_012</t>
         </is>
       </c>
       <c r="B197" s="5" t="n">
@@ -13215,7 +13227,7 @@
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D197" s="5" t="inlineStr">
@@ -13230,40 +13242,44 @@
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H197" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I197" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J197" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K197" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L197" s="5" t="n"/>
-      <c r="M197" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L197" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M197" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N197" s="5" t="n">
-        <v>12.51</v>
+        <v>15.37</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
         <is>
-          <t>open_kg_003</t>
+          <t>cross_kg_012</t>
         </is>
       </c>
       <c r="B198" s="5" t="n">
@@ -13271,7 +13287,7 @@
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D198" s="5" t="inlineStr">
@@ -13286,40 +13302,44 @@
       </c>
       <c r="F198" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H198" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I198" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J198" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K198" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L198" s="5" t="n"/>
-      <c r="M198" s="5" t="n"/>
+      <c r="L198" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M198" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N198" s="5" t="n">
-        <v>9.890000000000001</v>
+        <v>16.69</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
         <is>
-          <t>open_kg_003</t>
+          <t>cross_kg_012</t>
         </is>
       </c>
       <c r="B199" s="5" t="n">
@@ -13327,7 +13347,7 @@
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D199" s="5" t="inlineStr">
@@ -13342,40 +13362,44 @@
       </c>
       <c r="F199" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I199" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J199" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K199" s="5" t="inlineStr">
         <is>
-          <t>param_extraction_failure</t>
-        </is>
-      </c>
-      <c r="L199" s="5" t="n"/>
-      <c r="M199" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L199" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M199" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N199" s="5" t="n">
-        <v>13.05</v>
+        <v>17.04</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
         <is>
-          <t>open_kg_004</t>
+          <t>open_kg_001</t>
         </is>
       </c>
       <c r="B200" s="5" t="n">
@@ -13398,7 +13422,7 @@
       </c>
       <c r="F200" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
@@ -13425,13 +13449,13 @@
       <c r="L200" s="5" t="n"/>
       <c r="M200" s="5" t="n"/>
       <c r="N200" s="5" t="n">
-        <v>31.38</v>
+        <v>22.81</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>open_kg_004</t>
+          <t>open_kg_001</t>
         </is>
       </c>
       <c r="B201" s="5" t="n">
@@ -13454,7 +13478,7 @@
       </c>
       <c r="F201" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G201" s="5" t="inlineStr">
@@ -13481,13 +13505,13 @@
       <c r="L201" s="5" t="n"/>
       <c r="M201" s="5" t="n"/>
       <c r="N201" s="5" t="n">
-        <v>33.09</v>
+        <v>21.27</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
         <is>
-          <t>open_kg_004</t>
+          <t>open_kg_001</t>
         </is>
       </c>
       <c r="B202" s="5" t="n">
@@ -13510,7 +13534,7 @@
       </c>
       <c r="F202" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G202" s="5" t="inlineStr">
@@ -13537,13 +13561,13 @@
       <c r="L202" s="5" t="n"/>
       <c r="M202" s="5" t="n"/>
       <c r="N202" s="5" t="n">
-        <v>34.7</v>
+        <v>21.79</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
         <is>
-          <t>open_kg_005</t>
+          <t>open_kg_002</t>
         </is>
       </c>
       <c r="B203" s="5" t="n">
@@ -13566,7 +13590,7 @@
       </c>
       <c r="F203" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
@@ -13576,7 +13600,7 @@
       </c>
       <c r="H203" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I203" s="5" t="b">
@@ -13587,19 +13611,23 @@
       </c>
       <c r="K203" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L203" s="5" t="n"/>
-      <c r="M203" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L203" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M203" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N203" s="5" t="n">
-        <v>13.74</v>
+        <v>8.98</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="5" t="inlineStr">
         <is>
-          <t>open_kg_005</t>
+          <t>open_kg_002</t>
         </is>
       </c>
       <c r="B204" s="5" t="n">
@@ -13622,7 +13650,7 @@
       </c>
       <c r="F204" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
@@ -13632,7 +13660,7 @@
       </c>
       <c r="H204" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I204" s="5" t="b">
@@ -13643,19 +13671,23 @@
       </c>
       <c r="K204" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L204" s="5" t="n"/>
-      <c r="M204" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L204" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M204" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N204" s="5" t="n">
-        <v>14.9</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="5" t="inlineStr">
         <is>
-          <t>open_kg_005</t>
+          <t>open_kg_002</t>
         </is>
       </c>
       <c r="B205" s="5" t="n">
@@ -13678,7 +13710,7 @@
       </c>
       <c r="F205" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
@@ -13702,29 +13734,33 @@
           <t>sparql_build_failure</t>
         </is>
       </c>
-      <c r="L205" s="5" t="n"/>
-      <c r="M205" s="5" t="n"/>
+      <c r="L205" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M205" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N205" s="5" t="n">
-        <v>12.43</v>
+        <v>7.73</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_001</t>
+          <t>open_kg_003</t>
         </is>
       </c>
       <c r="B206" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
@@ -13734,53 +13770,57 @@
       </c>
       <c r="F206" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G206" s="5" t="inlineStr">
         <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="H206" s="5" t="inlineStr">
+        <is>
           <t>template</t>
         </is>
       </c>
-      <c r="H206" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
       <c r="I206" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J206" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K206" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L206" s="5" t="n"/>
-      <c r="M206" s="5" t="n"/>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L206" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M206" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N206" s="5" t="n">
-        <v>14.95</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_001</t>
+          <t>open_kg_003</t>
         </is>
       </c>
       <c r="B207" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E207" s="5" t="inlineStr">
@@ -13790,53 +13830,57 @@
       </c>
       <c r="F207" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H207" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I207" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J207" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K207" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L207" s="5" t="n"/>
-      <c r="M207" s="5" t="n"/>
+      <c r="L207" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M207" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N207" s="5" t="n">
-        <v>14.87</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_001</t>
+          <t>open_kg_003</t>
         </is>
       </c>
       <c r="B208" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
@@ -13846,53 +13890,57 @@
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
         <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="H208" s="5" t="inlineStr">
+        <is>
           <t>template</t>
         </is>
       </c>
-      <c r="H208" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
       <c r="I208" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J208" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K208" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L208" s="5" t="n"/>
-      <c r="M208" s="5" t="n"/>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L208" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M208" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N208" s="5" t="n">
-        <v>15.36</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_001</t>
+          <t>open_kg_004</t>
         </is>
       </c>
       <c r="B209" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E209" s="5" t="inlineStr">
@@ -13902,17 +13950,17 @@
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H209" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I209" s="5" t="b">
@@ -13926,29 +13974,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L209" s="5" t="n"/>
-      <c r="M209" s="5" t="n"/>
+      <c r="L209" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M209" s="5" t="n">
+        <v>0.6667</v>
+      </c>
       <c r="N209" s="5" t="n">
-        <v>14.93</v>
+        <v>28.25</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_001</t>
+          <t>open_kg_004</t>
         </is>
       </c>
       <c r="B210" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
@@ -13958,53 +14010,57 @@
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
         <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="H210" s="5" t="inlineStr">
+        <is>
           <t>template</t>
         </is>
       </c>
-      <c r="H210" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
       <c r="I210" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J210" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K210" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L210" s="5" t="n"/>
-      <c r="M210" s="5" t="n"/>
+          <t>execution_failure</t>
+        </is>
+      </c>
+      <c r="L210" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M210" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N210" s="5" t="n">
-        <v>15.05</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_001</t>
+          <t>open_kg_004</t>
         </is>
       </c>
       <c r="B211" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E211" s="5" t="inlineStr">
@@ -14014,17 +14070,17 @@
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H211" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I211" s="5" t="b">
@@ -14038,29 +14094,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L211" s="5" t="n"/>
-      <c r="M211" s="5" t="n"/>
+      <c r="L211" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M211" s="5" t="n">
+        <v>0.6667</v>
+      </c>
       <c r="N211" s="5" t="n">
-        <v>14.84</v>
+        <v>27.11</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_002</t>
+          <t>open_kg_005</t>
         </is>
       </c>
       <c r="B212" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
@@ -14070,53 +14130,53 @@
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
         <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="H212" s="5" t="inlineStr">
+        <is>
           <t>template</t>
         </is>
       </c>
-      <c r="H212" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
       <c r="I212" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J212" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K212" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>sparql_build_failure</t>
         </is>
       </c>
       <c r="L212" s="5" t="n"/>
       <c r="M212" s="5" t="n"/>
       <c r="N212" s="5" t="n">
-        <v>15.15</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_002</t>
+          <t>open_kg_005</t>
         </is>
       </c>
       <c r="B213" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E213" s="5" t="inlineStr">
@@ -14126,53 +14186,53 @@
       </c>
       <c r="F213" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="H213" s="5" t="inlineStr">
+        <is>
           <t>template</t>
         </is>
       </c>
-      <c r="H213" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
       <c r="I213" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J213" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K213" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>sparql_build_failure</t>
         </is>
       </c>
       <c r="L213" s="5" t="n"/>
       <c r="M213" s="5" t="n"/>
       <c r="N213" s="5" t="n">
-        <v>27.37</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_002</t>
+          <t>open_kg_005</t>
         </is>
       </c>
       <c r="B214" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
@@ -14182,53 +14242,53 @@
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="H214" s="5" t="inlineStr">
+        <is>
           <t>template</t>
         </is>
       </c>
-      <c r="H214" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
       <c r="I214" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J214" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K214" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>sparql_build_failure</t>
         </is>
       </c>
       <c r="L214" s="5" t="n"/>
       <c r="M214" s="5" t="n"/>
       <c r="N214" s="5" t="n">
-        <v>19.23</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_003</t>
+          <t>open_kg_006</t>
         </is>
       </c>
       <c r="B215" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E215" s="5" t="inlineStr">
@@ -14238,17 +14298,17 @@
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H215" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I215" s="5" t="b">
@@ -14265,26 +14325,26 @@
       <c r="L215" s="5" t="n"/>
       <c r="M215" s="5" t="n"/>
       <c r="N215" s="5" t="n">
-        <v>13.67</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_003</t>
+          <t>open_kg_006</t>
         </is>
       </c>
       <c r="B216" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
@@ -14294,17 +14354,17 @@
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I216" s="5" t="b">
@@ -14321,26 +14381,26 @@
       <c r="L216" s="5" t="n"/>
       <c r="M216" s="5" t="n"/>
       <c r="N216" s="5" t="n">
-        <v>13.76</v>
+        <v>22.19</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_003</t>
+          <t>open_kg_006</t>
         </is>
       </c>
       <c r="B217" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E217" s="5" t="inlineStr">
@@ -14350,17 +14410,17 @@
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I217" s="5" t="b">
@@ -14377,13 +14437,13 @@
       <c r="L217" s="5" t="n"/>
       <c r="M217" s="5" t="n"/>
       <c r="N217" s="5" t="n">
-        <v>14.15</v>
+        <v>22.37</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_001</t>
+          <t>count_kg1_001</t>
         </is>
       </c>
       <c r="B218" s="5" t="n">
@@ -14391,12 +14451,12 @@
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
@@ -14406,7 +14466,7 @@
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
@@ -14423,23 +14483,27 @@
         <v>1</v>
       </c>
       <c r="J218" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K218" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L218" s="5" t="n"/>
-      <c r="M218" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L218" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M218" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N218" s="5" t="n">
-        <v>14.77</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_001</t>
+          <t>count_kg1_001</t>
         </is>
       </c>
       <c r="B219" s="5" t="n">
@@ -14447,12 +14511,12 @@
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E219" s="5" t="inlineStr">
@@ -14462,7 +14526,7 @@
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
@@ -14486,16 +14550,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L219" s="5" t="n"/>
-      <c r="M219" s="5" t="n"/>
+      <c r="L219" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M219" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N219" s="5" t="n">
-        <v>15.68</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_001</t>
+          <t>count_kg1_001</t>
         </is>
       </c>
       <c r="B220" s="5" t="n">
@@ -14503,12 +14571,12 @@
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
@@ -14518,7 +14586,7 @@
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
@@ -14526,28 +14594,36 @@
           <t>template</t>
         </is>
       </c>
-      <c r="H220" s="5" t="n"/>
+      <c r="H220" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
       <c r="I220" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J220" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K220" s="5" t="inlineStr">
         <is>
-          <t>exception: int() argument must be a string, a bytes-like object or a real number, not 'NoneType'</t>
-        </is>
-      </c>
-      <c r="L220" s="5" t="n"/>
-      <c r="M220" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L220" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M220" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N220" s="5" t="n">
-        <v>21.08</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>count_kg1_002</t>
         </is>
       </c>
       <c r="B221" s="5" t="n">
@@ -14555,12 +14631,12 @@
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E221" s="5" t="inlineStr">
@@ -14570,7 +14646,7 @@
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr">
@@ -14594,16 +14670,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L221" s="5" t="n"/>
-      <c r="M221" s="5" t="n"/>
+      <c r="L221" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M221" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N221" s="5" t="n">
-        <v>16.11</v>
+        <v>11.07</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>count_kg1_002</t>
         </is>
       </c>
       <c r="B222" s="5" t="n">
@@ -14611,12 +14691,12 @@
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
@@ -14626,7 +14706,7 @@
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr">
@@ -14650,16 +14730,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L222" s="5" t="n"/>
-      <c r="M222" s="5" t="n"/>
+      <c r="L222" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M222" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N222" s="5" t="n">
-        <v>15.32</v>
+        <v>8.34</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>count_kg1_002</t>
         </is>
       </c>
       <c r="B223" s="5" t="n">
@@ -14667,12 +14751,12 @@
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E223" s="5" t="inlineStr">
@@ -14682,7 +14766,7 @@
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
@@ -14706,16 +14790,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L223" s="5" t="n"/>
-      <c r="M223" s="5" t="n"/>
+      <c r="L223" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M223" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N223" s="5" t="n">
-        <v>15.59</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>count_kg1_003</t>
         </is>
       </c>
       <c r="B224" s="5" t="n">
@@ -14723,12 +14811,12 @@
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E224" s="5" t="inlineStr">
@@ -14738,7 +14826,7 @@
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
@@ -14762,16 +14850,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L224" s="5" t="n"/>
-      <c r="M224" s="5" t="n"/>
+      <c r="L224" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M224" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N224" s="5" t="n">
-        <v>16.67</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>count_kg1_003</t>
         </is>
       </c>
       <c r="B225" s="5" t="n">
@@ -14779,12 +14871,12 @@
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E225" s="5" t="inlineStr">
@@ -14794,7 +14886,7 @@
       </c>
       <c r="F225" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr">
@@ -14818,16 +14910,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L225" s="5" t="n"/>
-      <c r="M225" s="5" t="n"/>
+      <c r="L225" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M225" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N225" s="5" t="n">
-        <v>15.76</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>count_kg1_003</t>
         </is>
       </c>
       <c r="B226" s="5" t="n">
@@ -14835,12 +14931,12 @@
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E226" s="5" t="inlineStr">
@@ -14850,7 +14946,7 @@
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
@@ -14874,16 +14970,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L226" s="5" t="n"/>
-      <c r="M226" s="5" t="n"/>
+      <c r="L226" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M226" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N226" s="5" t="n">
-        <v>18.69</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_001</t>
+          <t>filter_numeric_kg1_001</t>
         </is>
       </c>
       <c r="B227" s="5" t="n">
@@ -14891,12 +14991,12 @@
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E227" s="5" t="inlineStr">
@@ -14906,7 +15006,7 @@
       </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
@@ -14930,16 +15030,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L227" s="5" t="n"/>
-      <c r="M227" s="5" t="n"/>
+      <c r="L227" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M227" s="5" t="n">
+        <v>0.4348</v>
+      </c>
       <c r="N227" s="5" t="n">
-        <v>14.2</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_001</t>
+          <t>filter_numeric_kg1_001</t>
         </is>
       </c>
       <c r="B228" s="5" t="n">
@@ -14947,12 +15051,12 @@
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
@@ -14962,7 +15066,7 @@
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
@@ -14986,16 +15090,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L228" s="5" t="n"/>
-      <c r="M228" s="5" t="n"/>
+      <c r="L228" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M228" s="5" t="n">
+        <v>0.4348</v>
+      </c>
       <c r="N228" s="5" t="n">
-        <v>14.37</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_001</t>
+          <t>filter_numeric_kg1_001</t>
         </is>
       </c>
       <c r="B229" s="5" t="n">
@@ -15003,12 +15111,12 @@
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E229" s="5" t="inlineStr">
@@ -15018,7 +15126,7 @@
       </c>
       <c r="F229" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr">
@@ -15042,16 +15150,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L229" s="5" t="n"/>
-      <c r="M229" s="5" t="n"/>
+      <c r="L229" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M229" s="5" t="n">
+        <v>0.4348</v>
+      </c>
       <c r="N229" s="5" t="n">
-        <v>15.89</v>
+        <v>8.470000000000001</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_002</t>
+          <t>filter_numeric_kg1_002</t>
         </is>
       </c>
       <c r="B230" s="5" t="n">
@@ -15059,12 +15171,12 @@
       </c>
       <c r="C230" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E230" s="5" t="inlineStr">
@@ -15074,7 +15186,7 @@
       </c>
       <c r="F230" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G230" s="5" t="inlineStr">
@@ -15098,16 +15210,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L230" s="5" t="n"/>
-      <c r="M230" s="5" t="n"/>
+      <c r="L230" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M230" s="5" t="n">
+        <v>0.5</v>
+      </c>
       <c r="N230" s="5" t="n">
-        <v>13.56</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_002</t>
+          <t>filter_numeric_kg1_002</t>
         </is>
       </c>
       <c r="B231" s="5" t="n">
@@ -15115,12 +15231,12 @@
       </c>
       <c r="C231" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E231" s="5" t="inlineStr">
@@ -15130,7 +15246,7 @@
       </c>
       <c r="F231" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
@@ -15154,16 +15270,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L231" s="5" t="n"/>
-      <c r="M231" s="5" t="n"/>
+      <c r="L231" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M231" s="5" t="n">
+        <v>0.5</v>
+      </c>
       <c r="N231" s="5" t="n">
-        <v>13.72</v>
+        <v>18.05</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_002</t>
+          <t>filter_numeric_kg1_002</t>
         </is>
       </c>
       <c r="B232" s="5" t="n">
@@ -15171,12 +15291,12 @@
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E232" s="5" t="inlineStr">
@@ -15186,7 +15306,7 @@
       </c>
       <c r="F232" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr">
@@ -15210,16 +15330,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L232" s="5" t="n"/>
-      <c r="M232" s="5" t="n"/>
+      <c r="L232" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M232" s="5" t="n">
+        <v>0.5</v>
+      </c>
       <c r="N232" s="5" t="n">
-        <v>13.77</v>
+        <v>12.55</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_003</t>
+          <t>filter_numeric_kg1_003</t>
         </is>
       </c>
       <c r="B233" s="5" t="n">
@@ -15227,12 +15351,12 @@
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E233" s="5" t="inlineStr">
@@ -15242,7 +15366,7 @@
       </c>
       <c r="F233" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
@@ -15266,16 +15390,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L233" s="5" t="n"/>
-      <c r="M233" s="5" t="n"/>
+      <c r="L233" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M233" s="5" t="n">
+        <v>0.5</v>
+      </c>
       <c r="N233" s="5" t="n">
-        <v>13.92</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_003</t>
+          <t>filter_numeric_kg1_003</t>
         </is>
       </c>
       <c r="B234" s="5" t="n">
@@ -15283,12 +15411,12 @@
       </c>
       <c r="C234" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
@@ -15298,7 +15426,7 @@
       </c>
       <c r="F234" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G234" s="5" t="inlineStr">
@@ -15322,16 +15450,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L234" s="5" t="n"/>
-      <c r="M234" s="5" t="n"/>
+      <c r="L234" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M234" s="5" t="n">
+        <v>0.5</v>
+      </c>
       <c r="N234" s="5" t="n">
-        <v>22.08</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_003</t>
+          <t>filter_numeric_kg1_003</t>
         </is>
       </c>
       <c r="B235" s="5" t="n">
@@ -15339,12 +15471,12 @@
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E235" s="5" t="inlineStr">
@@ -15354,7 +15486,7 @@
       </c>
       <c r="F235" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
@@ -15378,28 +15510,34 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L235" s="5" t="n"/>
-      <c r="M235" s="5" t="n"/>
+      <c r="L235" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M235" s="5" t="n">
+        <v>0.5</v>
+      </c>
       <c r="N235" s="5" t="n">
-        <v>15.17</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>filter_numeric_kg2_001</t>
         </is>
       </c>
       <c r="B236" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C236" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D236" s="5" t="n">
-        <v/>
+          <t>filter_numeric_kg2</t>
+        </is>
+      </c>
+      <c r="D236" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
       </c>
       <c r="E236" s="5" t="inlineStr">
         <is>
@@ -15408,52 +15546,58 @@
       </c>
       <c r="F236" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H236" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I236" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J236" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K236" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L236" s="5" t="n"/>
-      <c r="M236" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L236" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M236" s="5" t="n">
+        <v>0.2</v>
+      </c>
       <c r="N236" s="5" t="n">
-        <v>4.09</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>filter_numeric_kg2_001</t>
         </is>
       </c>
       <c r="B237" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D237" s="5" t="n">
-        <v/>
+          <t>filter_numeric_kg2</t>
+        </is>
+      </c>
+      <c r="D237" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
       </c>
       <c r="E237" s="5" t="inlineStr">
         <is>
@@ -15462,52 +15606,58 @@
       </c>
       <c r="F237" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H237" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I237" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J237" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K237" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L237" s="5" t="n"/>
-      <c r="M237" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L237" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M237" s="5" t="n">
+        <v>0.2</v>
+      </c>
       <c r="N237" s="5" t="n">
-        <v>3.9</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>filter_numeric_kg2_001</t>
         </is>
       </c>
       <c r="B238" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C238" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D238" s="5" t="n">
-        <v/>
+          <t>filter_numeric_kg2</t>
+        </is>
+      </c>
+      <c r="D238" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
         <is>
@@ -15516,52 +15666,58 @@
       </c>
       <c r="F238" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H238" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I238" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J238" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K238" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L238" s="5" t="n"/>
-      <c r="M238" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L238" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M238" s="5" t="n">
+        <v>0.2</v>
+      </c>
       <c r="N238" s="5" t="n">
-        <v>4.26</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B239" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D239" s="5" t="n">
-        <v/>
+          <t>filter_numeric_kg2</t>
+        </is>
+      </c>
+      <c r="D239" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
       </c>
       <c r="E239" s="5" t="inlineStr">
         <is>
@@ -15570,21 +15726,21 @@
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I239" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J239" s="5" t="b">
         <v>1</v>
@@ -15594,28 +15750,34 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L239" s="5" t="n"/>
-      <c r="M239" s="5" t="n"/>
+      <c r="L239" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M239" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N239" s="5" t="n">
-        <v>21.12</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B240" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C240" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D240" s="5" t="n">
-        <v/>
+          <t>filter_numeric_kg2</t>
+        </is>
+      </c>
+      <c r="D240" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
       </c>
       <c r="E240" s="5" t="inlineStr">
         <is>
@@ -15624,52 +15786,58 @@
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H240" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I240" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J240" s="5" t="b">
         <v>1</v>
       </c>
       <c r="K240" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L240" s="5" t="n"/>
-      <c r="M240" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L240" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M240" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N240" s="5" t="n">
-        <v>44.56</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B241" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D241" s="5" t="n">
-        <v/>
+          <t>filter_numeric_kg2</t>
+        </is>
+      </c>
+      <c r="D241" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
       </c>
       <c r="E241" s="5" t="inlineStr">
         <is>
@@ -15678,12 +15846,12 @@
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H241" s="5" t="inlineStr">
@@ -15692,39 +15860,43 @@
         </is>
       </c>
       <c r="I241" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J241" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K241" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L241" s="5" t="n"/>
-      <c r="M241" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L241" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M241" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N241" s="5" t="n">
-        <v>12.53</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B242" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E242" s="5" t="inlineStr">
@@ -15734,17 +15906,17 @@
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H242" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I242" s="5" t="b">
@@ -15759,32 +15931,32 @@
         </is>
       </c>
       <c r="L242" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M242" s="5" t="n">
-        <v>1</v>
+        <v>0.1667</v>
       </c>
       <c r="N242" s="5" t="n">
-        <v>4.41</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B243" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E243" s="5" t="inlineStr">
@@ -15794,28 +15966,28 @@
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H243" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I243" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J243" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K243" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L243" s="5" t="b">
@@ -15825,26 +15997,26 @@
         <v>0</v>
       </c>
       <c r="N243" s="5" t="n">
-        <v>3.66</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B244" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E244" s="5" t="inlineStr">
@@ -15854,28 +16026,28 @@
       </c>
       <c r="F244" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H244" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I244" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J244" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K244" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L244" s="5" t="b">
@@ -15885,7 +16057,7 @@
         <v>0</v>
       </c>
       <c r="N244" s="5" t="n">
-        <v>4.99</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="245">
@@ -15938,10 +16110,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L245" s="5" t="n"/>
-      <c r="M245" s="5" t="n"/>
+      <c r="L245" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M245" s="5" t="n">
+        <v>0.1798</v>
+      </c>
       <c r="N245" s="5" t="n">
-        <v>35.74</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="246">
@@ -15994,10 +16170,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L246" s="5" t="n"/>
-      <c r="M246" s="5" t="n"/>
+      <c r="L246" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M246" s="5" t="n">
+        <v>0.1798</v>
+      </c>
       <c r="N246" s="5" t="n">
-        <v>13.07</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="247">
@@ -16036,11 +16216,11 @@
       </c>
       <c r="H247" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I247" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J247" s="5" t="b">
         <v>1</v>
@@ -16050,10 +16230,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L247" s="5" t="n"/>
-      <c r="M247" s="5" t="n"/>
+      <c r="L247" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M247" s="5" t="n">
+        <v>0.7945</v>
+      </c>
       <c r="N247" s="5" t="n">
-        <v>13.34</v>
+        <v>32.55</v>
       </c>
     </row>
     <row r="248">
@@ -16092,24 +16276,24 @@
       </c>
       <c r="H248" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I248" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J248" s="5" t="b">
         <v>1</v>
       </c>
       <c r="K248" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L248" s="5" t="n"/>
       <c r="M248" s="5" t="n"/>
       <c r="N248" s="5" t="n">
-        <v>13.46</v>
+        <v>25.51</v>
       </c>
     </row>
     <row r="249">
@@ -16155,17 +16339,17 @@
         <v>1</v>
       </c>
       <c r="J249" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K249" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>sparql_build_failure</t>
         </is>
       </c>
       <c r="L249" s="5" t="n"/>
       <c r="M249" s="5" t="n"/>
       <c r="N249" s="5" t="n">
-        <v>13.03</v>
+        <v>12.53</v>
       </c>
     </row>
     <row r="250">
@@ -16204,14 +16388,14 @@
       </c>
       <c r="H250" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I250" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J250" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K250" s="5" t="inlineStr">
         <is>
@@ -16221,7 +16405,7 @@
       <c r="L250" s="5" t="n"/>
       <c r="M250" s="5" t="n"/>
       <c r="N250" s="5" t="n">
-        <v>8.83</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="251">
@@ -16274,10 +16458,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L251" s="5" t="n"/>
-      <c r="M251" s="5" t="n"/>
+      <c r="L251" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M251" s="5" t="n">
+        <v>0.2353</v>
+      </c>
       <c r="N251" s="5" t="n">
-        <v>10.85</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="252">
@@ -16330,10 +16518,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L252" s="5" t="n"/>
-      <c r="M252" s="5" t="n"/>
+      <c r="L252" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M252" s="5" t="n">
+        <v>0.2353</v>
+      </c>
       <c r="N252" s="5" t="n">
-        <v>9.619999999999999</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="253">
@@ -16386,16 +16578,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L253" s="5" t="n"/>
-      <c r="M253" s="5" t="n"/>
+      <c r="L253" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M253" s="5" t="n">
+        <v>0.2353</v>
+      </c>
       <c r="N253" s="5" t="n">
-        <v>9.75</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_002</t>
+          <t>ranking_kg2_001</t>
         </is>
       </c>
       <c r="B254" s="5" t="n">
@@ -16403,12 +16599,12 @@
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E254" s="5" t="inlineStr">
@@ -16442,16 +16638,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L254" s="5" t="n"/>
-      <c r="M254" s="5" t="n"/>
+      <c r="L254" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M254" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N254" s="5" t="n">
-        <v>17.01</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_002</t>
+          <t>ranking_kg2_001</t>
         </is>
       </c>
       <c r="B255" s="5" t="n">
@@ -16459,12 +16659,12 @@
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E255" s="5" t="inlineStr">
@@ -16498,16 +16698,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L255" s="5" t="n"/>
-      <c r="M255" s="5" t="n"/>
+      <c r="L255" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M255" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N255" s="5" t="n">
-        <v>14.33</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_002</t>
+          <t>ranking_kg2_001</t>
         </is>
       </c>
       <c r="B256" s="5" t="n">
@@ -16515,12 +16719,12 @@
       </c>
       <c r="C256" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E256" s="5" t="inlineStr">
@@ -16554,16 +16758,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L256" s="5" t="n"/>
-      <c r="M256" s="5" t="n"/>
+      <c r="L256" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M256" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N256" s="5" t="n">
-        <v>12.65</v>
+        <v>13.26</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_003</t>
+          <t>ranking_kg2_002</t>
         </is>
       </c>
       <c r="B257" s="5" t="n">
@@ -16571,12 +16779,12 @@
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E257" s="5" t="inlineStr">
@@ -16610,16 +16818,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L257" s="5" t="n"/>
-      <c r="M257" s="5" t="n"/>
+      <c r="L257" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M257" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N257" s="5" t="n">
-        <v>9.17</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_003</t>
+          <t>ranking_kg2_002</t>
         </is>
       </c>
       <c r="B258" s="5" t="n">
@@ -16627,12 +16839,12 @@
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E258" s="5" t="inlineStr">
@@ -16666,16 +16878,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L258" s="5" t="n"/>
-      <c r="M258" s="5" t="n"/>
+      <c r="L258" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M258" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N258" s="5" t="n">
-        <v>9.73</v>
+        <v>7.73</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_003</t>
+          <t>ranking_kg2_002</t>
         </is>
       </c>
       <c r="B259" s="5" t="n">
@@ -16683,12 +16899,12 @@
       </c>
       <c r="C259" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E259" s="5" t="inlineStr">
@@ -16722,29 +16938,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L259" s="5" t="n"/>
-      <c r="M259" s="5" t="n"/>
+      <c r="L259" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M259" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N259" s="5" t="n">
-        <v>9.43</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_005</t>
+          <t>ranking_kg2_003</t>
         </is>
       </c>
       <c r="B260" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E260" s="5" t="inlineStr">
@@ -16759,16 +16979,16 @@
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H260" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I260" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J260" s="5" t="b">
         <v>1</v>
@@ -16785,26 +17005,26 @@
         <v>0</v>
       </c>
       <c r="N260" s="5" t="n">
-        <v>28.93</v>
+        <v>7.61</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_005</t>
+          <t>ranking_kg2_003</t>
         </is>
       </c>
       <c r="B261" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E261" s="5" t="inlineStr">
@@ -16819,12 +17039,12 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I261" s="5" t="b">
@@ -16839,32 +17059,32 @@
         </is>
       </c>
       <c r="L261" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M261" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N261" s="5" t="n">
-        <v>19.93</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_005</t>
+          <t>ranking_kg2_003</t>
         </is>
       </c>
       <c r="B262" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E262" s="5" t="inlineStr">
@@ -16879,16 +17099,16 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I262" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J262" s="5" t="b">
         <v>1</v>
@@ -16905,26 +17125,26 @@
         <v>0</v>
       </c>
       <c r="N262" s="5" t="n">
-        <v>16.47</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_009</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B263" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C263" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E263" s="5" t="inlineStr">
@@ -16939,16 +17159,16 @@
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H263" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I263" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J263" s="5" t="b">
         <v>1</v>
@@ -16962,29 +17182,29 @@
         <v>0</v>
       </c>
       <c r="M263" s="5" t="n">
-        <v>0</v>
+        <v>0.2222</v>
       </c>
       <c r="N263" s="5" t="n">
-        <v>18.45</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_009</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B264" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E264" s="5" t="inlineStr">
@@ -16999,12 +17219,12 @@
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H264" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I264" s="5" t="b">
@@ -17019,32 +17239,32 @@
         </is>
       </c>
       <c r="L264" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M264" s="5" t="n">
-        <v>1</v>
+        <v>0.2222</v>
       </c>
       <c r="N264" s="5" t="n">
-        <v>24.79</v>
+        <v>8.710000000000001</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_009</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B265" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E265" s="5" t="inlineStr">
@@ -17059,16 +17279,16 @@
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H265" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I265" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J265" s="5" t="b">
         <v>1</v>
@@ -17082,29 +17302,29 @@
         <v>0</v>
       </c>
       <c r="M265" s="5" t="n">
-        <v>0</v>
+        <v>0.2222</v>
       </c>
       <c r="N265" s="5" t="n">
-        <v>17.84</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="5" t="inlineStr">
         <is>
-          <t>open_kg_001</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B266" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
@@ -17119,12 +17339,12 @@
       </c>
       <c r="G266" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H266" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I266" s="5" t="b">
@@ -17138,29 +17358,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L266" s="5" t="n"/>
-      <c r="M266" s="5" t="n"/>
+      <c r="L266" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M266" s="5" t="n">
+        <v>0.1905</v>
+      </c>
       <c r="N266" s="5" t="n">
-        <v>23.17</v>
+        <v>8.56</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
         <is>
-          <t>open_kg_001</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B267" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E267" s="5" t="inlineStr">
@@ -17175,12 +17399,12 @@
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H267" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I267" s="5" t="b">
@@ -17194,29 +17418,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L267" s="5" t="n"/>
-      <c r="M267" s="5" t="n"/>
+      <c r="L267" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M267" s="5" t="n">
+        <v>0.1905</v>
+      </c>
       <c r="N267" s="5" t="n">
-        <v>22.38</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="5" t="inlineStr">
         <is>
-          <t>open_kg_001</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B268" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
@@ -17231,12 +17459,12 @@
       </c>
       <c r="G268" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H268" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I268" s="5" t="b">
@@ -17250,29 +17478,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L268" s="5" t="n"/>
-      <c r="M268" s="5" t="n"/>
+      <c r="L268" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M268" s="5" t="n">
+        <v>0.1905</v>
+      </c>
       <c r="N268" s="5" t="n">
-        <v>23.04</v>
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
         <is>
-          <t>open_kg_006</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B269" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E269" s="5" t="inlineStr">
@@ -17287,12 +17519,12 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I269" s="5" t="b">
@@ -17306,29 +17538,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L269" s="5" t="n"/>
-      <c r="M269" s="5" t="n"/>
+      <c r="L269" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M269" s="5" t="n">
+        <v>0.25</v>
+      </c>
       <c r="N269" s="5" t="n">
-        <v>24.88</v>
+        <v>8.710000000000001</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="5" t="inlineStr">
         <is>
-          <t>open_kg_006</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B270" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
@@ -17343,12 +17579,12 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I270" s="5" t="b">
@@ -17362,29 +17598,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L270" s="5" t="n"/>
-      <c r="M270" s="5" t="n"/>
+      <c r="L270" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M270" s="5" t="n">
+        <v>0.25</v>
+      </c>
       <c r="N270" s="5" t="n">
-        <v>24.77</v>
+        <v>8.74</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
         <is>
-          <t>open_kg_006</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B271" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
@@ -17399,12 +17639,12 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I271" s="5" t="b">
@@ -17418,30 +17658,32 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L271" s="5" t="n"/>
-      <c r="M271" s="5" t="n"/>
+      <c r="L271" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M271" s="5" t="n">
+        <v>0.25</v>
+      </c>
       <c r="N271" s="5" t="n">
-        <v>23.62</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B272" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D272" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D272" s="5" t="n">
+        <v/>
       </c>
       <c r="E272" s="5" t="inlineStr">
         <is>
@@ -17455,53 +17697,47 @@
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H272" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I272" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J272" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K272" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L272" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M272" s="5" t="n">
-        <v>0.2667</v>
-      </c>
+          <t>mapping_failure</t>
+        </is>
+      </c>
+      <c r="L272" s="5" t="n"/>
+      <c r="M272" s="5" t="n"/>
       <c r="N272" s="5" t="n">
-        <v>13.54</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B273" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C273" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D273" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D273" s="5" t="n">
+        <v/>
       </c>
       <c r="E273" s="5" t="inlineStr">
         <is>
@@ -17515,53 +17751,47 @@
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H273" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I273" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J273" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K273" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L273" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M273" s="5" t="n">
-        <v>0.2667</v>
-      </c>
+          <t>mapping_failure</t>
+        </is>
+      </c>
+      <c r="L273" s="5" t="n"/>
+      <c r="M273" s="5" t="n"/>
       <c r="N273" s="5" t="n">
-        <v>12.56</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B274" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C274" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D274" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D274" s="5" t="n">
+        <v/>
       </c>
       <c r="E274" s="5" t="inlineStr">
         <is>
@@ -17575,53 +17805,47 @@
       </c>
       <c r="G274" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H274" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I274" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J274" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K274" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L274" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M274" s="5" t="n">
-        <v>0.2667</v>
-      </c>
+          <t>mapping_failure</t>
+        </is>
+      </c>
+      <c r="L274" s="5" t="n"/>
+      <c r="M274" s="5" t="n"/>
       <c r="N274" s="5" t="n">
-        <v>12.22</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B275" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D275" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D275" s="5" t="n">
+        <v/>
       </c>
       <c r="E275" s="5" t="inlineStr">
         <is>
@@ -17635,53 +17859,47 @@
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H275" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I275" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J275" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K275" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L275" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M275" s="5" t="n">
-        <v>0.2222</v>
-      </c>
+          <t>mapping_failure</t>
+        </is>
+      </c>
+      <c r="L275" s="5" t="n"/>
+      <c r="M275" s="5" t="n"/>
       <c r="N275" s="5" t="n">
-        <v>11.89</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B276" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D276" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D276" s="5" t="n">
+        <v/>
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
@@ -17695,16 +17913,16 @@
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H276" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I276" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J276" s="5" t="b">
         <v>1</v>
@@ -17714,34 +17932,28 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L276" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M276" s="5" t="n">
-        <v>0.2222</v>
-      </c>
+      <c r="L276" s="5" t="n"/>
+      <c r="M276" s="5" t="n"/>
       <c r="N276" s="5" t="n">
-        <v>11.82</v>
+        <v>27.42</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B277" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C277" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D277" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D277" s="5" t="n">
+        <v/>
       </c>
       <c r="E277" s="5" t="inlineStr">
         <is>
@@ -17755,53 +17967,47 @@
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H277" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I277" s="5" t="b">
         <v>0</v>
       </c>
       <c r="J277" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K277" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L277" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M277" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L277" s="5" t="n"/>
+      <c r="M277" s="5" t="n"/>
       <c r="N277" s="5" t="n">
-        <v>20.53</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B278" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D278" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D278" s="5" t="n">
+        <v/>
       </c>
       <c r="E278" s="5" t="inlineStr">
         <is>
@@ -17815,16 +18021,16 @@
       </c>
       <c r="G278" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H278" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I278" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J278" s="5" t="b">
         <v>1</v>
@@ -17834,34 +18040,28 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L278" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M278" s="5" t="n">
-        <v>0.3077</v>
-      </c>
+      <c r="L278" s="5" t="n"/>
+      <c r="M278" s="5" t="n"/>
       <c r="N278" s="5" t="n">
-        <v>9.710000000000001</v>
+        <v>21.65</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B279" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D279" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D279" s="5" t="n">
+        <v/>
       </c>
       <c r="E279" s="5" t="inlineStr">
         <is>
@@ -17875,16 +18075,16 @@
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H279" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I279" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J279" s="5" t="b">
         <v>1</v>
@@ -17894,34 +18094,28 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L279" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M279" s="5" t="n">
-        <v>0.3077</v>
-      </c>
+      <c r="L279" s="5" t="n"/>
+      <c r="M279" s="5" t="n"/>
       <c r="N279" s="5" t="n">
-        <v>8.82</v>
+        <v>15.46</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B280" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D280" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D280" s="5" t="n">
+        <v/>
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
@@ -17935,16 +18129,16 @@
       </c>
       <c r="G280" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H280" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I280" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J280" s="5" t="b">
         <v>1</v>
@@ -17954,20 +18148,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L280" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M280" s="5" t="n">
-        <v>0.3077</v>
-      </c>
+      <c r="L280" s="5" t="n"/>
+      <c r="M280" s="5" t="n"/>
       <c r="N280" s="5" t="n">
-        <v>8.93</v>
+        <v>20.19</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B281" s="5" t="n">
@@ -17975,11 +18165,13 @@
       </c>
       <c r="C281" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D281" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D281" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E281" s="5" t="inlineStr">
         <is>
@@ -17993,35 +18185,39 @@
       </c>
       <c r="G281" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H281" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I281" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J281" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K281" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L281" s="5" t="n"/>
-      <c r="M281" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L281" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M281" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N281" s="5" t="n">
-        <v>21.08</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B282" s="5" t="n">
@@ -18029,11 +18225,13 @@
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D282" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D282" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E282" s="5" t="inlineStr">
         <is>
@@ -18047,7 +18245,7 @@
       </c>
       <c r="G282" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H282" s="5" t="inlineStr">
@@ -18066,16 +18264,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L282" s="5" t="n"/>
-      <c r="M282" s="5" t="n"/>
+      <c r="L282" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M282" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N282" s="5" t="n">
-        <v>34.21</v>
+        <v>14.69</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B283" s="5" t="n">
@@ -18083,11 +18285,13 @@
       </c>
       <c r="C283" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D283" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D283" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E283" s="5" t="inlineStr">
         <is>
@@ -18101,7 +18305,7 @@
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H283" s="5" t="inlineStr">
@@ -18110,7 +18314,7 @@
         </is>
       </c>
       <c r="I283" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J283" s="5" t="b">
         <v>1</v>
@@ -18120,16 +18324,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L283" s="5" t="n"/>
-      <c r="M283" s="5" t="n"/>
+      <c r="L283" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M283" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N283" s="5" t="n">
-        <v>4.78</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B284" s="5" t="n">
@@ -18183,13 +18391,13 @@
         <v>0</v>
       </c>
       <c r="N284" s="5" t="n">
-        <v>4.12</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B285" s="5" t="n">
@@ -18222,7 +18430,7 @@
       </c>
       <c r="H285" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I285" s="5" t="b">
@@ -18243,13 +18451,13 @@
         <v>0</v>
       </c>
       <c r="N285" s="5" t="n">
-        <v>17.07</v>
+        <v>17.94</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B286" s="5" t="n">
@@ -18289,11 +18497,11 @@
         <v>1</v>
       </c>
       <c r="J286" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K286" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L286" s="5" t="b">
@@ -18303,13 +18511,13 @@
         <v>0</v>
       </c>
       <c r="N286" s="5" t="n">
-        <v>5.2</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B287" s="5" t="n">
@@ -18357,19 +18565,19 @@
         </is>
       </c>
       <c r="L287" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M287" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N287" s="5" t="n">
-        <v>4.39</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B288" s="5" t="n">
@@ -18409,11 +18617,11 @@
         <v>0</v>
       </c>
       <c r="J288" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K288" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L288" s="5" t="b">
@@ -18423,13 +18631,13 @@
         <v>0</v>
       </c>
       <c r="N288" s="5" t="n">
-        <v>15.32</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B289" s="5" t="n">
@@ -18483,7 +18691,7 @@
         <v>0</v>
       </c>
       <c r="N289" s="5" t="n">
-        <v>4.58</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="290">
@@ -18543,7 +18751,7 @@
         <v>1</v>
       </c>
       <c r="N290" s="5" t="n">
-        <v>4.85</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="291">
@@ -18603,7 +18811,7 @@
         <v>0</v>
       </c>
       <c r="N291" s="5" t="n">
-        <v>21.18</v>
+        <v>21.83</v>
       </c>
     </row>
     <row r="292">
@@ -18663,7 +18871,7 @@
         <v>0</v>
       </c>
       <c r="N292" s="5" t="n">
-        <v>5.59</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="293">
@@ -18723,7 +18931,7 @@
         <v>1</v>
       </c>
       <c r="N293" s="5" t="n">
-        <v>14.5</v>
+        <v>14.83</v>
       </c>
     </row>
     <row r="294">
@@ -18783,7 +18991,7 @@
         <v>1</v>
       </c>
       <c r="N294" s="5" t="n">
-        <v>15.44</v>
+        <v>16.71</v>
       </c>
     </row>
     <row r="295">
@@ -18843,7 +19051,7 @@
         <v>1</v>
       </c>
       <c r="N295" s="5" t="n">
-        <v>15.16</v>
+        <v>14.42</v>
       </c>
     </row>
     <row r="296">
@@ -18903,7 +19111,7 @@
         <v>1</v>
       </c>
       <c r="N296" s="5" t="n">
-        <v>29.89</v>
+        <v>26.53</v>
       </c>
     </row>
     <row r="297">
@@ -18963,7 +19171,7 @@
         <v>0.2</v>
       </c>
       <c r="N297" s="5" t="n">
-        <v>16.52</v>
+        <v>15.43</v>
       </c>
     </row>
     <row r="298">
@@ -19002,28 +19210,28 @@
       </c>
       <c r="H298" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I298" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J298" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K298" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L298" s="5" t="b">
         <v>0</v>
       </c>
       <c r="M298" s="5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N298" s="5" t="n">
-        <v>22.66</v>
+        <v>14.04</v>
       </c>
     </row>
     <row r="299">
@@ -19083,7 +19291,7 @@
         <v>1</v>
       </c>
       <c r="N299" s="5" t="n">
-        <v>19.57</v>
+        <v>20.03</v>
       </c>
     </row>
     <row r="300">
@@ -19143,7 +19351,7 @@
         <v>1</v>
       </c>
       <c r="N300" s="5" t="n">
-        <v>21.27</v>
+        <v>20.58</v>
       </c>
     </row>
     <row r="301">
@@ -19203,7 +19411,7 @@
         <v>1</v>
       </c>
       <c r="N301" s="5" t="n">
-        <v>21.57</v>
+        <v>19.78</v>
       </c>
     </row>
     <row r="302">
@@ -19263,7 +19471,7 @@
         <v>1</v>
       </c>
       <c r="N302" s="5" t="n">
-        <v>15.36</v>
+        <v>14.93</v>
       </c>
     </row>
     <row r="303">
@@ -19323,7 +19531,7 @@
         <v>1</v>
       </c>
       <c r="N303" s="5" t="n">
-        <v>15.36</v>
+        <v>14.35</v>
       </c>
     </row>
     <row r="304">
@@ -19383,7 +19591,7 @@
         <v>1</v>
       </c>
       <c r="N304" s="5" t="n">
-        <v>16.23</v>
+        <v>14.77</v>
       </c>
     </row>
     <row r="305">
@@ -19443,7 +19651,7 @@
         <v>1</v>
       </c>
       <c r="N305" s="5" t="n">
-        <v>14.86</v>
+        <v>14.15</v>
       </c>
     </row>
     <row r="306">
@@ -19503,7 +19711,7 @@
         <v>1</v>
       </c>
       <c r="N306" s="5" t="n">
-        <v>15.9</v>
+        <v>15.01</v>
       </c>
     </row>
     <row r="307">
@@ -19563,7 +19771,7 @@
         <v>0</v>
       </c>
       <c r="N307" s="5" t="n">
-        <v>11.04</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="308">
@@ -19623,7 +19831,7 @@
         <v>0</v>
       </c>
       <c r="N308" s="5" t="n">
-        <v>4.22</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="309">
@@ -19683,7 +19891,7 @@
         <v>0</v>
       </c>
       <c r="N309" s="5" t="n">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="310">
@@ -19743,7 +19951,7 @@
         <v>0</v>
       </c>
       <c r="N310" s="5" t="n">
-        <v>4.87</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="311">
@@ -19803,7 +20011,7 @@
         <v>1</v>
       </c>
       <c r="N311" s="5" t="n">
-        <v>14.06</v>
+        <v>13.36</v>
       </c>
     </row>
     <row r="312">
@@ -19863,7 +20071,7 @@
         <v>1</v>
       </c>
       <c r="N312" s="5" t="n">
-        <v>16.75</v>
+        <v>15.68</v>
       </c>
     </row>
     <row r="313">
@@ -19923,7 +20131,7 @@
         <v>1</v>
       </c>
       <c r="N313" s="5" t="n">
-        <v>15.6</v>
+        <v>15.17</v>
       </c>
     </row>
     <row r="314">
@@ -19979,7 +20187,7 @@
       <c r="L314" s="5" t="n"/>
       <c r="M314" s="5" t="n"/>
       <c r="N314" s="5" t="n">
-        <v>10.87</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="315">
@@ -20035,7 +20243,7 @@
       <c r="L315" s="5" t="n"/>
       <c r="M315" s="5" t="n"/>
       <c r="N315" s="5" t="n">
-        <v>13.26</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="316">
@@ -20091,7 +20299,7 @@
       <c r="L316" s="5" t="n"/>
       <c r="M316" s="5" t="n"/>
       <c r="N316" s="5" t="n">
-        <v>13.13</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="317">
@@ -20151,7 +20359,7 @@
         <v>0.5</v>
       </c>
       <c r="N317" s="5" t="n">
-        <v>12</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="318">
@@ -20211,7 +20419,7 @@
         <v>0.5</v>
       </c>
       <c r="N318" s="5" t="n">
-        <v>12.31</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="319">
@@ -20271,7 +20479,7 @@
         <v>0.5</v>
       </c>
       <c r="N319" s="5" t="n">
-        <v>12.68</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="320">
@@ -20327,7 +20535,7 @@
       <c r="L320" s="5" t="n"/>
       <c r="M320" s="5" t="n"/>
       <c r="N320" s="5" t="n">
-        <v>11.94</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="321">
@@ -20383,7 +20591,7 @@
       <c r="L321" s="5" t="n"/>
       <c r="M321" s="5" t="n"/>
       <c r="N321" s="5" t="n">
-        <v>11.78</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="322">
@@ -20439,7 +20647,7 @@
       <c r="L322" s="5" t="n"/>
       <c r="M322" s="5" t="n"/>
       <c r="N322" s="5" t="n">
-        <v>12.98</v>
+        <v>12.06</v>
       </c>
     </row>
     <row r="323">
@@ -20495,7 +20703,7 @@
       <c r="L323" s="5" t="n"/>
       <c r="M323" s="5" t="n"/>
       <c r="N323" s="5" t="n">
-        <v>11.8</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="324">
@@ -20551,7 +20759,7 @@
       <c r="L324" s="5" t="n"/>
       <c r="M324" s="5" t="n"/>
       <c r="N324" s="5" t="n">
-        <v>12.43</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="325">
@@ -20607,7 +20815,7 @@
       <c r="L325" s="5" t="n"/>
       <c r="M325" s="5" t="n"/>
       <c r="N325" s="5" t="n">
-        <v>11.56</v>
+        <v>11.19</v>
       </c>
     </row>
   </sheetData>

--- a/NL2SPARQL_Evaluation_Results.xlsx
+++ b/NL2SPARQL_Evaluation_Results.xlsx
@@ -13681,7 +13681,7 @@
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B206" s="5" t="n">
@@ -13689,7 +13689,7 @@
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D206" s="5" t="inlineStr">
@@ -13709,19 +13709,19 @@
       </c>
       <c r="G206" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H206" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I206" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J206" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K206" s="5" t="inlineStr">
         <is>
@@ -13729,19 +13729,19 @@
         </is>
       </c>
       <c r="L206" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M206" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N206" s="5" t="n">
-        <v>7.98</v>
+        <v>24.45</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B207" s="5" t="n">
@@ -13749,7 +13749,7 @@
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D207" s="5" t="inlineStr">
@@ -13769,7 +13769,7 @@
       </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H207" s="5" t="inlineStr">
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="I207" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J207" s="5" t="b">
         <v>1</v>
@@ -13789,19 +13789,19 @@
         </is>
       </c>
       <c r="L207" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M207" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N207" s="5" t="n">
-        <v>27.52</v>
+        <v>25.56</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B208" s="5" t="n">
@@ -13809,39 +13809,39 @@
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
+          <t>typo_fuzzy</t>
+        </is>
+      </c>
+      <c r="D208" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="E208" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F208" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G208" s="5" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="H208" s="5" t="inlineStr">
+        <is>
           <t>ask_query</t>
         </is>
       </c>
-      <c r="D208" s="5" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="E208" s="5" t="inlineStr">
-        <is>
-          <t>ar</t>
-        </is>
-      </c>
-      <c r="F208" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G208" s="5" t="inlineStr">
-        <is>
-          <t>ask_query</t>
-        </is>
-      </c>
-      <c r="H208" s="5" t="inlineStr">
-        <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
       <c r="I208" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J208" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K208" s="5" t="inlineStr">
         <is>
@@ -13855,13 +13855,13 @@
         <v>0</v>
       </c>
       <c r="N208" s="5" t="n">
-        <v>9.34</v>
+        <v>8.630000000000001</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B209" s="5" t="n">
@@ -13869,7 +13869,7 @@
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D209" s="5" t="inlineStr">
@@ -13889,12 +13889,12 @@
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H209" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I209" s="5" t="b">
@@ -13915,13 +13915,13 @@
         <v>1</v>
       </c>
       <c r="N209" s="5" t="n">
-        <v>9.140000000000001</v>
+        <v>29.55</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B210" s="5" t="n">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
@@ -13949,12 +13949,12 @@
       </c>
       <c r="G210" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H210" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I210" s="5" t="b">
@@ -13969,19 +13969,19 @@
         </is>
       </c>
       <c r="L210" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M210" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N210" s="5" t="n">
-        <v>10.59</v>
+        <v>30.76</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B211" s="5" t="n">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D211" s="5" t="inlineStr">
@@ -14009,12 +14009,12 @@
       </c>
       <c r="G211" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H211" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I211" s="5" t="b">
@@ -14029,19 +14029,19 @@
         </is>
       </c>
       <c r="L211" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M211" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N211" s="5" t="n">
-        <v>10.36</v>
+        <v>30.31</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B212" s="5" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D212" s="5" t="inlineStr">
@@ -14095,13 +14095,13 @@
         <v>1</v>
       </c>
       <c r="N212" s="5" t="n">
-        <v>24.45</v>
+        <v>23.62</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B213" s="5" t="n">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D213" s="5" t="inlineStr">
@@ -14155,13 +14155,13 @@
         <v>1</v>
       </c>
       <c r="N213" s="5" t="n">
-        <v>25.56</v>
+        <v>23.57</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B214" s="5" t="n">
@@ -14169,7 +14169,7 @@
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D214" s="5" t="inlineStr">
@@ -14194,7 +14194,7 @@
       </c>
       <c r="H214" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I214" s="5" t="b">
@@ -14209,19 +14209,19 @@
         </is>
       </c>
       <c r="L214" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M214" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N214" s="5" t="n">
-        <v>8.630000000000001</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B215" s="5" t="n">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
@@ -14275,13 +14275,13 @@
         <v>1</v>
       </c>
       <c r="N215" s="5" t="n">
-        <v>29.55</v>
+        <v>23.02</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B216" s="5" t="n">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
@@ -14335,13 +14335,13 @@
         <v>1</v>
       </c>
       <c r="N216" s="5" t="n">
-        <v>30.76</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B217" s="5" t="n">
@@ -14349,7 +14349,7 @@
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D217" s="5" t="inlineStr">
@@ -14374,7 +14374,7 @@
       </c>
       <c r="H217" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I217" s="5" t="b">
@@ -14389,19 +14389,19 @@
         </is>
       </c>
       <c r="L217" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M217" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N217" s="5" t="n">
-        <v>30.31</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B218" s="5" t="n">
@@ -14455,13 +14455,13 @@
         <v>1</v>
       </c>
       <c r="N218" s="5" t="n">
-        <v>23.62</v>
+        <v>24.31</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B219" s="5" t="n">
@@ -14515,13 +14515,13 @@
         <v>1</v>
       </c>
       <c r="N219" s="5" t="n">
-        <v>23.57</v>
+        <v>25.74</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B220" s="5" t="n">
@@ -14575,13 +14575,13 @@
         <v>1</v>
       </c>
       <c r="N220" s="5" t="n">
-        <v>23.99</v>
+        <v>24.33</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B221" s="5" t="n">
@@ -14589,7 +14589,7 @@
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D221" s="5" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="H221" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I221" s="5" t="b">
@@ -14628,20 +14628,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L221" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M221" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L221" s="5" t="n"/>
+      <c r="M221" s="5" t="n"/>
       <c r="N221" s="5" t="n">
-        <v>23.02</v>
+        <v>16.79</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B222" s="5" t="n">
@@ -14649,7 +14645,7 @@
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
@@ -14674,7 +14670,7 @@
       </c>
       <c r="H222" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I222" s="5" t="b">
@@ -14688,20 +14684,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L222" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M222" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L222" s="5" t="n"/>
+      <c r="M222" s="5" t="n"/>
       <c r="N222" s="5" t="n">
-        <v>26.5</v>
+        <v>17.62</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B223" s="5" t="n">
@@ -14709,7 +14701,7 @@
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D223" s="5" t="inlineStr">
@@ -14734,7 +14726,7 @@
       </c>
       <c r="H223" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I223" s="5" t="b">
@@ -14748,20 +14740,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L223" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M223" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L223" s="5" t="n"/>
+      <c r="M223" s="5" t="n"/>
       <c r="N223" s="5" t="n">
-        <v>12.99</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B224" s="5" t="n">
@@ -14769,7 +14757,7 @@
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D224" s="5" t="inlineStr">
@@ -14794,7 +14782,7 @@
       </c>
       <c r="H224" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I224" s="5" t="b">
@@ -14809,19 +14797,19 @@
         </is>
       </c>
       <c r="L224" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M224" s="5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N224" s="5" t="n">
-        <v>24.31</v>
+        <v>16.79</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B225" s="5" t="n">
@@ -14829,7 +14817,7 @@
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D225" s="5" t="inlineStr">
@@ -14854,7 +14842,7 @@
       </c>
       <c r="H225" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I225" s="5" t="b">
@@ -14869,19 +14857,19 @@
         </is>
       </c>
       <c r="L225" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M225" s="5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N225" s="5" t="n">
-        <v>25.74</v>
+        <v>17.34</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B226" s="5" t="n">
@@ -14889,7 +14877,7 @@
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D226" s="5" t="inlineStr">
@@ -14914,7 +14902,7 @@
       </c>
       <c r="H226" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I226" s="5" t="b">
@@ -14929,19 +14917,19 @@
         </is>
       </c>
       <c r="L226" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M226" s="5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N226" s="5" t="n">
-        <v>24.33</v>
+        <v>18.02</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B227" s="5" t="n">
@@ -14991,13 +14979,13 @@
       <c r="L227" s="5" t="n"/>
       <c r="M227" s="5" t="n"/>
       <c r="N227" s="5" t="n">
-        <v>16.79</v>
+        <v>17.72</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B228" s="5" t="n">
@@ -15047,13 +15035,13 @@
       <c r="L228" s="5" t="n"/>
       <c r="M228" s="5" t="n"/>
       <c r="N228" s="5" t="n">
-        <v>17.62</v>
+        <v>17.71</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B229" s="5" t="n">
@@ -15103,13 +15091,13 @@
       <c r="L229" s="5" t="n"/>
       <c r="M229" s="5" t="n"/>
       <c r="N229" s="5" t="n">
-        <v>18.18</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B230" s="5" t="n">
@@ -15156,20 +15144,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L230" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M230" s="5" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="L230" s="5" t="n"/>
+      <c r="M230" s="5" t="n"/>
       <c r="N230" s="5" t="n">
-        <v>16.79</v>
+        <v>17.38</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B231" s="5" t="n">
@@ -15216,20 +15200,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L231" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M231" s="5" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="L231" s="5" t="n"/>
+      <c r="M231" s="5" t="n"/>
       <c r="N231" s="5" t="n">
-        <v>17.34</v>
+        <v>18.06</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B232" s="5" t="n">
@@ -15276,33 +15256,29 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L232" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M232" s="5" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="L232" s="5" t="n"/>
+      <c r="M232" s="5" t="n"/>
       <c r="N232" s="5" t="n">
-        <v>18.02</v>
+        <v>17.48</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>filter_string_kg2_001</t>
         </is>
       </c>
       <c r="B233" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E233" s="5" t="inlineStr">
@@ -15317,12 +15293,12 @@
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H233" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I233" s="5" t="b">
@@ -15336,29 +15312,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L233" s="5" t="n"/>
-      <c r="M233" s="5" t="n"/>
+      <c r="L233" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M233" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N233" s="5" t="n">
-        <v>17.72</v>
+        <v>33.06</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>filter_string_kg2_001</t>
         </is>
       </c>
       <c r="B234" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C234" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
@@ -15373,12 +15353,12 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I234" s="5" t="b">
@@ -15392,29 +15372,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L234" s="5" t="n"/>
-      <c r="M234" s="5" t="n"/>
+      <c r="L234" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M234" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N234" s="5" t="n">
-        <v>17.71</v>
+        <v>17.92</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>filter_string_kg2_001</t>
         </is>
       </c>
       <c r="B235" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E235" s="5" t="inlineStr">
@@ -15429,12 +15413,12 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I235" s="5" t="b">
@@ -15448,29 +15432,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L235" s="5" t="n"/>
-      <c r="M235" s="5" t="n"/>
+      <c r="L235" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M235" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N235" s="5" t="n">
-        <v>17.86</v>
+        <v>17.61</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B236" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C236" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E236" s="5" t="inlineStr">
@@ -15485,12 +15473,12 @@
       </c>
       <c r="G236" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H236" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I236" s="5" t="b">
@@ -15504,29 +15492,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L236" s="5" t="n"/>
-      <c r="M236" s="5" t="n"/>
+      <c r="L236" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M236" s="5" t="n">
+        <v>0.7368</v>
+      </c>
       <c r="N236" s="5" t="n">
-        <v>17.38</v>
+        <v>12.78</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B237" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E237" s="5" t="inlineStr">
@@ -15541,12 +15533,12 @@
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H237" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I237" s="5" t="b">
@@ -15560,29 +15552,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L237" s="5" t="n"/>
-      <c r="M237" s="5" t="n"/>
+      <c r="L237" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M237" s="5" t="n">
+        <v>0.7368</v>
+      </c>
       <c r="N237" s="5" t="n">
-        <v>18.06</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B238" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C238" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
@@ -15597,12 +15593,12 @@
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H238" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I238" s="5" t="b">
@@ -15616,29 +15612,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L238" s="5" t="n"/>
-      <c r="M238" s="5" t="n"/>
+      <c r="L238" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M238" s="5" t="n">
+        <v>0.4</v>
+      </c>
       <c r="N238" s="5" t="n">
-        <v>17.48</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_001</t>
+          <t>single_kg1_005</t>
         </is>
       </c>
       <c r="B239" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E239" s="5" t="inlineStr">
@@ -15653,12 +15653,12 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I239" s="5" t="b">
@@ -15679,46 +15679,46 @@
         <v>1</v>
       </c>
       <c r="N239" s="5" t="n">
-        <v>33.06</v>
+        <v>27.43</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_001</t>
+          <t>single_kg1_005</t>
         </is>
       </c>
       <c r="B240" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C240" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E240" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H240" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I240" s="5" t="b">
@@ -15739,46 +15739,46 @@
         <v>1</v>
       </c>
       <c r="N240" s="5" t="n">
-        <v>17.92</v>
+        <v>23.63</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_001</t>
+          <t>single_kg1_005</t>
         </is>
       </c>
       <c r="B241" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E241" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H241" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I241" s="5" t="b">
@@ -15799,31 +15799,31 @@
         <v>1</v>
       </c>
       <c r="N241" s="5" t="n">
-        <v>17.61</v>
+        <v>23.97</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>single_kg1_005</t>
         </is>
       </c>
       <c r="B242" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E242" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F242" s="5" t="inlineStr">
@@ -15833,12 +15833,12 @@
       </c>
       <c r="G242" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H242" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I242" s="5" t="b">
@@ -15856,29 +15856,29 @@
         <v>0</v>
       </c>
       <c r="M242" s="5" t="n">
-        <v>0.7368</v>
+        <v>0.2</v>
       </c>
       <c r="N242" s="5" t="n">
-        <v>12.78</v>
+        <v>23.36</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>single_kg1_005</t>
         </is>
       </c>
       <c r="B243" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E243" s="5" t="inlineStr">
@@ -15888,17 +15888,17 @@
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H243" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I243" s="5" t="b">
@@ -15916,49 +15916,49 @@
         <v>0</v>
       </c>
       <c r="M243" s="5" t="n">
-        <v>0.7368</v>
+        <v>0.2</v>
       </c>
       <c r="N243" s="5" t="n">
-        <v>18.18</v>
+        <v>20.15</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>single_kg1_005</t>
         </is>
       </c>
       <c r="B244" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E244" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F244" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H244" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I244" s="5" t="b">
@@ -15976,10 +15976,10 @@
         <v>0</v>
       </c>
       <c r="M244" s="5" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="N244" s="5" t="n">
-        <v>13.98</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="245">
@@ -16003,7 +16003,7 @@
       </c>
       <c r="E245" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F245" s="5" t="inlineStr">
@@ -16018,11 +16018,11 @@
       </c>
       <c r="H245" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I245" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J245" s="5" t="b">
         <v>1</v>
@@ -16033,13 +16033,13 @@
         </is>
       </c>
       <c r="L245" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M245" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N245" s="5" t="n">
-        <v>27.43</v>
+        <v>28.07</v>
       </c>
     </row>
     <row r="246">
@@ -16063,7 +16063,7 @@
       </c>
       <c r="E246" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F246" s="5" t="inlineStr">
@@ -16078,11 +16078,11 @@
       </c>
       <c r="H246" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I246" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J246" s="5" t="b">
         <v>1</v>
@@ -16093,13 +16093,13 @@
         </is>
       </c>
       <c r="L246" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M246" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N246" s="5" t="n">
-        <v>23.63</v>
+        <v>20.22</v>
       </c>
     </row>
     <row r="247">
@@ -16123,7 +16123,7 @@
       </c>
       <c r="E247" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F247" s="5" t="inlineStr">
@@ -16138,11 +16138,11 @@
       </c>
       <c r="H247" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I247" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J247" s="5" t="b">
         <v>1</v>
@@ -16153,19 +16153,19 @@
         </is>
       </c>
       <c r="L247" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M247" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N247" s="5" t="n">
-        <v>23.97</v>
+        <v>20.03</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_005</t>
+          <t>open_kg_004</t>
         </is>
       </c>
       <c r="B248" s="5" t="n">
@@ -16173,17 +16173,17 @@
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E248" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F248" s="5" t="inlineStr">
@@ -16193,12 +16193,12 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I248" s="5" t="b">
@@ -16216,16 +16216,16 @@
         <v>0</v>
       </c>
       <c r="M248" s="5" t="n">
-        <v>0.2</v>
+        <v>0.6667</v>
       </c>
       <c r="N248" s="5" t="n">
-        <v>23.36</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_005</t>
+          <t>open_kg_004</t>
         </is>
       </c>
       <c r="B249" s="5" t="n">
@@ -16233,12 +16233,12 @@
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E249" s="5" t="inlineStr">
@@ -16248,17 +16248,17 @@
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H249" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I249" s="5" t="b">
@@ -16276,16 +16276,16 @@
         <v>0</v>
       </c>
       <c r="M249" s="5" t="n">
-        <v>0.2</v>
+        <v>0.6667</v>
       </c>
       <c r="N249" s="5" t="n">
-        <v>20.15</v>
+        <v>45.41</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_005</t>
+          <t>open_kg_004</t>
         </is>
       </c>
       <c r="B250" s="5" t="n">
@@ -16293,32 +16293,32 @@
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E250" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I250" s="5" t="b">
@@ -16336,24 +16336,24 @@
         <v>0</v>
       </c>
       <c r="M250" s="5" t="n">
-        <v>0.2</v>
+        <v>0.6667</v>
       </c>
       <c r="N250" s="5" t="n">
-        <v>20.7</v>
+        <v>33.53</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_005</t>
+          <t>filter_numeric_kg1_003</t>
         </is>
       </c>
       <c r="B251" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C251" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D251" s="5" t="inlineStr">
@@ -16363,7 +16363,7 @@
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F251" s="5" t="inlineStr">
@@ -16373,16 +16373,16 @@
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H251" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I251" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J251" s="5" t="b">
         <v>1</v>
@@ -16393,27 +16393,27 @@
         </is>
       </c>
       <c r="L251" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M251" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N251" s="5" t="n">
-        <v>28.07</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_005</t>
+          <t>filter_numeric_kg1_003</t>
         </is>
       </c>
       <c r="B252" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C252" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D252" s="5" t="inlineStr">
@@ -16423,26 +16423,26 @@
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H252" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I252" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J252" s="5" t="b">
         <v>1</v>
@@ -16453,27 +16453,27 @@
         </is>
       </c>
       <c r="L252" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M252" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N252" s="5" t="n">
-        <v>20.22</v>
+        <v>27.05</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_005</t>
+          <t>filter_numeric_kg1_003</t>
         </is>
       </c>
       <c r="B253" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D253" s="5" t="inlineStr">
@@ -16488,21 +16488,21 @@
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I253" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J253" s="5" t="b">
         <v>1</v>
@@ -16513,32 +16513,32 @@
         </is>
       </c>
       <c r="L253" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M253" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N253" s="5" t="n">
-        <v>20.03</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
         <is>
-          <t>open_kg_004</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B254" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E254" s="5" t="inlineStr">
@@ -16553,12 +16553,12 @@
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H254" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I254" s="5" t="b">
@@ -16573,32 +16573,32 @@
         </is>
       </c>
       <c r="L254" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M254" s="5" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="N254" s="5" t="n">
-        <v>36.1</v>
+        <v>36.45</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
         <is>
-          <t>open_kg_004</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B255" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E255" s="5" t="inlineStr">
@@ -16613,12 +16613,12 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I255" s="5" t="b">
@@ -16636,29 +16636,29 @@
         <v>0</v>
       </c>
       <c r="M255" s="5" t="n">
-        <v>0.6667</v>
+        <v>0.2</v>
       </c>
       <c r="N255" s="5" t="n">
-        <v>45.41</v>
+        <v>24.47</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
         <is>
-          <t>open_kg_004</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B256" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C256" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E256" s="5" t="inlineStr">
@@ -16673,12 +16673,12 @@
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H256" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I256" s="5" t="b">
@@ -16696,24 +16696,24 @@
         <v>0</v>
       </c>
       <c r="M256" s="5" t="n">
-        <v>0.6667</v>
+        <v>0</v>
       </c>
       <c r="N256" s="5" t="n">
-        <v>33.53</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_003</t>
+          <t>single_kg1_004</t>
         </is>
       </c>
       <c r="B257" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D257" s="5" t="inlineStr">
@@ -16733,12 +16733,12 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I257" s="5" t="b">
@@ -16753,27 +16753,27 @@
         </is>
       </c>
       <c r="L257" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M257" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N257" s="5" t="n">
-        <v>13.07</v>
+        <v>34.95</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_003</t>
+          <t>single_kg1_004</t>
         </is>
       </c>
       <c r="B258" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
@@ -16783,22 +16783,22 @@
       </c>
       <c r="E258" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H258" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I258" s="5" t="b">
@@ -16813,27 +16813,27 @@
         </is>
       </c>
       <c r="L258" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M258" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N258" s="5" t="n">
-        <v>27.05</v>
+        <v>21.28</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_003</t>
+          <t>single_kg1_004</t>
         </is>
       </c>
       <c r="B259" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C259" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D259" s="5" t="inlineStr">
@@ -16843,22 +16843,22 @@
       </c>
       <c r="E259" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H259" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I259" s="5" t="b">
@@ -16873,37 +16873,37 @@
         </is>
       </c>
       <c r="L259" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M259" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N259" s="5" t="n">
-        <v>14.46</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>single_kg1_004</t>
         </is>
       </c>
       <c r="B260" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E260" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F260" s="5" t="inlineStr">
@@ -16913,12 +16913,12 @@
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H260" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I260" s="5" t="b">
@@ -16939,26 +16939,26 @@
         <v>0</v>
       </c>
       <c r="N260" s="5" t="n">
-        <v>8.18</v>
+        <v>19.28</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>single_kg1_004</t>
         </is>
       </c>
       <c r="B261" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E261" s="5" t="inlineStr">
@@ -16968,17 +16968,17 @@
       </c>
       <c r="F261" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I261" s="5" t="b">
@@ -16999,46 +16999,46 @@
         <v>0</v>
       </c>
       <c r="N261" s="5" t="n">
-        <v>8.66</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>single_kg1_004</t>
         </is>
       </c>
       <c r="B262" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E262" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I262" s="5" t="b">
@@ -17059,31 +17059,31 @@
         <v>0</v>
       </c>
       <c r="N262" s="5" t="n">
-        <v>9.09</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>single_kg1_004</t>
         </is>
       </c>
       <c r="B263" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C263" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E263" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F263" s="5" t="inlineStr">
@@ -17093,112 +17093,112 @@
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H263" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I263" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J263" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K263" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L263" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M263" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N263" s="5" t="n">
-        <v>36.45</v>
+        <v>30.44</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>single_kg1_004</t>
         </is>
       </c>
       <c r="B264" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E264" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H264" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I264" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J264" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K264" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L264" s="5" t="b">
         <v>0</v>
       </c>
       <c r="M264" s="5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N264" s="5" t="n">
-        <v>24.47</v>
+        <v>15.06</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>single_kg1_004</t>
         </is>
       </c>
       <c r="B265" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E265" s="5" t="inlineStr">
@@ -17208,12 +17208,12 @@
       </c>
       <c r="F265" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H265" s="5" t="inlineStr">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="I265" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J265" s="5" t="b">
         <v>1</v>
@@ -17239,13 +17239,13 @@
         <v>0</v>
       </c>
       <c r="N265" s="5" t="n">
-        <v>23.1</v>
+        <v>18.38</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_004</t>
+          <t>single_kg2_003</t>
         </is>
       </c>
       <c r="B266" s="5" t="n">
@@ -17253,12 +17253,12 @@
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
@@ -17273,12 +17273,12 @@
       </c>
       <c r="G266" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H266" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I266" s="5" t="b">
@@ -17293,19 +17293,19 @@
         </is>
       </c>
       <c r="L266" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M266" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N266" s="5" t="n">
-        <v>34.95</v>
+        <v>22.97</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_004</t>
+          <t>single_kg2_003</t>
         </is>
       </c>
       <c r="B267" s="5" t="n">
@@ -17313,12 +17313,12 @@
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E267" s="5" t="inlineStr">
@@ -17333,12 +17333,12 @@
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H267" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I267" s="5" t="b">
@@ -17353,19 +17353,19 @@
         </is>
       </c>
       <c r="L267" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M267" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N267" s="5" t="n">
-        <v>21.28</v>
+        <v>21.43</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_004</t>
+          <t>single_kg2_003</t>
         </is>
       </c>
       <c r="B268" s="5" t="n">
@@ -17373,12 +17373,12 @@
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
@@ -17393,12 +17393,12 @@
       </c>
       <c r="G268" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H268" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I268" s="5" t="b">
@@ -17413,19 +17413,19 @@
         </is>
       </c>
       <c r="L268" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M268" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N268" s="5" t="n">
-        <v>21.71</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_004</t>
+          <t>single_kg2_003</t>
         </is>
       </c>
       <c r="B269" s="5" t="n">
@@ -17433,12 +17433,12 @@
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E269" s="5" t="inlineStr">
@@ -17453,12 +17453,12 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I269" s="5" t="b">
@@ -17473,19 +17473,19 @@
         </is>
       </c>
       <c r="L269" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M269" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N269" s="5" t="n">
-        <v>19.28</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_004</t>
+          <t>single_kg2_003</t>
         </is>
       </c>
       <c r="B270" s="5" t="n">
@@ -17493,12 +17493,12 @@
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
@@ -17513,12 +17513,12 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I270" s="5" t="b">
@@ -17533,19 +17533,19 @@
         </is>
       </c>
       <c r="L270" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M270" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N270" s="5" t="n">
-        <v>16.7</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_004</t>
+          <t>single_kg2_003</t>
         </is>
       </c>
       <c r="B271" s="5" t="n">
@@ -17553,12 +17553,12 @@
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
@@ -17573,12 +17573,12 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I271" s="5" t="b">
@@ -17593,19 +17593,19 @@
         </is>
       </c>
       <c r="L271" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M271" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N271" s="5" t="n">
-        <v>18.3</v>
+        <v>23.31</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_004</t>
+          <t>single_kg2_003</t>
         </is>
       </c>
       <c r="B272" s="5" t="n">
@@ -17613,12 +17613,12 @@
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
@@ -17633,12 +17633,12 @@
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H272" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I272" s="5" t="b">
@@ -17659,13 +17659,13 @@
         <v>0</v>
       </c>
       <c r="N272" s="5" t="n">
-        <v>30.44</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_004</t>
+          <t>single_kg2_003</t>
         </is>
       </c>
       <c r="B273" s="5" t="n">
@@ -17673,12 +17673,12 @@
       </c>
       <c r="C273" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E273" s="5" t="inlineStr">
@@ -17693,39 +17693,39 @@
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H273" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I273" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J273" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K273" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L273" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M273" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N273" s="5" t="n">
-        <v>15.06</v>
+        <v>25.09</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_004</t>
+          <t>single_kg2_003</t>
         </is>
       </c>
       <c r="B274" s="5" t="n">
@@ -17733,12 +17733,12 @@
       </c>
       <c r="C274" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E274" s="5" t="inlineStr">
@@ -17753,23 +17753,23 @@
       </c>
       <c r="G274" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H274" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I274" s="5" t="b">
         <v>0</v>
       </c>
       <c r="J274" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K274" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L274" s="5" t="b">
@@ -17779,13 +17779,13 @@
         <v>0</v>
       </c>
       <c r="N274" s="5" t="n">
-        <v>18.38</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_003</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B275" s="5" t="n">
@@ -17839,13 +17839,13 @@
         <v>1</v>
       </c>
       <c r="N275" s="5" t="n">
-        <v>22.97</v>
+        <v>19.43</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_003</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B276" s="5" t="n">
@@ -17899,13 +17899,13 @@
         <v>1</v>
       </c>
       <c r="N276" s="5" t="n">
-        <v>21.43</v>
+        <v>17.39</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_003</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B277" s="5" t="n">
@@ -17959,13 +17959,13 @@
         <v>1</v>
       </c>
       <c r="N277" s="5" t="n">
-        <v>22.22</v>
+        <v>18.39</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_003</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B278" s="5" t="n">
@@ -18019,13 +18019,13 @@
         <v>1</v>
       </c>
       <c r="N278" s="5" t="n">
-        <v>24.7</v>
+        <v>21.28</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_003</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B279" s="5" t="n">
@@ -18079,13 +18079,13 @@
         <v>1</v>
       </c>
       <c r="N279" s="5" t="n">
-        <v>22.8</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_003</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B280" s="5" t="n">
@@ -18139,13 +18139,13 @@
         <v>1</v>
       </c>
       <c r="N280" s="5" t="n">
-        <v>23.31</v>
+        <v>19.81</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_003</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B281" s="5" t="n">
@@ -18199,13 +18199,13 @@
         <v>0</v>
       </c>
       <c r="N281" s="5" t="n">
-        <v>7.22</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_003</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B282" s="5" t="n">
@@ -18238,34 +18238,34 @@
       </c>
       <c r="H282" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I282" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J282" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K282" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L282" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M282" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N282" s="5" t="n">
-        <v>25.09</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_003</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B283" s="5" t="n">
@@ -18319,13 +18319,13 @@
         <v>0</v>
       </c>
       <c r="N283" s="5" t="n">
-        <v>5.69</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>single_kg2_008</t>
         </is>
       </c>
       <c r="B284" s="5" t="n">
@@ -18379,13 +18379,13 @@
         <v>1</v>
       </c>
       <c r="N284" s="5" t="n">
-        <v>19.43</v>
+        <v>23.36</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>single_kg2_008</t>
         </is>
       </c>
       <c r="B285" s="5" t="n">
@@ -18439,13 +18439,13 @@
         <v>1</v>
       </c>
       <c r="N285" s="5" t="n">
-        <v>17.39</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>single_kg2_008</t>
         </is>
       </c>
       <c r="B286" s="5" t="n">
@@ -18499,13 +18499,13 @@
         <v>1</v>
       </c>
       <c r="N286" s="5" t="n">
-        <v>18.39</v>
+        <v>22.36</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>single_kg2_008</t>
         </is>
       </c>
       <c r="B287" s="5" t="n">
@@ -18559,13 +18559,13 @@
         <v>1</v>
       </c>
       <c r="N287" s="5" t="n">
-        <v>21.28</v>
+        <v>24.36</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>single_kg2_008</t>
         </is>
       </c>
       <c r="B288" s="5" t="n">
@@ -18598,34 +18598,34 @@
       </c>
       <c r="H288" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I288" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J288" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K288" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L288" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M288" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N288" s="5" t="n">
-        <v>19.4</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>single_kg2_008</t>
         </is>
       </c>
       <c r="B289" s="5" t="n">
@@ -18658,34 +18658,34 @@
       </c>
       <c r="H289" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I289" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J289" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K289" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L289" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M289" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N289" s="5" t="n">
-        <v>19.81</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>single_kg2_008</t>
         </is>
       </c>
       <c r="B290" s="5" t="n">
@@ -18739,13 +18739,13 @@
         <v>0</v>
       </c>
       <c r="N290" s="5" t="n">
-        <v>7.37</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>single_kg2_008</t>
         </is>
       </c>
       <c r="B291" s="5" t="n">
@@ -18799,13 +18799,13 @@
         <v>0</v>
       </c>
       <c r="N291" s="5" t="n">
-        <v>6.3</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>single_kg2_008</t>
         </is>
       </c>
       <c r="B292" s="5" t="n">
@@ -18859,13 +18859,13 @@
         <v>0</v>
       </c>
       <c r="N292" s="5" t="n">
-        <v>6.05</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_008</t>
+          <t>open_kg_002</t>
         </is>
       </c>
       <c r="B293" s="5" t="n">
@@ -18873,12 +18873,12 @@
       </c>
       <c r="C293" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E293" s="5" t="inlineStr">
@@ -18893,39 +18893,39 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I293" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J293" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K293" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>sparql_build_failure</t>
         </is>
       </c>
       <c r="L293" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M293" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N293" s="5" t="n">
-        <v>23.36</v>
+        <v>15.59</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_008</t>
+          <t>open_kg_002</t>
         </is>
       </c>
       <c r="B294" s="5" t="n">
@@ -18933,32 +18933,32 @@
       </c>
       <c r="C294" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E294" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F294" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H294" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I294" s="5" t="b">
@@ -18969,23 +18969,23 @@
       </c>
       <c r="K294" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L294" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M294" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N294" s="5" t="n">
-        <v>20.83</v>
+        <v>33.69</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_008</t>
+          <t>open_kg_002</t>
         </is>
       </c>
       <c r="B295" s="5" t="n">
@@ -18993,59 +18993,59 @@
       </c>
       <c r="C295" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E295" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F295" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I295" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J295" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K295" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>sparql_build_failure</t>
         </is>
       </c>
       <c r="L295" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M295" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N295" s="5" t="n">
-        <v>22.36</v>
+        <v>12.42</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_008</t>
+          <t>open_kg_005</t>
         </is>
       </c>
       <c r="B296" s="5" t="n">
@@ -19053,17 +19053,17 @@
       </c>
       <c r="C296" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E296" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F296" s="5" t="inlineStr">
@@ -19073,39 +19073,35 @@
       </c>
       <c r="G296" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H296" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I296" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J296" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K296" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L296" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M296" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L296" s="5" t="n"/>
+      <c r="M296" s="5" t="n"/>
       <c r="N296" s="5" t="n">
-        <v>24.36</v>
+        <v>16.07</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_008</t>
+          <t>open_kg_005</t>
         </is>
       </c>
       <c r="B297" s="5" t="n">
@@ -19113,12 +19109,12 @@
       </c>
       <c r="C297" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E297" s="5" t="inlineStr">
@@ -19128,17 +19124,17 @@
       </c>
       <c r="F297" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I297" s="5" t="b">
@@ -19149,23 +19145,19 @@
       </c>
       <c r="K297" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L297" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M297" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L297" s="5" t="n"/>
+      <c r="M297" s="5" t="n"/>
       <c r="N297" s="5" t="n">
-        <v>6.23</v>
+        <v>16.11</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_008</t>
+          <t>open_kg_005</t>
         </is>
       </c>
       <c r="B298" s="5" t="n">
@@ -19173,32 +19165,32 @@
       </c>
       <c r="C298" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D298" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E298" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F298" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G298" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H298" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I298" s="5" t="b">
@@ -19209,31 +19201,27 @@
       </c>
       <c r="K298" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L298" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M298" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L298" s="5" t="n"/>
+      <c r="M298" s="5" t="n"/>
       <c r="N298" s="5" t="n">
-        <v>6.02</v>
+        <v>13.11</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_008</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B299" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C299" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D299" s="5" t="inlineStr">
@@ -19243,7 +19231,7 @@
       </c>
       <c r="E299" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F299" s="5" t="inlineStr">
@@ -19253,23 +19241,23 @@
       </c>
       <c r="G299" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H299" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I299" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J299" s="5" t="b">
         <v>0</v>
       </c>
       <c r="K299" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>sparql_build_failure</t>
         </is>
       </c>
       <c r="L299" s="5" t="b">
@@ -19279,21 +19267,21 @@
         <v>0</v>
       </c>
       <c r="N299" s="5" t="n">
-        <v>7.24</v>
+        <v>16.58</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_008</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B300" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C300" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D300" s="5" t="inlineStr">
@@ -19303,33 +19291,33 @@
       </c>
       <c r="E300" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F300" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G300" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H300" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I300" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J300" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K300" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L300" s="5" t="b">
@@ -19339,21 +19327,21 @@
         <v>0</v>
       </c>
       <c r="N300" s="5" t="n">
-        <v>5.95</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_008</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B301" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D301" s="5" t="inlineStr">
@@ -19368,28 +19356,28 @@
       </c>
       <c r="F301" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I301" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J301" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K301" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L301" s="5" t="b">
@@ -19399,26 +19387,26 @@
         <v>0</v>
       </c>
       <c r="N301" s="5" t="n">
-        <v>6.24</v>
+        <v>17.82</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="5" t="inlineStr">
         <is>
-          <t>open_kg_002</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B302" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C302" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D302" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E302" s="5" t="inlineStr">
@@ -19433,7 +19421,7 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
@@ -19442,7 +19430,7 @@
         </is>
       </c>
       <c r="I302" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J302" s="5" t="b">
         <v>0</v>
@@ -19459,26 +19447,26 @@
         <v>0</v>
       </c>
       <c r="N302" s="5" t="n">
-        <v>15.59</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="5" t="inlineStr">
         <is>
-          <t>open_kg_002</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B303" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C303" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E303" s="5" t="inlineStr">
@@ -19493,12 +19481,12 @@
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H303" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I303" s="5" t="b">
@@ -19509,7 +19497,7 @@
       </c>
       <c r="K303" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L303" s="5" t="b">
@@ -19519,26 +19507,26 @@
         <v>0</v>
       </c>
       <c r="N303" s="5" t="n">
-        <v>33.69</v>
+        <v>15.19</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="5" t="inlineStr">
         <is>
-          <t>open_kg_002</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B304" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C304" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D304" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E304" s="5" t="inlineStr">
@@ -19553,7 +19541,7 @@
       </c>
       <c r="G304" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H304" s="5" t="inlineStr">
@@ -19562,7 +19550,7 @@
         </is>
       </c>
       <c r="I304" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J304" s="5" t="b">
         <v>0</v>
@@ -19579,26 +19567,26 @@
         <v>0</v>
       </c>
       <c r="N304" s="5" t="n">
-        <v>12.42</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="5" t="inlineStr">
         <is>
-          <t>open_kg_005</t>
+          <t>filter_string_kg2_002</t>
         </is>
       </c>
       <c r="B305" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C305" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D305" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E305" s="5" t="inlineStr">
@@ -19613,7 +19601,7 @@
       </c>
       <c r="G305" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H305" s="5" t="inlineStr">
@@ -19622,61 +19610,61 @@
         </is>
       </c>
       <c r="I305" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J305" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K305" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L305" s="5" t="n"/>
       <c r="M305" s="5" t="n"/>
       <c r="N305" s="5" t="n">
-        <v>16.07</v>
+        <v>15.78</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="5" t="inlineStr">
         <is>
-          <t>open_kg_005</t>
+          <t>filter_string_kg2_002</t>
         </is>
       </c>
       <c r="B306" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C306" s="5" t="inlineStr">
         <is>
+          <t>filter_string_kg2</t>
+        </is>
+      </c>
+      <c r="D306" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
+      </c>
+      <c r="E306" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F306" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G306" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="H306" s="5" t="inlineStr">
+        <is>
           <t>open_kg</t>
         </is>
       </c>
-      <c r="D306" s="5" t="inlineStr">
-        <is>
-          <t>cross</t>
-        </is>
-      </c>
-      <c r="E306" s="5" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="F306" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G306" s="5" t="inlineStr">
-        <is>
-          <t>open_kg</t>
-        </is>
-      </c>
-      <c r="H306" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
       <c r="I306" s="5" t="b">
         <v>0</v>
       </c>
@@ -19685,32 +19673,32 @@
       </c>
       <c r="K306" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
+          <t>generation_failure</t>
         </is>
       </c>
       <c r="L306" s="5" t="n"/>
       <c r="M306" s="5" t="n"/>
       <c r="N306" s="5" t="n">
-        <v>16.11</v>
+        <v>29.71</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="5" t="inlineStr">
         <is>
-          <t>open_kg_005</t>
+          <t>filter_string_kg2_002</t>
         </is>
       </c>
       <c r="B307" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C307" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D307" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E307" s="5" t="inlineStr">
@@ -19725,7 +19713,7 @@
       </c>
       <c r="G307" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H307" s="5" t="inlineStr">
@@ -19734,7 +19722,7 @@
         </is>
       </c>
       <c r="I307" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J307" s="5" t="b">
         <v>0</v>
@@ -19747,26 +19735,26 @@
       <c r="L307" s="5" t="n"/>
       <c r="M307" s="5" t="n"/>
       <c r="N307" s="5" t="n">
-        <v>13.11</v>
+        <v>11.77</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B308" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C308" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D308" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E308" s="5" t="inlineStr">
@@ -19781,23 +19769,23 @@
       </c>
       <c r="G308" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H308" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I308" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J308" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K308" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L308" s="5" t="b">
@@ -19807,26 +19795,26 @@
         <v>0</v>
       </c>
       <c r="N308" s="5" t="n">
-        <v>16.58</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B309" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C309" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D309" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E309" s="5" t="inlineStr">
@@ -19841,23 +19829,23 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I309" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J309" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K309" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L309" s="5" t="b">
@@ -19867,26 +19855,26 @@
         <v>0</v>
       </c>
       <c r="N309" s="5" t="n">
-        <v>13.51</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B310" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C310" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D310" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E310" s="5" t="inlineStr">
@@ -19901,23 +19889,23 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I310" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J310" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K310" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L310" s="5" t="b">
@@ -19927,26 +19915,26 @@
         <v>0</v>
       </c>
       <c r="N310" s="5" t="n">
-        <v>17.82</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>open_kg_003</t>
         </is>
       </c>
       <c r="B311" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C311" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D311" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E311" s="5" t="inlineStr">
@@ -19961,52 +19949,52 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I311" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J311" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K311" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L311" s="5" t="b">
         <v>0</v>
       </c>
       <c r="M311" s="5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="N311" s="5" t="n">
-        <v>12.19</v>
+        <v>45.43</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>open_kg_003</t>
         </is>
       </c>
       <c r="B312" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C312" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D312" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E312" s="5" t="inlineStr">
@@ -20021,19 +20009,19 @@
       </c>
       <c r="G312" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H312" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I312" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J312" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K312" s="5" t="inlineStr">
         <is>
@@ -20047,26 +20035,26 @@
         <v>0</v>
       </c>
       <c r="N312" s="5" t="n">
-        <v>15.19</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>open_kg_003</t>
         </is>
       </c>
       <c r="B313" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C313" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E313" s="5" t="inlineStr">
@@ -20081,16 +20069,16 @@
       </c>
       <c r="G313" s="5" t="inlineStr">
         <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="H313" s="5" t="inlineStr">
+        <is>
           <t>template</t>
         </is>
       </c>
-      <c r="H313" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
       <c r="I313" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J313" s="5" t="b">
         <v>0</v>
@@ -20107,26 +20095,26 @@
         <v>0</v>
       </c>
       <c r="N313" s="5" t="n">
-        <v>16.3</v>
+        <v>26.38</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_002</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B314" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C314" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D314" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E314" s="5" t="inlineStr">
@@ -20141,12 +20129,12 @@
       </c>
       <c r="G314" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H314" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I314" s="5" t="b">
@@ -20160,29 +20148,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L314" s="5" t="n"/>
-      <c r="M314" s="5" t="n"/>
+      <c r="L314" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M314" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N314" s="5" t="n">
-        <v>15.78</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_002</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B315" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C315" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D315" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E315" s="5" t="inlineStr">
@@ -20197,48 +20189,52 @@
       </c>
       <c r="G315" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H315" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I315" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J315" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K315" s="5" t="inlineStr">
         <is>
-          <t>generation_failure</t>
-        </is>
-      </c>
-      <c r="L315" s="5" t="n"/>
-      <c r="M315" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L315" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M315" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N315" s="5" t="n">
-        <v>29.71</v>
+        <v>8.56</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_002</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B316" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C316" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D316" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E316" s="5" t="inlineStr">
@@ -20253,35 +20249,39 @@
       </c>
       <c r="G316" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H316" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I316" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J316" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K316" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L316" s="5" t="n"/>
-      <c r="M316" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L316" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M316" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N316" s="5" t="n">
-        <v>11.77</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B317" s="5" t="n">
@@ -20314,14 +20314,14 @@
       </c>
       <c r="H317" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I317" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J317" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K317" s="5" t="inlineStr">
         <is>
@@ -20335,13 +20335,13 @@
         <v>0</v>
       </c>
       <c r="N317" s="5" t="n">
-        <v>6.97</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B318" s="5" t="n">
@@ -20374,18 +20374,18 @@
       </c>
       <c r="H318" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I318" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J318" s="5" t="b">
         <v>0</v>
       </c>
       <c r="K318" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L318" s="5" t="b">
@@ -20395,13 +20395,13 @@
         <v>0</v>
       </c>
       <c r="N318" s="5" t="n">
-        <v>7.75</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B319" s="5" t="n">
@@ -20434,18 +20434,18 @@
       </c>
       <c r="H319" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I319" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J319" s="5" t="b">
         <v>0</v>
       </c>
       <c r="K319" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L319" s="5" t="b">
@@ -20455,13 +20455,13 @@
         <v>0</v>
       </c>
       <c r="N319" s="5" t="n">
-        <v>7.7</v>
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B320" s="5" t="n">
@@ -20469,7 +20469,7 @@
       </c>
       <c r="C320" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D320" s="5" t="inlineStr">
@@ -20489,7 +20489,7 @@
       </c>
       <c r="G320" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H320" s="5" t="inlineStr">
@@ -20509,19 +20509,19 @@
         </is>
       </c>
       <c r="L320" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M320" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N320" s="5" t="n">
-        <v>6.9</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B321" s="5" t="n">
@@ -20529,7 +20529,7 @@
       </c>
       <c r="C321" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D321" s="5" t="inlineStr">
@@ -20549,7 +20549,7 @@
       </c>
       <c r="G321" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H321" s="5" t="inlineStr">
@@ -20561,11 +20561,11 @@
         <v>1</v>
       </c>
       <c r="J321" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K321" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L321" s="5" t="b">
@@ -20575,13 +20575,13 @@
         <v>0</v>
       </c>
       <c r="N321" s="5" t="n">
-        <v>7.54</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B322" s="5" t="n">
@@ -20589,7 +20589,7 @@
       </c>
       <c r="C322" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D322" s="5" t="inlineStr">
@@ -20609,7 +20609,7 @@
       </c>
       <c r="G322" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H322" s="5" t="inlineStr">
@@ -20621,11 +20621,11 @@
         <v>1</v>
       </c>
       <c r="J322" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K322" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L322" s="5" t="b">
@@ -20635,26 +20635,26 @@
         <v>0</v>
       </c>
       <c r="N322" s="5" t="n">
-        <v>7.63</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="5" t="inlineStr">
         <is>
-          <t>open_kg_003</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B323" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C323" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E323" s="5" t="inlineStr">
@@ -20669,12 +20669,12 @@
       </c>
       <c r="G323" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H323" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I323" s="5" t="b">
@@ -20695,26 +20695,26 @@
         <v>1</v>
       </c>
       <c r="N323" s="5" t="n">
-        <v>50.71</v>
+        <v>22.89</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="5" t="inlineStr">
         <is>
-          <t>open_kg_003</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B324" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C324" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D324" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E324" s="5" t="inlineStr">
@@ -20729,23 +20729,23 @@
       </c>
       <c r="G324" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H324" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I324" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J324" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K324" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L324" s="5" t="b">
@@ -20755,26 +20755,26 @@
         <v>0</v>
       </c>
       <c r="N324" s="5" t="n">
-        <v>17.9</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="5" t="inlineStr">
         <is>
-          <t>open_kg_003</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B325" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C325" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E325" s="5" t="inlineStr">
@@ -20789,23 +20789,23 @@
       </c>
       <c r="G325" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H325" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I325" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J325" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K325" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L325" s="5" t="b">
@@ -20815,7 +20815,7 @@
         <v>0</v>
       </c>
       <c r="N325" s="5" t="n">
-        <v>17.64</v>
+        <v>8.630000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/NL2SPARQL_Evaluation_Results.xlsx
+++ b/NL2SPARQL_Evaluation_Results.xlsx
@@ -1573,7 +1573,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>36.28</v>
+        <v>21.78</v>
       </c>
     </row>
     <row r="3">
@@ -1693,7 +1693,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>19.41</v>
+        <v>19.48</v>
       </c>
     </row>
     <row r="5">
@@ -1753,7 +1753,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>22.65</v>
+        <v>26.97</v>
       </c>
     </row>
     <row r="6">
@@ -1813,7 +1813,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>19.4</v>
+        <v>27.98</v>
       </c>
     </row>
     <row r="7">
@@ -1873,7 +1873,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>19.12</v>
+        <v>22.15</v>
       </c>
     </row>
     <row r="8">
@@ -1933,7 +1933,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>21.24</v>
+        <v>22.95</v>
       </c>
     </row>
     <row r="9">
@@ -1993,7 +1993,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>18.72</v>
+        <v>21.51</v>
       </c>
     </row>
     <row r="10">
@@ -2053,7 +2053,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>21.83</v>
+        <v>20.26</v>
       </c>
     </row>
     <row r="11">
@@ -2113,7 +2113,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>19.55</v>
+        <v>20.09</v>
       </c>
     </row>
     <row r="12">
@@ -2173,7 +2173,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>16.75</v>
+        <v>18.52</v>
       </c>
     </row>
     <row r="13">
@@ -2233,7 +2233,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>17.9</v>
+        <v>18.04</v>
       </c>
     </row>
     <row r="14">
@@ -2293,7 +2293,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>19.04</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="15">
@@ -2353,7 +2353,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>17.8</v>
+        <v>18.09</v>
       </c>
     </row>
     <row r="16">
@@ -2413,7 +2413,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>18.8</v>
+        <v>18.15</v>
       </c>
     </row>
     <row r="17">
@@ -2473,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>32.11</v>
+        <v>35.01</v>
       </c>
     </row>
     <row r="18">
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>18.49</v>
+        <v>18.39</v>
       </c>
     </row>
     <row r="19">
@@ -2593,7 +2593,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>17.67</v>
+        <v>19.53</v>
       </c>
     </row>
     <row r="20">
@@ -2653,7 +2653,7 @@
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>20.1</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="21">
@@ -2713,7 +2713,7 @@
         <v>1</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>18.59</v>
+        <v>19.37</v>
       </c>
     </row>
     <row r="22">
@@ -2773,7 +2773,7 @@
         <v>1</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>19.46</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="23">
@@ -2833,7 +2833,7 @@
         <v>1</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>21.06</v>
+        <v>22.63</v>
       </c>
     </row>
     <row r="24">
@@ -2893,7 +2893,7 @@
         <v>1</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>19.27</v>
+        <v>19.35</v>
       </c>
     </row>
     <row r="25">
@@ -2953,7 +2953,7 @@
         <v>1</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>19.22</v>
+        <v>19.76</v>
       </c>
     </row>
     <row r="26">
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>8.35</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -3073,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>6.75</v>
+        <v>7.57</v>
       </c>
     </row>
     <row r="28">
@@ -3133,7 +3133,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>6.91</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="29">
@@ -3193,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>24.64</v>
+        <v>26.51</v>
       </c>
     </row>
     <row r="30">
@@ -3253,7 +3253,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>22.44</v>
+        <v>23.93</v>
       </c>
     </row>
     <row r="31">
@@ -3313,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>23.41</v>
+        <v>28.73</v>
       </c>
     </row>
     <row r="32">
@@ -3373,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>20.29</v>
+        <v>24.49</v>
       </c>
     </row>
     <row r="33">
@@ -3433,7 +3433,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>17.55</v>
+        <v>20.63</v>
       </c>
     </row>
     <row r="34">
@@ -3493,7 +3493,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>19.07</v>
+        <v>21.03</v>
       </c>
     </row>
     <row r="35">
@@ -3532,18 +3532,18 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I35" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L35" s="5" t="b">
@@ -3553,7 +3553,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="5" t="n">
-        <v>42.28</v>
+        <v>32.58</v>
       </c>
     </row>
     <row r="36">
@@ -3590,20 +3590,16 @@
           <t>single_kg1</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>single_kg1</t>
-        </is>
-      </c>
+      <c r="H36" s="5" t="n"/>
       <c r="I36" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>exception: 'str' object has no attribute 'get'</t>
         </is>
       </c>
       <c r="L36" s="5" t="b">
@@ -3613,7 +3609,7 @@
         <v>0</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>35.86</v>
+        <v>23.74</v>
       </c>
     </row>
     <row r="37">
@@ -3652,11 +3648,11 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I37" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" s="5" t="b">
         <v>1</v>
@@ -3673,7 +3669,7 @@
         <v>0</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>27.12</v>
+        <v>39.07</v>
       </c>
     </row>
     <row r="38">
@@ -3733,7 +3729,7 @@
         <v>1</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>24.68</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="39">
@@ -3793,7 +3789,7 @@
         <v>1</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>24.49</v>
+        <v>27.06</v>
       </c>
     </row>
     <row r="40">
@@ -3853,7 +3849,7 @@
         <v>1</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>24.59</v>
+        <v>27.94</v>
       </c>
     </row>
     <row r="41">
@@ -3913,7 +3909,7 @@
         <v>0.2</v>
       </c>
       <c r="N41" s="5" t="n">
-        <v>21.41</v>
+        <v>24.82</v>
       </c>
     </row>
     <row r="42">
@@ -3973,7 +3969,7 @@
         <v>0.2</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>19.66</v>
+        <v>23.59</v>
       </c>
     </row>
     <row r="43">
@@ -4033,7 +4029,7 @@
         <v>0.2</v>
       </c>
       <c r="N43" s="5" t="n">
-        <v>19.71</v>
+        <v>22.74</v>
       </c>
     </row>
     <row r="44">
@@ -4079,11 +4075,11 @@
         <v>0</v>
       </c>
       <c r="J44" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L44" s="5" t="b">
@@ -4093,7 +4089,7 @@
         <v>0</v>
       </c>
       <c r="N44" s="5" t="n">
-        <v>19.88</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="45">
@@ -4153,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="N45" s="5" t="n">
-        <v>18.29</v>
+        <v>20.22</v>
       </c>
     </row>
     <row r="46">
@@ -4199,11 +4195,11 @@
         <v>0</v>
       </c>
       <c r="J46" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L46" s="5" t="b">
@@ -4213,7 +4209,7 @@
         <v>0</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>14.88</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="47">
@@ -4252,11 +4248,11 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I47" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" s="5" t="b">
         <v>1</v>
@@ -4273,7 +4269,7 @@
         <v>0</v>
       </c>
       <c r="N47" s="5" t="n">
-        <v>36.91</v>
+        <v>25.93</v>
       </c>
     </row>
     <row r="48">
@@ -4312,11 +4308,11 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I48" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" s="5" t="b">
         <v>1</v>
@@ -4333,7 +4329,7 @@
         <v>0</v>
       </c>
       <c r="N48" s="5" t="n">
-        <v>24.19</v>
+        <v>19.43</v>
       </c>
     </row>
     <row r="49">
@@ -4393,7 +4389,7 @@
         <v>0</v>
       </c>
       <c r="N49" s="5" t="n">
-        <v>19.46</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="50">
@@ -4453,7 +4449,7 @@
         <v>0</v>
       </c>
       <c r="N50" s="5" t="n">
-        <v>21.26</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="51">
@@ -4513,7 +4509,7 @@
         <v>0</v>
       </c>
       <c r="N51" s="5" t="n">
-        <v>19.21</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="52">
@@ -4573,7 +4569,7 @@
         <v>0</v>
       </c>
       <c r="N52" s="5" t="n">
-        <v>19.34</v>
+        <v>19.39</v>
       </c>
     </row>
     <row r="53">
@@ -4619,11 +4615,11 @@
         <v>0</v>
       </c>
       <c r="J53" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L53" s="5" t="b">
@@ -4633,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>23.97</v>
+        <v>24.13</v>
       </c>
     </row>
     <row r="54">
@@ -4693,7 +4689,7 @@
         <v>0</v>
       </c>
       <c r="N54" s="5" t="n">
-        <v>18.03</v>
+        <v>19.71</v>
       </c>
     </row>
     <row r="55">
@@ -4739,11 +4735,11 @@
         <v>0</v>
       </c>
       <c r="J55" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L55" s="5" t="b">
@@ -4753,7 +4749,7 @@
         <v>0</v>
       </c>
       <c r="N55" s="5" t="n">
-        <v>14.52</v>
+        <v>21.82</v>
       </c>
     </row>
     <row r="56">
@@ -4813,7 +4809,7 @@
         <v>1</v>
       </c>
       <c r="N56" s="5" t="n">
-        <v>21.11</v>
+        <v>21.85</v>
       </c>
     </row>
     <row r="57">
@@ -4873,7 +4869,7 @@
         <v>1</v>
       </c>
       <c r="N57" s="5" t="n">
-        <v>18.39</v>
+        <v>19.33</v>
       </c>
     </row>
     <row r="58">
@@ -4933,7 +4929,7 @@
         <v>1</v>
       </c>
       <c r="N58" s="5" t="n">
-        <v>18.76</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="59">
@@ -4993,7 +4989,7 @@
         <v>1</v>
       </c>
       <c r="N59" s="5" t="n">
-        <v>22.2</v>
+        <v>22.32</v>
       </c>
     </row>
     <row r="60">
@@ -5053,7 +5049,7 @@
         <v>1</v>
       </c>
       <c r="N60" s="5" t="n">
-        <v>18.71</v>
+        <v>20.36</v>
       </c>
     </row>
     <row r="61">
@@ -5113,7 +5109,7 @@
         <v>1</v>
       </c>
       <c r="N61" s="5" t="n">
-        <v>18.72</v>
+        <v>21.24</v>
       </c>
     </row>
     <row r="62">
@@ -5173,7 +5169,7 @@
         <v>0</v>
       </c>
       <c r="N62" s="5" t="n">
-        <v>22.49</v>
+        <v>25.07</v>
       </c>
     </row>
     <row r="63">
@@ -5233,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="N63" s="5" t="n">
-        <v>19.65</v>
+        <v>22.85</v>
       </c>
     </row>
     <row r="64">
@@ -5293,7 +5289,7 @@
         <v>0</v>
       </c>
       <c r="N64" s="5" t="n">
-        <v>20.06</v>
+        <v>22.66</v>
       </c>
     </row>
     <row r="65">
@@ -5353,7 +5349,7 @@
         <v>1</v>
       </c>
       <c r="N65" s="5" t="n">
-        <v>21.27</v>
+        <v>22.12</v>
       </c>
     </row>
     <row r="66">
@@ -5413,7 +5409,7 @@
         <v>1</v>
       </c>
       <c r="N66" s="5" t="n">
-        <v>18.12</v>
+        <v>18.74</v>
       </c>
     </row>
     <row r="67">
@@ -5473,7 +5469,7 @@
         <v>1</v>
       </c>
       <c r="N67" s="5" t="n">
-        <v>19.37</v>
+        <v>19.46</v>
       </c>
     </row>
     <row r="68">
@@ -5533,7 +5529,7 @@
         <v>1</v>
       </c>
       <c r="N68" s="5" t="n">
-        <v>22.46</v>
+        <v>22.29</v>
       </c>
     </row>
     <row r="69">
@@ -5593,7 +5589,7 @@
         <v>1</v>
       </c>
       <c r="N69" s="5" t="n">
-        <v>19.18</v>
+        <v>19.58</v>
       </c>
     </row>
     <row r="70">
@@ -5653,7 +5649,7 @@
         <v>1</v>
       </c>
       <c r="N70" s="5" t="n">
-        <v>19.08</v>
+        <v>19.78</v>
       </c>
     </row>
     <row r="71">
@@ -5713,7 +5709,7 @@
         <v>1</v>
       </c>
       <c r="N71" s="5" t="n">
-        <v>21.65</v>
+        <v>23.95</v>
       </c>
     </row>
     <row r="72">
@@ -5773,7 +5769,7 @@
         <v>1</v>
       </c>
       <c r="N72" s="5" t="n">
-        <v>20.52</v>
+        <v>19.14</v>
       </c>
     </row>
     <row r="73">
@@ -5833,7 +5829,7 @@
         <v>1</v>
       </c>
       <c r="N73" s="5" t="n">
-        <v>19.82</v>
+        <v>19.37</v>
       </c>
     </row>
     <row r="74">
@@ -5893,7 +5889,7 @@
         <v>1</v>
       </c>
       <c r="N74" s="5" t="n">
-        <v>20.57</v>
+        <v>20.35</v>
       </c>
     </row>
     <row r="75">
@@ -5953,7 +5949,7 @@
         <v>1</v>
       </c>
       <c r="N75" s="5" t="n">
-        <v>17.62</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="76">
@@ -6013,7 +6009,7 @@
         <v>1</v>
       </c>
       <c r="N76" s="5" t="n">
-        <v>18.14</v>
+        <v>18.07</v>
       </c>
     </row>
     <row r="77">
@@ -6073,7 +6069,7 @@
         <v>1</v>
       </c>
       <c r="N77" s="5" t="n">
-        <v>20.91</v>
+        <v>20.97</v>
       </c>
     </row>
     <row r="78">
@@ -6133,7 +6129,7 @@
         <v>1</v>
       </c>
       <c r="N78" s="5" t="n">
-        <v>17.73</v>
+        <v>19.67</v>
       </c>
     </row>
     <row r="79">
@@ -6193,7 +6189,7 @@
         <v>1</v>
       </c>
       <c r="N79" s="5" t="n">
-        <v>18.39</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="80">
@@ -6253,7 +6249,7 @@
         <v>1</v>
       </c>
       <c r="N80" s="5" t="n">
-        <v>20.56</v>
+        <v>21.08</v>
       </c>
     </row>
     <row r="81">
@@ -6313,7 +6309,7 @@
         <v>1</v>
       </c>
       <c r="N81" s="5" t="n">
-        <v>18.06</v>
+        <v>18.63</v>
       </c>
     </row>
     <row r="82">
@@ -6373,7 +6369,7 @@
         <v>1</v>
       </c>
       <c r="N82" s="5" t="n">
-        <v>18.37</v>
+        <v>18.41</v>
       </c>
     </row>
     <row r="83">
@@ -6433,7 +6429,7 @@
         <v>1</v>
       </c>
       <c r="N83" s="5" t="n">
-        <v>22.81</v>
+        <v>22.78</v>
       </c>
     </row>
     <row r="84">
@@ -6493,7 +6489,7 @@
         <v>1</v>
       </c>
       <c r="N84" s="5" t="n">
-        <v>19.21</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="85">
@@ -6553,7 +6549,7 @@
         <v>1</v>
       </c>
       <c r="N85" s="5" t="n">
-        <v>19.59</v>
+        <v>19.42</v>
       </c>
     </row>
     <row r="86">
@@ -6613,7 +6609,7 @@
         <v>1</v>
       </c>
       <c r="N86" s="5" t="n">
-        <v>25.19</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="87">
@@ -6673,7 +6669,7 @@
         <v>1</v>
       </c>
       <c r="N87" s="5" t="n">
-        <v>20.66</v>
+        <v>21.95</v>
       </c>
     </row>
     <row r="88">
@@ -6733,7 +6729,7 @@
         <v>1</v>
       </c>
       <c r="N88" s="5" t="n">
-        <v>19.9</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="89">
@@ -6793,7 +6789,7 @@
         <v>1</v>
       </c>
       <c r="N89" s="5" t="n">
-        <v>23.02</v>
+        <v>23.88</v>
       </c>
     </row>
     <row r="90">
@@ -6853,7 +6849,7 @@
         <v>1</v>
       </c>
       <c r="N90" s="5" t="n">
-        <v>19.79</v>
+        <v>20.35</v>
       </c>
     </row>
     <row r="91">
@@ -6913,7 +6909,7 @@
         <v>1</v>
       </c>
       <c r="N91" s="5" t="n">
-        <v>20.87</v>
+        <v>20.56</v>
       </c>
     </row>
     <row r="92">
@@ -6973,7 +6969,7 @@
         <v>1</v>
       </c>
       <c r="N92" s="5" t="n">
-        <v>23.43</v>
+        <v>23.64</v>
       </c>
     </row>
     <row r="93">
@@ -7033,7 +7029,7 @@
         <v>1</v>
       </c>
       <c r="N93" s="5" t="n">
-        <v>19.06</v>
+        <v>19.48</v>
       </c>
     </row>
     <row r="94">
@@ -7093,7 +7089,7 @@
         <v>1</v>
       </c>
       <c r="N94" s="5" t="n">
-        <v>20.14</v>
+        <v>19.48</v>
       </c>
     </row>
     <row r="95">
@@ -7153,7 +7149,7 @@
         <v>1</v>
       </c>
       <c r="N95" s="5" t="n">
-        <v>24.5</v>
+        <v>24.33</v>
       </c>
     </row>
     <row r="96">
@@ -7199,21 +7195,21 @@
         <v>1</v>
       </c>
       <c r="J96" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>generation_failure</t>
         </is>
       </c>
       <c r="L96" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N96" s="5" t="n">
-        <v>20.37</v>
+        <v>17.74</v>
       </c>
     </row>
     <row r="97">
@@ -7273,7 +7269,7 @@
         <v>1</v>
       </c>
       <c r="N97" s="5" t="n">
-        <v>20.5</v>
+        <v>20.66</v>
       </c>
     </row>
     <row r="98">
@@ -7312,11 +7308,11 @@
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I98" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J98" s="5" t="b">
         <v>1</v>
@@ -7327,13 +7323,13 @@
         </is>
       </c>
       <c r="L98" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N98" s="5" t="n">
-        <v>24.1</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="99">
@@ -7393,7 +7389,7 @@
         <v>1</v>
       </c>
       <c r="N99" s="5" t="n">
-        <v>20</v>
+        <v>22.43</v>
       </c>
     </row>
     <row r="100">
@@ -7453,7 +7449,7 @@
         <v>1</v>
       </c>
       <c r="N100" s="5" t="n">
-        <v>21</v>
+        <v>20.84</v>
       </c>
     </row>
     <row r="101">
@@ -7513,7 +7509,7 @@
         <v>1</v>
       </c>
       <c r="N101" s="5" t="n">
-        <v>26.49</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="102">
@@ -7573,7 +7569,7 @@
         <v>1</v>
       </c>
       <c r="N102" s="5" t="n">
-        <v>24.1</v>
+        <v>22.92</v>
       </c>
     </row>
     <row r="103">
@@ -7633,7 +7629,7 @@
         <v>1</v>
       </c>
       <c r="N103" s="5" t="n">
-        <v>24.35</v>
+        <v>24.54</v>
       </c>
     </row>
     <row r="104">
@@ -7693,7 +7689,7 @@
         <v>1</v>
       </c>
       <c r="N104" s="5" t="n">
-        <v>27.84</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="105">
@@ -7753,7 +7749,7 @@
         <v>1</v>
       </c>
       <c r="N105" s="5" t="n">
-        <v>25.2</v>
+        <v>25.84</v>
       </c>
     </row>
     <row r="106">
@@ -7813,7 +7809,7 @@
         <v>1</v>
       </c>
       <c r="N106" s="5" t="n">
-        <v>25.88</v>
+        <v>25.51</v>
       </c>
     </row>
     <row r="107">
@@ -7852,14 +7848,14 @@
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I107" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J107" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K107" s="5" t="inlineStr">
         <is>
@@ -7867,13 +7863,13 @@
         </is>
       </c>
       <c r="L107" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N107" s="5" t="n">
-        <v>8.91</v>
+        <v>29.05</v>
       </c>
     </row>
     <row r="108">
@@ -7912,11 +7908,11 @@
       </c>
       <c r="H108" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I108" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J108" s="5" t="b">
         <v>1</v>
@@ -7927,13 +7923,13 @@
         </is>
       </c>
       <c r="L108" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N108" s="5" t="n">
-        <v>8.029999999999999</v>
+        <v>24.79</v>
       </c>
     </row>
     <row r="109">
@@ -7972,14 +7968,14 @@
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I109" s="5" t="b">
         <v>0</v>
       </c>
       <c r="J109" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K109" s="5" t="inlineStr">
         <is>
@@ -7993,7 +7989,7 @@
         <v>0</v>
       </c>
       <c r="N109" s="5" t="n">
-        <v>6.36</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="110">
@@ -8053,7 +8049,7 @@
         <v>1</v>
       </c>
       <c r="N110" s="5" t="n">
-        <v>22</v>
+        <v>22.12</v>
       </c>
     </row>
     <row r="111">
@@ -8113,7 +8109,7 @@
         <v>1</v>
       </c>
       <c r="N111" s="5" t="n">
-        <v>18.46</v>
+        <v>18.63</v>
       </c>
     </row>
     <row r="112">
@@ -8173,7 +8169,7 @@
         <v>1</v>
       </c>
       <c r="N112" s="5" t="n">
-        <v>18.89</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="113">
@@ -8233,7 +8229,7 @@
         <v>1</v>
       </c>
       <c r="N113" s="5" t="n">
-        <v>24.92</v>
+        <v>24.53</v>
       </c>
     </row>
     <row r="114">
@@ -8293,7 +8289,7 @@
         <v>1</v>
       </c>
       <c r="N114" s="5" t="n">
-        <v>21.68</v>
+        <v>20.53</v>
       </c>
     </row>
     <row r="115">
@@ -8353,7 +8349,7 @@
         <v>1</v>
       </c>
       <c r="N115" s="5" t="n">
-        <v>22.11</v>
+        <v>22.09</v>
       </c>
     </row>
     <row r="116">
@@ -8413,7 +8409,7 @@
         <v>0</v>
       </c>
       <c r="N116" s="5" t="n">
-        <v>9</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="117">
@@ -8473,7 +8469,7 @@
         <v>0</v>
       </c>
       <c r="N117" s="5" t="n">
-        <v>6.84</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="118">
@@ -8533,7 +8529,7 @@
         <v>0</v>
       </c>
       <c r="N118" s="5" t="n">
-        <v>6.61</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="119">
@@ -8593,7 +8589,7 @@
         <v>1</v>
       </c>
       <c r="N119" s="5" t="n">
-        <v>28.63</v>
+        <v>29.35</v>
       </c>
     </row>
     <row r="120">
@@ -8653,7 +8649,7 @@
         <v>1</v>
       </c>
       <c r="N120" s="5" t="n">
-        <v>24.71</v>
+        <v>24.34</v>
       </c>
     </row>
     <row r="121">
@@ -8713,7 +8709,7 @@
         <v>1</v>
       </c>
       <c r="N121" s="5" t="n">
-        <v>25.7</v>
+        <v>25.48</v>
       </c>
     </row>
     <row r="122">
@@ -8773,7 +8769,7 @@
         <v>1</v>
       </c>
       <c r="N122" s="5" t="n">
-        <v>30.75</v>
+        <v>30.33</v>
       </c>
     </row>
     <row r="123">
@@ -8833,7 +8829,7 @@
         <v>1</v>
       </c>
       <c r="N123" s="5" t="n">
-        <v>26.14</v>
+        <v>25.39</v>
       </c>
     </row>
     <row r="124">
@@ -8893,7 +8889,7 @@
         <v>1</v>
       </c>
       <c r="N124" s="5" t="n">
-        <v>27.56</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="125">
@@ -8953,7 +8949,7 @@
         <v>1</v>
       </c>
       <c r="N125" s="5" t="n">
-        <v>29.73</v>
+        <v>28.73</v>
       </c>
     </row>
     <row r="126">
@@ -9013,7 +9009,7 @@
         <v>1</v>
       </c>
       <c r="N126" s="5" t="n">
-        <v>25.28</v>
+        <v>25.03</v>
       </c>
     </row>
     <row r="127">
@@ -9073,7 +9069,7 @@
         <v>1</v>
       </c>
       <c r="N127" s="5" t="n">
-        <v>27.11</v>
+        <v>25.94</v>
       </c>
     </row>
     <row r="128">
@@ -9133,7 +9129,7 @@
         <v>0</v>
       </c>
       <c r="N128" s="5" t="n">
-        <v>29.44</v>
+        <v>27.77</v>
       </c>
     </row>
     <row r="129">
@@ -9193,7 +9189,7 @@
         <v>0</v>
       </c>
       <c r="N129" s="5" t="n">
-        <v>24.18</v>
+        <v>23.96</v>
       </c>
     </row>
     <row r="130">
@@ -9253,7 +9249,7 @@
         <v>0</v>
       </c>
       <c r="N130" s="5" t="n">
-        <v>25.75</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="131">
@@ -9313,7 +9309,7 @@
         <v>0</v>
       </c>
       <c r="N131" s="5" t="n">
-        <v>29.51</v>
+        <v>30.02</v>
       </c>
     </row>
     <row r="132">
@@ -9373,7 +9369,7 @@
         <v>0</v>
       </c>
       <c r="N132" s="5" t="n">
-        <v>25.48</v>
+        <v>24.56</v>
       </c>
     </row>
     <row r="133">
@@ -9433,7 +9429,7 @@
         <v>0</v>
       </c>
       <c r="N133" s="5" t="n">
-        <v>26.15</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="134">
@@ -9493,7 +9489,7 @@
         <v>0</v>
       </c>
       <c r="N134" s="5" t="n">
-        <v>30.78</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="135">
@@ -9553,7 +9549,7 @@
         <v>0</v>
       </c>
       <c r="N135" s="5" t="n">
-        <v>26.27</v>
+        <v>26.14</v>
       </c>
     </row>
     <row r="136">
@@ -9613,7 +9609,7 @@
         <v>0</v>
       </c>
       <c r="N136" s="5" t="n">
-        <v>26.44</v>
+        <v>26.55</v>
       </c>
     </row>
     <row r="137">
@@ -9673,7 +9669,7 @@
         <v>1</v>
       </c>
       <c r="N137" s="5" t="n">
-        <v>23.33</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="138">
@@ -9733,7 +9729,7 @@
         <v>1</v>
       </c>
       <c r="N138" s="5" t="n">
-        <v>19.54</v>
+        <v>18.78</v>
       </c>
     </row>
     <row r="139">
@@ -9793,7 +9789,7 @@
         <v>1</v>
       </c>
       <c r="N139" s="5" t="n">
-        <v>18.97</v>
+        <v>18.36</v>
       </c>
     </row>
     <row r="140">
@@ -9853,7 +9849,7 @@
         <v>1</v>
       </c>
       <c r="N140" s="5" t="n">
-        <v>26.63</v>
+        <v>24.68</v>
       </c>
     </row>
     <row r="141">
@@ -9913,7 +9909,7 @@
         <v>1</v>
       </c>
       <c r="N141" s="5" t="n">
-        <v>21.22</v>
+        <v>20.35</v>
       </c>
     </row>
     <row r="142">
@@ -9973,7 +9969,7 @@
         <v>1</v>
       </c>
       <c r="N142" s="5" t="n">
-        <v>21.1</v>
+        <v>20.24</v>
       </c>
     </row>
     <row r="143">
@@ -10033,7 +10029,7 @@
         <v>0</v>
       </c>
       <c r="N143" s="5" t="n">
-        <v>8.94</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="144">
@@ -10093,7 +10089,7 @@
         <v>0</v>
       </c>
       <c r="N144" s="5" t="n">
-        <v>6.75</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="145">
@@ -10153,7 +10149,7 @@
         <v>0</v>
       </c>
       <c r="N145" s="5" t="n">
-        <v>6.86</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="146">
@@ -10213,7 +10209,7 @@
         <v>1</v>
       </c>
       <c r="N146" s="5" t="n">
-        <v>28.04</v>
+        <v>26.62</v>
       </c>
     </row>
     <row r="147">
@@ -10273,7 +10269,7 @@
         <v>1</v>
       </c>
       <c r="N147" s="5" t="n">
-        <v>23.85</v>
+        <v>22.66</v>
       </c>
     </row>
     <row r="148">
@@ -10333,7 +10329,7 @@
         <v>1</v>
       </c>
       <c r="N148" s="5" t="n">
-        <v>24.13</v>
+        <v>23.48</v>
       </c>
     </row>
     <row r="149">
@@ -10393,7 +10389,7 @@
         <v>0</v>
       </c>
       <c r="N149" s="5" t="n">
-        <v>8.9</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="150">
@@ -10432,28 +10428,28 @@
       </c>
       <c r="H150" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I150" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J150" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K150" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L150" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M150" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N150" s="5" t="n">
-        <v>26.8</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="151">
@@ -10513,7 +10509,7 @@
         <v>0</v>
       </c>
       <c r="N151" s="5" t="n">
-        <v>6.18</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="152">
@@ -10573,7 +10569,7 @@
         <v>0</v>
       </c>
       <c r="N152" s="5" t="n">
-        <v>9.720000000000001</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="153">
@@ -10633,7 +10629,7 @@
         <v>0</v>
       </c>
       <c r="N153" s="5" t="n">
-        <v>6.41</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="154">
@@ -10693,7 +10689,7 @@
         <v>0</v>
       </c>
       <c r="N154" s="5" t="n">
-        <v>6.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="155">
@@ -10753,7 +10749,7 @@
         <v>1</v>
       </c>
       <c r="N155" s="5" t="n">
-        <v>23.63</v>
+        <v>23.48</v>
       </c>
     </row>
     <row r="156">
@@ -10813,7 +10809,7 @@
         <v>1</v>
       </c>
       <c r="N156" s="5" t="n">
-        <v>18.49</v>
+        <v>19.95</v>
       </c>
     </row>
     <row r="157">
@@ -10873,7 +10869,7 @@
         <v>1</v>
       </c>
       <c r="N157" s="5" t="n">
-        <v>19.6</v>
+        <v>19.63</v>
       </c>
     </row>
     <row r="158">
@@ -10933,7 +10929,7 @@
         <v>1</v>
       </c>
       <c r="N158" s="5" t="n">
-        <v>25.42</v>
+        <v>26.97</v>
       </c>
     </row>
     <row r="159">
@@ -10993,7 +10989,7 @@
         <v>1</v>
       </c>
       <c r="N159" s="5" t="n">
-        <v>20.66</v>
+        <v>21.77</v>
       </c>
     </row>
     <row r="160">
@@ -11053,7 +11049,7 @@
         <v>1</v>
       </c>
       <c r="N160" s="5" t="n">
-        <v>21.13</v>
+        <v>22.16</v>
       </c>
     </row>
     <row r="161">
@@ -11092,11 +11088,11 @@
       </c>
       <c r="H161" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I161" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J161" s="5" t="b">
         <v>1</v>
@@ -11107,13 +11103,13 @@
         </is>
       </c>
       <c r="L161" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M161" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N161" s="5" t="n">
-        <v>8.56</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="162">
@@ -11173,7 +11169,7 @@
         <v>1</v>
       </c>
       <c r="N162" s="5" t="n">
-        <v>22.24</v>
+        <v>20.13</v>
       </c>
     </row>
     <row r="163">
@@ -11233,7 +11229,7 @@
         <v>1</v>
       </c>
       <c r="N163" s="5" t="n">
-        <v>19.91</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="164">
@@ -11293,7 +11289,7 @@
         <v>1</v>
       </c>
       <c r="N164" s="5" t="n">
-        <v>25.45</v>
+        <v>29.87</v>
       </c>
     </row>
     <row r="165">
@@ -11353,7 +11349,7 @@
         <v>1</v>
       </c>
       <c r="N165" s="5" t="n">
-        <v>23.82</v>
+        <v>27.17</v>
       </c>
     </row>
     <row r="166">
@@ -11413,7 +11409,7 @@
         <v>1</v>
       </c>
       <c r="N166" s="5" t="n">
-        <v>27.44</v>
+        <v>29</v>
       </c>
     </row>
     <row r="167">
@@ -11473,7 +11469,7 @@
         <v>1</v>
       </c>
       <c r="N167" s="5" t="n">
-        <v>21.06</v>
+        <v>21.58</v>
       </c>
     </row>
     <row r="168">
@@ -11533,7 +11529,7 @@
         <v>1</v>
       </c>
       <c r="N168" s="5" t="n">
-        <v>21.72</v>
+        <v>24.25</v>
       </c>
     </row>
     <row r="169">
@@ -11593,7 +11589,7 @@
         <v>1</v>
       </c>
       <c r="N169" s="5" t="n">
-        <v>22.4</v>
+        <v>22.41</v>
       </c>
     </row>
     <row r="170">
@@ -11632,28 +11628,28 @@
       </c>
       <c r="H170" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I170" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J170" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K170" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L170" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M170" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N170" s="5" t="n">
-        <v>23.12</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="171">
@@ -11690,30 +11686,26 @@
           <t>cross_kg</t>
         </is>
       </c>
-      <c r="H171" s="5" t="inlineStr">
-        <is>
-          <t>cross_kg</t>
-        </is>
-      </c>
+      <c r="H171" s="5" t="n"/>
       <c r="I171" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J171" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K171" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>exception: 'str' object has no attribute 'get'</t>
         </is>
       </c>
       <c r="L171" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M171" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N171" s="5" t="n">
-        <v>30.22</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="172">
@@ -11773,7 +11765,7 @@
         <v>1</v>
       </c>
       <c r="N172" s="5" t="n">
-        <v>22.92</v>
+        <v>34.68</v>
       </c>
     </row>
     <row r="173">
@@ -11833,7 +11825,7 @@
         <v>1</v>
       </c>
       <c r="N173" s="5" t="n">
-        <v>26.53</v>
+        <v>22.78</v>
       </c>
     </row>
     <row r="174">
@@ -11893,7 +11885,7 @@
         <v>1</v>
       </c>
       <c r="N174" s="5" t="n">
-        <v>24.27</v>
+        <v>23.27</v>
       </c>
     </row>
     <row r="175">
@@ -11953,7 +11945,7 @@
         <v>1</v>
       </c>
       <c r="N175" s="5" t="n">
-        <v>23.24</v>
+        <v>20.22</v>
       </c>
     </row>
     <row r="176">
@@ -12013,7 +12005,7 @@
         <v>0</v>
       </c>
       <c r="N176" s="5" t="n">
-        <v>23.03</v>
+        <v>19.08</v>
       </c>
     </row>
     <row r="177">
@@ -12073,7 +12065,7 @@
         <v>1</v>
       </c>
       <c r="N177" s="5" t="n">
-        <v>27.4</v>
+        <v>23.63</v>
       </c>
     </row>
     <row r="178">
@@ -12133,7 +12125,7 @@
         <v>0</v>
       </c>
       <c r="N178" s="5" t="n">
-        <v>23.6</v>
+        <v>20.28</v>
       </c>
     </row>
     <row r="179">
@@ -12193,7 +12185,7 @@
         <v>1</v>
       </c>
       <c r="N179" s="5" t="n">
-        <v>21.55</v>
+        <v>25.67</v>
       </c>
     </row>
     <row r="180">
@@ -12253,7 +12245,7 @@
         <v>1</v>
       </c>
       <c r="N180" s="5" t="n">
-        <v>22.25</v>
+        <v>18.81</v>
       </c>
     </row>
     <row r="181">
@@ -12313,7 +12305,7 @@
         <v>1</v>
       </c>
       <c r="N181" s="5" t="n">
-        <v>23.78</v>
+        <v>21.04</v>
       </c>
     </row>
     <row r="182">
@@ -12350,30 +12342,26 @@
           <t>cross_kg</t>
         </is>
       </c>
-      <c r="H182" s="5" t="inlineStr">
-        <is>
-          <t>cross_kg</t>
-        </is>
-      </c>
+      <c r="H182" s="5" t="n"/>
       <c r="I182" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J182" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K182" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>exception: 'str' object has no attribute 'get'</t>
         </is>
       </c>
       <c r="L182" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M182" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N182" s="5" t="n">
-        <v>32.93</v>
+        <v>21.06</v>
       </c>
     </row>
     <row r="183">
@@ -12433,7 +12421,7 @@
         <v>1</v>
       </c>
       <c r="N183" s="5" t="n">
-        <v>29.72</v>
+        <v>27.22</v>
       </c>
     </row>
     <row r="184">
@@ -12493,7 +12481,7 @@
         <v>1</v>
       </c>
       <c r="N184" s="5" t="n">
-        <v>23.95</v>
+        <v>22.12</v>
       </c>
     </row>
     <row r="185">
@@ -12553,7 +12541,7 @@
         <v>1</v>
       </c>
       <c r="N185" s="5" t="n">
-        <v>26.67</v>
+        <v>25.05</v>
       </c>
     </row>
     <row r="186">
@@ -12613,7 +12601,7 @@
         <v>1</v>
       </c>
       <c r="N186" s="5" t="n">
-        <v>24.51</v>
+        <v>24.81</v>
       </c>
     </row>
     <row r="187">
@@ -12673,7 +12661,7 @@
         <v>1</v>
       </c>
       <c r="N187" s="5" t="n">
-        <v>23.05</v>
+        <v>22.47</v>
       </c>
     </row>
     <row r="188">
@@ -12733,7 +12721,7 @@
         <v>0</v>
       </c>
       <c r="N188" s="5" t="n">
-        <v>22.14</v>
+        <v>21.04</v>
       </c>
     </row>
     <row r="189">
@@ -12793,7 +12781,7 @@
         <v>1</v>
       </c>
       <c r="N189" s="5" t="n">
-        <v>29.66</v>
+        <v>26.46</v>
       </c>
     </row>
     <row r="190">
@@ -12853,7 +12841,7 @@
         <v>0</v>
       </c>
       <c r="N190" s="5" t="n">
-        <v>23.48</v>
+        <v>22.42</v>
       </c>
     </row>
     <row r="191">
@@ -12913,7 +12901,7 @@
         <v>1</v>
       </c>
       <c r="N191" s="5" t="n">
-        <v>21.09</v>
+        <v>20.11</v>
       </c>
     </row>
     <row r="192">
@@ -12973,7 +12961,7 @@
         <v>1</v>
       </c>
       <c r="N192" s="5" t="n">
-        <v>21.74</v>
+        <v>20.92</v>
       </c>
     </row>
     <row r="193">
@@ -13033,7 +13021,7 @@
         <v>1</v>
       </c>
       <c r="N193" s="5" t="n">
-        <v>21.32</v>
+        <v>20.63</v>
       </c>
     </row>
     <row r="194">
@@ -13093,7 +13081,7 @@
         <v>1</v>
       </c>
       <c r="N194" s="5" t="n">
-        <v>21.96</v>
+        <v>21.65</v>
       </c>
     </row>
     <row r="195">
@@ -13153,7 +13141,7 @@
         <v>1</v>
       </c>
       <c r="N195" s="5" t="n">
-        <v>25.37</v>
+        <v>22.11</v>
       </c>
     </row>
     <row r="196">
@@ -13213,7 +13201,7 @@
         <v>1</v>
       </c>
       <c r="N196" s="5" t="n">
-        <v>21.84</v>
+        <v>21.87</v>
       </c>
     </row>
     <row r="197">
@@ -13273,7 +13261,7 @@
         <v>1</v>
       </c>
       <c r="N197" s="5" t="n">
-        <v>22.53</v>
+        <v>20.93</v>
       </c>
     </row>
     <row r="198">
@@ -13333,7 +13321,7 @@
         <v>1</v>
       </c>
       <c r="N198" s="5" t="n">
-        <v>23.86</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="199">
@@ -13393,7 +13381,7 @@
         <v>1</v>
       </c>
       <c r="N199" s="5" t="n">
-        <v>22.38</v>
+        <v>22.44</v>
       </c>
     </row>
     <row r="200">
@@ -13449,7 +13437,7 @@
       <c r="L200" s="5" t="n"/>
       <c r="M200" s="5" t="n"/>
       <c r="N200" s="5" t="n">
-        <v>29.46</v>
+        <v>28.51</v>
       </c>
     </row>
     <row r="201">
@@ -13505,7 +13493,7 @@
       <c r="L201" s="5" t="n"/>
       <c r="M201" s="5" t="n"/>
       <c r="N201" s="5" t="n">
-        <v>28.27</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="202">
@@ -13561,7 +13549,7 @@
       <c r="L202" s="5" t="n"/>
       <c r="M202" s="5" t="n"/>
       <c r="N202" s="5" t="n">
-        <v>10.04</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="203">
@@ -13621,7 +13609,7 @@
         <v>0</v>
       </c>
       <c r="N203" s="5" t="n">
-        <v>30.89</v>
+        <v>27.56</v>
       </c>
     </row>
     <row r="204">
@@ -13681,7 +13669,7 @@
         <v>0</v>
       </c>
       <c r="N204" s="5" t="n">
-        <v>39.53</v>
+        <v>35.57</v>
       </c>
     </row>
     <row r="205">
@@ -13720,18 +13708,18 @@
       </c>
       <c r="H205" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I205" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J205" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K205" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L205" s="5" t="b">
@@ -13741,7 +13729,7 @@
         <v>0</v>
       </c>
       <c r="N205" s="5" t="n">
-        <v>23.83</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="206">
@@ -13780,7 +13768,7 @@
       </c>
       <c r="H206" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I206" s="5" t="b">
@@ -13791,7 +13779,7 @@
       </c>
       <c r="K206" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>sparql_build_failure</t>
         </is>
       </c>
       <c r="L206" s="5" t="b">
@@ -13801,7 +13789,7 @@
         <v>0</v>
       </c>
       <c r="N206" s="5" t="n">
-        <v>28.54</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="207">
@@ -13840,28 +13828,28 @@
       </c>
       <c r="H207" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I207" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J207" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K207" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L207" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M207" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N207" s="5" t="n">
-        <v>13.49</v>
+        <v>21.76</v>
       </c>
     </row>
     <row r="208">
@@ -13900,28 +13888,28 @@
       </c>
       <c r="H208" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I208" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J208" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K208" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L208" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M208" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N208" s="5" t="n">
-        <v>12.42</v>
+        <v>21.57</v>
       </c>
     </row>
     <row r="209">
@@ -13981,7 +13969,7 @@
         <v>0.6667</v>
       </c>
       <c r="N209" s="5" t="n">
-        <v>37.96</v>
+        <v>34.54</v>
       </c>
     </row>
     <row r="210">
@@ -14041,7 +14029,7 @@
         <v>0.6667</v>
       </c>
       <c r="N210" s="5" t="n">
-        <v>34.66</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="211">
@@ -14101,7 +14089,7 @@
         <v>0.6667</v>
       </c>
       <c r="N211" s="5" t="n">
-        <v>35.55</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="212">
@@ -14157,7 +14145,7 @@
       <c r="L212" s="5" t="n"/>
       <c r="M212" s="5" t="n"/>
       <c r="N212" s="5" t="n">
-        <v>19.56</v>
+        <v>11.84</v>
       </c>
     </row>
     <row r="213">
@@ -14213,7 +14201,7 @@
       <c r="L213" s="5" t="n"/>
       <c r="M213" s="5" t="n"/>
       <c r="N213" s="5" t="n">
-        <v>14.43</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="214">
@@ -14263,13 +14251,13 @@
       </c>
       <c r="K214" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L214" s="5" t="n"/>
       <c r="M214" s="5" t="n"/>
       <c r="N214" s="5" t="n">
-        <v>34.11</v>
+        <v>30.18</v>
       </c>
     </row>
     <row r="215">
@@ -14325,7 +14313,7 @@
       <c r="L215" s="5" t="n"/>
       <c r="M215" s="5" t="n"/>
       <c r="N215" s="5" t="n">
-        <v>28.18</v>
+        <v>23.79</v>
       </c>
     </row>
     <row r="216">
@@ -14375,13 +14363,13 @@
       </c>
       <c r="K216" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L216" s="5" t="n"/>
       <c r="M216" s="5" t="n"/>
       <c r="N216" s="5" t="n">
-        <v>30.04</v>
+        <v>28.35</v>
       </c>
     </row>
     <row r="217">
@@ -14437,7 +14425,7 @@
       <c r="L217" s="5" t="n"/>
       <c r="M217" s="5" t="n"/>
       <c r="N217" s="5" t="n">
-        <v>9.83</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="218">
@@ -14497,7 +14485,7 @@
         <v>1</v>
       </c>
       <c r="N218" s="5" t="n">
-        <v>13.68</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="219">
@@ -14557,7 +14545,7 @@
         <v>1</v>
       </c>
       <c r="N219" s="5" t="n">
-        <v>15.03</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="220">
@@ -14603,21 +14591,21 @@
         <v>1</v>
       </c>
       <c r="J220" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K220" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L220" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M220" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N220" s="5" t="n">
-        <v>14.03</v>
+        <v>13.17</v>
       </c>
     </row>
     <row r="221">
@@ -14677,7 +14665,7 @@
         <v>1</v>
       </c>
       <c r="N221" s="5" t="n">
-        <v>25.38</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="222">
@@ -14737,7 +14725,7 @@
         <v>1</v>
       </c>
       <c r="N222" s="5" t="n">
-        <v>14.33</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="223">
@@ -14797,7 +14785,7 @@
         <v>1</v>
       </c>
       <c r="N223" s="5" t="n">
-        <v>14.89</v>
+        <v>17.47</v>
       </c>
     </row>
     <row r="224">
@@ -14857,7 +14845,7 @@
         <v>1</v>
       </c>
       <c r="N224" s="5" t="n">
-        <v>14.26</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="225">
@@ -14917,7 +14905,7 @@
         <v>1</v>
       </c>
       <c r="N225" s="5" t="n">
-        <v>14.9</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="226">
@@ -14977,7 +14965,7 @@
         <v>1</v>
       </c>
       <c r="N226" s="5" t="n">
-        <v>15.15</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="227">
@@ -15031,13 +15019,13 @@
         </is>
       </c>
       <c r="L227" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M227" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N227" s="5" t="n">
-        <v>14.79</v>
+        <v>12.18</v>
       </c>
     </row>
     <row r="228">
@@ -15091,13 +15079,13 @@
         </is>
       </c>
       <c r="L228" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M228" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N228" s="5" t="n">
-        <v>15.94</v>
+        <v>13.35</v>
       </c>
     </row>
     <row r="229">
@@ -15151,13 +15139,13 @@
         </is>
       </c>
       <c r="L229" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M229" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N229" s="5" t="n">
-        <v>14.43</v>
+        <v>13.13</v>
       </c>
     </row>
     <row r="230">
@@ -15196,11 +15184,11 @@
       </c>
       <c r="H230" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I230" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J230" s="5" t="b">
         <v>1</v>
@@ -15211,13 +15199,13 @@
         </is>
       </c>
       <c r="L230" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M230" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N230" s="5" t="n">
-        <v>49.27</v>
+        <v>12.57</v>
       </c>
     </row>
     <row r="231">
@@ -15271,13 +15259,13 @@
         </is>
       </c>
       <c r="L231" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M231" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N231" s="5" t="n">
-        <v>19.68</v>
+        <v>16.18</v>
       </c>
     </row>
     <row r="232">
@@ -15331,13 +15319,13 @@
         </is>
       </c>
       <c r="L232" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M232" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N232" s="5" t="n">
-        <v>29.11</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="233">
@@ -15391,13 +15379,13 @@
         </is>
       </c>
       <c r="L233" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M233" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N233" s="5" t="n">
-        <v>15.36</v>
+        <v>11.81</v>
       </c>
     </row>
     <row r="234">
@@ -15451,13 +15439,13 @@
         </is>
       </c>
       <c r="L234" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M234" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N234" s="5" t="n">
-        <v>15.81</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="235">
@@ -15511,13 +15499,13 @@
         </is>
       </c>
       <c r="L235" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M235" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N235" s="5" t="n">
-        <v>14.84</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="236">
@@ -15563,21 +15551,21 @@
         <v>1</v>
       </c>
       <c r="J236" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K236" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L236" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M236" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N236" s="5" t="n">
-        <v>24.97</v>
+        <v>19.86</v>
       </c>
     </row>
     <row r="237">
@@ -15631,13 +15619,13 @@
         </is>
       </c>
       <c r="L237" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M237" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N237" s="5" t="n">
-        <v>20.01</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="238">
@@ -15691,13 +15679,13 @@
         </is>
       </c>
       <c r="L238" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M238" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N238" s="5" t="n">
-        <v>26.79</v>
+        <v>14.12</v>
       </c>
     </row>
     <row r="239">
@@ -15743,21 +15731,21 @@
         <v>1</v>
       </c>
       <c r="J239" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K239" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L239" s="5" t="b">
         <v>0</v>
       </c>
       <c r="M239" s="5" t="n">
-        <v>0</v>
+        <v>0.7692</v>
       </c>
       <c r="N239" s="5" t="n">
-        <v>16.72</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="240">
@@ -15803,21 +15791,21 @@
         <v>1</v>
       </c>
       <c r="J240" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K240" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L240" s="5" t="b">
         <v>0</v>
       </c>
       <c r="M240" s="5" t="n">
-        <v>0</v>
+        <v>0.7692</v>
       </c>
       <c r="N240" s="5" t="n">
-        <v>14.44</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="241">
@@ -15863,21 +15851,21 @@
         <v>1</v>
       </c>
       <c r="J241" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K241" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L241" s="5" t="b">
         <v>0</v>
       </c>
       <c r="M241" s="5" t="n">
-        <v>0</v>
+        <v>0.7692</v>
       </c>
       <c r="N241" s="5" t="n">
-        <v>15.34</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="242">
@@ -15916,18 +15904,18 @@
       </c>
       <c r="H242" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I242" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J242" s="5" t="b">
         <v>1</v>
       </c>
       <c r="K242" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L242" s="5" t="b">
@@ -15937,7 +15925,7 @@
         <v>0</v>
       </c>
       <c r="N242" s="5" t="n">
-        <v>21.7</v>
+        <v>36.93</v>
       </c>
     </row>
     <row r="243">
@@ -15991,13 +15979,13 @@
         </is>
       </c>
       <c r="L243" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M243" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N243" s="5" t="n">
-        <v>16.61</v>
+        <v>13.09</v>
       </c>
     </row>
     <row r="244">
@@ -16051,13 +16039,13 @@
         </is>
       </c>
       <c r="L244" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M244" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N244" s="5" t="n">
-        <v>17.48</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="245">
@@ -16111,13 +16099,13 @@
         </is>
       </c>
       <c r="L245" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M245" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N245" s="5" t="n">
-        <v>15.38</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="246">
@@ -16171,13 +16159,13 @@
         </is>
       </c>
       <c r="L246" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M246" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N246" s="5" t="n">
-        <v>15.77</v>
+        <v>14.03</v>
       </c>
     </row>
     <row r="247">
@@ -16216,28 +16204,28 @@
       </c>
       <c r="H247" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I247" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J247" s="5" t="b">
         <v>1</v>
       </c>
       <c r="K247" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L247" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M247" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N247" s="5" t="n">
-        <v>55.48</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="248">
@@ -16276,11 +16264,11 @@
       </c>
       <c r="H248" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I248" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J248" s="5" t="b">
         <v>1</v>
@@ -16293,7 +16281,7 @@
       <c r="L248" s="5" t="n"/>
       <c r="M248" s="5" t="n"/>
       <c r="N248" s="5" t="n">
-        <v>17.29</v>
+        <v>37.75</v>
       </c>
     </row>
     <row r="249">
@@ -16332,14 +16320,14 @@
       </c>
       <c r="H249" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I249" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J249" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K249" s="5" t="inlineStr">
         <is>
@@ -16349,7 +16337,7 @@
       <c r="L249" s="5" t="n"/>
       <c r="M249" s="5" t="n"/>
       <c r="N249" s="5" t="n">
-        <v>30.83</v>
+        <v>12.45</v>
       </c>
     </row>
     <row r="250">
@@ -16405,7 +16393,7 @@
       <c r="L250" s="5" t="n"/>
       <c r="M250" s="5" t="n"/>
       <c r="N250" s="5" t="n">
-        <v>15.03</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="251">
@@ -16462,10 +16450,10 @@
         <v>0</v>
       </c>
       <c r="M251" s="5" t="n">
-        <v>0</v>
+        <v>0.7368</v>
       </c>
       <c r="N251" s="5" t="n">
-        <v>13.62</v>
+        <v>13.55</v>
       </c>
     </row>
     <row r="252">
@@ -16522,10 +16510,10 @@
         <v>0</v>
       </c>
       <c r="M252" s="5" t="n">
-        <v>0.2353</v>
+        <v>0.7368</v>
       </c>
       <c r="N252" s="5" t="n">
-        <v>19.78</v>
+        <v>15.41</v>
       </c>
     </row>
     <row r="253">
@@ -16582,10 +16570,10 @@
         <v>0</v>
       </c>
       <c r="M253" s="5" t="n">
-        <v>0</v>
+        <v>0.7368</v>
       </c>
       <c r="N253" s="5" t="n">
-        <v>12.94</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="254">
@@ -16624,18 +16612,18 @@
       </c>
       <c r="H254" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I254" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J254" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K254" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>generation_failure</t>
         </is>
       </c>
       <c r="L254" s="5" t="b">
@@ -16645,7 +16633,7 @@
         <v>0</v>
       </c>
       <c r="N254" s="5" t="n">
-        <v>13.05</v>
+        <v>36.72</v>
       </c>
     </row>
     <row r="255">
@@ -16691,11 +16679,11 @@
         <v>1</v>
       </c>
       <c r="J255" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K255" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L255" s="5" t="b">
@@ -16705,7 +16693,7 @@
         <v>0</v>
       </c>
       <c r="N255" s="5" t="n">
-        <v>16.76</v>
+        <v>12.97</v>
       </c>
     </row>
     <row r="256">
@@ -16759,13 +16747,13 @@
         </is>
       </c>
       <c r="L256" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M256" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N256" s="5" t="n">
-        <v>16.15</v>
+        <v>13.54</v>
       </c>
     </row>
     <row r="257">
@@ -16825,7 +16813,7 @@
         <v>0.5</v>
       </c>
       <c r="N257" s="5" t="n">
-        <v>12.2</v>
+        <v>12.53</v>
       </c>
     </row>
     <row r="258">
@@ -16885,7 +16873,7 @@
         <v>0.5</v>
       </c>
       <c r="N258" s="5" t="n">
-        <v>12.9</v>
+        <v>10.95</v>
       </c>
     </row>
     <row r="259">
@@ -16931,11 +16919,11 @@
         <v>1</v>
       </c>
       <c r="J259" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K259" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L259" s="5" t="b">
@@ -16945,7 +16933,7 @@
         <v>0</v>
       </c>
       <c r="N259" s="5" t="n">
-        <v>10.16</v>
+        <v>11.79</v>
       </c>
     </row>
     <row r="260">
@@ -16999,13 +16987,13 @@
         </is>
       </c>
       <c r="L260" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M260" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N260" s="5" t="n">
-        <v>14.16</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="261">
@@ -17055,7 +17043,7 @@
       </c>
       <c r="K261" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L261" s="5" t="b">
@@ -17065,7 +17053,7 @@
         <v>0</v>
       </c>
       <c r="N261" s="5" t="n">
-        <v>14.49</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="262">
@@ -17119,13 +17107,13 @@
         </is>
       </c>
       <c r="L262" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M262" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N262" s="5" t="n">
-        <v>13.31</v>
+        <v>12.93</v>
       </c>
     </row>
     <row r="263">
@@ -17179,13 +17167,13 @@
         </is>
       </c>
       <c r="L263" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M263" s="5" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="N263" s="5" t="n">
-        <v>14.24</v>
+        <v>22.31</v>
       </c>
     </row>
     <row r="264">
@@ -17239,13 +17227,13 @@
         </is>
       </c>
       <c r="L264" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M264" s="5" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="N264" s="5" t="n">
-        <v>14.2</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="265">
@@ -17299,13 +17287,13 @@
         </is>
       </c>
       <c r="L265" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M265" s="5" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="N265" s="5" t="n">
-        <v>14.99</v>
+        <v>21.77</v>
       </c>
     </row>
     <row r="266">
@@ -17359,13 +17347,13 @@
         </is>
       </c>
       <c r="L266" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M266" s="5" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="N266" s="5" t="n">
-        <v>15.54</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="267">
@@ -17419,13 +17407,13 @@
         </is>
       </c>
       <c r="L267" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M267" s="5" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="N267" s="5" t="n">
-        <v>15.62</v>
+        <v>11.59</v>
       </c>
     </row>
     <row r="268">
@@ -17479,13 +17467,13 @@
         </is>
       </c>
       <c r="L268" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M268" s="5" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="N268" s="5" t="n">
-        <v>14.09</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="269">
@@ -17524,28 +17512,28 @@
       </c>
       <c r="H269" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I269" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J269" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K269" s="5" t="inlineStr">
         <is>
-          <t>generation_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L269" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M269" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N269" s="5" t="n">
-        <v>48.95</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="270">
@@ -17599,13 +17587,13 @@
         </is>
       </c>
       <c r="L270" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M270" s="5" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="N270" s="5" t="n">
-        <v>14.42</v>
+        <v>11.53</v>
       </c>
     </row>
     <row r="271">
@@ -17659,13 +17647,13 @@
         </is>
       </c>
       <c r="L271" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M271" s="5" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="N271" s="5" t="n">
-        <v>13.52</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="272">
@@ -17719,7 +17707,7 @@
       <c r="L272" s="5" t="n"/>
       <c r="M272" s="5" t="n"/>
       <c r="N272" s="5" t="n">
-        <v>8.970000000000001</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="273">
@@ -17773,7 +17761,7 @@
       <c r="L273" s="5" t="n"/>
       <c r="M273" s="5" t="n"/>
       <c r="N273" s="5" t="n">
-        <v>9.85</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="274">
@@ -17827,7 +17815,7 @@
       <c r="L274" s="5" t="n"/>
       <c r="M274" s="5" t="n"/>
       <c r="N274" s="5" t="n">
-        <v>9.539999999999999</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="275">
@@ -17881,7 +17869,7 @@
       <c r="L275" s="5" t="n"/>
       <c r="M275" s="5" t="n"/>
       <c r="N275" s="5" t="n">
-        <v>8.59</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="276">
@@ -17935,7 +17923,7 @@
       <c r="L276" s="5" t="n"/>
       <c r="M276" s="5" t="n"/>
       <c r="N276" s="5" t="n">
-        <v>9.84</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="277">
@@ -17989,7 +17977,7 @@
       <c r="L277" s="5" t="n"/>
       <c r="M277" s="5" t="n"/>
       <c r="N277" s="5" t="n">
-        <v>7.07</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="278">
@@ -18043,7 +18031,7 @@
       <c r="L278" s="5" t="n"/>
       <c r="M278" s="5" t="n"/>
       <c r="N278" s="5" t="n">
-        <v>8.68</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="279">
@@ -18097,7 +18085,7 @@
       <c r="L279" s="5" t="n"/>
       <c r="M279" s="5" t="n"/>
       <c r="N279" s="5" t="n">
-        <v>9.109999999999999</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="280">
@@ -18151,7 +18139,7 @@
       <c r="L280" s="5" t="n"/>
       <c r="M280" s="5" t="n"/>
       <c r="N280" s="5" t="n">
-        <v>8.539999999999999</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="281">
@@ -18211,7 +18199,7 @@
         <v>1</v>
       </c>
       <c r="N281" s="5" t="n">
-        <v>8.59</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="282">
@@ -18271,7 +18259,7 @@
         <v>1</v>
       </c>
       <c r="N282" s="5" t="n">
-        <v>9.09</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="283">
@@ -18331,7 +18319,7 @@
         <v>1</v>
       </c>
       <c r="N283" s="5" t="n">
-        <v>4.83</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="284">
@@ -18391,7 +18379,7 @@
         <v>1</v>
       </c>
       <c r="N284" s="5" t="n">
-        <v>8.93</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="285">
@@ -18451,7 +18439,7 @@
         <v>0</v>
       </c>
       <c r="N285" s="5" t="n">
-        <v>9.199999999999999</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="286">
@@ -18511,7 +18499,7 @@
         <v>0</v>
       </c>
       <c r="N286" s="5" t="n">
-        <v>5</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="287">
@@ -18567,7 +18555,7 @@
       <c r="L287" s="5" t="n"/>
       <c r="M287" s="5" t="n"/>
       <c r="N287" s="5" t="n">
-        <v>8.76</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="288">
@@ -18623,7 +18611,7 @@
       <c r="L288" s="5" t="n"/>
       <c r="M288" s="5" t="n"/>
       <c r="N288" s="5" t="n">
-        <v>8.43</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="289">
@@ -18683,7 +18671,7 @@
         <v>1</v>
       </c>
       <c r="N289" s="5" t="n">
-        <v>4.35</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="290">
@@ -18743,7 +18731,7 @@
         <v>1</v>
       </c>
       <c r="N290" s="5" t="n">
-        <v>9.109999999999999</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="291">
@@ -18803,7 +18791,7 @@
         <v>1</v>
       </c>
       <c r="N291" s="5" t="n">
-        <v>10.09</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="292">
@@ -18849,17 +18837,21 @@
         <v>1</v>
       </c>
       <c r="J292" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K292" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L292" s="5" t="n"/>
-      <c r="M292" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L292" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M292" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N292" s="5" t="n">
-        <v>6.24</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="293">
@@ -18919,7 +18911,7 @@
         <v>1</v>
       </c>
       <c r="N293" s="5" t="n">
-        <v>23.41</v>
+        <v>21.33</v>
       </c>
     </row>
     <row r="294">
@@ -18979,7 +18971,7 @@
         <v>1</v>
       </c>
       <c r="N294" s="5" t="n">
-        <v>25.76</v>
+        <v>21.07</v>
       </c>
     </row>
     <row r="295">
@@ -19018,7 +19010,7 @@
       </c>
       <c r="H295" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I295" s="5" t="b">
@@ -19033,13 +19025,13 @@
         </is>
       </c>
       <c r="L295" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M295" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N295" s="5" t="n">
-        <v>8.130000000000001</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="296">
@@ -19099,7 +19091,7 @@
         <v>1</v>
       </c>
       <c r="N296" s="5" t="n">
-        <v>37.12</v>
+        <v>34.24</v>
       </c>
     </row>
     <row r="297">
@@ -19159,7 +19151,7 @@
         <v>0.2</v>
       </c>
       <c r="N297" s="5" t="n">
-        <v>21.61</v>
+        <v>24.74</v>
       </c>
     </row>
     <row r="298">
@@ -19198,28 +19190,28 @@
       </c>
       <c r="H298" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I298" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J298" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K298" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L298" s="5" t="b">
         <v>0</v>
       </c>
       <c r="M298" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N298" s="5" t="n">
-        <v>19.69</v>
+        <v>39.64</v>
       </c>
     </row>
     <row r="299">
@@ -19279,7 +19271,7 @@
         <v>1</v>
       </c>
       <c r="N299" s="5" t="n">
-        <v>29.51</v>
+        <v>27.13</v>
       </c>
     </row>
     <row r="300">
@@ -19339,7 +19331,7 @@
         <v>1</v>
       </c>
       <c r="N300" s="5" t="n">
-        <v>31.76</v>
+        <v>29.42</v>
       </c>
     </row>
     <row r="301">
@@ -19399,7 +19391,7 @@
         <v>1</v>
       </c>
       <c r="N301" s="5" t="n">
-        <v>30.67</v>
+        <v>32.16</v>
       </c>
     </row>
     <row r="302">
@@ -19459,7 +19451,7 @@
         <v>1</v>
       </c>
       <c r="N302" s="5" t="n">
-        <v>23.84</v>
+        <v>26.34</v>
       </c>
     </row>
     <row r="303">
@@ -19519,7 +19511,7 @@
         <v>1</v>
       </c>
       <c r="N303" s="5" t="n">
-        <v>23.89</v>
+        <v>24.87</v>
       </c>
     </row>
     <row r="304">
@@ -19579,7 +19571,7 @@
         <v>1</v>
       </c>
       <c r="N304" s="5" t="n">
-        <v>23.64</v>
+        <v>24.72</v>
       </c>
     </row>
     <row r="305">
@@ -19639,7 +19631,7 @@
         <v>1</v>
       </c>
       <c r="N305" s="5" t="n">
-        <v>23.6</v>
+        <v>22.06</v>
       </c>
     </row>
     <row r="306">
@@ -19699,7 +19691,7 @@
         <v>1</v>
       </c>
       <c r="N306" s="5" t="n">
-        <v>25.81</v>
+        <v>21.92</v>
       </c>
     </row>
     <row r="307">
@@ -19745,11 +19737,11 @@
         <v>1</v>
       </c>
       <c r="J307" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K307" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L307" s="5" t="b">
@@ -19759,7 +19751,7 @@
         <v>0</v>
       </c>
       <c r="N307" s="5" t="n">
-        <v>16.63</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="308">
@@ -19819,7 +19811,7 @@
         <v>0</v>
       </c>
       <c r="N308" s="5" t="n">
-        <v>8.65</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="309">
@@ -19879,7 +19871,7 @@
         <v>0</v>
       </c>
       <c r="N309" s="5" t="n">
-        <v>9.83</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="310">
@@ -19939,7 +19931,7 @@
         <v>0</v>
       </c>
       <c r="N310" s="5" t="n">
-        <v>5.49</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="311">
@@ -19999,7 +19991,7 @@
         <v>1</v>
       </c>
       <c r="N311" s="5" t="n">
-        <v>22.15</v>
+        <v>20.09</v>
       </c>
     </row>
     <row r="312">
@@ -20059,7 +20051,7 @@
         <v>1</v>
       </c>
       <c r="N312" s="5" t="n">
-        <v>26.44</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="313">
@@ -20119,7 +20111,7 @@
         <v>1</v>
       </c>
       <c r="N313" s="5" t="n">
-        <v>24.83</v>
+        <v>21.93</v>
       </c>
     </row>
     <row r="314">
@@ -20175,7 +20167,7 @@
       <c r="L314" s="5" t="n"/>
       <c r="M314" s="5" t="n"/>
       <c r="N314" s="5" t="n">
-        <v>16.94</v>
+        <v>14.53</v>
       </c>
     </row>
     <row r="315">
@@ -20231,7 +20223,7 @@
       <c r="L315" s="5" t="n"/>
       <c r="M315" s="5" t="n"/>
       <c r="N315" s="5" t="n">
-        <v>17.62</v>
+        <v>16.97</v>
       </c>
     </row>
     <row r="316">
@@ -20270,7 +20262,7 @@
       </c>
       <c r="H316" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I316" s="5" t="b">
@@ -20287,7 +20279,7 @@
       <c r="L316" s="5" t="n"/>
       <c r="M316" s="5" t="n"/>
       <c r="N316" s="5" t="n">
-        <v>9.890000000000001</v>
+        <v>18.95</v>
       </c>
     </row>
     <row r="317">
@@ -20347,7 +20339,7 @@
         <v>0.5</v>
       </c>
       <c r="N317" s="5" t="n">
-        <v>16.22</v>
+        <v>16.03</v>
       </c>
     </row>
     <row r="318">
@@ -20407,7 +20399,7 @@
         <v>0.5</v>
       </c>
       <c r="N318" s="5" t="n">
-        <v>18.05</v>
+        <v>17.29</v>
       </c>
     </row>
     <row r="319">
@@ -20457,17 +20449,17 @@
       </c>
       <c r="K319" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L319" s="5" t="b">
         <v>0</v>
       </c>
       <c r="M319" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N319" s="5" t="n">
-        <v>17.97</v>
+        <v>17.43</v>
       </c>
     </row>
     <row r="320">
@@ -20517,13 +20509,13 @@
       </c>
       <c r="K320" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L320" s="5" t="n"/>
       <c r="M320" s="5" t="n"/>
       <c r="N320" s="5" t="n">
-        <v>17.32</v>
+        <v>15.17</v>
       </c>
     </row>
     <row r="321">
@@ -20579,7 +20571,7 @@
       <c r="L321" s="5" t="n"/>
       <c r="M321" s="5" t="n"/>
       <c r="N321" s="5" t="n">
-        <v>18</v>
+        <v>15.73</v>
       </c>
     </row>
     <row r="322">
@@ -20635,7 +20627,7 @@
       <c r="L322" s="5" t="n"/>
       <c r="M322" s="5" t="n"/>
       <c r="N322" s="5" t="n">
-        <v>16.98</v>
+        <v>16.63</v>
       </c>
     </row>
     <row r="323">
@@ -20685,7 +20677,7 @@
       </c>
       <c r="K323" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L323" s="5" t="n"/>
@@ -20730,7 +20722,7 @@
       </c>
       <c r="H324" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I324" s="5" t="b">
@@ -20747,7 +20739,7 @@
       <c r="L324" s="5" t="n"/>
       <c r="M324" s="5" t="n"/>
       <c r="N324" s="5" t="n">
-        <v>10.37</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="325">
@@ -20803,7 +20795,7 @@
       <c r="L325" s="5" t="n"/>
       <c r="M325" s="5" t="n"/>
       <c r="N325" s="5" t="n">
-        <v>18.31</v>
+        <v>15.5</v>
       </c>
     </row>
   </sheetData>

--- a/NL2SPARQL_Evaluation_Results.xlsx
+++ b/NL2SPARQL_Evaluation_Results.xlsx
@@ -16579,7 +16579,7 @@
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_001</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B254" s="5" t="n">
@@ -16587,7 +16587,7 @@
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D254" s="5" t="inlineStr">
@@ -16612,34 +16612,34 @@
       </c>
       <c r="H254" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I254" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J254" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K254" s="5" t="inlineStr">
         <is>
-          <t>generation_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L254" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M254" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N254" s="5" t="n">
-        <v>36.72</v>
+        <v>22.31</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_001</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B255" s="5" t="n">
@@ -16647,7 +16647,7 @@
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D255" s="5" t="inlineStr">
@@ -16687,19 +16687,19 @@
         </is>
       </c>
       <c r="L255" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M255" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N255" s="5" t="n">
-        <v>12.97</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_001</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B256" s="5" t="n">
@@ -16707,7 +16707,7 @@
       </c>
       <c r="C256" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D256" s="5" t="inlineStr">
@@ -16753,13 +16753,13 @@
         <v>1</v>
       </c>
       <c r="N256" s="5" t="n">
-        <v>13.54</v>
+        <v>21.77</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_002</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B257" s="5" t="n">
@@ -16767,7 +16767,7 @@
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D257" s="5" t="inlineStr">
@@ -16807,19 +16807,19 @@
         </is>
       </c>
       <c r="L257" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M257" s="5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N257" s="5" t="n">
-        <v>12.53</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_002</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B258" s="5" t="n">
@@ -16827,7 +16827,7 @@
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
@@ -16867,19 +16867,19 @@
         </is>
       </c>
       <c r="L258" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M258" s="5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N258" s="5" t="n">
-        <v>10.95</v>
+        <v>11.59</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_002</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B259" s="5" t="n">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C259" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D259" s="5" t="inlineStr">
@@ -16927,19 +16927,19 @@
         </is>
       </c>
       <c r="L259" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M259" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N259" s="5" t="n">
-        <v>11.79</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_003</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B260" s="5" t="n">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D260" s="5" t="inlineStr">
@@ -16993,13 +16993,13 @@
         <v>1</v>
       </c>
       <c r="N260" s="5" t="n">
-        <v>12.25</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_003</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B261" s="5" t="n">
@@ -17007,7 +17007,7 @@
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D261" s="5" t="inlineStr">
@@ -17039,27 +17039,27 @@
         <v>1</v>
       </c>
       <c r="J261" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K261" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L261" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M261" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N261" s="5" t="n">
-        <v>15.89</v>
+        <v>11.53</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_003</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B262" s="5" t="n">
@@ -17067,7 +17067,7 @@
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D262" s="5" t="inlineStr">
@@ -17113,27 +17113,25 @@
         <v>1</v>
       </c>
       <c r="N262" s="5" t="n">
-        <v>12.93</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B263" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C263" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D263" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D263" s="5" t="n">
+        <v/>
       </c>
       <c r="E263" s="5" t="inlineStr">
         <is>
@@ -17147,53 +17145,47 @@
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H263" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I263" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J263" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K263" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L263" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M263" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L263" s="5" t="n"/>
+      <c r="M263" s="5" t="n"/>
       <c r="N263" s="5" t="n">
-        <v>22.31</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B264" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D264" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D264" s="5" t="n">
+        <v/>
       </c>
       <c r="E264" s="5" t="inlineStr">
         <is>
@@ -17207,53 +17199,47 @@
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H264" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I264" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J264" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K264" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L264" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M264" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L264" s="5" t="n"/>
+      <c r="M264" s="5" t="n"/>
       <c r="N264" s="5" t="n">
-        <v>15.03</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B265" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D265" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="n">
+        <v/>
       </c>
       <c r="E265" s="5" t="inlineStr">
         <is>
@@ -17267,53 +17253,47 @@
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H265" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I265" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J265" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K265" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L265" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M265" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L265" s="5" t="n"/>
+      <c r="M265" s="5" t="n"/>
       <c r="N265" s="5" t="n">
-        <v>21.77</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B266" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D266" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D266" s="5" t="n">
+        <v/>
       </c>
       <c r="E266" s="5" t="inlineStr">
         <is>
@@ -17327,53 +17307,47 @@
       </c>
       <c r="G266" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H266" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I266" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J266" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K266" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L266" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M266" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L266" s="5" t="n"/>
+      <c r="M266" s="5" t="n"/>
       <c r="N266" s="5" t="n">
-        <v>17.2</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B267" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D267" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D267" s="5" t="n">
+        <v/>
       </c>
       <c r="E267" s="5" t="inlineStr">
         <is>
@@ -17387,53 +17361,47 @@
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H267" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I267" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J267" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K267" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L267" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M267" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L267" s="5" t="n"/>
+      <c r="M267" s="5" t="n"/>
       <c r="N267" s="5" t="n">
-        <v>11.59</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B268" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D268" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D268" s="5" t="n">
+        <v/>
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
@@ -17447,53 +17415,47 @@
       </c>
       <c r="G268" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H268" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I268" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J268" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K268" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L268" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M268" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>mapping_failure</t>
+        </is>
+      </c>
+      <c r="L268" s="5" t="n"/>
+      <c r="M268" s="5" t="n"/>
       <c r="N268" s="5" t="n">
-        <v>18.53</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B269" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D269" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="n">
+        <v/>
       </c>
       <c r="E269" s="5" t="inlineStr">
         <is>
@@ -17507,53 +17469,47 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I269" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J269" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K269" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L269" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M269" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L269" s="5" t="n"/>
+      <c r="M269" s="5" t="n"/>
       <c r="N269" s="5" t="n">
-        <v>12.31</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B270" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D270" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D270" s="5" t="n">
+        <v/>
       </c>
       <c r="E270" s="5" t="inlineStr">
         <is>
@@ -17567,53 +17523,47 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I270" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J270" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K270" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L270" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M270" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L270" s="5" t="n"/>
+      <c r="M270" s="5" t="n"/>
       <c r="N270" s="5" t="n">
-        <v>11.53</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B271" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D271" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="n">
+        <v/>
       </c>
       <c r="E271" s="5" t="inlineStr">
         <is>
@@ -17627,39 +17577,35 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I271" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J271" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K271" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L271" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M271" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L271" s="5" t="n"/>
+      <c r="M271" s="5" t="n"/>
       <c r="N271" s="5" t="n">
-        <v>12.22</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B272" s="5" t="n">
@@ -17667,11 +17613,13 @@
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D272" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D272" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
         <is>
@@ -17685,35 +17633,39 @@
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H272" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I272" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J272" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K272" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L272" s="5" t="n"/>
-      <c r="M272" s="5" t="n"/>
+      <c r="L272" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M272" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N272" s="5" t="n">
-        <v>6.87</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B273" s="5" t="n">
@@ -17721,11 +17673,13 @@
       </c>
       <c r="C273" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D273" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D273" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E273" s="5" t="inlineStr">
         <is>
@@ -17739,35 +17693,39 @@
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H273" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I273" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J273" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K273" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L273" s="5" t="n"/>
-      <c r="M273" s="5" t="n"/>
+      <c r="L273" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M273" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N273" s="5" t="n">
-        <v>7.12</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B274" s="5" t="n">
@@ -17775,11 +17733,13 @@
       </c>
       <c r="C274" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D274" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D274" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E274" s="5" t="inlineStr">
         <is>
@@ -17793,35 +17753,39 @@
       </c>
       <c r="G274" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H274" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I274" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J274" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K274" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L274" s="5" t="n"/>
-      <c r="M274" s="5" t="n"/>
+      <c r="L274" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M274" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N274" s="5" t="n">
-        <v>7.48</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B275" s="5" t="n">
@@ -17829,11 +17793,13 @@
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D275" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D275" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E275" s="5" t="inlineStr">
         <is>
@@ -17847,35 +17813,39 @@
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H275" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I275" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J275" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K275" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L275" s="5" t="n"/>
-      <c r="M275" s="5" t="n"/>
+      <c r="L275" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M275" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N275" s="5" t="n">
-        <v>6.99</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B276" s="5" t="n">
@@ -17883,11 +17853,13 @@
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D276" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D276" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
@@ -17901,35 +17873,39 @@
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H276" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I276" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J276" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K276" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L276" s="5" t="n"/>
-      <c r="M276" s="5" t="n"/>
+      <c r="L276" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M276" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N276" s="5" t="n">
-        <v>7.94</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B277" s="5" t="n">
@@ -17937,11 +17913,13 @@
       </c>
       <c r="C277" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D277" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D277" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E277" s="5" t="inlineStr">
         <is>
@@ -17955,7 +17933,7 @@
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H277" s="5" t="inlineStr">
@@ -17964,26 +17942,30 @@
         </is>
       </c>
       <c r="I277" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J277" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K277" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L277" s="5" t="n"/>
-      <c r="M277" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L277" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M277" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N277" s="5" t="n">
-        <v>6.59</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B278" s="5" t="n">
@@ -17991,34 +17973,36 @@
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D278" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="E278" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F278" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G278" s="5" t="inlineStr">
+        <is>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="H278" s="5" t="inlineStr">
+        <is>
           <t>out_of_scope</t>
         </is>
       </c>
-      <c r="D278" s="5" t="n">
-        <v/>
-      </c>
-      <c r="E278" s="5" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="F278" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G278" s="5" t="inlineStr">
-        <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="H278" s="5" t="inlineStr">
-        <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
       <c r="I278" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J278" s="5" t="b">
         <v>0</v>
@@ -18031,13 +18015,13 @@
       <c r="L278" s="5" t="n"/>
       <c r="M278" s="5" t="n"/>
       <c r="N278" s="5" t="n">
-        <v>14.02</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B279" s="5" t="n">
@@ -18045,34 +18029,36 @@
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D279" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="E279" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F279" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G279" s="5" t="inlineStr">
+        <is>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="H279" s="5" t="inlineStr">
+        <is>
           <t>out_of_scope</t>
         </is>
       </c>
-      <c r="D279" s="5" t="n">
-        <v/>
-      </c>
-      <c r="E279" s="5" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="F279" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G279" s="5" t="inlineStr">
-        <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="H279" s="5" t="inlineStr">
-        <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
       <c r="I279" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J279" s="5" t="b">
         <v>0</v>
@@ -18085,13 +18071,13 @@
       <c r="L279" s="5" t="n"/>
       <c r="M279" s="5" t="n"/>
       <c r="N279" s="5" t="n">
-        <v>7.47</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B280" s="5" t="n">
@@ -18099,11 +18085,13 @@
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D280" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D280" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
@@ -18117,35 +18105,39 @@
       </c>
       <c r="G280" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H280" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I280" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J280" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K280" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L280" s="5" t="n"/>
-      <c r="M280" s="5" t="n"/>
+      <c r="L280" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M280" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N280" s="5" t="n">
-        <v>7.15</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B281" s="5" t="n">
@@ -18199,13 +18191,13 @@
         <v>1</v>
       </c>
       <c r="N281" s="5" t="n">
-        <v>7.04</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B282" s="5" t="n">
@@ -18259,13 +18251,13 @@
         <v>1</v>
       </c>
       <c r="N282" s="5" t="n">
-        <v>7.06</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B283" s="5" t="n">
@@ -18319,13 +18311,13 @@
         <v>1</v>
       </c>
       <c r="N283" s="5" t="n">
-        <v>3.78</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B284" s="5" t="n">
@@ -18333,7 +18325,7 @@
       </c>
       <c r="C284" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D284" s="5" t="inlineStr">
@@ -18353,12 +18345,12 @@
       </c>
       <c r="G284" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H284" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I284" s="5" t="b">
@@ -18379,13 +18371,13 @@
         <v>1</v>
       </c>
       <c r="N284" s="5" t="n">
-        <v>6.9</v>
+        <v>21.33</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B285" s="5" t="n">
@@ -18393,7 +18385,7 @@
       </c>
       <c r="C285" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D285" s="5" t="inlineStr">
@@ -18413,12 +18405,12 @@
       </c>
       <c r="G285" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H285" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I285" s="5" t="b">
@@ -18433,19 +18425,19 @@
         </is>
       </c>
       <c r="L285" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M285" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N285" s="5" t="n">
-        <v>7.44</v>
+        <v>21.07</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B286" s="5" t="n">
@@ -18453,7 +18445,7 @@
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D286" s="5" t="inlineStr">
@@ -18473,12 +18465,12 @@
       </c>
       <c r="G286" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H286" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I286" s="5" t="b">
@@ -18493,19 +18485,19 @@
         </is>
       </c>
       <c r="L286" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M286" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N286" s="5" t="n">
-        <v>4.01</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B287" s="5" t="n">
@@ -18513,7 +18505,7 @@
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D287" s="5" t="inlineStr">
@@ -18533,35 +18525,39 @@
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H287" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I287" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J287" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K287" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L287" s="5" t="n"/>
-      <c r="M287" s="5" t="n"/>
+      <c r="L287" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M287" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N287" s="5" t="n">
-        <v>6.79</v>
+        <v>34.24</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B288" s="5" t="n">
@@ -18569,7 +18565,7 @@
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D288" s="5" t="inlineStr">
@@ -18589,35 +18585,39 @@
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H288" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I288" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J288" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K288" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L288" s="5" t="n"/>
-      <c r="M288" s="5" t="n"/>
+      <c r="L288" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M288" s="5" t="n">
+        <v>0.2</v>
+      </c>
       <c r="N288" s="5" t="n">
-        <v>6.79</v>
+        <v>24.74</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B289" s="5" t="n">
@@ -18625,7 +18625,7 @@
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D289" s="5" t="inlineStr">
@@ -18645,12 +18645,12 @@
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H289" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I289" s="5" t="b">
@@ -18665,19 +18665,19 @@
         </is>
       </c>
       <c r="L289" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M289" s="5" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="N289" s="5" t="n">
-        <v>4.06</v>
+        <v>39.64</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B290" s="5" t="n">
@@ -18685,7 +18685,7 @@
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D290" s="5" t="inlineStr">
@@ -18705,12 +18705,12 @@
       </c>
       <c r="G290" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H290" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I290" s="5" t="b">
@@ -18731,13 +18731,13 @@
         <v>1</v>
       </c>
       <c r="N290" s="5" t="n">
-        <v>7.51</v>
+        <v>27.13</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B291" s="5" t="n">
@@ -18745,7 +18745,7 @@
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
@@ -18765,12 +18765,12 @@
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H291" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I291" s="5" t="b">
@@ -18791,13 +18791,13 @@
         <v>1</v>
       </c>
       <c r="N291" s="5" t="n">
-        <v>8.460000000000001</v>
+        <v>29.42</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B292" s="5" t="n">
@@ -18805,7 +18805,7 @@
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
@@ -18825,12 +18825,12 @@
       </c>
       <c r="G292" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H292" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I292" s="5" t="b">
@@ -18851,13 +18851,13 @@
         <v>1</v>
       </c>
       <c r="N292" s="5" t="n">
-        <v>4.94</v>
+        <v>32.16</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B293" s="5" t="n">
@@ -18865,7 +18865,7 @@
       </c>
       <c r="C293" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D293" s="5" t="inlineStr">
@@ -18911,13 +18911,13 @@
         <v>1</v>
       </c>
       <c r="N293" s="5" t="n">
-        <v>21.33</v>
+        <v>26.34</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B294" s="5" t="n">
@@ -18925,7 +18925,7 @@
       </c>
       <c r="C294" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D294" s="5" t="inlineStr">
@@ -18971,13 +18971,13 @@
         <v>1</v>
       </c>
       <c r="N294" s="5" t="n">
-        <v>21.07</v>
+        <v>24.87</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B295" s="5" t="n">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C295" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D295" s="5" t="inlineStr">
@@ -19031,13 +19031,13 @@
         <v>1</v>
       </c>
       <c r="N295" s="5" t="n">
-        <v>20.4</v>
+        <v>24.72</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B296" s="5" t="n">
@@ -19045,7 +19045,7 @@
       </c>
       <c r="C296" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D296" s="5" t="inlineStr">
@@ -19070,7 +19070,7 @@
       </c>
       <c r="H296" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I296" s="5" t="b">
@@ -19091,13 +19091,13 @@
         <v>1</v>
       </c>
       <c r="N296" s="5" t="n">
-        <v>34.24</v>
+        <v>22.06</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B297" s="5" t="n">
@@ -19105,7 +19105,7 @@
       </c>
       <c r="C297" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D297" s="5" t="inlineStr">
@@ -19130,7 +19130,7 @@
       </c>
       <c r="H297" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I297" s="5" t="b">
@@ -19145,19 +19145,19 @@
         </is>
       </c>
       <c r="L297" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M297" s="5" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="N297" s="5" t="n">
-        <v>24.74</v>
+        <v>21.92</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B298" s="5" t="n">
@@ -19165,7 +19165,7 @@
       </c>
       <c r="C298" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D298" s="5" t="inlineStr">
@@ -19190,7 +19190,7 @@
       </c>
       <c r="H298" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I298" s="5" t="b">
@@ -19208,16 +19208,16 @@
         <v>0</v>
       </c>
       <c r="M298" s="5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N298" s="5" t="n">
-        <v>39.64</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B299" s="5" t="n">
@@ -19225,7 +19225,7 @@
       </c>
       <c r="C299" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D299" s="5" t="inlineStr">
@@ -19250,7 +19250,7 @@
       </c>
       <c r="H299" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I299" s="5" t="b">
@@ -19265,19 +19265,19 @@
         </is>
       </c>
       <c r="L299" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M299" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N299" s="5" t="n">
-        <v>27.13</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B300" s="5" t="n">
@@ -19285,7 +19285,7 @@
       </c>
       <c r="C300" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D300" s="5" t="inlineStr">
@@ -19310,7 +19310,7 @@
       </c>
       <c r="H300" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I300" s="5" t="b">
@@ -19325,19 +19325,19 @@
         </is>
       </c>
       <c r="L300" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M300" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N300" s="5" t="n">
-        <v>29.42</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B301" s="5" t="n">
@@ -19345,7 +19345,7 @@
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D301" s="5" t="inlineStr">
@@ -19370,7 +19370,7 @@
       </c>
       <c r="H301" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I301" s="5" t="b">
@@ -19385,19 +19385,19 @@
         </is>
       </c>
       <c r="L301" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M301" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N301" s="5" t="n">
-        <v>32.16</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B302" s="5" t="n">
@@ -19451,13 +19451,13 @@
         <v>1</v>
       </c>
       <c r="N302" s="5" t="n">
-        <v>26.34</v>
+        <v>20.09</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B303" s="5" t="n">
@@ -19511,13 +19511,13 @@
         <v>1</v>
       </c>
       <c r="N303" s="5" t="n">
-        <v>24.87</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B304" s="5" t="n">
@@ -19571,13 +19571,13 @@
         <v>1</v>
       </c>
       <c r="N304" s="5" t="n">
-        <v>24.72</v>
+        <v>21.93</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B305" s="5" t="n">
@@ -19585,7 +19585,7 @@
       </c>
       <c r="C305" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D305" s="5" t="inlineStr">
@@ -19610,7 +19610,7 @@
       </c>
       <c r="H305" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I305" s="5" t="b">
@@ -19624,20 +19624,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L305" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M305" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L305" s="5" t="n"/>
+      <c r="M305" s="5" t="n"/>
       <c r="N305" s="5" t="n">
-        <v>22.06</v>
+        <v>14.53</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B306" s="5" t="n">
@@ -19645,7 +19641,7 @@
       </c>
       <c r="C306" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D306" s="5" t="inlineStr">
@@ -19670,7 +19666,7 @@
       </c>
       <c r="H306" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I306" s="5" t="b">
@@ -19684,20 +19680,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L306" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M306" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L306" s="5" t="n"/>
+      <c r="M306" s="5" t="n"/>
       <c r="N306" s="5" t="n">
-        <v>21.92</v>
+        <v>16.97</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B307" s="5" t="n">
@@ -19705,7 +19697,7 @@
       </c>
       <c r="C307" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D307" s="5" t="inlineStr">
@@ -19730,7 +19722,7 @@
       </c>
       <c r="H307" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I307" s="5" t="b">
@@ -19744,20 +19736,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L307" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M307" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L307" s="5" t="n"/>
+      <c r="M307" s="5" t="n"/>
       <c r="N307" s="5" t="n">
-        <v>13.4</v>
+        <v>18.95</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B308" s="5" t="n">
@@ -19765,7 +19753,7 @@
       </c>
       <c r="C308" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D308" s="5" t="inlineStr">
@@ -19790,7 +19778,7 @@
       </c>
       <c r="H308" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I308" s="5" t="b">
@@ -19808,16 +19796,16 @@
         <v>0</v>
       </c>
       <c r="M308" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N308" s="5" t="n">
-        <v>6.67</v>
+        <v>16.03</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B309" s="5" t="n">
@@ -19825,7 +19813,7 @@
       </c>
       <c r="C309" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D309" s="5" t="inlineStr">
@@ -19850,7 +19838,7 @@
       </c>
       <c r="H309" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I309" s="5" t="b">
@@ -19868,16 +19856,16 @@
         <v>0</v>
       </c>
       <c r="M309" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N309" s="5" t="n">
-        <v>7.35</v>
+        <v>17.29</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B310" s="5" t="n">
@@ -19885,7 +19873,7 @@
       </c>
       <c r="C310" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D310" s="5" t="inlineStr">
@@ -19910,7 +19898,7 @@
       </c>
       <c r="H310" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I310" s="5" t="b">
@@ -19921,7 +19909,7 @@
       </c>
       <c r="K310" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L310" s="5" t="b">
@@ -19931,13 +19919,13 @@
         <v>0</v>
       </c>
       <c r="N310" s="5" t="n">
-        <v>4.44</v>
+        <v>17.43</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B311" s="5" t="n">
@@ -19945,7 +19933,7 @@
       </c>
       <c r="C311" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D311" s="5" t="inlineStr">
@@ -19970,7 +19958,7 @@
       </c>
       <c r="H311" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I311" s="5" t="b">
@@ -19981,23 +19969,19 @@
       </c>
       <c r="K311" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L311" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M311" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>execution_failure</t>
+        </is>
+      </c>
+      <c r="L311" s="5" t="n"/>
+      <c r="M311" s="5" t="n"/>
       <c r="N311" s="5" t="n">
-        <v>20.09</v>
+        <v>15.17</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B312" s="5" t="n">
@@ -20005,7 +19989,7 @@
       </c>
       <c r="C312" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D312" s="5" t="inlineStr">
@@ -20030,7 +20014,7 @@
       </c>
       <c r="H312" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I312" s="5" t="b">
@@ -20044,20 +20028,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L312" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M312" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L312" s="5" t="n"/>
+      <c r="M312" s="5" t="n"/>
       <c r="N312" s="5" t="n">
-        <v>22.25</v>
+        <v>15.73</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B313" s="5" t="n">
@@ -20065,7 +20045,7 @@
       </c>
       <c r="C313" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D313" s="5" t="inlineStr">
@@ -20090,7 +20070,7 @@
       </c>
       <c r="H313" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I313" s="5" t="b">
@@ -20104,20 +20084,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L313" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M313" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L313" s="5" t="n"/>
+      <c r="M313" s="5" t="n"/>
       <c r="N313" s="5" t="n">
-        <v>21.93</v>
+        <v>16.63</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B314" s="5" t="n">
@@ -20167,13 +20143,13 @@
       <c r="L314" s="5" t="n"/>
       <c r="M314" s="5" t="n"/>
       <c r="N314" s="5" t="n">
-        <v>14.53</v>
+        <v>16.55</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B315" s="5" t="n">
@@ -20223,13 +20199,13 @@
       <c r="L315" s="5" t="n"/>
       <c r="M315" s="5" t="n"/>
       <c r="N315" s="5" t="n">
-        <v>16.97</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B316" s="5" t="n">
@@ -20279,26 +20255,26 @@
       <c r="L316" s="5" t="n"/>
       <c r="M316" s="5" t="n"/>
       <c r="N316" s="5" t="n">
-        <v>18.95</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>ranking_kg2_001</t>
         </is>
       </c>
       <c r="B317" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C317" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D317" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E317" s="5" t="inlineStr">
@@ -20313,12 +20289,12 @@
       </c>
       <c r="G317" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H317" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I317" s="5" t="b">
@@ -20333,32 +20309,32 @@
         </is>
       </c>
       <c r="L317" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M317" s="5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N317" s="5" t="n">
-        <v>16.03</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>ranking_kg2_001</t>
         </is>
       </c>
       <c r="B318" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C318" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D318" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E318" s="5" t="inlineStr">
@@ -20373,52 +20349,52 @@
       </c>
       <c r="G318" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H318" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I318" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J318" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K318" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>generation_failure</t>
         </is>
       </c>
       <c r="L318" s="5" t="b">
         <v>0</v>
       </c>
       <c r="M318" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N318" s="5" t="n">
-        <v>17.29</v>
+        <v>51.14</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>ranking_kg2_001</t>
         </is>
       </c>
       <c r="B319" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C319" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E319" s="5" t="inlineStr">
@@ -20433,12 +20409,12 @@
       </c>
       <c r="G319" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H319" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I319" s="5" t="b">
@@ -20449,36 +20425,36 @@
       </c>
       <c r="K319" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L319" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M319" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N319" s="5" t="n">
-        <v>17.43</v>
+        <v>17.12</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>ranking_kg2_002</t>
         </is>
       </c>
       <c r="B320" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C320" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D320" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E320" s="5" t="inlineStr">
@@ -20493,48 +20469,52 @@
       </c>
       <c r="G320" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H320" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I320" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J320" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K320" s="5" t="inlineStr">
         <is>
           <t>execution_failure</t>
         </is>
       </c>
-      <c r="L320" s="5" t="n"/>
-      <c r="M320" s="5" t="n"/>
+      <c r="L320" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M320" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N320" s="5" t="n">
-        <v>15.17</v>
+        <v>16.33</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>ranking_kg2_002</t>
         </is>
       </c>
       <c r="B321" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C321" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D321" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E321" s="5" t="inlineStr">
@@ -20549,12 +20529,12 @@
       </c>
       <c r="G321" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H321" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I321" s="5" t="b">
@@ -20568,29 +20548,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L321" s="5" t="n"/>
-      <c r="M321" s="5" t="n"/>
+      <c r="L321" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M321" s="5" t="n">
+        <v>0.5</v>
+      </c>
       <c r="N321" s="5" t="n">
-        <v>15.73</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>ranking_kg2_002</t>
         </is>
       </c>
       <c r="B322" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C322" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D322" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E322" s="5" t="inlineStr">
@@ -20605,12 +20589,12 @@
       </c>
       <c r="G322" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H322" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I322" s="5" t="b">
@@ -20624,29 +20608,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L322" s="5" t="n"/>
-      <c r="M322" s="5" t="n"/>
+      <c r="L322" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M322" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N322" s="5" t="n">
-        <v>16.63</v>
+        <v>12.28</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>ranking_kg2_003</t>
         </is>
       </c>
       <c r="B323" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C323" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E323" s="5" t="inlineStr">
@@ -20661,48 +20649,52 @@
       </c>
       <c r="G323" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H323" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I323" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J323" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K323" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L323" s="5" t="n"/>
-      <c r="M323" s="5" t="n"/>
+          <t>generation_failure</t>
+        </is>
+      </c>
+      <c r="L323" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M323" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N323" s="5" t="n">
-        <v>16.55</v>
+        <v>40.39</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>ranking_kg2_003</t>
         </is>
       </c>
       <c r="B324" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C324" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D324" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E324" s="5" t="inlineStr">
@@ -20717,48 +20709,52 @@
       </c>
       <c r="G324" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H324" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I324" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J324" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K324" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L324" s="5" t="n"/>
-      <c r="M324" s="5" t="n"/>
+          <t>execution_failure</t>
+        </is>
+      </c>
+      <c r="L324" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M324" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N324" s="5" t="n">
-        <v>16.57</v>
+        <v>17.44</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>ranking_kg2_003</t>
         </is>
       </c>
       <c r="B325" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C325" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E325" s="5" t="inlineStr">
@@ -20773,12 +20769,12 @@
       </c>
       <c r="G325" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H325" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I325" s="5" t="b">
@@ -20792,10 +20788,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L325" s="5" t="n"/>
-      <c r="M325" s="5" t="n"/>
+      <c r="L325" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M325" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N325" s="5" t="n">
-        <v>15.5</v>
+        <v>14.68</v>
       </c>
     </row>
   </sheetData>

--- a/NL2SPARQL_Evaluation_Results.xlsx
+++ b/NL2SPARQL_Evaluation_Results.xlsx
@@ -13387,7 +13387,7 @@
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
         <is>
-          <t>open_kg_001</t>
+          <t>open_kg_002</t>
         </is>
       </c>
       <c r="B200" s="5" t="n">
@@ -13434,16 +13434,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L200" s="5" t="n"/>
-      <c r="M200" s="5" t="n"/>
+      <c r="L200" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M200" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N200" s="5" t="n">
-        <v>28.51</v>
+        <v>27.56</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>open_kg_001</t>
+          <t>open_kg_002</t>
         </is>
       </c>
       <c r="B201" s="5" t="n">
@@ -13490,16 +13494,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L201" s="5" t="n"/>
-      <c r="M201" s="5" t="n"/>
+      <c r="L201" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M201" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N201" s="5" t="n">
-        <v>27.5</v>
+        <v>35.57</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
         <is>
-          <t>open_kg_001</t>
+          <t>open_kg_002</t>
         </is>
       </c>
       <c r="B202" s="5" t="n">
@@ -13532,30 +13540,34 @@
       </c>
       <c r="H202" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I202" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J202" s="5" t="b">
         <v>1</v>
       </c>
       <c r="K202" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L202" s="5" t="n"/>
-      <c r="M202" s="5" t="n"/>
+          <t>execution_failure</t>
+        </is>
+      </c>
+      <c r="L202" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M202" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N202" s="5" t="n">
-        <v>8.82</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
         <is>
-          <t>open_kg_002</t>
+          <t>open_kg_003</t>
         </is>
       </c>
       <c r="B203" s="5" t="n">
@@ -13588,18 +13600,18 @@
       </c>
       <c r="H203" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I203" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J203" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K203" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>sparql_build_failure</t>
         </is>
       </c>
       <c r="L203" s="5" t="b">
@@ -13609,13 +13621,13 @@
         <v>0</v>
       </c>
       <c r="N203" s="5" t="n">
-        <v>27.56</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="5" t="inlineStr">
         <is>
-          <t>open_kg_002</t>
+          <t>open_kg_003</t>
         </is>
       </c>
       <c r="B204" s="5" t="n">
@@ -13663,19 +13675,19 @@
         </is>
       </c>
       <c r="L204" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M204" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N204" s="5" t="n">
-        <v>35.57</v>
+        <v>21.76</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="5" t="inlineStr">
         <is>
-          <t>open_kg_002</t>
+          <t>open_kg_003</t>
         </is>
       </c>
       <c r="B205" s="5" t="n">
@@ -13719,23 +13731,23 @@
       </c>
       <c r="K205" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L205" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M205" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N205" s="5" t="n">
-        <v>28.4</v>
+        <v>21.57</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
         <is>
-          <t>open_kg_003</t>
+          <t>open_kg_004</t>
         </is>
       </c>
       <c r="B206" s="5" t="n">
@@ -13768,34 +13780,34 @@
       </c>
       <c r="H206" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I206" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J206" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K206" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L206" s="5" t="b">
         <v>0</v>
       </c>
       <c r="M206" s="5" t="n">
-        <v>0</v>
+        <v>0.6667</v>
       </c>
       <c r="N206" s="5" t="n">
-        <v>12.73</v>
+        <v>34.54</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
         <is>
-          <t>open_kg_003</t>
+          <t>open_kg_004</t>
         </is>
       </c>
       <c r="B207" s="5" t="n">
@@ -13843,19 +13855,19 @@
         </is>
       </c>
       <c r="L207" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M207" s="5" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="N207" s="5" t="n">
-        <v>21.76</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="5" t="inlineStr">
         <is>
-          <t>open_kg_003</t>
+          <t>open_kg_004</t>
         </is>
       </c>
       <c r="B208" s="5" t="n">
@@ -13903,32 +13915,32 @@
         </is>
       </c>
       <c r="L208" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M208" s="5" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="N208" s="5" t="n">
-        <v>21.57</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
         <is>
-          <t>open_kg_004</t>
+          <t>count_kg1_001</t>
         </is>
       </c>
       <c r="B209" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E209" s="5" t="inlineStr">
@@ -13943,12 +13955,12 @@
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H209" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I209" s="5" t="b">
@@ -13963,32 +13975,32 @@
         </is>
       </c>
       <c r="L209" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M209" s="5" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="N209" s="5" t="n">
-        <v>34.54</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
         <is>
-          <t>open_kg_004</t>
+          <t>count_kg1_001</t>
         </is>
       </c>
       <c r="B210" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
@@ -14003,12 +14015,12 @@
       </c>
       <c r="G210" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H210" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I210" s="5" t="b">
@@ -14023,32 +14035,32 @@
         </is>
       </c>
       <c r="L210" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M210" s="5" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="N210" s="5" t="n">
-        <v>31.8</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
         <is>
-          <t>open_kg_004</t>
+          <t>count_kg1_001</t>
         </is>
       </c>
       <c r="B211" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E211" s="5" t="inlineStr">
@@ -14063,12 +14075,12 @@
       </c>
       <c r="G211" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H211" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I211" s="5" t="b">
@@ -14083,32 +14095,32 @@
         </is>
       </c>
       <c r="L211" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M211" s="5" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="N211" s="5" t="n">
-        <v>33.6</v>
+        <v>13.17</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="5" t="inlineStr">
         <is>
-          <t>open_kg_005</t>
+          <t>count_kg1_002</t>
         </is>
       </c>
       <c r="B212" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
@@ -14123,7 +14135,7 @@
       </c>
       <c r="G212" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H212" s="5" t="inlineStr">
@@ -14132,39 +14144,43 @@
         </is>
       </c>
       <c r="I212" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J212" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K212" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L212" s="5" t="n"/>
-      <c r="M212" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L212" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M212" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N212" s="5" t="n">
-        <v>11.84</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
         <is>
-          <t>open_kg_005</t>
+          <t>count_kg1_002</t>
         </is>
       </c>
       <c r="B213" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E213" s="5" t="inlineStr">
@@ -14179,7 +14195,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -14188,39 +14204,43 @@
         </is>
       </c>
       <c r="I213" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J213" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K213" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L213" s="5" t="n"/>
-      <c r="M213" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L213" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M213" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N213" s="5" t="n">
-        <v>14.23</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
         <is>
-          <t>open_kg_005</t>
+          <t>count_kg1_002</t>
         </is>
       </c>
       <c r="B214" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
@@ -14235,12 +14255,12 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I214" s="5" t="b">
@@ -14251,32 +14271,36 @@
       </c>
       <c r="K214" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L214" s="5" t="n"/>
-      <c r="M214" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L214" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M214" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N214" s="5" t="n">
-        <v>30.18</v>
+        <v>17.47</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
         <is>
-          <t>open_kg_006</t>
+          <t>count_kg1_003</t>
         </is>
       </c>
       <c r="B215" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E215" s="5" t="inlineStr">
@@ -14291,12 +14315,12 @@
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H215" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I215" s="5" t="b">
@@ -14307,32 +14331,36 @@
       </c>
       <c r="K215" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L215" s="5" t="n"/>
-      <c r="M215" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L215" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M215" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N215" s="5" t="n">
-        <v>23.79</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
         <is>
-          <t>open_kg_006</t>
+          <t>count_kg1_003</t>
         </is>
       </c>
       <c r="B216" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
@@ -14347,12 +14375,12 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I216" s="5" t="b">
@@ -14366,29 +14394,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L216" s="5" t="n"/>
-      <c r="M216" s="5" t="n"/>
+      <c r="L216" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M216" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N216" s="5" t="n">
-        <v>28.35</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
         <is>
-          <t>open_kg_006</t>
+          <t>count_kg1_003</t>
         </is>
       </c>
       <c r="B217" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E217" s="5" t="inlineStr">
@@ -14403,16 +14435,16 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I217" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J217" s="5" t="b">
         <v>1</v>
@@ -14422,16 +14454,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L217" s="5" t="n"/>
-      <c r="M217" s="5" t="n"/>
+      <c r="L217" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M217" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N217" s="5" t="n">
-        <v>8.99</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_001</t>
+          <t>filter_numeric_kg1_001</t>
         </is>
       </c>
       <c r="B218" s="5" t="n">
@@ -14439,7 +14475,7 @@
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D218" s="5" t="inlineStr">
@@ -14485,13 +14521,13 @@
         <v>1</v>
       </c>
       <c r="N218" s="5" t="n">
-        <v>12.62</v>
+        <v>12.18</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_001</t>
+          <t>filter_numeric_kg1_001</t>
         </is>
       </c>
       <c r="B219" s="5" t="n">
@@ -14499,7 +14535,7 @@
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D219" s="5" t="inlineStr">
@@ -14545,13 +14581,13 @@
         <v>1</v>
       </c>
       <c r="N219" s="5" t="n">
-        <v>14.4</v>
+        <v>13.35</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_001</t>
+          <t>filter_numeric_kg1_001</t>
         </is>
       </c>
       <c r="B220" s="5" t="n">
@@ -14559,7 +14595,7 @@
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D220" s="5" t="inlineStr">
@@ -14605,13 +14641,13 @@
         <v>1</v>
       </c>
       <c r="N220" s="5" t="n">
-        <v>13.17</v>
+        <v>13.13</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_002</t>
+          <t>filter_numeric_kg1_002</t>
         </is>
       </c>
       <c r="B221" s="5" t="n">
@@ -14619,7 +14655,7 @@
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D221" s="5" t="inlineStr">
@@ -14665,13 +14701,13 @@
         <v>1</v>
       </c>
       <c r="N221" s="5" t="n">
-        <v>14.59</v>
+        <v>12.57</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_002</t>
+          <t>filter_numeric_kg1_002</t>
         </is>
       </c>
       <c r="B222" s="5" t="n">
@@ -14679,7 +14715,7 @@
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
@@ -14725,13 +14761,13 @@
         <v>1</v>
       </c>
       <c r="N222" s="5" t="n">
-        <v>12.23</v>
+        <v>16.18</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_002</t>
+          <t>filter_numeric_kg1_002</t>
         </is>
       </c>
       <c r="B223" s="5" t="n">
@@ -14739,7 +14775,7 @@
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D223" s="5" t="inlineStr">
@@ -14785,13 +14821,13 @@
         <v>1</v>
       </c>
       <c r="N223" s="5" t="n">
-        <v>17.47</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_003</t>
+          <t>filter_numeric_kg1_003</t>
         </is>
       </c>
       <c r="B224" s="5" t="n">
@@ -14799,7 +14835,7 @@
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D224" s="5" t="inlineStr">
@@ -14845,13 +14881,13 @@
         <v>1</v>
       </c>
       <c r="N224" s="5" t="n">
-        <v>11.48</v>
+        <v>11.81</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_003</t>
+          <t>filter_numeric_kg1_003</t>
         </is>
       </c>
       <c r="B225" s="5" t="n">
@@ -14859,7 +14895,7 @@
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D225" s="5" t="inlineStr">
@@ -14905,13 +14941,13 @@
         <v>1</v>
       </c>
       <c r="N225" s="5" t="n">
-        <v>12.2</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_003</t>
+          <t>filter_numeric_kg1_003</t>
         </is>
       </c>
       <c r="B226" s="5" t="n">
@@ -14919,7 +14955,7 @@
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D226" s="5" t="inlineStr">
@@ -14965,13 +15001,13 @@
         <v>1</v>
       </c>
       <c r="N226" s="5" t="n">
-        <v>11.98</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_001</t>
+          <t>filter_numeric_kg2_001</t>
         </is>
       </c>
       <c r="B227" s="5" t="n">
@@ -14979,12 +15015,12 @@
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E227" s="5" t="inlineStr">
@@ -15025,13 +15061,13 @@
         <v>1</v>
       </c>
       <c r="N227" s="5" t="n">
-        <v>12.18</v>
+        <v>19.86</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_001</t>
+          <t>filter_numeric_kg2_001</t>
         </is>
       </c>
       <c r="B228" s="5" t="n">
@@ -15039,12 +15075,12 @@
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
@@ -15085,13 +15121,13 @@
         <v>1</v>
       </c>
       <c r="N228" s="5" t="n">
-        <v>13.35</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_001</t>
+          <t>filter_numeric_kg2_001</t>
         </is>
       </c>
       <c r="B229" s="5" t="n">
@@ -15099,12 +15135,12 @@
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E229" s="5" t="inlineStr">
@@ -15145,13 +15181,13 @@
         <v>1</v>
       </c>
       <c r="N229" s="5" t="n">
-        <v>13.13</v>
+        <v>14.12</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_002</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B230" s="5" t="n">
@@ -15159,12 +15195,12 @@
       </c>
       <c r="C230" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E230" s="5" t="inlineStr">
@@ -15199,19 +15235,19 @@
         </is>
       </c>
       <c r="L230" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M230" s="5" t="n">
-        <v>1</v>
+        <v>0.7692</v>
       </c>
       <c r="N230" s="5" t="n">
-        <v>12.57</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_002</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B231" s="5" t="n">
@@ -15219,12 +15255,12 @@
       </c>
       <c r="C231" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E231" s="5" t="inlineStr">
@@ -15259,19 +15295,19 @@
         </is>
       </c>
       <c r="L231" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M231" s="5" t="n">
-        <v>1</v>
+        <v>0.7692</v>
       </c>
       <c r="N231" s="5" t="n">
-        <v>16.18</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_002</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B232" s="5" t="n">
@@ -15279,12 +15315,12 @@
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E232" s="5" t="inlineStr">
@@ -15319,19 +15355,19 @@
         </is>
       </c>
       <c r="L232" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M232" s="5" t="n">
-        <v>1</v>
+        <v>0.7692</v>
       </c>
       <c r="N232" s="5" t="n">
-        <v>17.1</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_003</t>
+          <t>filter_string_kg2_001</t>
         </is>
       </c>
       <c r="B233" s="5" t="n">
@@ -15339,12 +15375,12 @@
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E233" s="5" t="inlineStr">
@@ -15385,13 +15421,13 @@
         <v>1</v>
       </c>
       <c r="N233" s="5" t="n">
-        <v>11.81</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_003</t>
+          <t>filter_string_kg2_001</t>
         </is>
       </c>
       <c r="B234" s="5" t="n">
@@ -15399,12 +15435,12 @@
       </c>
       <c r="C234" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
@@ -15445,13 +15481,13 @@
         <v>1</v>
       </c>
       <c r="N234" s="5" t="n">
-        <v>13.04</v>
+        <v>14.03</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_003</t>
+          <t>filter_string_kg2_001</t>
         </is>
       </c>
       <c r="B235" s="5" t="n">
@@ -15459,12 +15495,12 @@
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E235" s="5" t="inlineStr">
@@ -15505,13 +15541,13 @@
         <v>1</v>
       </c>
       <c r="N235" s="5" t="n">
-        <v>12.58</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_001</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B236" s="5" t="n">
@@ -15519,7 +15555,7 @@
       </c>
       <c r="C236" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D236" s="5" t="inlineStr">
@@ -15559,19 +15595,19 @@
         </is>
       </c>
       <c r="L236" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M236" s="5" t="n">
-        <v>1</v>
+        <v>0.7368</v>
       </c>
       <c r="N236" s="5" t="n">
-        <v>19.86</v>
+        <v>13.55</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_001</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B237" s="5" t="n">
@@ -15579,7 +15615,7 @@
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D237" s="5" t="inlineStr">
@@ -15619,19 +15655,19 @@
         </is>
       </c>
       <c r="L237" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M237" s="5" t="n">
-        <v>1</v>
+        <v>0.7368</v>
       </c>
       <c r="N237" s="5" t="n">
-        <v>15.05</v>
+        <v>15.41</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_001</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B238" s="5" t="n">
@@ -15639,7 +15675,7 @@
       </c>
       <c r="C238" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D238" s="5" t="inlineStr">
@@ -15679,19 +15715,19 @@
         </is>
       </c>
       <c r="L238" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M238" s="5" t="n">
-        <v>1</v>
+        <v>0.7368</v>
       </c>
       <c r="N238" s="5" t="n">
-        <v>14.12</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B239" s="5" t="n">
@@ -15699,7 +15735,7 @@
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D239" s="5" t="inlineStr">
@@ -15739,19 +15775,19 @@
         </is>
       </c>
       <c r="L239" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M239" s="5" t="n">
-        <v>0.7692</v>
+        <v>1</v>
       </c>
       <c r="N239" s="5" t="n">
-        <v>13.76</v>
+        <v>22.31</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B240" s="5" t="n">
@@ -15759,7 +15795,7 @@
       </c>
       <c r="C240" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D240" s="5" t="inlineStr">
@@ -15799,19 +15835,19 @@
         </is>
       </c>
       <c r="L240" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M240" s="5" t="n">
-        <v>0.7692</v>
+        <v>1</v>
       </c>
       <c r="N240" s="5" t="n">
-        <v>11.69</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B241" s="5" t="n">
@@ -15819,7 +15855,7 @@
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D241" s="5" t="inlineStr">
@@ -15859,19 +15895,19 @@
         </is>
       </c>
       <c r="L241" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M241" s="5" t="n">
-        <v>0.7692</v>
+        <v>1</v>
       </c>
       <c r="N241" s="5" t="n">
-        <v>12.59</v>
+        <v>21.77</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B242" s="5" t="n">
@@ -15879,7 +15915,7 @@
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D242" s="5" t="inlineStr">
@@ -15904,34 +15940,34 @@
       </c>
       <c r="H242" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I242" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J242" s="5" t="b">
         <v>1</v>
       </c>
       <c r="K242" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L242" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M242" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N242" s="5" t="n">
-        <v>36.93</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B243" s="5" t="n">
@@ -15939,7 +15975,7 @@
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D243" s="5" t="inlineStr">
@@ -15985,13 +16021,13 @@
         <v>1</v>
       </c>
       <c r="N243" s="5" t="n">
-        <v>13.09</v>
+        <v>11.59</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B244" s="5" t="n">
@@ -15999,7 +16035,7 @@
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D244" s="5" t="inlineStr">
@@ -16045,13 +16081,13 @@
         <v>1</v>
       </c>
       <c r="N244" s="5" t="n">
-        <v>11.47</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_001</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B245" s="5" t="n">
@@ -16059,7 +16095,7 @@
       </c>
       <c r="C245" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D245" s="5" t="inlineStr">
@@ -16105,13 +16141,13 @@
         <v>1</v>
       </c>
       <c r="N245" s="5" t="n">
-        <v>13.73</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_001</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B246" s="5" t="n">
@@ -16119,7 +16155,7 @@
       </c>
       <c r="C246" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D246" s="5" t="inlineStr">
@@ -16165,13 +16201,13 @@
         <v>1</v>
       </c>
       <c r="N246" s="5" t="n">
-        <v>14.03</v>
+        <v>11.53</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_001</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B247" s="5" t="n">
@@ -16179,7 +16215,7 @@
       </c>
       <c r="C247" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D247" s="5" t="inlineStr">
@@ -16225,27 +16261,25 @@
         <v>1</v>
       </c>
       <c r="N247" s="5" t="n">
-        <v>13.41</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_002</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B248" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
-        </is>
-      </c>
-      <c r="D248" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D248" s="5" t="n">
+        <v/>
       </c>
       <c r="E248" s="5" t="inlineStr">
         <is>
@@ -16259,19 +16293,19 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I248" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J248" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K248" s="5" t="inlineStr">
         <is>
@@ -16281,27 +16315,25 @@
       <c r="L248" s="5" t="n"/>
       <c r="M248" s="5" t="n"/>
       <c r="N248" s="5" t="n">
-        <v>37.75</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_002</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B249" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
-        </is>
-      </c>
-      <c r="D249" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D249" s="5" t="n">
+        <v/>
       </c>
       <c r="E249" s="5" t="inlineStr">
         <is>
@@ -16315,12 +16347,12 @@
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H249" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I249" s="5" t="b">
@@ -16331,33 +16363,31 @@
       </c>
       <c r="K249" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L249" s="5" t="n"/>
       <c r="M249" s="5" t="n"/>
       <c r="N249" s="5" t="n">
-        <v>12.45</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_002</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B250" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
-        </is>
-      </c>
-      <c r="D250" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D250" s="5" t="n">
+        <v/>
       </c>
       <c r="E250" s="5" t="inlineStr">
         <is>
@@ -16371,19 +16401,19 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I250" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J250" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K250" s="5" t="inlineStr">
         <is>
@@ -16393,27 +16423,25 @@
       <c r="L250" s="5" t="n"/>
       <c r="M250" s="5" t="n"/>
       <c r="N250" s="5" t="n">
-        <v>10.44</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B251" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C251" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
-        </is>
-      </c>
-      <c r="D251" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D251" s="5" t="n">
+        <v/>
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
@@ -16427,53 +16455,47 @@
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H251" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I251" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J251" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K251" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L251" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M251" s="5" t="n">
-        <v>0.7368</v>
-      </c>
+      <c r="L251" s="5" t="n"/>
+      <c r="M251" s="5" t="n"/>
       <c r="N251" s="5" t="n">
-        <v>13.55</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B252" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C252" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
-        </is>
-      </c>
-      <c r="D252" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D252" s="5" t="n">
+        <v/>
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
@@ -16487,53 +16509,47 @@
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H252" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I252" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J252" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K252" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L252" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M252" s="5" t="n">
-        <v>0.7368</v>
-      </c>
+      <c r="L252" s="5" t="n"/>
+      <c r="M252" s="5" t="n"/>
       <c r="N252" s="5" t="n">
-        <v>15.41</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B253" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
-        </is>
-      </c>
-      <c r="D253" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D253" s="5" t="n">
+        <v/>
       </c>
       <c r="E253" s="5" t="inlineStr">
         <is>
@@ -16547,53 +16563,47 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I253" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J253" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K253" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L253" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M253" s="5" t="n">
-        <v>0.7368</v>
-      </c>
+          <t>mapping_failure</t>
+        </is>
+      </c>
+      <c r="L253" s="5" t="n"/>
+      <c r="M253" s="5" t="n"/>
       <c r="N253" s="5" t="n">
-        <v>13.64</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B254" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D254" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D254" s="5" t="n">
+        <v/>
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
@@ -16607,53 +16617,47 @@
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H254" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I254" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J254" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K254" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L254" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M254" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L254" s="5" t="n"/>
+      <c r="M254" s="5" t="n"/>
       <c r="N254" s="5" t="n">
-        <v>22.31</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B255" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D255" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D255" s="5" t="n">
+        <v/>
       </c>
       <c r="E255" s="5" t="inlineStr">
         <is>
@@ -16667,53 +16671,47 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I255" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J255" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K255" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L255" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M255" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L255" s="5" t="n"/>
+      <c r="M255" s="5" t="n"/>
       <c r="N255" s="5" t="n">
-        <v>15.03</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B256" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C256" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D256" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D256" s="5" t="n">
+        <v/>
       </c>
       <c r="E256" s="5" t="inlineStr">
         <is>
@@ -16727,52 +16725,48 @@
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H256" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I256" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J256" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K256" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L256" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M256" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L256" s="5" t="n"/>
+      <c r="M256" s="5" t="n"/>
       <c r="N256" s="5" t="n">
-        <v>21.77</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B257" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E257" s="5" t="inlineStr">
@@ -16787,12 +16781,12 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I257" s="5" t="b">
@@ -16813,26 +16807,26 @@
         <v>1</v>
       </c>
       <c r="N257" s="5" t="n">
-        <v>17.2</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B258" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E258" s="5" t="inlineStr">
@@ -16847,12 +16841,12 @@
       </c>
       <c r="G258" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H258" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I258" s="5" t="b">
@@ -16873,26 +16867,26 @@
         <v>1</v>
       </c>
       <c r="N258" s="5" t="n">
-        <v>11.59</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B259" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C259" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E259" s="5" t="inlineStr">
@@ -16907,12 +16901,12 @@
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H259" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I259" s="5" t="b">
@@ -16933,26 +16927,26 @@
         <v>1</v>
       </c>
       <c r="N259" s="5" t="n">
-        <v>18.53</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B260" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E260" s="5" t="inlineStr">
@@ -16967,12 +16961,12 @@
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H260" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I260" s="5" t="b">
@@ -16993,26 +16987,26 @@
         <v>1</v>
       </c>
       <c r="N260" s="5" t="n">
-        <v>12.31</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B261" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E261" s="5" t="inlineStr">
@@ -17027,12 +17021,12 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I261" s="5" t="b">
@@ -17047,32 +17041,32 @@
         </is>
       </c>
       <c r="L261" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M261" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N261" s="5" t="n">
-        <v>11.53</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B262" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E262" s="5" t="inlineStr">
@@ -17087,12 +17081,12 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I262" s="5" t="b">
@@ -17107,19 +17101,19 @@
         </is>
       </c>
       <c r="L262" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M262" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N262" s="5" t="n">
-        <v>12.22</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B263" s="5" t="n">
@@ -17127,11 +17121,13 @@
       </c>
       <c r="C263" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D263" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D263" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E263" s="5" t="inlineStr">
         <is>
@@ -17145,35 +17141,39 @@
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H263" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I263" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J263" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K263" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L263" s="5" t="n"/>
-      <c r="M263" s="5" t="n"/>
+      <c r="L263" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M263" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N263" s="5" t="n">
-        <v>6.87</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B264" s="5" t="n">
@@ -17181,11 +17181,13 @@
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D264" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D264" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E264" s="5" t="inlineStr">
         <is>
@@ -17199,35 +17201,39 @@
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H264" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I264" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J264" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K264" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L264" s="5" t="n"/>
-      <c r="M264" s="5" t="n"/>
+      <c r="L264" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M264" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N264" s="5" t="n">
-        <v>7.12</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B265" s="5" t="n">
@@ -17235,11 +17241,13 @@
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D265" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E265" s="5" t="inlineStr">
         <is>
@@ -17253,35 +17261,39 @@
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H265" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I265" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J265" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K265" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L265" s="5" t="n"/>
-      <c r="M265" s="5" t="n"/>
+      <c r="L265" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M265" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N265" s="5" t="n">
-        <v>7.48</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B266" s="5" t="n">
@@ -17289,11 +17301,13 @@
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D266" s="5" t="n">
-        <v/>
+          <t>typo_fuzzy</t>
+        </is>
+      </c>
+      <c r="D266" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
         <is>
@@ -17307,35 +17321,39 @@
       </c>
       <c r="G266" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H266" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I266" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J266" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K266" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L266" s="5" t="n"/>
-      <c r="M266" s="5" t="n"/>
+      <c r="L266" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M266" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N266" s="5" t="n">
-        <v>6.99</v>
+        <v>21.33</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B267" s="5" t="n">
@@ -17343,11 +17361,13 @@
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D267" s="5" t="n">
-        <v/>
+          <t>typo_fuzzy</t>
+        </is>
+      </c>
+      <c r="D267" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E267" s="5" t="inlineStr">
         <is>
@@ -17361,35 +17381,39 @@
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H267" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I267" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J267" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K267" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L267" s="5" t="n"/>
-      <c r="M267" s="5" t="n"/>
+      <c r="L267" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M267" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N267" s="5" t="n">
-        <v>7.94</v>
+        <v>21.07</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B268" s="5" t="n">
@@ -17397,11 +17421,13 @@
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D268" s="5" t="n">
-        <v/>
+          <t>typo_fuzzy</t>
+        </is>
+      </c>
+      <c r="D268" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
@@ -17415,35 +17441,39 @@
       </c>
       <c r="G268" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H268" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I268" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J268" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K268" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L268" s="5" t="n"/>
-      <c r="M268" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L268" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M268" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N268" s="5" t="n">
-        <v>6.59</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B269" s="5" t="n">
@@ -17451,11 +17481,13 @@
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D269" s="5" t="n">
-        <v/>
+          <t>typo_fuzzy</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E269" s="5" t="inlineStr">
         <is>
@@ -17469,35 +17501,39 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I269" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J269" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K269" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L269" s="5" t="n"/>
-      <c r="M269" s="5" t="n"/>
+      <c r="L269" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M269" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N269" s="5" t="n">
-        <v>14.02</v>
+        <v>34.24</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B270" s="5" t="n">
@@ -17505,11 +17541,13 @@
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D270" s="5" t="n">
-        <v/>
+          <t>typo_fuzzy</t>
+        </is>
+      </c>
+      <c r="D270" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
         <is>
@@ -17523,35 +17561,39 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I270" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J270" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K270" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L270" s="5" t="n"/>
-      <c r="M270" s="5" t="n"/>
+      <c r="L270" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M270" s="5" t="n">
+        <v>0.2</v>
+      </c>
       <c r="N270" s="5" t="n">
-        <v>7.47</v>
+        <v>24.74</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B271" s="5" t="n">
@@ -17559,11 +17601,13 @@
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D271" s="5" t="n">
-        <v/>
+          <t>typo_fuzzy</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
         <is>
@@ -17577,35 +17621,39 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I271" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J271" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K271" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L271" s="5" t="n"/>
-      <c r="M271" s="5" t="n"/>
+      <c r="L271" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M271" s="5" t="n">
+        <v>0.2</v>
+      </c>
       <c r="N271" s="5" t="n">
-        <v>7.15</v>
+        <v>39.64</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B272" s="5" t="n">
@@ -17613,7 +17661,7 @@
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D272" s="5" t="inlineStr">
@@ -17633,12 +17681,12 @@
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H272" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I272" s="5" t="b">
@@ -17659,13 +17707,13 @@
         <v>1</v>
       </c>
       <c r="N272" s="5" t="n">
-        <v>7.04</v>
+        <v>27.13</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B273" s="5" t="n">
@@ -17673,7 +17721,7 @@
       </c>
       <c r="C273" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D273" s="5" t="inlineStr">
@@ -17693,12 +17741,12 @@
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H273" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I273" s="5" t="b">
@@ -17719,13 +17767,13 @@
         <v>1</v>
       </c>
       <c r="N273" s="5" t="n">
-        <v>7.06</v>
+        <v>29.42</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B274" s="5" t="n">
@@ -17733,7 +17781,7 @@
       </c>
       <c r="C274" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D274" s="5" t="inlineStr">
@@ -17753,12 +17801,12 @@
       </c>
       <c r="G274" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H274" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I274" s="5" t="b">
@@ -17779,13 +17827,13 @@
         <v>1</v>
       </c>
       <c r="N274" s="5" t="n">
-        <v>3.78</v>
+        <v>32.16</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B275" s="5" t="n">
@@ -17793,7 +17841,7 @@
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D275" s="5" t="inlineStr">
@@ -17813,12 +17861,12 @@
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H275" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I275" s="5" t="b">
@@ -17839,13 +17887,13 @@
         <v>1</v>
       </c>
       <c r="N275" s="5" t="n">
-        <v>6.9</v>
+        <v>26.34</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B276" s="5" t="n">
@@ -17853,7 +17901,7 @@
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D276" s="5" t="inlineStr">
@@ -17873,12 +17921,12 @@
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H276" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I276" s="5" t="b">
@@ -17893,19 +17941,19 @@
         </is>
       </c>
       <c r="L276" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M276" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N276" s="5" t="n">
-        <v>7.44</v>
+        <v>24.87</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B277" s="5" t="n">
@@ -17913,7 +17961,7 @@
       </c>
       <c r="C277" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D277" s="5" t="inlineStr">
@@ -17933,12 +17981,12 @@
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H277" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I277" s="5" t="b">
@@ -17953,19 +18001,19 @@
         </is>
       </c>
       <c r="L277" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M277" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N277" s="5" t="n">
-        <v>4.01</v>
+        <v>24.72</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B278" s="5" t="n">
@@ -17973,7 +18021,7 @@
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D278" s="5" t="inlineStr">
@@ -17993,35 +18041,39 @@
       </c>
       <c r="G278" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H278" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I278" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J278" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K278" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L278" s="5" t="n"/>
-      <c r="M278" s="5" t="n"/>
+      <c r="L278" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M278" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N278" s="5" t="n">
-        <v>6.79</v>
+        <v>22.06</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B279" s="5" t="n">
@@ -18029,7 +18081,7 @@
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D279" s="5" t="inlineStr">
@@ -18049,35 +18101,39 @@
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H279" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I279" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J279" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K279" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L279" s="5" t="n"/>
-      <c r="M279" s="5" t="n"/>
+      <c r="L279" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M279" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N279" s="5" t="n">
-        <v>6.79</v>
+        <v>21.92</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B280" s="5" t="n">
@@ -18085,7 +18141,7 @@
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D280" s="5" t="inlineStr">
@@ -18105,12 +18161,12 @@
       </c>
       <c r="G280" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H280" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I280" s="5" t="b">
@@ -18125,19 +18181,19 @@
         </is>
       </c>
       <c r="L280" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M280" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N280" s="5" t="n">
-        <v>4.06</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B281" s="5" t="n">
@@ -18145,34 +18201,34 @@
       </c>
       <c r="C281" s="5" t="inlineStr">
         <is>
+          <t>multilingual_edge</t>
+        </is>
+      </c>
+      <c r="D281" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="E281" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F281" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G281" s="5" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="H281" s="5" t="inlineStr">
+        <is>
           <t>ask_query</t>
         </is>
       </c>
-      <c r="D281" s="5" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="E281" s="5" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="F281" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G281" s="5" t="inlineStr">
-        <is>
-          <t>ask_query</t>
-        </is>
-      </c>
-      <c r="H281" s="5" t="inlineStr">
-        <is>
-          <t>ask_query</t>
-        </is>
-      </c>
       <c r="I281" s="5" t="b">
         <v>1</v>
       </c>
@@ -18185,19 +18241,19 @@
         </is>
       </c>
       <c r="L281" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M281" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N281" s="5" t="n">
-        <v>7.51</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B282" s="5" t="n">
@@ -18205,34 +18261,34 @@
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
+          <t>multilingual_edge</t>
+        </is>
+      </c>
+      <c r="D282" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="E282" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F282" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G282" s="5" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="H282" s="5" t="inlineStr">
+        <is>
           <t>ask_query</t>
         </is>
       </c>
-      <c r="D282" s="5" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="E282" s="5" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="F282" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G282" s="5" t="inlineStr">
-        <is>
-          <t>ask_query</t>
-        </is>
-      </c>
-      <c r="H282" s="5" t="inlineStr">
-        <is>
-          <t>ask_query</t>
-        </is>
-      </c>
       <c r="I282" s="5" t="b">
         <v>1</v>
       </c>
@@ -18245,19 +18301,19 @@
         </is>
       </c>
       <c r="L282" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M282" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N282" s="5" t="n">
-        <v>8.460000000000001</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B283" s="5" t="n">
@@ -18265,34 +18321,34 @@
       </c>
       <c r="C283" s="5" t="inlineStr">
         <is>
+          <t>multilingual_edge</t>
+        </is>
+      </c>
+      <c r="D283" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="E283" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F283" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G283" s="5" t="inlineStr">
+        <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="H283" s="5" t="inlineStr">
+        <is>
           <t>ask_query</t>
         </is>
       </c>
-      <c r="D283" s="5" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="E283" s="5" t="inlineStr">
-        <is>
-          <t>ar</t>
-        </is>
-      </c>
-      <c r="F283" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G283" s="5" t="inlineStr">
-        <is>
-          <t>ask_query</t>
-        </is>
-      </c>
-      <c r="H283" s="5" t="inlineStr">
-        <is>
-          <t>ask_query</t>
-        </is>
-      </c>
       <c r="I283" s="5" t="b">
         <v>1</v>
       </c>
@@ -18305,19 +18361,19 @@
         </is>
       </c>
       <c r="L283" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M283" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N283" s="5" t="n">
-        <v>4.94</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B284" s="5" t="n">
@@ -18325,7 +18381,7 @@
       </c>
       <c r="C284" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D284" s="5" t="inlineStr">
@@ -18371,13 +18427,13 @@
         <v>1</v>
       </c>
       <c r="N284" s="5" t="n">
-        <v>21.33</v>
+        <v>20.09</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B285" s="5" t="n">
@@ -18385,7 +18441,7 @@
       </c>
       <c r="C285" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D285" s="5" t="inlineStr">
@@ -18431,13 +18487,13 @@
         <v>1</v>
       </c>
       <c r="N285" s="5" t="n">
-        <v>21.07</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B286" s="5" t="n">
@@ -18445,7 +18501,7 @@
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D286" s="5" t="inlineStr">
@@ -18491,13 +18547,13 @@
         <v>1</v>
       </c>
       <c r="N286" s="5" t="n">
-        <v>20.4</v>
+        <v>21.93</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B287" s="5" t="n">
@@ -18505,7 +18561,7 @@
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D287" s="5" t="inlineStr">
@@ -18530,7 +18586,7 @@
       </c>
       <c r="H287" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I287" s="5" t="b">
@@ -18544,20 +18600,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L287" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M287" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L287" s="5" t="n"/>
+      <c r="M287" s="5" t="n"/>
       <c r="N287" s="5" t="n">
-        <v>34.24</v>
+        <v>14.53</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B288" s="5" t="n">
@@ -18565,7 +18617,7 @@
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D288" s="5" t="inlineStr">
@@ -18590,7 +18642,7 @@
       </c>
       <c r="H288" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I288" s="5" t="b">
@@ -18604,20 +18656,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L288" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M288" s="5" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="L288" s="5" t="n"/>
+      <c r="M288" s="5" t="n"/>
       <c r="N288" s="5" t="n">
-        <v>24.74</v>
+        <v>16.97</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B289" s="5" t="n">
@@ -18625,7 +18673,7 @@
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D289" s="5" t="inlineStr">
@@ -18650,7 +18698,7 @@
       </c>
       <c r="H289" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I289" s="5" t="b">
@@ -18664,20 +18712,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L289" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M289" s="5" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="L289" s="5" t="n"/>
+      <c r="M289" s="5" t="n"/>
       <c r="N289" s="5" t="n">
-        <v>39.64</v>
+        <v>18.95</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B290" s="5" t="n">
@@ -18685,7 +18729,7 @@
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D290" s="5" t="inlineStr">
@@ -18710,7 +18754,7 @@
       </c>
       <c r="H290" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I290" s="5" t="b">
@@ -18725,19 +18769,19 @@
         </is>
       </c>
       <c r="L290" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M290" s="5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N290" s="5" t="n">
-        <v>27.13</v>
+        <v>16.03</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B291" s="5" t="n">
@@ -18745,7 +18789,7 @@
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
@@ -18770,7 +18814,7 @@
       </c>
       <c r="H291" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I291" s="5" t="b">
@@ -18785,19 +18829,19 @@
         </is>
       </c>
       <c r="L291" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M291" s="5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N291" s="5" t="n">
-        <v>29.42</v>
+        <v>17.29</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B292" s="5" t="n">
@@ -18805,7 +18849,7 @@
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
@@ -18830,7 +18874,7 @@
       </c>
       <c r="H292" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I292" s="5" t="b">
@@ -18841,23 +18885,23 @@
       </c>
       <c r="K292" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L292" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M292" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N292" s="5" t="n">
-        <v>32.16</v>
+        <v>17.43</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B293" s="5" t="n">
@@ -18865,7 +18909,7 @@
       </c>
       <c r="C293" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D293" s="5" t="inlineStr">
@@ -18890,7 +18934,7 @@
       </c>
       <c r="H293" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I293" s="5" t="b">
@@ -18901,23 +18945,19 @@
       </c>
       <c r="K293" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L293" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M293" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>execution_failure</t>
+        </is>
+      </c>
+      <c r="L293" s="5" t="n"/>
+      <c r="M293" s="5" t="n"/>
       <c r="N293" s="5" t="n">
-        <v>26.34</v>
+        <v>15.17</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B294" s="5" t="n">
@@ -18925,7 +18965,7 @@
       </c>
       <c r="C294" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D294" s="5" t="inlineStr">
@@ -18950,7 +18990,7 @@
       </c>
       <c r="H294" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I294" s="5" t="b">
@@ -18964,20 +19004,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L294" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M294" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L294" s="5" t="n"/>
+      <c r="M294" s="5" t="n"/>
       <c r="N294" s="5" t="n">
-        <v>24.87</v>
+        <v>15.73</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B295" s="5" t="n">
@@ -18985,7 +19021,7 @@
       </c>
       <c r="C295" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D295" s="5" t="inlineStr">
@@ -19010,7 +19046,7 @@
       </c>
       <c r="H295" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I295" s="5" t="b">
@@ -19024,20 +19060,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L295" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M295" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L295" s="5" t="n"/>
+      <c r="M295" s="5" t="n"/>
       <c r="N295" s="5" t="n">
-        <v>24.72</v>
+        <v>16.63</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B296" s="5" t="n">
@@ -19045,7 +19077,7 @@
       </c>
       <c r="C296" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D296" s="5" t="inlineStr">
@@ -19070,7 +19102,7 @@
       </c>
       <c r="H296" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I296" s="5" t="b">
@@ -19084,20 +19116,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L296" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M296" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L296" s="5" t="n"/>
+      <c r="M296" s="5" t="n"/>
       <c r="N296" s="5" t="n">
-        <v>22.06</v>
+        <v>16.55</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B297" s="5" t="n">
@@ -19105,7 +19133,7 @@
       </c>
       <c r="C297" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D297" s="5" t="inlineStr">
@@ -19130,7 +19158,7 @@
       </c>
       <c r="H297" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I297" s="5" t="b">
@@ -19144,20 +19172,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L297" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M297" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L297" s="5" t="n"/>
+      <c r="M297" s="5" t="n"/>
       <c r="N297" s="5" t="n">
-        <v>21.92</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B298" s="5" t="n">
@@ -19165,7 +19189,7 @@
       </c>
       <c r="C298" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D298" s="5" t="inlineStr">
@@ -19190,7 +19214,7 @@
       </c>
       <c r="H298" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I298" s="5" t="b">
@@ -19204,33 +19228,29 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L298" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M298" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L298" s="5" t="n"/>
+      <c r="M298" s="5" t="n"/>
       <c r="N298" s="5" t="n">
-        <v>13.4</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>ranking_kg2_001</t>
         </is>
       </c>
       <c r="B299" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C299" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D299" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E299" s="5" t="inlineStr">
@@ -19245,12 +19265,12 @@
       </c>
       <c r="G299" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H299" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I299" s="5" t="b">
@@ -19265,32 +19285,32 @@
         </is>
       </c>
       <c r="L299" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M299" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N299" s="5" t="n">
-        <v>6.67</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>ranking_kg2_001</t>
         </is>
       </c>
       <c r="B300" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C300" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D300" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E300" s="5" t="inlineStr">
@@ -19305,12 +19325,12 @@
       </c>
       <c r="G300" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H300" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I300" s="5" t="b">
@@ -19325,32 +19345,32 @@
         </is>
       </c>
       <c r="L300" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M300" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N300" s="5" t="n">
-        <v>7.35</v>
+        <v>14.12</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>ranking_kg2_001</t>
         </is>
       </c>
       <c r="B301" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D301" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E301" s="5" t="inlineStr">
@@ -19365,12 +19385,12 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I301" s="5" t="b">
@@ -19385,32 +19405,32 @@
         </is>
       </c>
       <c r="L301" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M301" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N301" s="5" t="n">
-        <v>4.44</v>
+        <v>14.12</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>ranking_kg2_002</t>
         </is>
       </c>
       <c r="B302" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C302" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D302" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E302" s="5" t="inlineStr">
@@ -19425,12 +19445,12 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I302" s="5" t="b">
@@ -19445,32 +19465,32 @@
         </is>
       </c>
       <c r="L302" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M302" s="5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N302" s="5" t="n">
-        <v>20.09</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>ranking_kg2_002</t>
         </is>
       </c>
       <c r="B303" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C303" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E303" s="5" t="inlineStr">
@@ -19485,12 +19505,12 @@
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H303" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I303" s="5" t="b">
@@ -19505,32 +19525,32 @@
         </is>
       </c>
       <c r="L303" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M303" s="5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N303" s="5" t="n">
-        <v>22.25</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>ranking_kg2_002</t>
         </is>
       </c>
       <c r="B304" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C304" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D304" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E304" s="5" t="inlineStr">
@@ -19545,12 +19565,12 @@
       </c>
       <c r="G304" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H304" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I304" s="5" t="b">
@@ -19565,32 +19585,32 @@
         </is>
       </c>
       <c r="L304" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M304" s="5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N304" s="5" t="n">
-        <v>21.93</v>
+        <v>13.63</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>ranking_kg2_003</t>
         </is>
       </c>
       <c r="B305" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C305" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D305" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E305" s="5" t="inlineStr">
@@ -19605,12 +19625,12 @@
       </c>
       <c r="G305" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H305" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I305" s="5" t="b">
@@ -19624,29 +19644,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L305" s="5" t="n"/>
-      <c r="M305" s="5" t="n"/>
+      <c r="L305" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M305" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N305" s="5" t="n">
-        <v>14.53</v>
+        <v>13.71</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>ranking_kg2_003</t>
         </is>
       </c>
       <c r="B306" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C306" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D306" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E306" s="5" t="inlineStr">
@@ -19661,12 +19685,12 @@
       </c>
       <c r="G306" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H306" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I306" s="5" t="b">
@@ -19680,29 +19704,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L306" s="5" t="n"/>
-      <c r="M306" s="5" t="n"/>
+      <c r="L306" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M306" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N306" s="5" t="n">
-        <v>16.97</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>ranking_kg2_003</t>
         </is>
       </c>
       <c r="B307" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C307" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D307" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E307" s="5" t="inlineStr">
@@ -19717,12 +19745,12 @@
       </c>
       <c r="G307" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H307" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I307" s="5" t="b">
@@ -19736,29 +19764,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L307" s="5" t="n"/>
-      <c r="M307" s="5" t="n"/>
+      <c r="L307" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M307" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N307" s="5" t="n">
-        <v>18.95</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>open_kg_001</t>
         </is>
       </c>
       <c r="B308" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C308" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D308" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E308" s="5" t="inlineStr">
@@ -19773,12 +19805,12 @@
       </c>
       <c r="G308" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H308" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I308" s="5" t="b">
@@ -19792,33 +19824,29 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L308" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M308" s="5" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="L308" s="5" t="n"/>
+      <c r="M308" s="5" t="n"/>
       <c r="N308" s="5" t="n">
-        <v>16.03</v>
+        <v>29.65</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>open_kg_001</t>
         </is>
       </c>
       <c r="B309" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C309" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D309" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E309" s="5" t="inlineStr">
@@ -19833,12 +19861,12 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I309" s="5" t="b">
@@ -19852,33 +19880,29 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L309" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M309" s="5" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="L309" s="5" t="n"/>
+      <c r="M309" s="5" t="n"/>
       <c r="N309" s="5" t="n">
-        <v>17.29</v>
+        <v>28.33</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>open_kg_001</t>
         </is>
       </c>
       <c r="B310" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C310" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D310" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E310" s="5" t="inlineStr">
@@ -19893,52 +19917,48 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I310" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J310" s="5" t="b">
         <v>1</v>
       </c>
       <c r="K310" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L310" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M310" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L310" s="5" t="n"/>
+      <c r="M310" s="5" t="n"/>
       <c r="N310" s="5" t="n">
-        <v>17.43</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>open_kg_005</t>
         </is>
       </c>
       <c r="B311" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C311" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D311" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E311" s="5" t="inlineStr">
@@ -19953,19 +19973,19 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I311" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J311" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K311" s="5" t="inlineStr">
         <is>
@@ -19975,26 +19995,26 @@
       <c r="L311" s="5" t="n"/>
       <c r="M311" s="5" t="n"/>
       <c r="N311" s="5" t="n">
-        <v>15.17</v>
+        <v>12.44</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>open_kg_005</t>
         </is>
       </c>
       <c r="B312" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C312" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D312" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E312" s="5" t="inlineStr">
@@ -20009,48 +20029,48 @@
       </c>
       <c r="G312" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H312" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I312" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J312" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K312" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L312" s="5" t="n"/>
       <c r="M312" s="5" t="n"/>
       <c r="N312" s="5" t="n">
-        <v>15.73</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>open_kg_005</t>
         </is>
       </c>
       <c r="B313" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C313" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E313" s="5" t="inlineStr">
@@ -20065,12 +20085,12 @@
       </c>
       <c r="G313" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H313" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I313" s="5" t="b">
@@ -20087,26 +20107,26 @@
       <c r="L313" s="5" t="n"/>
       <c r="M313" s="5" t="n"/>
       <c r="N313" s="5" t="n">
-        <v>16.63</v>
+        <v>31.63</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>open_kg_006</t>
         </is>
       </c>
       <c r="B314" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C314" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D314" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E314" s="5" t="inlineStr">
@@ -20121,12 +20141,12 @@
       </c>
       <c r="G314" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H314" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I314" s="5" t="b">
@@ -20143,26 +20163,26 @@
       <c r="L314" s="5" t="n"/>
       <c r="M314" s="5" t="n"/>
       <c r="N314" s="5" t="n">
-        <v>16.55</v>
+        <v>28.86</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>open_kg_006</t>
         </is>
       </c>
       <c r="B315" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C315" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D315" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E315" s="5" t="inlineStr">
@@ -20177,12 +20197,12 @@
       </c>
       <c r="G315" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H315" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I315" s="5" t="b">
@@ -20199,26 +20219,26 @@
       <c r="L315" s="5" t="n"/>
       <c r="M315" s="5" t="n"/>
       <c r="N315" s="5" t="n">
-        <v>16.57</v>
+        <v>28.82</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>open_kg_006</t>
         </is>
       </c>
       <c r="B316" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C316" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D316" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E316" s="5" t="inlineStr">
@@ -20233,16 +20253,16 @@
       </c>
       <c r="G316" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H316" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I316" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J316" s="5" t="b">
         <v>1</v>
@@ -20255,13 +20275,13 @@
       <c r="L316" s="5" t="n"/>
       <c r="M316" s="5" t="n"/>
       <c r="N316" s="5" t="n">
-        <v>15.5</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_001</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B317" s="5" t="n">
@@ -20269,7 +20289,7 @@
       </c>
       <c r="C317" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D317" s="5" t="inlineStr">
@@ -20315,13 +20335,13 @@
         <v>1</v>
       </c>
       <c r="N317" s="5" t="n">
-        <v>34.3</v>
+        <v>14.97</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_001</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B318" s="5" t="n">
@@ -20329,7 +20349,7 @@
       </c>
       <c r="C318" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D318" s="5" t="inlineStr">
@@ -20354,34 +20374,34 @@
       </c>
       <c r="H318" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I318" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J318" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K318" s="5" t="inlineStr">
         <is>
-          <t>generation_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L318" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M318" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N318" s="5" t="n">
-        <v>51.14</v>
+        <v>14.68</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_001</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B319" s="5" t="n">
@@ -20389,7 +20409,7 @@
       </c>
       <c r="C319" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D319" s="5" t="inlineStr">
@@ -20435,13 +20455,13 @@
         <v>1</v>
       </c>
       <c r="N319" s="5" t="n">
-        <v>17.12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_002</t>
+          <t>filter_string_kg2_002</t>
         </is>
       </c>
       <c r="B320" s="5" t="n">
@@ -20449,7 +20469,7 @@
       </c>
       <c r="C320" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D320" s="5" t="inlineStr">
@@ -20481,27 +20501,23 @@
         <v>1</v>
       </c>
       <c r="J320" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K320" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L320" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M320" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L320" s="5" t="n"/>
+      <c r="M320" s="5" t="n"/>
       <c r="N320" s="5" t="n">
-        <v>16.33</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_002</t>
+          <t>filter_string_kg2_002</t>
         </is>
       </c>
       <c r="B321" s="5" t="n">
@@ -20509,7 +20525,7 @@
       </c>
       <c r="C321" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D321" s="5" t="inlineStr">
@@ -20548,20 +20564,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L321" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M321" s="5" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="L321" s="5" t="n"/>
+      <c r="M321" s="5" t="n"/>
       <c r="N321" s="5" t="n">
-        <v>15.94</v>
+        <v>12.92</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_002</t>
+          <t>filter_string_kg2_002</t>
         </is>
       </c>
       <c r="B322" s="5" t="n">
@@ -20569,7 +20581,7 @@
       </c>
       <c r="C322" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D322" s="5" t="inlineStr">
@@ -20608,33 +20620,29 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L322" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M322" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L322" s="5" t="n"/>
+      <c r="M322" s="5" t="n"/>
       <c r="N322" s="5" t="n">
-        <v>12.28</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_003</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B323" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C323" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E323" s="5" t="inlineStr">
@@ -20649,12 +20657,12 @@
       </c>
       <c r="G323" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H323" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I323" s="5" t="b">
@@ -20665,36 +20673,32 @@
       </c>
       <c r="K323" s="5" t="inlineStr">
         <is>
-          <t>generation_failure</t>
-        </is>
-      </c>
-      <c r="L323" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M323" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L323" s="5" t="n"/>
+      <c r="M323" s="5" t="n"/>
       <c r="N323" s="5" t="n">
-        <v>40.39</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_003</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B324" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C324" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D324" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E324" s="5" t="inlineStr">
@@ -20709,52 +20713,48 @@
       </c>
       <c r="G324" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H324" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I324" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J324" s="5" t="b">
         <v>0</v>
       </c>
       <c r="K324" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L324" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M324" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L324" s="5" t="n"/>
+      <c r="M324" s="5" t="n"/>
       <c r="N324" s="5" t="n">
-        <v>17.44</v>
+        <v>8.27</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_003</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B325" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C325" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E325" s="5" t="inlineStr">
@@ -20769,12 +20769,12 @@
       </c>
       <c r="G325" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H325" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I325" s="5" t="b">
@@ -20795,7 +20795,7 @@
         <v>1</v>
       </c>
       <c r="N325" s="5" t="n">
-        <v>14.68</v>
+        <v>4.41</v>
       </c>
     </row>
   </sheetData>

--- a/NL2SPARQL_Evaluation_Results.xlsx
+++ b/NL2SPARQL_Evaluation_Results.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Raw" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw'!$A$1:$N$322</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw'!$A$1:$N$325</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -551,27 +551,27 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Raw!E2:E322,"en")</f>
+        <f>COUNTIF(Raw!E2:E325,"en")</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E322,"en",Raw!I2:I322,TRUE)/COUNTIF(Raw!E2:E322,"en"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E325,"en",Raw!I2:I325,TRUE)/COUNTIF(Raw!E2:E325,"en"),"")</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E322,"en",Raw!K2:K322,"success")/COUNTIF(Raw!E2:E322,"en"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E325,"en",Raw!K2:K325,"success")/COUNTIF(Raw!E2:E325,"en"),"")</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E322,"en",Raw!J2:J322,TRUE)/COUNTIF(Raw!E2:E322,"en"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E325,"en",Raw!J2:J325,TRUE)/COUNTIF(Raw!E2:E325,"en"),"")</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!E2:E322,"en"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!E2:E325,"en"),"")</f>
         <v/>
       </c>
       <c r="G6" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!E2:E322,"en"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!E2:E325,"en"),"")</f>
         <v/>
       </c>
     </row>
@@ -582,27 +582,27 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Raw!E2:E322,"fr")</f>
+        <f>COUNTIF(Raw!E2:E325,"fr")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E322,"fr",Raw!I2:I322,TRUE)/COUNTIF(Raw!E2:E322,"fr"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E325,"fr",Raw!I2:I325,TRUE)/COUNTIF(Raw!E2:E325,"fr"),"")</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E322,"fr",Raw!K2:K322,"success")/COUNTIF(Raw!E2:E322,"fr"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E325,"fr",Raw!K2:K325,"success")/COUNTIF(Raw!E2:E325,"fr"),"")</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E322,"fr",Raw!J2:J322,TRUE)/COUNTIF(Raw!E2:E322,"fr"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E325,"fr",Raw!J2:J325,TRUE)/COUNTIF(Raw!E2:E325,"fr"),"")</f>
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!E2:E322,"fr"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!E2:E325,"fr"),"")</f>
         <v/>
       </c>
       <c r="G7" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!E2:E322,"fr"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!E2:E325,"fr"),"")</f>
         <v/>
       </c>
     </row>
@@ -613,27 +613,27 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Raw!E2:E322,"ar")</f>
+        <f>COUNTIF(Raw!E2:E325,"ar")</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E322,"ar",Raw!I2:I322,TRUE)/COUNTIF(Raw!E2:E322,"ar"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E325,"ar",Raw!I2:I325,TRUE)/COUNTIF(Raw!E2:E325,"ar"),"")</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E322,"ar",Raw!K2:K322,"success")/COUNTIF(Raw!E2:E322,"ar"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E325,"ar",Raw!K2:K325,"success")/COUNTIF(Raw!E2:E325,"ar"),"")</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E322,"ar",Raw!J2:J322,TRUE)/COUNTIF(Raw!E2:E322,"ar"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E325,"ar",Raw!J2:J325,TRUE)/COUNTIF(Raw!E2:E325,"ar"),"")</f>
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!E2:E322,"ar"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!E2:E325,"ar"),"")</f>
         <v/>
       </c>
       <c r="G8" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!E2:E322,"ar"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!E2:E325,"ar"),"")</f>
         <v/>
       </c>
     </row>
@@ -688,27 +688,27 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIF(Raw!F2:F322,"zero-shot")</f>
+        <f>COUNTIF(Raw!F2:F325,"zero-shot")</f>
         <v/>
       </c>
       <c r="C12" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F322,"zero-shot",Raw!I2:I322,TRUE)/COUNTIF(Raw!F2:F322,"zero-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F325,"zero-shot",Raw!I2:I325,TRUE)/COUNTIF(Raw!F2:F325,"zero-shot"),"")</f>
         <v/>
       </c>
       <c r="D12" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F322,"zero-shot",Raw!K2:K322,"success")/COUNTIF(Raw!F2:F322,"zero-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F325,"zero-shot",Raw!K2:K325,"success")/COUNTIF(Raw!F2:F325,"zero-shot"),"")</f>
         <v/>
       </c>
       <c r="E12" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F322,"zero-shot",Raw!J2:J322,TRUE)/COUNTIF(Raw!F2:F322,"zero-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F325,"zero-shot",Raw!J2:J325,TRUE)/COUNTIF(Raw!F2:F325,"zero-shot"),"")</f>
         <v/>
       </c>
       <c r="F12" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!F2:F322,"zero-shot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!F2:F325,"zero-shot"),"")</f>
         <v/>
       </c>
       <c r="G12" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!F2:F322,"zero-shot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!F2:F325,"zero-shot"),"")</f>
         <v/>
       </c>
     </row>
@@ -719,27 +719,27 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIF(Raw!F2:F322,"few-shot")</f>
+        <f>COUNTIF(Raw!F2:F325,"few-shot")</f>
         <v/>
       </c>
       <c r="C13" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F322,"few-shot",Raw!I2:I322,TRUE)/COUNTIF(Raw!F2:F322,"few-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F325,"few-shot",Raw!I2:I325,TRUE)/COUNTIF(Raw!F2:F325,"few-shot"),"")</f>
         <v/>
       </c>
       <c r="D13" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F322,"few-shot",Raw!K2:K322,"success")/COUNTIF(Raw!F2:F322,"few-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F325,"few-shot",Raw!K2:K325,"success")/COUNTIF(Raw!F2:F325,"few-shot"),"")</f>
         <v/>
       </c>
       <c r="E13" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F322,"few-shot",Raw!J2:J322,TRUE)/COUNTIF(Raw!F2:F322,"few-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F325,"few-shot",Raw!J2:J325,TRUE)/COUNTIF(Raw!F2:F325,"few-shot"),"")</f>
         <v/>
       </c>
       <c r="F13" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!F2:F322,"few-shot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!F2:F325,"few-shot"),"")</f>
         <v/>
       </c>
       <c r="G13" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!F2:F322,"few-shot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!F2:F325,"few-shot"),"")</f>
         <v/>
       </c>
     </row>
@@ -750,27 +750,27 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIF(Raw!F2:F322,"cot")</f>
+        <f>COUNTIF(Raw!F2:F325,"cot")</f>
         <v/>
       </c>
       <c r="C14" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F322,"cot",Raw!I2:I322,TRUE)/COUNTIF(Raw!F2:F322,"cot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F325,"cot",Raw!I2:I325,TRUE)/COUNTIF(Raw!F2:F325,"cot"),"")</f>
         <v/>
       </c>
       <c r="D14" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F322,"cot",Raw!K2:K322,"success")/COUNTIF(Raw!F2:F322,"cot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F325,"cot",Raw!K2:K325,"success")/COUNTIF(Raw!F2:F325,"cot"),"")</f>
         <v/>
       </c>
       <c r="E14" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F322,"cot",Raw!J2:J322,TRUE)/COUNTIF(Raw!F2:F322,"cot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F325,"cot",Raw!J2:J325,TRUE)/COUNTIF(Raw!F2:F325,"cot"),"")</f>
         <v/>
       </c>
       <c r="F14" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!F2:F322,"cot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!F2:F325,"cot"),"")</f>
         <v/>
       </c>
       <c r="G14" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!F2:F322,"cot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!F2:F325,"cot"),"")</f>
         <v/>
       </c>
     </row>
@@ -823,27 +823,27 @@
         <v>1</v>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Raw!B2:B322,"1")</f>
+        <f>COUNTIF(Raw!B2:B325,"1")</f>
         <v/>
       </c>
       <c r="C18" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B322,"1",Raw!I2:I322,TRUE)/COUNTIF(Raw!B2:B322,"1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B325,"1",Raw!I2:I325,TRUE)/COUNTIF(Raw!B2:B325,"1"),"")</f>
         <v/>
       </c>
       <c r="D18" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B322,"1",Raw!K2:K322,"success")/COUNTIF(Raw!B2:B322,"1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B325,"1",Raw!K2:K325,"success")/COUNTIF(Raw!B2:B325,"1"),"")</f>
         <v/>
       </c>
       <c r="E18" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B322,"1",Raw!J2:J322,TRUE)/COUNTIF(Raw!B2:B322,"1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B325,"1",Raw!J2:J325,TRUE)/COUNTIF(Raw!B2:B325,"1"),"")</f>
         <v/>
       </c>
       <c r="F18" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!B2:B322,"1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!B2:B325,"1"),"")</f>
         <v/>
       </c>
       <c r="G18" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!B2:B322,"1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!B2:B325,"1"),"")</f>
         <v/>
       </c>
     </row>
@@ -852,27 +852,27 @@
         <v>2</v>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Raw!B2:B322,"2")</f>
+        <f>COUNTIF(Raw!B2:B325,"2")</f>
         <v/>
       </c>
       <c r="C19" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B322,"2",Raw!I2:I322,TRUE)/COUNTIF(Raw!B2:B322,"2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B325,"2",Raw!I2:I325,TRUE)/COUNTIF(Raw!B2:B325,"2"),"")</f>
         <v/>
       </c>
       <c r="D19" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B322,"2",Raw!K2:K322,"success")/COUNTIF(Raw!B2:B322,"2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B325,"2",Raw!K2:K325,"success")/COUNTIF(Raw!B2:B325,"2"),"")</f>
         <v/>
       </c>
       <c r="E19" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B322,"2",Raw!J2:J322,TRUE)/COUNTIF(Raw!B2:B322,"2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B325,"2",Raw!J2:J325,TRUE)/COUNTIF(Raw!B2:B325,"2"),"")</f>
         <v/>
       </c>
       <c r="F19" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!B2:B322,"2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!B2:B325,"2"),"")</f>
         <v/>
       </c>
       <c r="G19" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!B2:B322,"2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!B2:B325,"2"),"")</f>
         <v/>
       </c>
     </row>
@@ -881,27 +881,27 @@
         <v>3</v>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Raw!B2:B322,"3")</f>
+        <f>COUNTIF(Raw!B2:B325,"3")</f>
         <v/>
       </c>
       <c r="C20" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B322,"3",Raw!I2:I322,TRUE)/COUNTIF(Raw!B2:B322,"3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B325,"3",Raw!I2:I325,TRUE)/COUNTIF(Raw!B2:B325,"3"),"")</f>
         <v/>
       </c>
       <c r="D20" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B322,"3",Raw!K2:K322,"success")/COUNTIF(Raw!B2:B322,"3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B325,"3",Raw!K2:K325,"success")/COUNTIF(Raw!B2:B325,"3"),"")</f>
         <v/>
       </c>
       <c r="E20" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B322,"3",Raw!J2:J322,TRUE)/COUNTIF(Raw!B2:B322,"3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B325,"3",Raw!J2:J325,TRUE)/COUNTIF(Raw!B2:B325,"3"),"")</f>
         <v/>
       </c>
       <c r="F20" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!B2:B322,"3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!B2:B325,"3"),"")</f>
         <v/>
       </c>
       <c r="G20" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!B2:B322,"3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!B2:B325,"3"),"")</f>
         <v/>
       </c>
     </row>
@@ -956,27 +956,27 @@
         </is>
       </c>
       <c r="B24" s="5">
-        <f>COUNTIF(Raw!C2:C322,"single_kg1")</f>
+        <f>COUNTIF(Raw!C2:C325,"single_kg1")</f>
         <v/>
       </c>
       <c r="C24" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"single_kg1",Raw!I2:I322,TRUE)/COUNTIF(Raw!C2:C322,"single_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"single_kg1",Raw!I2:I325,TRUE)/COUNTIF(Raw!C2:C325,"single_kg1"),"")</f>
         <v/>
       </c>
       <c r="D24" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"single_kg1",Raw!K2:K322,"success")/COUNTIF(Raw!C2:C322,"single_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"single_kg1",Raw!K2:K325,"success")/COUNTIF(Raw!C2:C325,"single_kg1"),"")</f>
         <v/>
       </c>
       <c r="E24" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"single_kg1",Raw!J2:J322,TRUE)/COUNTIF(Raw!C2:C322,"single_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"single_kg1",Raw!J2:J325,TRUE)/COUNTIF(Raw!C2:C325,"single_kg1"),"")</f>
         <v/>
       </c>
       <c r="F24" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!C2:C322,"single_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"single_kg1"),"")</f>
         <v/>
       </c>
       <c r="G24" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!C2:C322,"single_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"single_kg1"),"")</f>
         <v/>
       </c>
     </row>
@@ -987,27 +987,27 @@
         </is>
       </c>
       <c r="B25" s="5">
-        <f>COUNTIF(Raw!C2:C322,"single_kg2")</f>
+        <f>COUNTIF(Raw!C2:C325,"single_kg2")</f>
         <v/>
       </c>
       <c r="C25" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"single_kg2",Raw!I2:I322,TRUE)/COUNTIF(Raw!C2:C322,"single_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"single_kg2",Raw!I2:I325,TRUE)/COUNTIF(Raw!C2:C325,"single_kg2"),"")</f>
         <v/>
       </c>
       <c r="D25" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"single_kg2",Raw!K2:K322,"success")/COUNTIF(Raw!C2:C322,"single_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"single_kg2",Raw!K2:K325,"success")/COUNTIF(Raw!C2:C325,"single_kg2"),"")</f>
         <v/>
       </c>
       <c r="E25" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"single_kg2",Raw!J2:J322,TRUE)/COUNTIF(Raw!C2:C322,"single_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"single_kg2",Raw!J2:J325,TRUE)/COUNTIF(Raw!C2:C325,"single_kg2"),"")</f>
         <v/>
       </c>
       <c r="F25" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!C2:C322,"single_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"single_kg2"),"")</f>
         <v/>
       </c>
       <c r="G25" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!C2:C322,"single_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"single_kg2"),"")</f>
         <v/>
       </c>
     </row>
@@ -1018,27 +1018,27 @@
         </is>
       </c>
       <c r="B26" s="5">
-        <f>COUNTIF(Raw!C2:C322,"cross_kg")</f>
+        <f>COUNTIF(Raw!C2:C325,"cross_kg")</f>
         <v/>
       </c>
       <c r="C26" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"cross_kg",Raw!I2:I322,TRUE)/COUNTIF(Raw!C2:C322,"cross_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"cross_kg",Raw!I2:I325,TRUE)/COUNTIF(Raw!C2:C325,"cross_kg"),"")</f>
         <v/>
       </c>
       <c r="D26" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"cross_kg",Raw!K2:K322,"success")/COUNTIF(Raw!C2:C322,"cross_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"cross_kg",Raw!K2:K325,"success")/COUNTIF(Raw!C2:C325,"cross_kg"),"")</f>
         <v/>
       </c>
       <c r="E26" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"cross_kg",Raw!J2:J322,TRUE)/COUNTIF(Raw!C2:C322,"cross_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"cross_kg",Raw!J2:J325,TRUE)/COUNTIF(Raw!C2:C325,"cross_kg"),"")</f>
         <v/>
       </c>
       <c r="F26" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!C2:C322,"cross_kg"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"cross_kg"),"")</f>
         <v/>
       </c>
       <c r="G26" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!C2:C322,"cross_kg"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"cross_kg"),"")</f>
         <v/>
       </c>
     </row>
@@ -1049,27 +1049,27 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Raw!C2:C322,"open_kg")</f>
+        <f>COUNTIF(Raw!C2:C325,"open_kg")</f>
         <v/>
       </c>
       <c r="C27" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"open_kg",Raw!I2:I322,TRUE)/COUNTIF(Raw!C2:C322,"open_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"open_kg",Raw!I2:I325,TRUE)/COUNTIF(Raw!C2:C325,"open_kg"),"")</f>
         <v/>
       </c>
       <c r="D27" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"open_kg",Raw!K2:K322,"success")/COUNTIF(Raw!C2:C322,"open_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"open_kg",Raw!K2:K325,"success")/COUNTIF(Raw!C2:C325,"open_kg"),"")</f>
         <v/>
       </c>
       <c r="E27" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"open_kg",Raw!J2:J322,TRUE)/COUNTIF(Raw!C2:C322,"open_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"open_kg",Raw!J2:J325,TRUE)/COUNTIF(Raw!C2:C325,"open_kg"),"")</f>
         <v/>
       </c>
       <c r="F27" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!C2:C322,"open_kg"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"open_kg"),"")</f>
         <v/>
       </c>
       <c r="G27" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!C2:C322,"open_kg"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"open_kg"),"")</f>
         <v/>
       </c>
     </row>
@@ -1080,27 +1080,27 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Raw!C2:C322,"count_kg1")</f>
+        <f>COUNTIF(Raw!C2:C325,"count_kg1")</f>
         <v/>
       </c>
       <c r="C28" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"count_kg1",Raw!I2:I322,TRUE)/COUNTIF(Raw!C2:C322,"count_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"count_kg1",Raw!I2:I325,TRUE)/COUNTIF(Raw!C2:C325,"count_kg1"),"")</f>
         <v/>
       </c>
       <c r="D28" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"count_kg1",Raw!K2:K322,"success")/COUNTIF(Raw!C2:C322,"count_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"count_kg1",Raw!K2:K325,"success")/COUNTIF(Raw!C2:C325,"count_kg1"),"")</f>
         <v/>
       </c>
       <c r="E28" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"count_kg1",Raw!J2:J322,TRUE)/COUNTIF(Raw!C2:C322,"count_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"count_kg1",Raw!J2:J325,TRUE)/COUNTIF(Raw!C2:C325,"count_kg1"),"")</f>
         <v/>
       </c>
       <c r="F28" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!C2:C322,"count_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"count_kg1"),"")</f>
         <v/>
       </c>
       <c r="G28" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!C2:C322,"count_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"count_kg1"),"")</f>
         <v/>
       </c>
     </row>
@@ -1111,27 +1111,27 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Raw!C2:C322,"filter_numeric_kg1")</f>
+        <f>COUNTIF(Raw!C2:C325,"filter_numeric_kg1")</f>
         <v/>
       </c>
       <c r="C29" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"filter_numeric_kg1",Raw!I2:I322,TRUE)/COUNTIF(Raw!C2:C322,"filter_numeric_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"filter_numeric_kg1",Raw!I2:I325,TRUE)/COUNTIF(Raw!C2:C325,"filter_numeric_kg1"),"")</f>
         <v/>
       </c>
       <c r="D29" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"filter_numeric_kg1",Raw!K2:K322,"success")/COUNTIF(Raw!C2:C322,"filter_numeric_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"filter_numeric_kg1",Raw!K2:K325,"success")/COUNTIF(Raw!C2:C325,"filter_numeric_kg1"),"")</f>
         <v/>
       </c>
       <c r="E29" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"filter_numeric_kg1",Raw!J2:J322,TRUE)/COUNTIF(Raw!C2:C322,"filter_numeric_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"filter_numeric_kg1",Raw!J2:J325,TRUE)/COUNTIF(Raw!C2:C325,"filter_numeric_kg1"),"")</f>
         <v/>
       </c>
       <c r="F29" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!C2:C322,"filter_numeric_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"filter_numeric_kg1"),"")</f>
         <v/>
       </c>
       <c r="G29" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!C2:C322,"filter_numeric_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"filter_numeric_kg1"),"")</f>
         <v/>
       </c>
     </row>
@@ -1142,27 +1142,27 @@
         </is>
       </c>
       <c r="B30" s="5">
-        <f>COUNTIF(Raw!C2:C322,"filter_numeric_kg2")</f>
+        <f>COUNTIF(Raw!C2:C325,"filter_numeric_kg2")</f>
         <v/>
       </c>
       <c r="C30" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"filter_numeric_kg2",Raw!I2:I322,TRUE)/COUNTIF(Raw!C2:C322,"filter_numeric_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"filter_numeric_kg2",Raw!I2:I325,TRUE)/COUNTIF(Raw!C2:C325,"filter_numeric_kg2"),"")</f>
         <v/>
       </c>
       <c r="D30" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"filter_numeric_kg2",Raw!K2:K322,"success")/COUNTIF(Raw!C2:C322,"filter_numeric_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"filter_numeric_kg2",Raw!K2:K325,"success")/COUNTIF(Raw!C2:C325,"filter_numeric_kg2"),"")</f>
         <v/>
       </c>
       <c r="E30" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"filter_numeric_kg2",Raw!J2:J322,TRUE)/COUNTIF(Raw!C2:C322,"filter_numeric_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"filter_numeric_kg2",Raw!J2:J325,TRUE)/COUNTIF(Raw!C2:C325,"filter_numeric_kg2"),"")</f>
         <v/>
       </c>
       <c r="F30" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!C2:C322,"filter_numeric_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"filter_numeric_kg2"),"")</f>
         <v/>
       </c>
       <c r="G30" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!C2:C322,"filter_numeric_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"filter_numeric_kg2"),"")</f>
         <v/>
       </c>
     </row>
@@ -1173,27 +1173,27 @@
         </is>
       </c>
       <c r="B31" s="5">
-        <f>COUNTIF(Raw!C2:C322,"filter_string_kg2")</f>
+        <f>COUNTIF(Raw!C2:C325,"filter_string_kg2")</f>
         <v/>
       </c>
       <c r="C31" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"filter_string_kg2",Raw!I2:I322,TRUE)/COUNTIF(Raw!C2:C322,"filter_string_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"filter_string_kg2",Raw!I2:I325,TRUE)/COUNTIF(Raw!C2:C325,"filter_string_kg2"),"")</f>
         <v/>
       </c>
       <c r="D31" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"filter_string_kg2",Raw!K2:K322,"success")/COUNTIF(Raw!C2:C322,"filter_string_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"filter_string_kg2",Raw!K2:K325,"success")/COUNTIF(Raw!C2:C325,"filter_string_kg2"),"")</f>
         <v/>
       </c>
       <c r="E31" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"filter_string_kg2",Raw!J2:J322,TRUE)/COUNTIF(Raw!C2:C322,"filter_string_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"filter_string_kg2",Raw!J2:J325,TRUE)/COUNTIF(Raw!C2:C325,"filter_string_kg2"),"")</f>
         <v/>
       </c>
       <c r="F31" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!C2:C322,"filter_string_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"filter_string_kg2"),"")</f>
         <v/>
       </c>
       <c r="G31" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!C2:C322,"filter_string_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"filter_string_kg2"),"")</f>
         <v/>
       </c>
     </row>
@@ -1204,27 +1204,27 @@
         </is>
       </c>
       <c r="B32" s="5">
-        <f>COUNTIF(Raw!C2:C322,"ranking_kg2")</f>
+        <f>COUNTIF(Raw!C2:C325,"ranking_kg2")</f>
         <v/>
       </c>
       <c r="C32" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"ranking_kg2",Raw!I2:I322,TRUE)/COUNTIF(Raw!C2:C322,"ranking_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"ranking_kg2",Raw!I2:I325,TRUE)/COUNTIF(Raw!C2:C325,"ranking_kg2"),"")</f>
         <v/>
       </c>
       <c r="D32" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"ranking_kg2",Raw!K2:K322,"success")/COUNTIF(Raw!C2:C322,"ranking_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"ranking_kg2",Raw!K2:K325,"success")/COUNTIF(Raw!C2:C325,"ranking_kg2"),"")</f>
         <v/>
       </c>
       <c r="E32" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"ranking_kg2",Raw!J2:J322,TRUE)/COUNTIF(Raw!C2:C322,"ranking_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"ranking_kg2",Raw!J2:J325,TRUE)/COUNTIF(Raw!C2:C325,"ranking_kg2"),"")</f>
         <v/>
       </c>
       <c r="F32" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!C2:C322,"ranking_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"ranking_kg2"),"")</f>
         <v/>
       </c>
       <c r="G32" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!C2:C322,"ranking_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"ranking_kg2"),"")</f>
         <v/>
       </c>
     </row>
@@ -1235,27 +1235,27 @@
         </is>
       </c>
       <c r="B33" s="5">
-        <f>COUNTIF(Raw!C2:C322,"compare_two_airports")</f>
+        <f>COUNTIF(Raw!C2:C325,"compare_two_airports")</f>
         <v/>
       </c>
       <c r="C33" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"compare_two_airports",Raw!I2:I322,TRUE)/COUNTIF(Raw!C2:C322,"compare_two_airports"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"compare_two_airports",Raw!I2:I325,TRUE)/COUNTIF(Raw!C2:C325,"compare_two_airports"),"")</f>
         <v/>
       </c>
       <c r="D33" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"compare_two_airports",Raw!K2:K322,"success")/COUNTIF(Raw!C2:C322,"compare_two_airports"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"compare_two_airports",Raw!K2:K325,"success")/COUNTIF(Raw!C2:C325,"compare_two_airports"),"")</f>
         <v/>
       </c>
       <c r="E33" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"compare_two_airports",Raw!J2:J322,TRUE)/COUNTIF(Raw!C2:C322,"compare_two_airports"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"compare_two_airports",Raw!J2:J325,TRUE)/COUNTIF(Raw!C2:C325,"compare_two_airports"),"")</f>
         <v/>
       </c>
       <c r="F33" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!C2:C322,"compare_two_airports"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"compare_two_airports"),"")</f>
         <v/>
       </c>
       <c r="G33" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!C2:C322,"compare_two_airports"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"compare_two_airports"),"")</f>
         <v/>
       </c>
     </row>
@@ -1266,27 +1266,27 @@
         </is>
       </c>
       <c r="B34" s="5">
-        <f>COUNTIF(Raw!C2:C322,"out_of_scope")</f>
+        <f>COUNTIF(Raw!C2:C325,"out_of_scope")</f>
         <v/>
       </c>
       <c r="C34" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"out_of_scope",Raw!I2:I322,TRUE)/COUNTIF(Raw!C2:C322,"out_of_scope"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"out_of_scope",Raw!I2:I325,TRUE)/COUNTIF(Raw!C2:C325,"out_of_scope"),"")</f>
         <v/>
       </c>
       <c r="D34" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"out_of_scope",Raw!K2:K322,"success")/COUNTIF(Raw!C2:C322,"out_of_scope"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"out_of_scope",Raw!K2:K325,"success")/COUNTIF(Raw!C2:C325,"out_of_scope"),"")</f>
         <v/>
       </c>
       <c r="E34" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"out_of_scope",Raw!J2:J322,TRUE)/COUNTIF(Raw!C2:C322,"out_of_scope"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"out_of_scope",Raw!J2:J325,TRUE)/COUNTIF(Raw!C2:C325,"out_of_scope"),"")</f>
         <v/>
       </c>
       <c r="F34" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!C2:C322,"out_of_scope"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"out_of_scope"),"")</f>
         <v/>
       </c>
       <c r="G34" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!C2:C322,"out_of_scope"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"out_of_scope"),"")</f>
         <v/>
       </c>
     </row>
@@ -1297,27 +1297,27 @@
         </is>
       </c>
       <c r="B35" s="5">
-        <f>COUNTIF(Raw!C2:C322,"ask_query")</f>
+        <f>COUNTIF(Raw!C2:C325,"ask_query")</f>
         <v/>
       </c>
       <c r="C35" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"ask_query",Raw!I2:I322,TRUE)/COUNTIF(Raw!C2:C322,"ask_query"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"ask_query",Raw!I2:I325,TRUE)/COUNTIF(Raw!C2:C325,"ask_query"),"")</f>
         <v/>
       </c>
       <c r="D35" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"ask_query",Raw!K2:K322,"success")/COUNTIF(Raw!C2:C322,"ask_query"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"ask_query",Raw!K2:K325,"success")/COUNTIF(Raw!C2:C325,"ask_query"),"")</f>
         <v/>
       </c>
       <c r="E35" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"ask_query",Raw!J2:J322,TRUE)/COUNTIF(Raw!C2:C322,"ask_query"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"ask_query",Raw!J2:J325,TRUE)/COUNTIF(Raw!C2:C325,"ask_query"),"")</f>
         <v/>
       </c>
       <c r="F35" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!C2:C322,"ask_query"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"ask_query"),"")</f>
         <v/>
       </c>
       <c r="G35" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!C2:C322,"ask_query"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"ask_query"),"")</f>
         <v/>
       </c>
     </row>
@@ -1328,27 +1328,27 @@
         </is>
       </c>
       <c r="B36" s="5">
-        <f>COUNTIF(Raw!C2:C322,"typo_fuzzy")</f>
+        <f>COUNTIF(Raw!C2:C325,"typo_fuzzy")</f>
         <v/>
       </c>
       <c r="C36" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"typo_fuzzy",Raw!I2:I322,TRUE)/COUNTIF(Raw!C2:C322,"typo_fuzzy"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"typo_fuzzy",Raw!I2:I325,TRUE)/COUNTIF(Raw!C2:C325,"typo_fuzzy"),"")</f>
         <v/>
       </c>
       <c r="D36" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"typo_fuzzy",Raw!K2:K322,"success")/COUNTIF(Raw!C2:C322,"typo_fuzzy"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"typo_fuzzy",Raw!K2:K325,"success")/COUNTIF(Raw!C2:C325,"typo_fuzzy"),"")</f>
         <v/>
       </c>
       <c r="E36" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"typo_fuzzy",Raw!J2:J322,TRUE)/COUNTIF(Raw!C2:C322,"typo_fuzzy"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"typo_fuzzy",Raw!J2:J325,TRUE)/COUNTIF(Raw!C2:C325,"typo_fuzzy"),"")</f>
         <v/>
       </c>
       <c r="F36" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!C2:C322,"typo_fuzzy"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"typo_fuzzy"),"")</f>
         <v/>
       </c>
       <c r="G36" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!C2:C322,"typo_fuzzy"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"typo_fuzzy"),"")</f>
         <v/>
       </c>
     </row>
@@ -1359,27 +1359,27 @@
         </is>
       </c>
       <c r="B37" s="5">
-        <f>COUNTIF(Raw!C2:C322,"multilingual_edge")</f>
+        <f>COUNTIF(Raw!C2:C325,"multilingual_edge")</f>
         <v/>
       </c>
       <c r="C37" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"multilingual_edge",Raw!I2:I322,TRUE)/COUNTIF(Raw!C2:C322,"multilingual_edge"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"multilingual_edge",Raw!I2:I325,TRUE)/COUNTIF(Raw!C2:C325,"multilingual_edge"),"")</f>
         <v/>
       </c>
       <c r="D37" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"multilingual_edge",Raw!K2:K322,"success")/COUNTIF(Raw!C2:C322,"multilingual_edge"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"multilingual_edge",Raw!K2:K325,"success")/COUNTIF(Raw!C2:C325,"multilingual_edge"),"")</f>
         <v/>
       </c>
       <c r="E37" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"multilingual_edge",Raw!J2:J322,TRUE)/COUNTIF(Raw!C2:C322,"multilingual_edge"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"multilingual_edge",Raw!J2:J325,TRUE)/COUNTIF(Raw!C2:C325,"multilingual_edge"),"")</f>
         <v/>
       </c>
       <c r="F37" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!C2:C322,"multilingual_edge"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"multilingual_edge"),"")</f>
         <v/>
       </c>
       <c r="G37" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!C2:C322,"multilingual_edge"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"multilingual_edge"),"")</f>
         <v/>
       </c>
     </row>
@@ -1390,27 +1390,27 @@
         </is>
       </c>
       <c r="B38" s="5">
-        <f>COUNTIF(Raw!C2:C322,"property_ambiguity")</f>
+        <f>COUNTIF(Raw!C2:C325,"property_ambiguity")</f>
         <v/>
       </c>
       <c r="C38" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"property_ambiguity",Raw!I2:I322,TRUE)/COUNTIF(Raw!C2:C322,"property_ambiguity"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"property_ambiguity",Raw!I2:I325,TRUE)/COUNTIF(Raw!C2:C325,"property_ambiguity"),"")</f>
         <v/>
       </c>
       <c r="D38" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"property_ambiguity",Raw!K2:K322,"success")/COUNTIF(Raw!C2:C322,"property_ambiguity"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"property_ambiguity",Raw!K2:K325,"success")/COUNTIF(Raw!C2:C325,"property_ambiguity"),"")</f>
         <v/>
       </c>
       <c r="E38" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C322,"property_ambiguity",Raw!J2:J322,TRUE)/COUNTIF(Raw!C2:C322,"property_ambiguity"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C325,"property_ambiguity",Raw!J2:J325,TRUE)/COUNTIF(Raw!C2:C325,"property_ambiguity"),"")</f>
         <v/>
       </c>
       <c r="F38" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L322,Raw!C2:C322,"property_ambiguity"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"property_ambiguity"),"")</f>
         <v/>
       </c>
       <c r="G38" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M322,Raw!C2:C322,"property_ambiguity"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"property_ambiguity"),"")</f>
         <v/>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N322"/>
+  <dimension ref="A1:N325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16591,7 +16591,7 @@
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B254" s="5" t="n">
@@ -16624,18 +16624,18 @@
       </c>
       <c r="H254" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I254" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J254" s="5" t="b">
         <v>1</v>
       </c>
       <c r="K254" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L254" s="5" t="b">
@@ -16645,13 +16645,13 @@
         <v>0</v>
       </c>
       <c r="N254" s="5" t="n">
-        <v>55.04</v>
+        <v>15.43</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B255" s="5" t="n">
@@ -16691,11 +16691,11 @@
         <v>1</v>
       </c>
       <c r="J255" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K255" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>sparql_build_failure</t>
         </is>
       </c>
       <c r="L255" s="5" t="b">
@@ -16705,13 +16705,13 @@
         <v>0</v>
       </c>
       <c r="N255" s="5" t="n">
-        <v>13.79</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B256" s="5" t="n">
@@ -16751,11 +16751,11 @@
         <v>1</v>
       </c>
       <c r="J256" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K256" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L256" s="5" t="b">
@@ -16765,27 +16765,25 @@
         <v>0</v>
       </c>
       <c r="N256" s="5" t="n">
-        <v>15.09</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B257" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D257" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D257" s="5" t="n">
+        <v/>
       </c>
       <c r="E257" s="5" t="inlineStr">
         <is>
@@ -16799,53 +16797,47 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I257" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J257" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K257" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L257" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M257" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L257" s="5" t="n"/>
+      <c r="M257" s="5" t="n"/>
       <c r="N257" s="5" t="n">
-        <v>15.43</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B258" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D258" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D258" s="5" t="n">
+        <v/>
       </c>
       <c r="E258" s="5" t="inlineStr">
         <is>
@@ -16859,12 +16851,12 @@
       </c>
       <c r="G258" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H258" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I258" s="5" t="b">
@@ -16875,37 +16867,31 @@
       </c>
       <c r="K258" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L258" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M258" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L258" s="5" t="n"/>
+      <c r="M258" s="5" t="n"/>
       <c r="N258" s="5" t="n">
-        <v>14.45</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B259" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C259" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D259" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D259" s="5" t="n">
+        <v/>
       </c>
       <c r="E259" s="5" t="inlineStr">
         <is>
@@ -16919,53 +16905,47 @@
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H259" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I259" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J259" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K259" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L259" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M259" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L259" s="5" t="n"/>
+      <c r="M259" s="5" t="n"/>
       <c r="N259" s="5" t="n">
-        <v>11.37</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B260" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D260" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D260" s="5" t="n">
+        <v/>
       </c>
       <c r="E260" s="5" t="inlineStr">
         <is>
@@ -16979,53 +16959,47 @@
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H260" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I260" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J260" s="5" t="b">
         <v>0</v>
       </c>
       <c r="K260" s="5" t="inlineStr">
         <is>
-          <t>generation_failure</t>
-        </is>
-      </c>
-      <c r="L260" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M260" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L260" s="5" t="n"/>
+      <c r="M260" s="5" t="n"/>
       <c r="N260" s="5" t="n">
-        <v>59.86</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B261" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D261" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D261" s="5" t="n">
+        <v/>
       </c>
       <c r="E261" s="5" t="inlineStr">
         <is>
@@ -17039,12 +17013,12 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I261" s="5" t="b">
@@ -17055,37 +17029,31 @@
       </c>
       <c r="K261" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L261" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M261" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L261" s="5" t="n"/>
+      <c r="M261" s="5" t="n"/>
       <c r="N261" s="5" t="n">
-        <v>15.32</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B262" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D262" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D262" s="5" t="n">
+        <v/>
       </c>
       <c r="E262" s="5" t="inlineStr">
         <is>
@@ -17099,39 +17067,35 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I262" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J262" s="5" t="b">
         <v>0</v>
       </c>
       <c r="K262" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L262" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M262" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>mapping_failure</t>
+        </is>
+      </c>
+      <c r="L262" s="5" t="n"/>
+      <c r="M262" s="5" t="n"/>
       <c r="N262" s="5" t="n">
-        <v>12.91</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B263" s="5" t="n">
@@ -17179,13 +17143,13 @@
       <c r="L263" s="5" t="n"/>
       <c r="M263" s="5" t="n"/>
       <c r="N263" s="5" t="n">
-        <v>3.59</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B264" s="5" t="n">
@@ -17233,13 +17197,13 @@
       <c r="L264" s="5" t="n"/>
       <c r="M264" s="5" t="n"/>
       <c r="N264" s="5" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B265" s="5" t="n">
@@ -17287,13 +17251,13 @@
       <c r="L265" s="5" t="n"/>
       <c r="M265" s="5" t="n"/>
       <c r="N265" s="5" t="n">
-        <v>3.61</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B266" s="5" t="n">
@@ -17301,11 +17265,13 @@
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D266" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D266" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
         <is>
@@ -17319,35 +17285,39 @@
       </c>
       <c r="G266" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H266" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I266" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J266" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K266" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L266" s="5" t="n"/>
-      <c r="M266" s="5" t="n"/>
+      <c r="L266" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M266" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N266" s="5" t="n">
-        <v>7.14</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B267" s="5" t="n">
@@ -17355,11 +17325,13 @@
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D267" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D267" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E267" s="5" t="inlineStr">
         <is>
@@ -17373,35 +17345,39 @@
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H267" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I267" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J267" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K267" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L267" s="5" t="n"/>
-      <c r="M267" s="5" t="n"/>
+      <c r="L267" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M267" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N267" s="5" t="n">
-        <v>8.01</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B268" s="5" t="n">
@@ -17409,11 +17385,13 @@
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D268" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D268" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
@@ -17427,7 +17405,7 @@
       </c>
       <c r="G268" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H268" s="5" t="inlineStr">
@@ -17436,26 +17414,30 @@
         </is>
       </c>
       <c r="I268" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J268" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K268" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L268" s="5" t="n"/>
-      <c r="M268" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L268" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M268" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N268" s="5" t="n">
-        <v>5.7</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B269" s="5" t="n">
@@ -17463,11 +17445,13 @@
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D269" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E269" s="5" t="inlineStr">
         <is>
@@ -17481,35 +17465,39 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I269" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J269" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K269" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L269" s="5" t="n"/>
-      <c r="M269" s="5" t="n"/>
+      <c r="L269" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M269" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N269" s="5" t="n">
-        <v>3.39</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B270" s="5" t="n">
@@ -17517,11 +17505,13 @@
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D270" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D270" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
         <is>
@@ -17535,35 +17525,39 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I270" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J270" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K270" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L270" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="K270" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L270" s="5" t="n"/>
-      <c r="M270" s="5" t="n"/>
+      <c r="M270" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N270" s="5" t="n">
-        <v>3.45</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B271" s="5" t="n">
@@ -17571,11 +17565,13 @@
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D271" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
         <is>
@@ -17589,35 +17585,39 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I271" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J271" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K271" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L271" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="K271" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L271" s="5" t="n"/>
-      <c r="M271" s="5" t="n"/>
+      <c r="M271" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N271" s="5" t="n">
-        <v>3.46</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B272" s="5" t="n">
@@ -17671,13 +17671,13 @@
         <v>1</v>
       </c>
       <c r="N272" s="5" t="n">
-        <v>7.09</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B273" s="5" t="n">
@@ -17710,26 +17710,22 @@
       </c>
       <c r="H273" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I273" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J273" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K273" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L273" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M273" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L273" s="5" t="n"/>
+      <c r="M273" s="5" t="n"/>
       <c r="N273" s="5" t="n">
         <v>7.41</v>
       </c>
@@ -17737,7 +17733,7 @@
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B274" s="5" t="n">
@@ -17791,13 +17787,13 @@
         <v>1</v>
       </c>
       <c r="N274" s="5" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B275" s="5" t="n">
@@ -17851,13 +17847,13 @@
         <v>1</v>
       </c>
       <c r="N275" s="5" t="n">
-        <v>7.03</v>
+        <v>8.06</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B276" s="5" t="n">
@@ -17905,19 +17901,19 @@
         </is>
       </c>
       <c r="L276" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M276" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N276" s="5" t="n">
-        <v>7.89</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B277" s="5" t="n">
@@ -17965,19 +17961,19 @@
         </is>
       </c>
       <c r="L277" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M277" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N277" s="5" t="n">
-        <v>4.35</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B278" s="5" t="n">
@@ -17985,7 +17981,7 @@
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D278" s="5" t="inlineStr">
@@ -18005,12 +18001,12 @@
       </c>
       <c r="G278" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H278" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I278" s="5" t="b">
@@ -18031,13 +18027,13 @@
         <v>1</v>
       </c>
       <c r="N278" s="5" t="n">
-        <v>6.81</v>
+        <v>16.87</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B279" s="5" t="n">
@@ -18045,7 +18041,7 @@
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D279" s="5" t="inlineStr">
@@ -18065,35 +18061,39 @@
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H279" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I279" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J279" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K279" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L279" s="5" t="n"/>
-      <c r="M279" s="5" t="n"/>
+      <c r="L279" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M279" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N279" s="5" t="n">
-        <v>7.41</v>
+        <v>18.32</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B280" s="5" t="n">
@@ -18101,7 +18101,7 @@
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D280" s="5" t="inlineStr">
@@ -18121,12 +18121,12 @@
       </c>
       <c r="G280" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H280" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I280" s="5" t="b">
@@ -18147,13 +18147,13 @@
         <v>1</v>
       </c>
       <c r="N280" s="5" t="n">
-        <v>3.8</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B281" s="5" t="n">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="C281" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D281" s="5" t="inlineStr">
@@ -18181,12 +18181,12 @@
       </c>
       <c r="G281" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H281" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I281" s="5" t="b">
@@ -18207,13 +18207,13 @@
         <v>1</v>
       </c>
       <c r="N281" s="5" t="n">
-        <v>8.06</v>
+        <v>34.43</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B282" s="5" t="n">
@@ -18221,7 +18221,7 @@
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D282" s="5" t="inlineStr">
@@ -18241,12 +18241,12 @@
       </c>
       <c r="G282" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H282" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I282" s="5" t="b">
@@ -18267,13 +18267,13 @@
         <v>1</v>
       </c>
       <c r="N282" s="5" t="n">
-        <v>8.300000000000001</v>
+        <v>24.86</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B283" s="5" t="n">
@@ -18281,7 +18281,7 @@
       </c>
       <c r="C283" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D283" s="5" t="inlineStr">
@@ -18301,12 +18301,12 @@
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H283" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I283" s="5" t="b">
@@ -18327,13 +18327,13 @@
         <v>1</v>
       </c>
       <c r="N283" s="5" t="n">
-        <v>4.63</v>
+        <v>24.79</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B284" s="5" t="n">
@@ -18387,13 +18387,13 @@
         <v>1</v>
       </c>
       <c r="N284" s="5" t="n">
-        <v>16.87</v>
+        <v>31.19</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B285" s="5" t="n">
@@ -18447,13 +18447,13 @@
         <v>1</v>
       </c>
       <c r="N285" s="5" t="n">
-        <v>18.32</v>
+        <v>26.24</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B286" s="5" t="n">
@@ -18507,13 +18507,13 @@
         <v>1</v>
       </c>
       <c r="N286" s="5" t="n">
-        <v>17.7</v>
+        <v>26.78</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B287" s="5" t="n">
@@ -18521,7 +18521,7 @@
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D287" s="5" t="inlineStr">
@@ -18546,7 +18546,7 @@
       </c>
       <c r="H287" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I287" s="5" t="b">
@@ -18567,13 +18567,13 @@
         <v>1</v>
       </c>
       <c r="N287" s="5" t="n">
-        <v>34.43</v>
+        <v>20.04</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B288" s="5" t="n">
@@ -18581,7 +18581,7 @@
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D288" s="5" t="inlineStr">
@@ -18606,7 +18606,7 @@
       </c>
       <c r="H288" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I288" s="5" t="b">
@@ -18627,13 +18627,13 @@
         <v>1</v>
       </c>
       <c r="N288" s="5" t="n">
-        <v>24.86</v>
+        <v>23.97</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B289" s="5" t="n">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D289" s="5" t="inlineStr">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="H289" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I289" s="5" t="b">
@@ -18687,13 +18687,13 @@
         <v>1</v>
       </c>
       <c r="N289" s="5" t="n">
-        <v>24.79</v>
+        <v>19.79</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B290" s="5" t="n">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D290" s="5" t="inlineStr">
@@ -18747,13 +18747,13 @@
         <v>1</v>
       </c>
       <c r="N290" s="5" t="n">
-        <v>31.19</v>
+        <v>18.47</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B291" s="5" t="n">
@@ -18761,7 +18761,7 @@
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
@@ -18807,13 +18807,13 @@
         <v>1</v>
       </c>
       <c r="N291" s="5" t="n">
-        <v>26.24</v>
+        <v>21.19</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B292" s="5" t="n">
@@ -18821,7 +18821,7 @@
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
@@ -18846,7 +18846,7 @@
       </c>
       <c r="H292" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I292" s="5" t="b">
@@ -18861,19 +18861,19 @@
         </is>
       </c>
       <c r="L292" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M292" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N292" s="5" t="n">
-        <v>26.78</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B293" s="5" t="n">
@@ -18906,7 +18906,7 @@
       </c>
       <c r="H293" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I293" s="5" t="b">
@@ -18921,19 +18921,19 @@
         </is>
       </c>
       <c r="L293" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M293" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N293" s="5" t="n">
-        <v>20.04</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B294" s="5" t="n">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="H294" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I294" s="5" t="b">
@@ -18981,19 +18981,19 @@
         </is>
       </c>
       <c r="L294" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M294" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N294" s="5" t="n">
-        <v>23.97</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B295" s="5" t="n">
@@ -19026,7 +19026,7 @@
       </c>
       <c r="H295" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I295" s="5" t="b">
@@ -19041,19 +19041,19 @@
         </is>
       </c>
       <c r="L295" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M295" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N295" s="5" t="n">
-        <v>19.79</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B296" s="5" t="n">
@@ -19107,13 +19107,13 @@
         <v>1</v>
       </c>
       <c r="N296" s="5" t="n">
-        <v>18.47</v>
+        <v>19.02</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B297" s="5" t="n">
@@ -19167,13 +19167,13 @@
         <v>1</v>
       </c>
       <c r="N297" s="5" t="n">
-        <v>21.19</v>
+        <v>25.62</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B298" s="5" t="n">
@@ -19206,7 +19206,7 @@
       </c>
       <c r="H298" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I298" s="5" t="b">
@@ -19221,19 +19221,19 @@
         </is>
       </c>
       <c r="L298" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M298" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N298" s="5" t="n">
-        <v>10.15</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B299" s="5" t="n">
@@ -19241,7 +19241,7 @@
       </c>
       <c r="C299" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D299" s="5" t="inlineStr">
@@ -19266,7 +19266,7 @@
       </c>
       <c r="H299" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I299" s="5" t="b">
@@ -19280,20 +19280,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L299" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M299" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L299" s="5" t="n"/>
+      <c r="M299" s="5" t="n"/>
       <c r="N299" s="5" t="n">
-        <v>7.89</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B300" s="5" t="n">
@@ -19301,7 +19297,7 @@
       </c>
       <c r="C300" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D300" s="5" t="inlineStr">
@@ -19326,7 +19322,7 @@
       </c>
       <c r="H300" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I300" s="5" t="b">
@@ -19340,20 +19336,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L300" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M300" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L300" s="5" t="n"/>
+      <c r="M300" s="5" t="n"/>
       <c r="N300" s="5" t="n">
-        <v>8.33</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B301" s="5" t="n">
@@ -19361,7 +19353,7 @@
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D301" s="5" t="inlineStr">
@@ -19386,7 +19378,7 @@
       </c>
       <c r="H301" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I301" s="5" t="b">
@@ -19400,20 +19392,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L301" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M301" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L301" s="5" t="n"/>
+      <c r="M301" s="5" t="n"/>
       <c r="N301" s="5" t="n">
-        <v>4.93</v>
+        <v>18.72</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B302" s="5" t="n">
@@ -19421,7 +19409,7 @@
       </c>
       <c r="C302" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D302" s="5" t="inlineStr">
@@ -19446,7 +19434,7 @@
       </c>
       <c r="H302" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I302" s="5" t="b">
@@ -19460,20 +19448,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L302" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M302" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L302" s="5" t="n"/>
+      <c r="M302" s="5" t="n"/>
       <c r="N302" s="5" t="n">
-        <v>19.02</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B303" s="5" t="n">
@@ -19481,7 +19465,7 @@
       </c>
       <c r="C303" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D303" s="5" t="inlineStr">
@@ -19506,7 +19490,7 @@
       </c>
       <c r="H303" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I303" s="5" t="b">
@@ -19520,20 +19504,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L303" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M303" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L303" s="5" t="n"/>
+      <c r="M303" s="5" t="n"/>
       <c r="N303" s="5" t="n">
-        <v>25.62</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B304" s="5" t="n">
@@ -19541,7 +19521,7 @@
       </c>
       <c r="C304" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D304" s="5" t="inlineStr">
@@ -19566,7 +19546,7 @@
       </c>
       <c r="H304" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I304" s="5" t="b">
@@ -19580,20 +19560,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L304" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M304" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L304" s="5" t="n"/>
+      <c r="M304" s="5" t="n"/>
       <c r="N304" s="5" t="n">
-        <v>21.4</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B305" s="5" t="n">
@@ -19643,13 +19619,13 @@
       <c r="L305" s="5" t="n"/>
       <c r="M305" s="5" t="n"/>
       <c r="N305" s="5" t="n">
-        <v>13.2</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B306" s="5" t="n">
@@ -19699,13 +19675,13 @@
       <c r="L306" s="5" t="n"/>
       <c r="M306" s="5" t="n"/>
       <c r="N306" s="5" t="n">
-        <v>18.8</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B307" s="5" t="n">
@@ -19755,26 +19731,26 @@
       <c r="L307" s="5" t="n"/>
       <c r="M307" s="5" t="n"/>
       <c r="N307" s="5" t="n">
-        <v>18.72</v>
+        <v>11.85</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>single_kg1_006</t>
         </is>
       </c>
       <c r="B308" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C308" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D308" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E308" s="5" t="inlineStr">
@@ -19789,12 +19765,12 @@
       </c>
       <c r="G308" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H308" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I308" s="5" t="b">
@@ -19808,49 +19784,53 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L308" s="5" t="n"/>
-      <c r="M308" s="5" t="n"/>
+      <c r="L308" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M308" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N308" s="5" t="n">
-        <v>11.37</v>
+        <v>28.04</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>single_kg1_006</t>
         </is>
       </c>
       <c r="B309" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C309" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D309" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E309" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F309" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I309" s="5" t="b">
@@ -19864,49 +19844,53 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L309" s="5" t="n"/>
-      <c r="M309" s="5" t="n"/>
+      <c r="L309" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M309" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N309" s="5" t="n">
-        <v>12.2</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>single_kg1_006</t>
         </is>
       </c>
       <c r="B310" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C310" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D310" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E310" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F310" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I310" s="5" t="b">
@@ -19920,34 +19904,38 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L310" s="5" t="n"/>
-      <c r="M310" s="5" t="n"/>
+      <c r="L310" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M310" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N310" s="5" t="n">
-        <v>11.93</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>single_kg1_006</t>
         </is>
       </c>
       <c r="B311" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C311" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D311" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E311" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F311" s="5" t="inlineStr">
@@ -19957,12 +19945,12 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I311" s="5" t="b">
@@ -19976,29 +19964,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L311" s="5" t="n"/>
-      <c r="M311" s="5" t="n"/>
+      <c r="L311" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M311" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N311" s="5" t="n">
-        <v>12.35</v>
+        <v>17.42</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>single_kg1_006</t>
         </is>
       </c>
       <c r="B312" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C312" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D312" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E312" s="5" t="inlineStr">
@@ -20008,17 +20000,17 @@
       </c>
       <c r="F312" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G312" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H312" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I312" s="5" t="b">
@@ -20032,49 +20024,53 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L312" s="5" t="n"/>
-      <c r="M312" s="5" t="n"/>
+      <c r="L312" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M312" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N312" s="5" t="n">
-        <v>12.65</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>single_kg1_006</t>
         </is>
       </c>
       <c r="B313" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C313" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E313" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F313" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G313" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H313" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I313" s="5" t="b">
@@ -20088,10 +20084,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L313" s="5" t="n"/>
-      <c r="M313" s="5" t="n"/>
+      <c r="L313" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M313" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N313" s="5" t="n">
-        <v>11.85</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="314">
@@ -20115,7 +20115,7 @@
       </c>
       <c r="E314" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F314" s="5" t="inlineStr">
@@ -20151,7 +20151,7 @@
         <v>1</v>
       </c>
       <c r="N314" s="5" t="n">
-        <v>28.04</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="315">
@@ -20175,7 +20175,7 @@
       </c>
       <c r="E315" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F315" s="5" t="inlineStr">
@@ -20211,7 +20211,7 @@
         <v>1</v>
       </c>
       <c r="N315" s="5" t="n">
-        <v>13.51</v>
+        <v>16.62</v>
       </c>
     </row>
     <row r="316">
@@ -20235,7 +20235,7 @@
       </c>
       <c r="E316" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F316" s="5" t="inlineStr">
@@ -20271,31 +20271,31 @@
         <v>1</v>
       </c>
       <c r="N316" s="5" t="n">
-        <v>13.84</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_006</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B317" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C317" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D317" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E317" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F317" s="5" t="inlineStr">
@@ -20305,12 +20305,12 @@
       </c>
       <c r="G317" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H317" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I317" s="5" t="b">
@@ -20331,26 +20331,26 @@
         <v>1</v>
       </c>
       <c r="N317" s="5" t="n">
-        <v>17.42</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_006</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B318" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C318" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D318" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E318" s="5" t="inlineStr">
@@ -20360,17 +20360,17 @@
       </c>
       <c r="F318" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G318" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H318" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I318" s="5" t="b">
@@ -20391,46 +20391,46 @@
         <v>1</v>
       </c>
       <c r="N318" s="5" t="n">
-        <v>16.6</v>
+        <v>12.38</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_006</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B319" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C319" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E319" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F319" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G319" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H319" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I319" s="5" t="b">
@@ -20451,31 +20451,31 @@
         <v>1</v>
       </c>
       <c r="N319" s="5" t="n">
-        <v>17.14</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_006</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B320" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C320" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D320" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E320" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F320" s="5" t="inlineStr">
@@ -20485,12 +20485,12 @@
       </c>
       <c r="G320" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H320" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I320" s="5" t="b">
@@ -20511,46 +20511,46 @@
         <v>1</v>
       </c>
       <c r="N320" s="5" t="n">
-        <v>17.5</v>
+        <v>20.11</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_006</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B321" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C321" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D321" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E321" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F321" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G321" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H321" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I321" s="5" t="b">
@@ -20571,26 +20571,26 @@
         <v>1</v>
       </c>
       <c r="N321" s="5" t="n">
-        <v>16.62</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_006</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B322" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C322" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D322" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E322" s="5" t="inlineStr">
@@ -20600,17 +20600,17 @@
       </c>
       <c r="F322" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G322" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H322" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I322" s="5" t="b">
@@ -20631,11 +20631,191 @@
         <v>1</v>
       </c>
       <c r="N322" s="5" t="n">
-        <v>17.3</v>
+        <v>5.13</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_airports_003</t>
+        </is>
+      </c>
+      <c r="B323" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C323" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_airports</t>
+        </is>
+      </c>
+      <c r="D323" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
+      </c>
+      <c r="E323" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F323" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G323" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="H323" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I323" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J323" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K323" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L323" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M323" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N323" s="5" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_airports_003</t>
+        </is>
+      </c>
+      <c r="B324" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C324" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_airports</t>
+        </is>
+      </c>
+      <c r="D324" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
+      </c>
+      <c r="E324" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F324" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G324" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="H324" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I324" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J324" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K324" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L324" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M324" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N324" s="5" t="n">
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_airports_003</t>
+        </is>
+      </c>
+      <c r="B325" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C325" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_airports</t>
+        </is>
+      </c>
+      <c r="D325" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
+      </c>
+      <c r="E325" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F325" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G325" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="H325" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I325" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J325" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K325" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L325" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M325" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N325" s="5" t="n">
+        <v>5.09</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N322"/>
+  <autoFilter ref="A1:N325"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/NL2SPARQL_Evaluation_Results.xlsx
+++ b/NL2SPARQL_Evaluation_Results.xlsx
@@ -13027,7 +13027,7 @@
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
         <is>
-          <t>open_kg_002</t>
+          <t>open_kg_003</t>
         </is>
       </c>
       <c r="B194" s="5" t="n">
@@ -13071,23 +13071,23 @@
       </c>
       <c r="K194" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L194" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M194" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N194" s="5" t="n">
-        <v>27.58</v>
+        <v>16.62</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>open_kg_002</t>
+          <t>open_kg_003</t>
         </is>
       </c>
       <c r="B195" s="5" t="n">
@@ -13135,19 +13135,19 @@
         </is>
       </c>
       <c r="L195" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M195" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N195" s="5" t="n">
-        <v>28.51</v>
+        <v>17.33</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
         <is>
-          <t>open_kg_002</t>
+          <t>open_kg_003</t>
         </is>
       </c>
       <c r="B196" s="5" t="n">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="K196" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L196" s="5" t="b">
@@ -13201,13 +13201,13 @@
         <v>0</v>
       </c>
       <c r="N196" s="5" t="n">
-        <v>26.28</v>
+        <v>15.68</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>open_kg_003</t>
+          <t>open_kg_004</t>
         </is>
       </c>
       <c r="B197" s="5" t="n">
@@ -13255,19 +13255,19 @@
         </is>
       </c>
       <c r="L197" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M197" s="5" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="N197" s="5" t="n">
-        <v>16.62</v>
+        <v>44.81</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
         <is>
-          <t>open_kg_003</t>
+          <t>open_kg_004</t>
         </is>
       </c>
       <c r="B198" s="5" t="n">
@@ -13315,19 +13315,19 @@
         </is>
       </c>
       <c r="L198" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M198" s="5" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="N198" s="5" t="n">
-        <v>17.33</v>
+        <v>26.48</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
         <is>
-          <t>open_kg_003</t>
+          <t>open_kg_004</t>
         </is>
       </c>
       <c r="B199" s="5" t="n">
@@ -13371,7 +13371,7 @@
       </c>
       <c r="K199" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L199" s="5" t="b">
@@ -13381,13 +13381,13 @@
         <v>0</v>
       </c>
       <c r="N199" s="5" t="n">
-        <v>15.68</v>
+        <v>21.66</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
         <is>
-          <t>open_kg_004</t>
+          <t>open_kg_005</t>
         </is>
       </c>
       <c r="B200" s="5" t="n">
@@ -13420,34 +13420,30 @@
       </c>
       <c r="H200" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I200" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J200" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K200" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L200" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M200" s="5" t="n">
-        <v>0.6667</v>
-      </c>
+          <t>execution_failure</t>
+        </is>
+      </c>
+      <c r="L200" s="5" t="n"/>
+      <c r="M200" s="5" t="n"/>
       <c r="N200" s="5" t="n">
-        <v>44.81</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>open_kg_004</t>
+          <t>open_kg_005</t>
         </is>
       </c>
       <c r="B201" s="5" t="n">
@@ -13480,34 +13476,30 @@
       </c>
       <c r="H201" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I201" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J201" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K201" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L201" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M201" s="5" t="n">
-        <v>0.6667</v>
-      </c>
+          <t>execution_failure</t>
+        </is>
+      </c>
+      <c r="L201" s="5" t="n"/>
+      <c r="M201" s="5" t="n"/>
       <c r="N201" s="5" t="n">
-        <v>26.48</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
         <is>
-          <t>open_kg_004</t>
+          <t>open_kg_005</t>
         </is>
       </c>
       <c r="B202" s="5" t="n">
@@ -13551,23 +13543,19 @@
       </c>
       <c r="K202" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L202" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M202" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>execution_failure</t>
+        </is>
+      </c>
+      <c r="L202" s="5" t="n"/>
+      <c r="M202" s="5" t="n"/>
       <c r="N202" s="5" t="n">
-        <v>21.66</v>
+        <v>28.63</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
         <is>
-          <t>open_kg_005</t>
+          <t>open_kg_006</t>
         </is>
       </c>
       <c r="B203" s="5" t="n">
@@ -13600,14 +13588,14 @@
       </c>
       <c r="H203" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I203" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J203" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K203" s="5" t="inlineStr">
         <is>
@@ -13617,13 +13605,13 @@
       <c r="L203" s="5" t="n"/>
       <c r="M203" s="5" t="n"/>
       <c r="N203" s="5" t="n">
-        <v>10.81</v>
+        <v>24.53</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="5" t="inlineStr">
         <is>
-          <t>open_kg_005</t>
+          <t>open_kg_006</t>
         </is>
       </c>
       <c r="B204" s="5" t="n">
@@ -13656,14 +13644,14 @@
       </c>
       <c r="H204" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I204" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J204" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K204" s="5" t="inlineStr">
         <is>
@@ -13673,13 +13661,13 @@
       <c r="L204" s="5" t="n"/>
       <c r="M204" s="5" t="n"/>
       <c r="N204" s="5" t="n">
-        <v>11.4</v>
+        <v>22.36</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="5" t="inlineStr">
         <is>
-          <t>open_kg_005</t>
+          <t>open_kg_006</t>
         </is>
       </c>
       <c r="B205" s="5" t="n">
@@ -13723,32 +13711,32 @@
       </c>
       <c r="K205" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L205" s="5" t="n"/>
       <c r="M205" s="5" t="n"/>
       <c r="N205" s="5" t="n">
-        <v>28.63</v>
+        <v>22.98</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
         <is>
-          <t>open_kg_006</t>
+          <t>count_kg1_001</t>
         </is>
       </c>
       <c r="B206" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
@@ -13763,48 +13751,52 @@
       </c>
       <c r="G206" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H206" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I206" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J206" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K206" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L206" s="5" t="n"/>
-      <c r="M206" s="5" t="n"/>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L206" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M206" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N206" s="5" t="n">
-        <v>24.53</v>
+        <v>7.62</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
         <is>
-          <t>open_kg_006</t>
+          <t>count_kg1_001</t>
         </is>
       </c>
       <c r="B207" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E207" s="5" t="inlineStr">
@@ -13819,48 +13811,52 @@
       </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H207" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I207" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J207" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K207" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L207" s="5" t="n"/>
-      <c r="M207" s="5" t="n"/>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L207" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M207" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N207" s="5" t="n">
-        <v>22.36</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="5" t="inlineStr">
         <is>
-          <t>open_kg_006</t>
+          <t>count_kg1_001</t>
         </is>
       </c>
       <c r="B208" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
@@ -13875,35 +13871,39 @@
       </c>
       <c r="G208" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H208" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I208" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J208" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K208" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L208" s="5" t="n"/>
-      <c r="M208" s="5" t="n"/>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L208" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M208" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N208" s="5" t="n">
-        <v>22.98</v>
+        <v>7.82</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_001</t>
+          <t>count_kg1_002</t>
         </is>
       </c>
       <c r="B209" s="5" t="n">
@@ -13943,27 +13943,27 @@
         <v>1</v>
       </c>
       <c r="J209" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K209" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L209" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M209" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N209" s="5" t="n">
-        <v>7.62</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_001</t>
+          <t>count_kg1_002</t>
         </is>
       </c>
       <c r="B210" s="5" t="n">
@@ -14003,27 +14003,27 @@
         <v>1</v>
       </c>
       <c r="J210" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K210" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L210" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M210" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N210" s="5" t="n">
-        <v>7.59</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_001</t>
+          <t>count_kg1_002</t>
         </is>
       </c>
       <c r="B211" s="5" t="n">
@@ -14063,27 +14063,27 @@
         <v>1</v>
       </c>
       <c r="J211" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K211" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L211" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M211" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N211" s="5" t="n">
-        <v>7.82</v>
+        <v>8.109999999999999</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_002</t>
+          <t>count_kg1_003</t>
         </is>
       </c>
       <c r="B212" s="5" t="n">
@@ -14137,13 +14137,13 @@
         <v>1</v>
       </c>
       <c r="N212" s="5" t="n">
-        <v>11.48</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_002</t>
+          <t>count_kg1_003</t>
         </is>
       </c>
       <c r="B213" s="5" t="n">
@@ -14197,13 +14197,13 @@
         <v>1</v>
       </c>
       <c r="N213" s="5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.449999999999999</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_002</t>
+          <t>count_kg1_003</t>
         </is>
       </c>
       <c r="B214" s="5" t="n">
@@ -14257,13 +14257,13 @@
         <v>1</v>
       </c>
       <c r="N214" s="5" t="n">
-        <v>8.109999999999999</v>
+        <v>8.470000000000001</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_003</t>
+          <t>filter_numeric_kg1_001</t>
         </is>
       </c>
       <c r="B215" s="5" t="n">
@@ -14271,7 +14271,7 @@
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
@@ -14317,13 +14317,13 @@
         <v>1</v>
       </c>
       <c r="N215" s="5" t="n">
-        <v>8.779999999999999</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_003</t>
+          <t>filter_numeric_kg1_001</t>
         </is>
       </c>
       <c r="B216" s="5" t="n">
@@ -14331,7 +14331,7 @@
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
@@ -14377,13 +14377,13 @@
         <v>1</v>
       </c>
       <c r="N216" s="5" t="n">
-        <v>8.449999999999999</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_003</t>
+          <t>filter_numeric_kg1_001</t>
         </is>
       </c>
       <c r="B217" s="5" t="n">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D217" s="5" t="inlineStr">
@@ -14437,13 +14437,13 @@
         <v>1</v>
       </c>
       <c r="N217" s="5" t="n">
-        <v>8.470000000000001</v>
+        <v>7.73</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_001</t>
+          <t>filter_numeric_kg1_002</t>
         </is>
       </c>
       <c r="B218" s="5" t="n">
@@ -14497,13 +14497,13 @@
         <v>1</v>
       </c>
       <c r="N218" s="5" t="n">
-        <v>8.15</v>
+        <v>8.27</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_001</t>
+          <t>filter_numeric_kg1_002</t>
         </is>
       </c>
       <c r="B219" s="5" t="n">
@@ -14557,13 +14557,13 @@
         <v>1</v>
       </c>
       <c r="N219" s="5" t="n">
-        <v>9.18</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_001</t>
+          <t>filter_numeric_kg1_002</t>
         </is>
       </c>
       <c r="B220" s="5" t="n">
@@ -14617,13 +14617,13 @@
         <v>1</v>
       </c>
       <c r="N220" s="5" t="n">
-        <v>7.73</v>
+        <v>10.97</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_002</t>
+          <t>filter_numeric_kg1_003</t>
         </is>
       </c>
       <c r="B221" s="5" t="n">
@@ -14677,13 +14677,13 @@
         <v>1</v>
       </c>
       <c r="N221" s="5" t="n">
-        <v>8.27</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_002</t>
+          <t>filter_numeric_kg1_003</t>
         </is>
       </c>
       <c r="B222" s="5" t="n">
@@ -14737,13 +14737,13 @@
         <v>1</v>
       </c>
       <c r="N222" s="5" t="n">
-        <v>10.99</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_002</t>
+          <t>filter_numeric_kg1_003</t>
         </is>
       </c>
       <c r="B223" s="5" t="n">
@@ -14797,13 +14797,13 @@
         <v>1</v>
       </c>
       <c r="N223" s="5" t="n">
-        <v>10.97</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_003</t>
+          <t>filter_numeric_kg2_001</t>
         </is>
       </c>
       <c r="B224" s="5" t="n">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E224" s="5" t="inlineStr">
@@ -14857,13 +14857,13 @@
         <v>1</v>
       </c>
       <c r="N224" s="5" t="n">
-        <v>7.91</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_003</t>
+          <t>filter_numeric_kg2_001</t>
         </is>
       </c>
       <c r="B225" s="5" t="n">
@@ -14871,12 +14871,12 @@
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E225" s="5" t="inlineStr">
@@ -14917,13 +14917,13 @@
         <v>1</v>
       </c>
       <c r="N225" s="5" t="n">
-        <v>7.86</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_003</t>
+          <t>filter_numeric_kg2_001</t>
         </is>
       </c>
       <c r="B226" s="5" t="n">
@@ -14931,12 +14931,12 @@
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E226" s="5" t="inlineStr">
@@ -14977,13 +14977,13 @@
         <v>1</v>
       </c>
       <c r="N226" s="5" t="n">
-        <v>8.19</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_001</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B227" s="5" t="n">
@@ -15031,19 +15031,19 @@
         </is>
       </c>
       <c r="L227" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M227" s="5" t="n">
-        <v>1</v>
+        <v>0.7692</v>
       </c>
       <c r="N227" s="5" t="n">
-        <v>10.01</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_001</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B228" s="5" t="n">
@@ -15091,19 +15091,19 @@
         </is>
       </c>
       <c r="L228" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M228" s="5" t="n">
-        <v>1</v>
+        <v>0.7692</v>
       </c>
       <c r="N228" s="5" t="n">
-        <v>10.03</v>
+        <v>8.960000000000001</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_001</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B229" s="5" t="n">
@@ -15151,19 +15151,19 @@
         </is>
       </c>
       <c r="L229" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M229" s="5" t="n">
-        <v>1</v>
+        <v>0.7692</v>
       </c>
       <c r="N229" s="5" t="n">
-        <v>9.94</v>
+        <v>8.44</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B230" s="5" t="n">
@@ -15211,19 +15211,19 @@
         </is>
       </c>
       <c r="L230" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M230" s="5" t="n">
-        <v>0.7692</v>
+        <v>1</v>
       </c>
       <c r="N230" s="5" t="n">
-        <v>8.119999999999999</v>
+        <v>9.51</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B231" s="5" t="n">
@@ -15271,19 +15271,19 @@
         </is>
       </c>
       <c r="L231" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M231" s="5" t="n">
-        <v>0.7692</v>
+        <v>1</v>
       </c>
       <c r="N231" s="5" t="n">
-        <v>8.960000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B232" s="5" t="n">
@@ -15331,19 +15331,19 @@
         </is>
       </c>
       <c r="L232" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M232" s="5" t="n">
-        <v>0.7692</v>
+        <v>1</v>
       </c>
       <c r="N232" s="5" t="n">
-        <v>8.44</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>filter_string_kg2_001</t>
         </is>
       </c>
       <c r="B233" s="5" t="n">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D233" s="5" t="inlineStr">
@@ -15397,13 +15397,13 @@
         <v>1</v>
       </c>
       <c r="N233" s="5" t="n">
-        <v>9.51</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>filter_string_kg2_001</t>
         </is>
       </c>
       <c r="B234" s="5" t="n">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="C234" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D234" s="5" t="inlineStr">
@@ -15457,13 +15457,13 @@
         <v>1</v>
       </c>
       <c r="N234" s="5" t="n">
-        <v>8.1</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>filter_string_kg2_001</t>
         </is>
       </c>
       <c r="B235" s="5" t="n">
@@ -15471,7 +15471,7 @@
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D235" s="5" t="inlineStr">
@@ -15517,13 +15517,13 @@
         <v>1</v>
       </c>
       <c r="N235" s="5" t="n">
-        <v>9.779999999999999</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_001</t>
+          <t>filter_string_kg2_002</t>
         </is>
       </c>
       <c r="B236" s="5" t="n">
@@ -15570,20 +15570,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L236" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M236" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L236" s="5" t="n"/>
+      <c r="M236" s="5" t="n"/>
       <c r="N236" s="5" t="n">
-        <v>9.25</v>
+        <v>14.39</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_001</t>
+          <t>filter_string_kg2_002</t>
         </is>
       </c>
       <c r="B237" s="5" t="n">
@@ -15630,20 +15626,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L237" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M237" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L237" s="5" t="n"/>
+      <c r="M237" s="5" t="n"/>
       <c r="N237" s="5" t="n">
-        <v>8.76</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_001</t>
+          <t>filter_string_kg2_002</t>
         </is>
       </c>
       <c r="B238" s="5" t="n">
@@ -15690,20 +15682,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L238" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M238" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L238" s="5" t="n"/>
+      <c r="M238" s="5" t="n"/>
       <c r="N238" s="5" t="n">
-        <v>8.83</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_002</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B239" s="5" t="n">
@@ -15750,16 +15738,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L239" s="5" t="n"/>
-      <c r="M239" s="5" t="n"/>
+      <c r="L239" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M239" s="5" t="n">
+        <v>0.7368</v>
+      </c>
       <c r="N239" s="5" t="n">
-        <v>14.39</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_002</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B240" s="5" t="n">
@@ -15806,16 +15798,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L240" s="5" t="n"/>
-      <c r="M240" s="5" t="n"/>
+      <c r="L240" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M240" s="5" t="n">
+        <v>0.7368</v>
+      </c>
       <c r="N240" s="5" t="n">
-        <v>11.36</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_002</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B241" s="5" t="n">
@@ -15862,16 +15858,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L241" s="5" t="n"/>
-      <c r="M241" s="5" t="n"/>
+      <c r="L241" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M241" s="5" t="n">
+        <v>0.7368</v>
+      </c>
       <c r="N241" s="5" t="n">
-        <v>11.69</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>ranking_kg2_001</t>
         </is>
       </c>
       <c r="B242" s="5" t="n">
@@ -15879,7 +15879,7 @@
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D242" s="5" t="inlineStr">
@@ -15919,19 +15919,19 @@
         </is>
       </c>
       <c r="L242" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M242" s="5" t="n">
-        <v>0.7368</v>
+        <v>1</v>
       </c>
       <c r="N242" s="5" t="n">
-        <v>9.529999999999999</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>ranking_kg2_001</t>
         </is>
       </c>
       <c r="B243" s="5" t="n">
@@ -15939,7 +15939,7 @@
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D243" s="5" t="inlineStr">
@@ -15979,19 +15979,19 @@
         </is>
       </c>
       <c r="L243" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M243" s="5" t="n">
-        <v>0.7368</v>
+        <v>1</v>
       </c>
       <c r="N243" s="5" t="n">
-        <v>9.279999999999999</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>ranking_kg2_001</t>
         </is>
       </c>
       <c r="B244" s="5" t="n">
@@ -15999,7 +15999,7 @@
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D244" s="5" t="inlineStr">
@@ -16039,19 +16039,19 @@
         </is>
       </c>
       <c r="L244" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M244" s="5" t="n">
-        <v>0.7368</v>
+        <v>1</v>
       </c>
       <c r="N244" s="5" t="n">
-        <v>9.02</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_001</t>
+          <t>ranking_kg2_003</t>
         </is>
       </c>
       <c r="B245" s="5" t="n">
@@ -16105,13 +16105,13 @@
         <v>1</v>
       </c>
       <c r="N245" s="5" t="n">
-        <v>7.04</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_001</t>
+          <t>ranking_kg2_003</t>
         </is>
       </c>
       <c r="B246" s="5" t="n">
@@ -16165,13 +16165,13 @@
         <v>1</v>
       </c>
       <c r="N246" s="5" t="n">
-        <v>7.09</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_001</t>
+          <t>ranking_kg2_003</t>
         </is>
       </c>
       <c r="B247" s="5" t="n">
@@ -16225,13 +16225,13 @@
         <v>1</v>
       </c>
       <c r="N247" s="5" t="n">
-        <v>7.56</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_002</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B248" s="5" t="n">
@@ -16239,7 +16239,7 @@
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D248" s="5" t="inlineStr">
@@ -16282,16 +16282,16 @@
         <v>0</v>
       </c>
       <c r="M248" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N248" s="5" t="n">
-        <v>7.77</v>
+        <v>15.43</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_002</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B249" s="5" t="n">
@@ -16299,7 +16299,7 @@
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D249" s="5" t="inlineStr">
@@ -16331,27 +16331,27 @@
         <v>1</v>
       </c>
       <c r="J249" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K249" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>sparql_build_failure</t>
         </is>
       </c>
       <c r="L249" s="5" t="b">
         <v>0</v>
       </c>
       <c r="M249" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N249" s="5" t="n">
-        <v>7.45</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_002</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B250" s="5" t="n">
@@ -16359,7 +16359,7 @@
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D250" s="5" t="inlineStr">
@@ -16402,30 +16402,28 @@
         <v>0</v>
       </c>
       <c r="M250" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N250" s="5" t="n">
-        <v>7.13</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_003</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B251" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C251" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
-        </is>
-      </c>
-      <c r="D251" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D251" s="5" t="n">
+        <v/>
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
@@ -16439,53 +16437,47 @@
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H251" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I251" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J251" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K251" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L251" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M251" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L251" s="5" t="n"/>
+      <c r="M251" s="5" t="n"/>
       <c r="N251" s="5" t="n">
-        <v>7.2</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_003</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B252" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C252" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
-        </is>
-      </c>
-      <c r="D252" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D252" s="5" t="n">
+        <v/>
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
@@ -16499,53 +16491,47 @@
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H252" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I252" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J252" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K252" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L252" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M252" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L252" s="5" t="n"/>
+      <c r="M252" s="5" t="n"/>
       <c r="N252" s="5" t="n">
-        <v>7.13</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_003</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B253" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
-        </is>
-      </c>
-      <c r="D253" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D253" s="5" t="n">
+        <v/>
       </c>
       <c r="E253" s="5" t="inlineStr">
         <is>
@@ -16559,53 +16545,47 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I253" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J253" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K253" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L253" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M253" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L253" s="5" t="n"/>
+      <c r="M253" s="5" t="n"/>
       <c r="N253" s="5" t="n">
-        <v>7.06</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B254" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D254" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D254" s="5" t="n">
+        <v/>
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
@@ -16619,53 +16599,47 @@
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H254" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I254" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J254" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K254" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L254" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M254" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L254" s="5" t="n"/>
+      <c r="M254" s="5" t="n"/>
       <c r="N254" s="5" t="n">
-        <v>15.43</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B255" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D255" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D255" s="5" t="n">
+        <v/>
       </c>
       <c r="E255" s="5" t="inlineStr">
         <is>
@@ -16679,12 +16653,12 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I255" s="5" t="b">
@@ -16695,37 +16669,31 @@
       </c>
       <c r="K255" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L255" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M255" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L255" s="5" t="n"/>
+      <c r="M255" s="5" t="n"/>
       <c r="N255" s="5" t="n">
-        <v>14.45</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B256" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C256" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
-        </is>
-      </c>
-      <c r="D256" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D256" s="5" t="n">
+        <v/>
       </c>
       <c r="E256" s="5" t="inlineStr">
         <is>
@@ -16739,39 +16707,35 @@
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H256" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I256" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J256" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K256" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L256" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M256" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>mapping_failure</t>
+        </is>
+      </c>
+      <c r="L256" s="5" t="n"/>
+      <c r="M256" s="5" t="n"/>
       <c r="N256" s="5" t="n">
-        <v>11.37</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B257" s="5" t="n">
@@ -16819,13 +16783,13 @@
       <c r="L257" s="5" t="n"/>
       <c r="M257" s="5" t="n"/>
       <c r="N257" s="5" t="n">
-        <v>3.59</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B258" s="5" t="n">
@@ -16873,13 +16837,13 @@
       <c r="L258" s="5" t="n"/>
       <c r="M258" s="5" t="n"/>
       <c r="N258" s="5" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B259" s="5" t="n">
@@ -16927,13 +16891,13 @@
       <c r="L259" s="5" t="n"/>
       <c r="M259" s="5" t="n"/>
       <c r="N259" s="5" t="n">
-        <v>3.61</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B260" s="5" t="n">
@@ -16941,11 +16905,13 @@
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D260" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D260" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E260" s="5" t="inlineStr">
         <is>
@@ -16959,35 +16925,39 @@
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H260" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I260" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J260" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K260" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L260" s="5" t="n"/>
-      <c r="M260" s="5" t="n"/>
+      <c r="L260" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M260" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N260" s="5" t="n">
-        <v>7.14</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B261" s="5" t="n">
@@ -16995,11 +16965,13 @@
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D261" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D261" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E261" s="5" t="inlineStr">
         <is>
@@ -17013,35 +16985,39 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I261" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J261" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K261" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L261" s="5" t="n"/>
-      <c r="M261" s="5" t="n"/>
+      <c r="L261" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M261" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N261" s="5" t="n">
-        <v>8.01</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B262" s="5" t="n">
@@ -17049,11 +17025,13 @@
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D262" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D262" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E262" s="5" t="inlineStr">
         <is>
@@ -17067,7 +17045,7 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
@@ -17076,26 +17054,30 @@
         </is>
       </c>
       <c r="I262" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J262" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K262" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L262" s="5" t="n"/>
-      <c r="M262" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L262" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M262" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N262" s="5" t="n">
-        <v>5.7</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B263" s="5" t="n">
@@ -17103,11 +17085,13 @@
       </c>
       <c r="C263" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D263" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D263" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E263" s="5" t="inlineStr">
         <is>
@@ -17121,35 +17105,39 @@
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H263" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I263" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J263" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K263" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L263" s="5" t="n"/>
-      <c r="M263" s="5" t="n"/>
+      <c r="L263" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M263" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N263" s="5" t="n">
-        <v>3.39</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B264" s="5" t="n">
@@ -17157,11 +17145,13 @@
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D264" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D264" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E264" s="5" t="inlineStr">
         <is>
@@ -17175,35 +17165,39 @@
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H264" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I264" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J264" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K264" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L264" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="K264" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L264" s="5" t="n"/>
-      <c r="M264" s="5" t="n"/>
+      <c r="M264" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N264" s="5" t="n">
-        <v>3.45</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B265" s="5" t="n">
@@ -17211,11 +17205,13 @@
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D265" s="5" t="n">
-        <v/>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E265" s="5" t="inlineStr">
         <is>
@@ -17229,35 +17225,39 @@
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H265" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I265" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J265" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K265" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L265" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="K265" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L265" s="5" t="n"/>
-      <c r="M265" s="5" t="n"/>
+      <c r="M265" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N265" s="5" t="n">
-        <v>3.46</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B266" s="5" t="n">
@@ -17311,13 +17311,13 @@
         <v>1</v>
       </c>
       <c r="N266" s="5" t="n">
-        <v>7.09</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B267" s="5" t="n">
@@ -17350,26 +17350,22 @@
       </c>
       <c r="H267" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I267" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J267" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K267" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L267" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M267" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L267" s="5" t="n"/>
+      <c r="M267" s="5" t="n"/>
       <c r="N267" s="5" t="n">
         <v>7.41</v>
       </c>
@@ -17377,7 +17373,7 @@
     <row r="268">
       <c r="A268" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B268" s="5" t="n">
@@ -17431,13 +17427,13 @@
         <v>1</v>
       </c>
       <c r="N268" s="5" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B269" s="5" t="n">
@@ -17491,13 +17487,13 @@
         <v>1</v>
       </c>
       <c r="N269" s="5" t="n">
-        <v>7.03</v>
+        <v>8.06</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B270" s="5" t="n">
@@ -17545,19 +17541,19 @@
         </is>
       </c>
       <c r="L270" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M270" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N270" s="5" t="n">
-        <v>7.89</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B271" s="5" t="n">
@@ -17605,19 +17601,19 @@
         </is>
       </c>
       <c r="L271" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M271" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N271" s="5" t="n">
-        <v>4.35</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B272" s="5" t="n">
@@ -17625,7 +17621,7 @@
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D272" s="5" t="inlineStr">
@@ -17645,12 +17641,12 @@
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H272" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I272" s="5" t="b">
@@ -17671,13 +17667,13 @@
         <v>1</v>
       </c>
       <c r="N272" s="5" t="n">
-        <v>6.81</v>
+        <v>16.87</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B273" s="5" t="n">
@@ -17685,7 +17681,7 @@
       </c>
       <c r="C273" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D273" s="5" t="inlineStr">
@@ -17705,35 +17701,39 @@
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H273" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I273" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J273" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K273" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L273" s="5" t="n"/>
-      <c r="M273" s="5" t="n"/>
+      <c r="L273" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M273" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N273" s="5" t="n">
-        <v>7.41</v>
+        <v>18.32</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B274" s="5" t="n">
@@ -17741,7 +17741,7 @@
       </c>
       <c r="C274" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D274" s="5" t="inlineStr">
@@ -17761,12 +17761,12 @@
       </c>
       <c r="G274" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H274" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I274" s="5" t="b">
@@ -17787,13 +17787,13 @@
         <v>1</v>
       </c>
       <c r="N274" s="5" t="n">
-        <v>3.8</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B275" s="5" t="n">
@@ -17801,7 +17801,7 @@
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D275" s="5" t="inlineStr">
@@ -17821,12 +17821,12 @@
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H275" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I275" s="5" t="b">
@@ -17847,13 +17847,13 @@
         <v>1</v>
       </c>
       <c r="N275" s="5" t="n">
-        <v>8.06</v>
+        <v>34.43</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B276" s="5" t="n">
@@ -17861,7 +17861,7 @@
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D276" s="5" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H276" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I276" s="5" t="b">
@@ -17907,13 +17907,13 @@
         <v>1</v>
       </c>
       <c r="N276" s="5" t="n">
-        <v>8.300000000000001</v>
+        <v>24.86</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B277" s="5" t="n">
@@ -17921,7 +17921,7 @@
       </c>
       <c r="C277" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D277" s="5" t="inlineStr">
@@ -17941,12 +17941,12 @@
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H277" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I277" s="5" t="b">
@@ -17967,13 +17967,13 @@
         <v>1</v>
       </c>
       <c r="N277" s="5" t="n">
-        <v>4.63</v>
+        <v>24.79</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B278" s="5" t="n">
@@ -18027,13 +18027,13 @@
         <v>1</v>
       </c>
       <c r="N278" s="5" t="n">
-        <v>16.87</v>
+        <v>31.19</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B279" s="5" t="n">
@@ -18087,13 +18087,13 @@
         <v>1</v>
       </c>
       <c r="N279" s="5" t="n">
-        <v>18.32</v>
+        <v>26.24</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B280" s="5" t="n">
@@ -18147,13 +18147,13 @@
         <v>1</v>
       </c>
       <c r="N280" s="5" t="n">
-        <v>17.7</v>
+        <v>26.78</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B281" s="5" t="n">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="C281" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D281" s="5" t="inlineStr">
@@ -18186,7 +18186,7 @@
       </c>
       <c r="H281" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I281" s="5" t="b">
@@ -18207,13 +18207,13 @@
         <v>1</v>
       </c>
       <c r="N281" s="5" t="n">
-        <v>34.43</v>
+        <v>20.04</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B282" s="5" t="n">
@@ -18221,7 +18221,7 @@
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D282" s="5" t="inlineStr">
@@ -18246,7 +18246,7 @@
       </c>
       <c r="H282" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I282" s="5" t="b">
@@ -18267,13 +18267,13 @@
         <v>1</v>
       </c>
       <c r="N282" s="5" t="n">
-        <v>24.86</v>
+        <v>23.97</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B283" s="5" t="n">
@@ -18281,7 +18281,7 @@
       </c>
       <c r="C283" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D283" s="5" t="inlineStr">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="H283" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I283" s="5" t="b">
@@ -18327,13 +18327,13 @@
         <v>1</v>
       </c>
       <c r="N283" s="5" t="n">
-        <v>24.79</v>
+        <v>19.79</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B284" s="5" t="n">
@@ -18341,7 +18341,7 @@
       </c>
       <c r="C284" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D284" s="5" t="inlineStr">
@@ -18387,13 +18387,13 @@
         <v>1</v>
       </c>
       <c r="N284" s="5" t="n">
-        <v>31.19</v>
+        <v>18.47</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B285" s="5" t="n">
@@ -18401,7 +18401,7 @@
       </c>
       <c r="C285" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D285" s="5" t="inlineStr">
@@ -18447,13 +18447,13 @@
         <v>1</v>
       </c>
       <c r="N285" s="5" t="n">
-        <v>26.24</v>
+        <v>21.19</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B286" s="5" t="n">
@@ -18461,7 +18461,7 @@
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D286" s="5" t="inlineStr">
@@ -18486,7 +18486,7 @@
       </c>
       <c r="H286" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I286" s="5" t="b">
@@ -18501,19 +18501,19 @@
         </is>
       </c>
       <c r="L286" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M286" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N286" s="5" t="n">
-        <v>26.78</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B287" s="5" t="n">
@@ -18546,7 +18546,7 @@
       </c>
       <c r="H287" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I287" s="5" t="b">
@@ -18561,19 +18561,19 @@
         </is>
       </c>
       <c r="L287" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M287" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N287" s="5" t="n">
-        <v>20.04</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B288" s="5" t="n">
@@ -18606,7 +18606,7 @@
       </c>
       <c r="H288" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I288" s="5" t="b">
@@ -18621,19 +18621,19 @@
         </is>
       </c>
       <c r="L288" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M288" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N288" s="5" t="n">
-        <v>23.97</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B289" s="5" t="n">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="H289" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I289" s="5" t="b">
@@ -18681,19 +18681,19 @@
         </is>
       </c>
       <c r="L289" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M289" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N289" s="5" t="n">
-        <v>19.79</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B290" s="5" t="n">
@@ -18747,13 +18747,13 @@
         <v>1</v>
       </c>
       <c r="N290" s="5" t="n">
-        <v>18.47</v>
+        <v>19.02</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B291" s="5" t="n">
@@ -18807,13 +18807,13 @@
         <v>1</v>
       </c>
       <c r="N291" s="5" t="n">
-        <v>21.19</v>
+        <v>25.62</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B292" s="5" t="n">
@@ -18846,7 +18846,7 @@
       </c>
       <c r="H292" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I292" s="5" t="b">
@@ -18861,19 +18861,19 @@
         </is>
       </c>
       <c r="L292" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M292" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N292" s="5" t="n">
-        <v>10.15</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B293" s="5" t="n">
@@ -18881,7 +18881,7 @@
       </c>
       <c r="C293" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D293" s="5" t="inlineStr">
@@ -18906,7 +18906,7 @@
       </c>
       <c r="H293" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I293" s="5" t="b">
@@ -18920,20 +18920,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L293" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M293" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L293" s="5" t="n"/>
+      <c r="M293" s="5" t="n"/>
       <c r="N293" s="5" t="n">
-        <v>7.89</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B294" s="5" t="n">
@@ -18941,7 +18937,7 @@
       </c>
       <c r="C294" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D294" s="5" t="inlineStr">
@@ -18966,7 +18962,7 @@
       </c>
       <c r="H294" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I294" s="5" t="b">
@@ -18980,20 +18976,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L294" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M294" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L294" s="5" t="n"/>
+      <c r="M294" s="5" t="n"/>
       <c r="N294" s="5" t="n">
-        <v>8.33</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B295" s="5" t="n">
@@ -19001,7 +18993,7 @@
       </c>
       <c r="C295" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D295" s="5" t="inlineStr">
@@ -19026,7 +19018,7 @@
       </c>
       <c r="H295" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I295" s="5" t="b">
@@ -19040,20 +19032,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L295" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M295" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L295" s="5" t="n"/>
+      <c r="M295" s="5" t="n"/>
       <c r="N295" s="5" t="n">
-        <v>4.93</v>
+        <v>18.72</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B296" s="5" t="n">
@@ -19061,7 +19049,7 @@
       </c>
       <c r="C296" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D296" s="5" t="inlineStr">
@@ -19086,7 +19074,7 @@
       </c>
       <c r="H296" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I296" s="5" t="b">
@@ -19100,20 +19088,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L296" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M296" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L296" s="5" t="n"/>
+      <c r="M296" s="5" t="n"/>
       <c r="N296" s="5" t="n">
-        <v>19.02</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B297" s="5" t="n">
@@ -19121,7 +19105,7 @@
       </c>
       <c r="C297" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D297" s="5" t="inlineStr">
@@ -19146,7 +19130,7 @@
       </c>
       <c r="H297" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I297" s="5" t="b">
@@ -19160,20 +19144,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L297" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M297" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L297" s="5" t="n"/>
+      <c r="M297" s="5" t="n"/>
       <c r="N297" s="5" t="n">
-        <v>25.62</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B298" s="5" t="n">
@@ -19181,7 +19161,7 @@
       </c>
       <c r="C298" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D298" s="5" t="inlineStr">
@@ -19206,7 +19186,7 @@
       </c>
       <c r="H298" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I298" s="5" t="b">
@@ -19220,20 +19200,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L298" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M298" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L298" s="5" t="n"/>
+      <c r="M298" s="5" t="n"/>
       <c r="N298" s="5" t="n">
-        <v>21.4</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B299" s="5" t="n">
@@ -19283,13 +19259,13 @@
       <c r="L299" s="5" t="n"/>
       <c r="M299" s="5" t="n"/>
       <c r="N299" s="5" t="n">
-        <v>13.2</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B300" s="5" t="n">
@@ -19339,13 +19315,13 @@
       <c r="L300" s="5" t="n"/>
       <c r="M300" s="5" t="n"/>
       <c r="N300" s="5" t="n">
-        <v>18.8</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B301" s="5" t="n">
@@ -19395,26 +19371,26 @@
       <c r="L301" s="5" t="n"/>
       <c r="M301" s="5" t="n"/>
       <c r="N301" s="5" t="n">
-        <v>18.72</v>
+        <v>11.85</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>single_kg1_006</t>
         </is>
       </c>
       <c r="B302" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C302" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D302" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E302" s="5" t="inlineStr">
@@ -19429,12 +19405,12 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I302" s="5" t="b">
@@ -19448,49 +19424,53 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L302" s="5" t="n"/>
-      <c r="M302" s="5" t="n"/>
+      <c r="L302" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M302" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N302" s="5" t="n">
-        <v>11.37</v>
+        <v>28.04</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>single_kg1_006</t>
         </is>
       </c>
       <c r="B303" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C303" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E303" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F303" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H303" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I303" s="5" t="b">
@@ -19504,49 +19484,53 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L303" s="5" t="n"/>
-      <c r="M303" s="5" t="n"/>
+      <c r="L303" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M303" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N303" s="5" t="n">
-        <v>12.2</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>single_kg1_006</t>
         </is>
       </c>
       <c r="B304" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C304" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D304" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E304" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F304" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G304" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H304" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I304" s="5" t="b">
@@ -19560,34 +19544,38 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L304" s="5" t="n"/>
-      <c r="M304" s="5" t="n"/>
+      <c r="L304" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M304" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N304" s="5" t="n">
-        <v>11.93</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>single_kg1_006</t>
         </is>
       </c>
       <c r="B305" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C305" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D305" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E305" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F305" s="5" t="inlineStr">
@@ -19597,12 +19585,12 @@
       </c>
       <c r="G305" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H305" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I305" s="5" t="b">
@@ -19616,29 +19604,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L305" s="5" t="n"/>
-      <c r="M305" s="5" t="n"/>
+      <c r="L305" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M305" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N305" s="5" t="n">
-        <v>12.35</v>
+        <v>17.42</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>single_kg1_006</t>
         </is>
       </c>
       <c r="B306" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C306" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D306" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E306" s="5" t="inlineStr">
@@ -19648,17 +19640,17 @@
       </c>
       <c r="F306" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G306" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H306" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I306" s="5" t="b">
@@ -19672,49 +19664,53 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L306" s="5" t="n"/>
-      <c r="M306" s="5" t="n"/>
+      <c r="L306" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M306" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N306" s="5" t="n">
-        <v>12.65</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>single_kg1_006</t>
         </is>
       </c>
       <c r="B307" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C307" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D307" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E307" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F307" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G307" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H307" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I307" s="5" t="b">
@@ -19728,10 +19724,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L307" s="5" t="n"/>
-      <c r="M307" s="5" t="n"/>
+      <c r="L307" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M307" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N307" s="5" t="n">
-        <v>11.85</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="308">
@@ -19755,7 +19755,7 @@
       </c>
       <c r="E308" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F308" s="5" t="inlineStr">
@@ -19791,7 +19791,7 @@
         <v>1</v>
       </c>
       <c r="N308" s="5" t="n">
-        <v>28.04</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="309">
@@ -19815,7 +19815,7 @@
       </c>
       <c r="E309" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F309" s="5" t="inlineStr">
@@ -19851,7 +19851,7 @@
         <v>1</v>
       </c>
       <c r="N309" s="5" t="n">
-        <v>13.51</v>
+        <v>16.62</v>
       </c>
     </row>
     <row r="310">
@@ -19875,7 +19875,7 @@
       </c>
       <c r="E310" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F310" s="5" t="inlineStr">
@@ -19911,31 +19911,31 @@
         <v>1</v>
       </c>
       <c r="N310" s="5" t="n">
-        <v>13.84</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_006</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B311" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C311" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D311" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E311" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F311" s="5" t="inlineStr">
@@ -19945,12 +19945,12 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I311" s="5" t="b">
@@ -19971,26 +19971,26 @@
         <v>1</v>
       </c>
       <c r="N311" s="5" t="n">
-        <v>17.42</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_006</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B312" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C312" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D312" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E312" s="5" t="inlineStr">
@@ -20000,17 +20000,17 @@
       </c>
       <c r="F312" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G312" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H312" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I312" s="5" t="b">
@@ -20031,46 +20031,46 @@
         <v>1</v>
       </c>
       <c r="N312" s="5" t="n">
-        <v>16.6</v>
+        <v>12.38</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_006</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B313" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C313" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E313" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F313" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G313" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H313" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I313" s="5" t="b">
@@ -20091,31 +20091,31 @@
         <v>1</v>
       </c>
       <c r="N313" s="5" t="n">
-        <v>17.14</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_006</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B314" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C314" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D314" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E314" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F314" s="5" t="inlineStr">
@@ -20125,12 +20125,12 @@
       </c>
       <c r="G314" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H314" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I314" s="5" t="b">
@@ -20151,46 +20151,46 @@
         <v>1</v>
       </c>
       <c r="N314" s="5" t="n">
-        <v>17.5</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_006</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B315" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C315" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D315" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E315" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F315" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G315" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H315" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I315" s="5" t="b">
@@ -20211,26 +20211,26 @@
         <v>1</v>
       </c>
       <c r="N315" s="5" t="n">
-        <v>16.62</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_006</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B316" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C316" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D316" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E316" s="5" t="inlineStr">
@@ -20240,17 +20240,17 @@
       </c>
       <c r="F316" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G316" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H316" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I316" s="5" t="b">
@@ -20271,26 +20271,26 @@
         <v>1</v>
       </c>
       <c r="N316" s="5" t="n">
-        <v>17.3</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B317" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C317" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D317" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E317" s="5" t="inlineStr">
@@ -20305,12 +20305,12 @@
       </c>
       <c r="G317" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H317" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I317" s="5" t="b">
@@ -20331,26 +20331,26 @@
         <v>1</v>
       </c>
       <c r="N317" s="5" t="n">
-        <v>10.63</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B318" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C318" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D318" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E318" s="5" t="inlineStr">
@@ -20365,12 +20365,12 @@
       </c>
       <c r="G318" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H318" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I318" s="5" t="b">
@@ -20391,26 +20391,26 @@
         <v>1</v>
       </c>
       <c r="N318" s="5" t="n">
-        <v>12.38</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B319" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C319" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E319" s="5" t="inlineStr">
@@ -20425,12 +20425,12 @@
       </c>
       <c r="G319" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H319" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I319" s="5" t="b">
@@ -20451,26 +20451,26 @@
         <v>1</v>
       </c>
       <c r="N319" s="5" t="n">
-        <v>12.66</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>open_kg_002</t>
         </is>
       </c>
       <c r="B320" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C320" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D320" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E320" s="5" t="inlineStr">
@@ -20485,12 +20485,12 @@
       </c>
       <c r="G320" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H320" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I320" s="5" t="b">
@@ -20511,26 +20511,26 @@
         <v>1</v>
       </c>
       <c r="N320" s="5" t="n">
-        <v>20.11</v>
+        <v>56.34</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>open_kg_002</t>
         </is>
       </c>
       <c r="B321" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C321" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D321" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E321" s="5" t="inlineStr">
@@ -20545,12 +20545,12 @@
       </c>
       <c r="G321" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H321" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I321" s="5" t="b">
@@ -20571,26 +20571,26 @@
         <v>1</v>
       </c>
       <c r="N321" s="5" t="n">
-        <v>5.43</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>open_kg_002</t>
         </is>
       </c>
       <c r="B322" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C322" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D322" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E322" s="5" t="inlineStr">
@@ -20605,12 +20605,12 @@
       </c>
       <c r="G322" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H322" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I322" s="5" t="b">
@@ -20631,13 +20631,13 @@
         <v>1</v>
       </c>
       <c r="N322" s="5" t="n">
-        <v>5.13</v>
+        <v>36.62</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>ranking_kg2_002</t>
         </is>
       </c>
       <c r="B323" s="5" t="n">
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C323" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D323" s="5" t="inlineStr">
@@ -20691,13 +20691,13 @@
         <v>1</v>
       </c>
       <c r="N323" s="5" t="n">
-        <v>4.75</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>ranking_kg2_002</t>
         </is>
       </c>
       <c r="B324" s="5" t="n">
@@ -20705,7 +20705,7 @@
       </c>
       <c r="C324" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D324" s="5" t="inlineStr">
@@ -20751,13 +20751,13 @@
         <v>1</v>
       </c>
       <c r="N324" s="5" t="n">
-        <v>4.67</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>ranking_kg2_002</t>
         </is>
       </c>
       <c r="B325" s="5" t="n">
@@ -20765,7 +20765,7 @@
       </c>
       <c r="C325" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D325" s="5" t="inlineStr">
@@ -20811,7 +20811,7 @@
         <v>1</v>
       </c>
       <c r="N325" s="5" t="n">
-        <v>5.09</v>
+        <v>11.22</v>
       </c>
     </row>
   </sheetData>

--- a/NL2SPARQL_Evaluation_Results.xlsx
+++ b/NL2SPARQL_Evaluation_Results.xlsx
@@ -7999,7 +7999,7 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>single_kg2_005</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
@@ -8053,13 +8053,13 @@
         <v>1</v>
       </c>
       <c r="N110" s="5" t="n">
-        <v>19.68</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>single_kg2_005</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
@@ -8113,13 +8113,13 @@
         <v>1</v>
       </c>
       <c r="N111" s="5" t="n">
-        <v>15.61</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>single_kg2_005</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
@@ -8173,13 +8173,13 @@
         <v>1</v>
       </c>
       <c r="N112" s="5" t="n">
-        <v>16.13</v>
+        <v>21.87</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>single_kg2_005</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
@@ -8233,13 +8233,13 @@
         <v>1</v>
       </c>
       <c r="N113" s="5" t="n">
-        <v>19.91</v>
+        <v>25.94</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>single_kg2_005</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
@@ -8293,13 +8293,13 @@
         <v>1</v>
       </c>
       <c r="N114" s="5" t="n">
-        <v>17.68</v>
+        <v>23.03</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>single_kg2_005</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
@@ -8353,13 +8353,13 @@
         <v>1</v>
       </c>
       <c r="N115" s="5" t="n">
-        <v>18.19</v>
+        <v>23.42</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>single_kg2_005</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
@@ -8399,27 +8399,27 @@
         <v>1</v>
       </c>
       <c r="J116" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K116" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L116" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N116" s="5" t="n">
-        <v>21.82</v>
+        <v>24.88</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>single_kg2_005</t>
         </is>
       </c>
       <c r="B117" s="5" t="n">
@@ -8459,27 +8459,27 @@
         <v>1</v>
       </c>
       <c r="J117" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K117" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L117" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N117" s="5" t="n">
-        <v>5.68</v>
+        <v>25.35</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>single_kg2_005</t>
         </is>
       </c>
       <c r="B118" s="5" t="n">
@@ -8519,27 +8519,27 @@
         <v>1</v>
       </c>
       <c r="J118" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K118" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L118" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N118" s="5" t="n">
-        <v>5.06</v>
+        <v>21.63</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_005</t>
+          <t>single_kg2_006</t>
         </is>
       </c>
       <c r="B119" s="5" t="n">
@@ -8593,13 +8593,13 @@
         <v>1</v>
       </c>
       <c r="N119" s="5" t="n">
-        <v>23.6</v>
+        <v>23.29</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_005</t>
+          <t>single_kg2_006</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
@@ -8653,13 +8653,13 @@
         <v>1</v>
       </c>
       <c r="N120" s="5" t="n">
-        <v>22.03</v>
+        <v>20.12</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_005</t>
+          <t>single_kg2_006</t>
         </is>
       </c>
       <c r="B121" s="5" t="n">
@@ -8713,13 +8713,13 @@
         <v>1</v>
       </c>
       <c r="N121" s="5" t="n">
-        <v>21.87</v>
+        <v>21.15</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_005</t>
+          <t>single_kg2_006</t>
         </is>
       </c>
       <c r="B122" s="5" t="n">
@@ -8773,13 +8773,13 @@
         <v>1</v>
       </c>
       <c r="N122" s="5" t="n">
-        <v>25.94</v>
+        <v>25.07</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_005</t>
+          <t>single_kg2_006</t>
         </is>
       </c>
       <c r="B123" s="5" t="n">
@@ -8833,13 +8833,13 @@
         <v>1</v>
       </c>
       <c r="N123" s="5" t="n">
-        <v>23.03</v>
+        <v>21.12</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_005</t>
+          <t>single_kg2_006</t>
         </is>
       </c>
       <c r="B124" s="5" t="n">
@@ -8893,13 +8893,13 @@
         <v>1</v>
       </c>
       <c r="N124" s="5" t="n">
-        <v>23.42</v>
+        <v>21.83</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_005</t>
+          <t>single_kg2_006</t>
         </is>
       </c>
       <c r="B125" s="5" t="n">
@@ -8953,13 +8953,13 @@
         <v>1</v>
       </c>
       <c r="N125" s="5" t="n">
-        <v>24.88</v>
+        <v>24.21</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_005</t>
+          <t>single_kg2_006</t>
         </is>
       </c>
       <c r="B126" s="5" t="n">
@@ -9013,13 +9013,13 @@
         <v>1</v>
       </c>
       <c r="N126" s="5" t="n">
-        <v>25.35</v>
+        <v>21.47</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_005</t>
+          <t>single_kg2_006</t>
         </is>
       </c>
       <c r="B127" s="5" t="n">
@@ -9073,13 +9073,13 @@
         <v>1</v>
       </c>
       <c r="N127" s="5" t="n">
-        <v>21.63</v>
+        <v>22.13</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_006</t>
+          <t>single_kg2_007</t>
         </is>
       </c>
       <c r="B128" s="5" t="n">
@@ -9133,13 +9133,13 @@
         <v>1</v>
       </c>
       <c r="N128" s="5" t="n">
-        <v>23.29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_006</t>
+          <t>single_kg2_007</t>
         </is>
       </c>
       <c r="B129" s="5" t="n">
@@ -9193,13 +9193,13 @@
         <v>1</v>
       </c>
       <c r="N129" s="5" t="n">
-        <v>20.12</v>
+        <v>15.54</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_006</t>
+          <t>single_kg2_007</t>
         </is>
       </c>
       <c r="B130" s="5" t="n">
@@ -9253,13 +9253,13 @@
         <v>1</v>
       </c>
       <c r="N130" s="5" t="n">
-        <v>21.15</v>
+        <v>16.26</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_006</t>
+          <t>single_kg2_007</t>
         </is>
       </c>
       <c r="B131" s="5" t="n">
@@ -9313,13 +9313,13 @@
         <v>1</v>
       </c>
       <c r="N131" s="5" t="n">
-        <v>25.07</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_006</t>
+          <t>single_kg2_007</t>
         </is>
       </c>
       <c r="B132" s="5" t="n">
@@ -9373,13 +9373,13 @@
         <v>1</v>
       </c>
       <c r="N132" s="5" t="n">
-        <v>21.12</v>
+        <v>17.33</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_006</t>
+          <t>single_kg2_007</t>
         </is>
       </c>
       <c r="B133" s="5" t="n">
@@ -9433,13 +9433,13 @@
         <v>1</v>
       </c>
       <c r="N133" s="5" t="n">
-        <v>21.83</v>
+        <v>17.82</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_006</t>
+          <t>single_kg2_007</t>
         </is>
       </c>
       <c r="B134" s="5" t="n">
@@ -9493,13 +9493,13 @@
         <v>1</v>
       </c>
       <c r="N134" s="5" t="n">
-        <v>24.21</v>
+        <v>19.31</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_006</t>
+          <t>single_kg2_007</t>
         </is>
       </c>
       <c r="B135" s="5" t="n">
@@ -9553,13 +9553,13 @@
         <v>1</v>
       </c>
       <c r="N135" s="5" t="n">
-        <v>21.47</v>
+        <v>15.85</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_006</t>
+          <t>single_kg2_007</t>
         </is>
       </c>
       <c r="B136" s="5" t="n">
@@ -9613,13 +9613,13 @@
         <v>1</v>
       </c>
       <c r="N136" s="5" t="n">
-        <v>22.13</v>
+        <v>16.03</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_007</t>
+          <t>single_kg2_008</t>
         </is>
       </c>
       <c r="B137" s="5" t="n">
@@ -9673,13 +9673,13 @@
         <v>1</v>
       </c>
       <c r="N137" s="5" t="n">
-        <v>18</v>
+        <v>22.61</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_007</t>
+          <t>single_kg2_008</t>
         </is>
       </c>
       <c r="B138" s="5" t="n">
@@ -9733,13 +9733,13 @@
         <v>1</v>
       </c>
       <c r="N138" s="5" t="n">
-        <v>15.54</v>
+        <v>21.67</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_007</t>
+          <t>single_kg2_008</t>
         </is>
       </c>
       <c r="B139" s="5" t="n">
@@ -9793,13 +9793,13 @@
         <v>1</v>
       </c>
       <c r="N139" s="5" t="n">
-        <v>16.26</v>
+        <v>20.82</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_007</t>
+          <t>single_kg2_008</t>
         </is>
       </c>
       <c r="B140" s="5" t="n">
@@ -9853,13 +9853,13 @@
         <v>1</v>
       </c>
       <c r="N140" s="5" t="n">
-        <v>20.99</v>
+        <v>23.48</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_007</t>
+          <t>single_kg2_008</t>
         </is>
       </c>
       <c r="B141" s="5" t="n">
@@ -9913,13 +9913,13 @@
         <v>1</v>
       </c>
       <c r="N141" s="5" t="n">
-        <v>17.33</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_007</t>
+          <t>single_kg2_008</t>
         </is>
       </c>
       <c r="B142" s="5" t="n">
@@ -9973,13 +9973,13 @@
         <v>1</v>
       </c>
       <c r="N142" s="5" t="n">
-        <v>17.82</v>
+        <v>21.28</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_007</t>
+          <t>single_kg2_008</t>
         </is>
       </c>
       <c r="B143" s="5" t="n">
@@ -10033,13 +10033,13 @@
         <v>1</v>
       </c>
       <c r="N143" s="5" t="n">
-        <v>19.31</v>
+        <v>24.89</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_007</t>
+          <t>single_kg2_008</t>
         </is>
       </c>
       <c r="B144" s="5" t="n">
@@ -10093,13 +10093,13 @@
         <v>1</v>
       </c>
       <c r="N144" s="5" t="n">
-        <v>15.85</v>
+        <v>21.65</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_007</t>
+          <t>single_kg2_008</t>
         </is>
       </c>
       <c r="B145" s="5" t="n">
@@ -10153,13 +10153,13 @@
         <v>1</v>
       </c>
       <c r="N145" s="5" t="n">
-        <v>16.03</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_008</t>
+          <t>single_kg2_009</t>
         </is>
       </c>
       <c r="B146" s="5" t="n">
@@ -10213,13 +10213,13 @@
         <v>1</v>
       </c>
       <c r="N146" s="5" t="n">
-        <v>22.61</v>
+        <v>18.67</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_008</t>
+          <t>single_kg2_009</t>
         </is>
       </c>
       <c r="B147" s="5" t="n">
@@ -10273,13 +10273,13 @@
         <v>1</v>
       </c>
       <c r="N147" s="5" t="n">
-        <v>21.67</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_008</t>
+          <t>single_kg2_009</t>
         </is>
       </c>
       <c r="B148" s="5" t="n">
@@ -10333,13 +10333,13 @@
         <v>1</v>
       </c>
       <c r="N148" s="5" t="n">
-        <v>20.82</v>
+        <v>16.14</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_008</t>
+          <t>single_kg2_009</t>
         </is>
       </c>
       <c r="B149" s="5" t="n">
@@ -10393,13 +10393,13 @@
         <v>1</v>
       </c>
       <c r="N149" s="5" t="n">
-        <v>23.48</v>
+        <v>20.41</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_008</t>
+          <t>single_kg2_009</t>
         </is>
       </c>
       <c r="B150" s="5" t="n">
@@ -10453,13 +10453,13 @@
         <v>1</v>
       </c>
       <c r="N150" s="5" t="n">
-        <v>20.7</v>
+        <v>17.59</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_008</t>
+          <t>single_kg2_009</t>
         </is>
       </c>
       <c r="B151" s="5" t="n">
@@ -10513,13 +10513,13 @@
         <v>1</v>
       </c>
       <c r="N151" s="5" t="n">
-        <v>21.28</v>
+        <v>18.07</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_008</t>
+          <t>single_kg2_009</t>
         </is>
       </c>
       <c r="B152" s="5" t="n">
@@ -10573,13 +10573,13 @@
         <v>1</v>
       </c>
       <c r="N152" s="5" t="n">
-        <v>24.89</v>
+        <v>18.77</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_008</t>
+          <t>single_kg2_009</t>
         </is>
       </c>
       <c r="B153" s="5" t="n">
@@ -10633,13 +10633,13 @@
         <v>1</v>
       </c>
       <c r="N153" s="5" t="n">
-        <v>21.65</v>
+        <v>16.34</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_008</t>
+          <t>single_kg2_009</t>
         </is>
       </c>
       <c r="B154" s="5" t="n">
@@ -10693,13 +10693,13 @@
         <v>1</v>
       </c>
       <c r="N154" s="5" t="n">
-        <v>22.22</v>
+        <v>16.71</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_009</t>
+          <t>cross_kg_001</t>
         </is>
       </c>
       <c r="B155" s="5" t="n">
@@ -10707,12 +10707,12 @@
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -10727,12 +10727,12 @@
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I155" s="5" t="b">
@@ -10753,13 +10753,13 @@
         <v>1</v>
       </c>
       <c r="N155" s="5" t="n">
-        <v>18.67</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_009</t>
+          <t>cross_kg_001</t>
         </is>
       </c>
       <c r="B156" s="5" t="n">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H156" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I156" s="5" t="b">
@@ -10813,13 +10813,13 @@
         <v>1</v>
       </c>
       <c r="N156" s="5" t="n">
-        <v>15.99</v>
+        <v>20.58</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_009</t>
+          <t>cross_kg_001</t>
         </is>
       </c>
       <c r="B157" s="5" t="n">
@@ -10827,32 +10827,32 @@
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I157" s="5" t="b">
@@ -10873,13 +10873,13 @@
         <v>1</v>
       </c>
       <c r="N157" s="5" t="n">
-        <v>16.14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_009</t>
+          <t>cross_kg_002</t>
         </is>
       </c>
       <c r="B158" s="5" t="n">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F158" s="5" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H158" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I158" s="5" t="b">
@@ -10933,13 +10933,13 @@
         <v>1</v>
       </c>
       <c r="N158" s="5" t="n">
-        <v>20.41</v>
+        <v>15.76</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_009</t>
+          <t>cross_kg_002</t>
         </is>
       </c>
       <c r="B159" s="5" t="n">
@@ -10947,12 +10947,12 @@
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -10962,17 +10962,17 @@
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I159" s="5" t="b">
@@ -10993,13 +10993,13 @@
         <v>1</v>
       </c>
       <c r="N159" s="5" t="n">
-        <v>17.59</v>
+        <v>14.51</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_009</t>
+          <t>cross_kg_002</t>
         </is>
       </c>
       <c r="B160" s="5" t="n">
@@ -11007,32 +11007,32 @@
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H160" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I160" s="5" t="b">
@@ -11053,13 +11053,13 @@
         <v>1</v>
       </c>
       <c r="N160" s="5" t="n">
-        <v>18.07</v>
+        <v>14.31</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_009</t>
+          <t>cross_kg_003</t>
         </is>
       </c>
       <c r="B161" s="5" t="n">
@@ -11067,17 +11067,17 @@
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
@@ -11087,12 +11087,12 @@
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I161" s="5" t="b">
@@ -11113,13 +11113,13 @@
         <v>1</v>
       </c>
       <c r="N161" s="5" t="n">
-        <v>18.77</v>
+        <v>14.87</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_009</t>
+          <t>cross_kg_003</t>
         </is>
       </c>
       <c r="B162" s="5" t="n">
@@ -11127,32 +11127,32 @@
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H162" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I162" s="5" t="b">
@@ -11173,13 +11173,13 @@
         <v>1</v>
       </c>
       <c r="N162" s="5" t="n">
-        <v>16.34</v>
+        <v>19.16</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_009</t>
+          <t>cross_kg_003</t>
         </is>
       </c>
       <c r="B163" s="5" t="n">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -11202,17 +11202,17 @@
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I163" s="5" t="b">
@@ -11233,13 +11233,13 @@
         <v>1</v>
       </c>
       <c r="N163" s="5" t="n">
-        <v>16.71</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_001</t>
+          <t>cross_kg_004</t>
         </is>
       </c>
       <c r="B164" s="5" t="n">
@@ -11293,13 +11293,13 @@
         <v>1</v>
       </c>
       <c r="N164" s="5" t="n">
-        <v>20.6</v>
+        <v>17.76</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_001</t>
+          <t>cross_kg_004</t>
         </is>
       </c>
       <c r="B165" s="5" t="n">
@@ -11353,13 +11353,13 @@
         <v>1</v>
       </c>
       <c r="N165" s="5" t="n">
-        <v>20.58</v>
+        <v>18.48</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_001</t>
+          <t>cross_kg_004</t>
         </is>
       </c>
       <c r="B166" s="5" t="n">
@@ -11413,13 +11413,13 @@
         <v>1</v>
       </c>
       <c r="N166" s="5" t="n">
-        <v>21</v>
+        <v>14.93</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_002</t>
+          <t>cross_kg_006</t>
         </is>
       </c>
       <c r="B167" s="5" t="n">
@@ -11473,13 +11473,13 @@
         <v>1</v>
       </c>
       <c r="N167" s="5" t="n">
-        <v>15.76</v>
+        <v>13.91</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_002</t>
+          <t>cross_kg_006</t>
         </is>
       </c>
       <c r="B168" s="5" t="n">
@@ -11533,13 +11533,13 @@
         <v>1</v>
       </c>
       <c r="N168" s="5" t="n">
-        <v>14.51</v>
+        <v>14.42</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_002</t>
+          <t>cross_kg_006</t>
         </is>
       </c>
       <c r="B169" s="5" t="n">
@@ -11593,13 +11593,13 @@
         <v>1</v>
       </c>
       <c r="N169" s="5" t="n">
-        <v>14.31</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_003</t>
+          <t>cross_kg_007</t>
         </is>
       </c>
       <c r="B170" s="5" t="n">
@@ -11653,13 +11653,13 @@
         <v>1</v>
       </c>
       <c r="N170" s="5" t="n">
-        <v>14.87</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_003</t>
+          <t>cross_kg_007</t>
         </is>
       </c>
       <c r="B171" s="5" t="n">
@@ -11713,13 +11713,13 @@
         <v>1</v>
       </c>
       <c r="N171" s="5" t="n">
-        <v>19.16</v>
+        <v>20.66</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_003</t>
+          <t>cross_kg_007</t>
         </is>
       </c>
       <c r="B172" s="5" t="n">
@@ -11773,13 +11773,13 @@
         <v>1</v>
       </c>
       <c r="N172" s="5" t="n">
-        <v>15.12</v>
+        <v>15.22</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_004</t>
+          <t>cross_kg_008</t>
         </is>
       </c>
       <c r="B173" s="5" t="n">
@@ -11833,13 +11833,13 @@
         <v>1</v>
       </c>
       <c r="N173" s="5" t="n">
-        <v>17.76</v>
+        <v>18.21</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_004</t>
+          <t>cross_kg_008</t>
         </is>
       </c>
       <c r="B174" s="5" t="n">
@@ -11893,13 +11893,13 @@
         <v>1</v>
       </c>
       <c r="N174" s="5" t="n">
-        <v>18.48</v>
+        <v>18.97</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_004</t>
+          <t>cross_kg_008</t>
         </is>
       </c>
       <c r="B175" s="5" t="n">
@@ -11953,13 +11953,13 @@
         <v>1</v>
       </c>
       <c r="N175" s="5" t="n">
-        <v>14.93</v>
+        <v>15.86</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_005</t>
+          <t>cross_kg_010</t>
         </is>
       </c>
       <c r="B176" s="5" t="n">
@@ -12013,13 +12013,13 @@
         <v>1</v>
       </c>
       <c r="N176" s="5" t="n">
-        <v>15.23</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_005</t>
+          <t>cross_kg_010</t>
         </is>
       </c>
       <c r="B177" s="5" t="n">
@@ -12073,13 +12073,13 @@
         <v>1</v>
       </c>
       <c r="N177" s="5" t="n">
-        <v>19.99</v>
+        <v>14.52</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_005</t>
+          <t>cross_kg_010</t>
         </is>
       </c>
       <c r="B178" s="5" t="n">
@@ -12112,11 +12112,11 @@
       </c>
       <c r="H178" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I178" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J178" s="5" t="b">
         <v>1</v>
@@ -12127,19 +12127,19 @@
         </is>
       </c>
       <c r="L178" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M178" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N178" s="5" t="n">
-        <v>16.71</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_006</t>
+          <t>cross_kg_011</t>
         </is>
       </c>
       <c r="B179" s="5" t="n">
@@ -12193,13 +12193,13 @@
         <v>1</v>
       </c>
       <c r="N179" s="5" t="n">
-        <v>13.91</v>
+        <v>14.66</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_006</t>
+          <t>cross_kg_011</t>
         </is>
       </c>
       <c r="B180" s="5" t="n">
@@ -12253,13 +12253,13 @@
         <v>1</v>
       </c>
       <c r="N180" s="5" t="n">
-        <v>14.42</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_006</t>
+          <t>cross_kg_011</t>
         </is>
       </c>
       <c r="B181" s="5" t="n">
@@ -12313,13 +12313,13 @@
         <v>1</v>
       </c>
       <c r="N181" s="5" t="n">
-        <v>18.99</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_007</t>
+          <t>cross_kg_012</t>
         </is>
       </c>
       <c r="B182" s="5" t="n">
@@ -12373,13 +12373,13 @@
         <v>1</v>
       </c>
       <c r="N182" s="5" t="n">
-        <v>15.71</v>
+        <v>14.31</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_007</t>
+          <t>cross_kg_012</t>
         </is>
       </c>
       <c r="B183" s="5" t="n">
@@ -12433,13 +12433,13 @@
         <v>1</v>
       </c>
       <c r="N183" s="5" t="n">
-        <v>20.66</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_007</t>
+          <t>cross_kg_012</t>
         </is>
       </c>
       <c r="B184" s="5" t="n">
@@ -12493,13 +12493,13 @@
         <v>1</v>
       </c>
       <c r="N184" s="5" t="n">
-        <v>15.22</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_008</t>
+          <t>open_kg_001</t>
         </is>
       </c>
       <c r="B185" s="5" t="n">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H185" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I185" s="5" t="b">
@@ -12543,23 +12543,19 @@
       </c>
       <c r="K185" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L185" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M185" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>execution_failure</t>
+        </is>
+      </c>
+      <c r="L185" s="5" t="n"/>
+      <c r="M185" s="5" t="n"/>
       <c r="N185" s="5" t="n">
-        <v>18.21</v>
+        <v>24.09</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_008</t>
+          <t>open_kg_001</t>
         </is>
       </c>
       <c r="B186" s="5" t="n">
@@ -12567,7 +12563,7 @@
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
@@ -12587,12 +12583,12 @@
       </c>
       <c r="G186" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H186" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I186" s="5" t="b">
@@ -12606,20 +12602,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L186" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M186" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L186" s="5" t="n"/>
+      <c r="M186" s="5" t="n"/>
       <c r="N186" s="5" t="n">
-        <v>18.97</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_008</t>
+          <t>open_kg_001</t>
         </is>
       </c>
       <c r="B187" s="5" t="n">
@@ -12627,7 +12619,7 @@
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
@@ -12647,12 +12639,12 @@
       </c>
       <c r="G187" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H187" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I187" s="5" t="b">
@@ -12666,20 +12658,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L187" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M187" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L187" s="5" t="n"/>
+      <c r="M187" s="5" t="n"/>
       <c r="N187" s="5" t="n">
-        <v>15.86</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_009</t>
+          <t>open_kg_002</t>
         </is>
       </c>
       <c r="B188" s="5" t="n">
@@ -12687,7 +12675,7 @@
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D188" s="5" t="inlineStr">
@@ -12707,12 +12695,12 @@
       </c>
       <c r="G188" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H188" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I188" s="5" t="b">
@@ -12733,13 +12721,13 @@
         <v>1</v>
       </c>
       <c r="N188" s="5" t="n">
-        <v>15.82</v>
+        <v>31.98</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_009</t>
+          <t>open_kg_002</t>
         </is>
       </c>
       <c r="B189" s="5" t="n">
@@ -12747,7 +12735,7 @@
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D189" s="5" t="inlineStr">
@@ -12767,12 +12755,12 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I189" s="5" t="b">
@@ -12793,13 +12781,13 @@
         <v>1</v>
       </c>
       <c r="N189" s="5" t="n">
-        <v>19.46</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_009</t>
+          <t>open_kg_002</t>
         </is>
       </c>
       <c r="B190" s="5" t="n">
@@ -12807,7 +12795,7 @@
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D190" s="5" t="inlineStr">
@@ -12827,16 +12815,16 @@
       </c>
       <c r="G190" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H190" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I190" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J190" s="5" t="b">
         <v>1</v>
@@ -12847,19 +12835,19 @@
         </is>
       </c>
       <c r="L190" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M190" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N190" s="5" t="n">
-        <v>13.83</v>
+        <v>28.32</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_010</t>
+          <t>open_kg_003</t>
         </is>
       </c>
       <c r="B191" s="5" t="n">
@@ -12867,7 +12855,7 @@
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D191" s="5" t="inlineStr">
@@ -12887,12 +12875,12 @@
       </c>
       <c r="G191" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H191" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I191" s="5" t="b">
@@ -12913,13 +12901,13 @@
         <v>1</v>
       </c>
       <c r="N191" s="5" t="n">
-        <v>13.62</v>
+        <v>16.66</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_010</t>
+          <t>open_kg_003</t>
         </is>
       </c>
       <c r="B192" s="5" t="n">
@@ -12927,7 +12915,7 @@
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D192" s="5" t="inlineStr">
@@ -12947,12 +12935,12 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I192" s="5" t="b">
@@ -12973,13 +12961,13 @@
         <v>1</v>
       </c>
       <c r="N192" s="5" t="n">
-        <v>14.52</v>
+        <v>16.45</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_010</t>
+          <t>open_kg_003</t>
         </is>
       </c>
       <c r="B193" s="5" t="n">
@@ -12987,7 +12975,7 @@
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D193" s="5" t="inlineStr">
@@ -13007,12 +12995,12 @@
       </c>
       <c r="G193" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H193" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I193" s="5" t="b">
@@ -13023,23 +13011,23 @@
       </c>
       <c r="K193" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L193" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M193" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N193" s="5" t="n">
-        <v>14.79</v>
+        <v>21.42</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_011</t>
+          <t>open_kg_004</t>
         </is>
       </c>
       <c r="B194" s="5" t="n">
@@ -13047,7 +13035,7 @@
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D194" s="5" t="inlineStr">
@@ -13067,12 +13055,12 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I194" s="5" t="b">
@@ -13087,19 +13075,19 @@
         </is>
       </c>
       <c r="L194" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M194" s="5" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="N194" s="5" t="n">
-        <v>14.66</v>
+        <v>30.16</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_011</t>
+          <t>open_kg_004</t>
         </is>
       </c>
       <c r="B195" s="5" t="n">
@@ -13107,7 +13095,7 @@
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D195" s="5" t="inlineStr">
@@ -13127,12 +13115,12 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I195" s="5" t="b">
@@ -13147,19 +13135,19 @@
         </is>
       </c>
       <c r="L195" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M195" s="5" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="N195" s="5" t="n">
-        <v>16.25</v>
+        <v>26.96</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_011</t>
+          <t>open_kg_004</t>
         </is>
       </c>
       <c r="B196" s="5" t="n">
@@ -13167,7 +13155,7 @@
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D196" s="5" t="inlineStr">
@@ -13187,12 +13175,12 @@
       </c>
       <c r="G196" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H196" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I196" s="5" t="b">
@@ -13207,19 +13195,19 @@
         </is>
       </c>
       <c r="L196" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M196" s="5" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="N196" s="5" t="n">
-        <v>15.25</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_012</t>
+          <t>open_kg_005</t>
         </is>
       </c>
       <c r="B197" s="5" t="n">
@@ -13227,7 +13215,7 @@
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D197" s="5" t="inlineStr">
@@ -13247,39 +13235,35 @@
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H197" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I197" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J197" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K197" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L197" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M197" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>execution_failure</t>
+        </is>
+      </c>
+      <c r="L197" s="5" t="n"/>
+      <c r="M197" s="5" t="n"/>
       <c r="N197" s="5" t="n">
-        <v>14.31</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_012</t>
+          <t>open_kg_005</t>
         </is>
       </c>
       <c r="B198" s="5" t="n">
@@ -13287,7 +13271,7 @@
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D198" s="5" t="inlineStr">
@@ -13307,39 +13291,35 @@
       </c>
       <c r="G198" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H198" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I198" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J198" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K198" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L198" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M198" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>execution_failure</t>
+        </is>
+      </c>
+      <c r="L198" s="5" t="n"/>
+      <c r="M198" s="5" t="n"/>
       <c r="N198" s="5" t="n">
-        <v>15.12</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_012</t>
+          <t>open_kg_005</t>
         </is>
       </c>
       <c r="B199" s="5" t="n">
@@ -13347,7 +13327,7 @@
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D199" s="5" t="inlineStr">
@@ -13367,12 +13347,12 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I199" s="5" t="b">
@@ -13386,20 +13366,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L199" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M199" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L199" s="5" t="n"/>
+      <c r="M199" s="5" t="n"/>
       <c r="N199" s="5" t="n">
-        <v>14.99</v>
+        <v>36.26</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
         <is>
-          <t>open_kg_001</t>
+          <t>open_kg_006</t>
         </is>
       </c>
       <c r="B200" s="5" t="n">
@@ -13449,13 +13425,13 @@
       <c r="L200" s="5" t="n"/>
       <c r="M200" s="5" t="n"/>
       <c r="N200" s="5" t="n">
-        <v>24.09</v>
+        <v>22.57</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>open_kg_001</t>
+          <t>open_kg_006</t>
         </is>
       </c>
       <c r="B201" s="5" t="n">
@@ -13505,13 +13481,13 @@
       <c r="L201" s="5" t="n"/>
       <c r="M201" s="5" t="n"/>
       <c r="N201" s="5" t="n">
-        <v>23.4</v>
+        <v>21.96</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
         <is>
-          <t>open_kg_001</t>
+          <t>open_kg_006</t>
         </is>
       </c>
       <c r="B202" s="5" t="n">
@@ -13561,26 +13537,26 @@
       <c r="L202" s="5" t="n"/>
       <c r="M202" s="5" t="n"/>
       <c r="N202" s="5" t="n">
-        <v>22.25</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
         <is>
-          <t>open_kg_002</t>
+          <t>count_kg1_002</t>
         </is>
       </c>
       <c r="B203" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
@@ -13595,12 +13571,12 @@
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H203" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I203" s="5" t="b">
@@ -13621,26 +13597,26 @@
         <v>1</v>
       </c>
       <c r="N203" s="5" t="n">
-        <v>31.98</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="5" t="inlineStr">
         <is>
-          <t>open_kg_002</t>
+          <t>count_kg1_002</t>
         </is>
       </c>
       <c r="B204" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
@@ -13655,12 +13631,12 @@
       </c>
       <c r="G204" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H204" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I204" s="5" t="b">
@@ -13681,26 +13657,26 @@
         <v>1</v>
       </c>
       <c r="N204" s="5" t="n">
-        <v>31.6</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="5" t="inlineStr">
         <is>
-          <t>open_kg_002</t>
+          <t>count_kg1_002</t>
         </is>
       </c>
       <c r="B205" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C205" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr">
@@ -13715,12 +13691,12 @@
       </c>
       <c r="G205" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H205" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I205" s="5" t="b">
@@ -13741,26 +13717,26 @@
         <v>1</v>
       </c>
       <c r="N205" s="5" t="n">
-        <v>28.32</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
         <is>
-          <t>open_kg_003</t>
+          <t>count_kg1_003</t>
         </is>
       </c>
       <c r="B206" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
@@ -13775,12 +13751,12 @@
       </c>
       <c r="G206" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H206" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I206" s="5" t="b">
@@ -13801,26 +13777,26 @@
         <v>1</v>
       </c>
       <c r="N206" s="5" t="n">
-        <v>16.66</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
         <is>
-          <t>open_kg_003</t>
+          <t>count_kg1_003</t>
         </is>
       </c>
       <c r="B207" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E207" s="5" t="inlineStr">
@@ -13835,12 +13811,12 @@
       </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H207" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I207" s="5" t="b">
@@ -13861,26 +13837,26 @@
         <v>1</v>
       </c>
       <c r="N207" s="5" t="n">
-        <v>16.45</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="5" t="inlineStr">
         <is>
-          <t>open_kg_003</t>
+          <t>count_kg1_003</t>
         </is>
       </c>
       <c r="B208" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
@@ -13895,12 +13871,12 @@
       </c>
       <c r="G208" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H208" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I208" s="5" t="b">
@@ -13911,36 +13887,36 @@
       </c>
       <c r="K208" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L208" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M208" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N208" s="5" t="n">
-        <v>21.42</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
         <is>
-          <t>open_kg_004</t>
+          <t>filter_numeric_kg1_001</t>
         </is>
       </c>
       <c r="B209" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E209" s="5" t="inlineStr">
@@ -13955,12 +13931,12 @@
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H209" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I209" s="5" t="b">
@@ -13975,32 +13951,32 @@
         </is>
       </c>
       <c r="L209" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M209" s="5" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="N209" s="5" t="n">
-        <v>30.16</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
         <is>
-          <t>open_kg_004</t>
+          <t>filter_numeric_kg1_001</t>
         </is>
       </c>
       <c r="B210" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
@@ -14015,12 +13991,12 @@
       </c>
       <c r="G210" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H210" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I210" s="5" t="b">
@@ -14035,32 +14011,32 @@
         </is>
       </c>
       <c r="L210" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M210" s="5" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="N210" s="5" t="n">
-        <v>26.96</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
         <is>
-          <t>open_kg_004</t>
+          <t>filter_numeric_kg1_001</t>
         </is>
       </c>
       <c r="B211" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E211" s="5" t="inlineStr">
@@ -14075,12 +14051,12 @@
       </c>
       <c r="G211" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H211" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I211" s="5" t="b">
@@ -14095,32 +14071,32 @@
         </is>
       </c>
       <c r="L211" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M211" s="5" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="N211" s="5" t="n">
-        <v>26.8</v>
+        <v>7.61</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="5" t="inlineStr">
         <is>
-          <t>open_kg_005</t>
+          <t>filter_numeric_kg1_002</t>
         </is>
       </c>
       <c r="B212" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
@@ -14135,7 +14111,7 @@
       </c>
       <c r="G212" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H212" s="5" t="inlineStr">
@@ -14144,39 +14120,43 @@
         </is>
       </c>
       <c r="I212" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J212" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K212" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L212" s="5" t="n"/>
-      <c r="M212" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L212" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M212" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N212" s="5" t="n">
-        <v>9.82</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
         <is>
-          <t>open_kg_005</t>
+          <t>filter_numeric_kg1_002</t>
         </is>
       </c>
       <c r="B213" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E213" s="5" t="inlineStr">
@@ -14191,7 +14171,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -14200,39 +14180,43 @@
         </is>
       </c>
       <c r="I213" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J213" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K213" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L213" s="5" t="n"/>
-      <c r="M213" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L213" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M213" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N213" s="5" t="n">
-        <v>11.1</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
         <is>
-          <t>open_kg_005</t>
+          <t>filter_numeric_kg1_002</t>
         </is>
       </c>
       <c r="B214" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
@@ -14247,12 +14231,12 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I214" s="5" t="b">
@@ -14266,29 +14250,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L214" s="5" t="n"/>
-      <c r="M214" s="5" t="n"/>
+      <c r="L214" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M214" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N214" s="5" t="n">
-        <v>36.26</v>
+        <v>11.14</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
         <is>
-          <t>open_kg_006</t>
+          <t>filter_numeric_kg1_003</t>
         </is>
       </c>
       <c r="B215" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E215" s="5" t="inlineStr">
@@ -14303,12 +14291,12 @@
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H215" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I215" s="5" t="b">
@@ -14319,32 +14307,36 @@
       </c>
       <c r="K215" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L215" s="5" t="n"/>
-      <c r="M215" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L215" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M215" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N215" s="5" t="n">
-        <v>22.57</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
         <is>
-          <t>open_kg_006</t>
+          <t>filter_numeric_kg1_003</t>
         </is>
       </c>
       <c r="B216" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
@@ -14359,12 +14351,12 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I216" s="5" t="b">
@@ -14378,29 +14370,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L216" s="5" t="n"/>
-      <c r="M216" s="5" t="n"/>
+      <c r="L216" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M216" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N216" s="5" t="n">
-        <v>21.96</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
         <is>
-          <t>open_kg_006</t>
+          <t>filter_numeric_kg1_003</t>
         </is>
       </c>
       <c r="B217" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E217" s="5" t="inlineStr">
@@ -14415,12 +14411,12 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I217" s="5" t="b">
@@ -14434,16 +14430,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L217" s="5" t="n"/>
-      <c r="M217" s="5" t="n"/>
+      <c r="L217" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M217" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N217" s="5" t="n">
-        <v>21.9</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_001</t>
+          <t>filter_numeric_kg2_001</t>
         </is>
       </c>
       <c r="B218" s="5" t="n">
@@ -14451,12 +14451,12 @@
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
@@ -14483,27 +14483,27 @@
         <v>1</v>
       </c>
       <c r="J218" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K218" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L218" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M218" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N218" s="5" t="n">
-        <v>7.46</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_001</t>
+          <t>filter_numeric_kg2_001</t>
         </is>
       </c>
       <c r="B219" s="5" t="n">
@@ -14511,12 +14511,12 @@
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E219" s="5" t="inlineStr">
@@ -14543,27 +14543,27 @@
         <v>1</v>
       </c>
       <c r="J219" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K219" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L219" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M219" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N219" s="5" t="n">
-        <v>7.6</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_001</t>
+          <t>filter_numeric_kg2_001</t>
         </is>
       </c>
       <c r="B220" s="5" t="n">
@@ -14571,12 +14571,12 @@
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
@@ -14617,13 +14617,13 @@
         <v>1</v>
       </c>
       <c r="N220" s="5" t="n">
-        <v>7.76</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_002</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B221" s="5" t="n">
@@ -14631,12 +14631,12 @@
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E221" s="5" t="inlineStr">
@@ -14671,19 +14671,19 @@
         </is>
       </c>
       <c r="L221" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M221" s="5" t="n">
-        <v>1</v>
+        <v>0.7692</v>
       </c>
       <c r="N221" s="5" t="n">
-        <v>10.08</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_002</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B222" s="5" t="n">
@@ -14691,12 +14691,12 @@
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
@@ -14731,19 +14731,19 @@
         </is>
       </c>
       <c r="L222" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M222" s="5" t="n">
-        <v>1</v>
+        <v>0.7692</v>
       </c>
       <c r="N222" s="5" t="n">
-        <v>7.59</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_002</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B223" s="5" t="n">
@@ -14751,12 +14751,12 @@
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E223" s="5" t="inlineStr">
@@ -14791,19 +14791,19 @@
         </is>
       </c>
       <c r="L223" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M223" s="5" t="n">
-        <v>1</v>
+        <v>0.7692</v>
       </c>
       <c r="N223" s="5" t="n">
-        <v>7.26</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_003</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B224" s="5" t="n">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E224" s="5" t="inlineStr">
@@ -14857,13 +14857,13 @@
         <v>1</v>
       </c>
       <c r="N224" s="5" t="n">
-        <v>7.41</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_003</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B225" s="5" t="n">
@@ -14871,12 +14871,12 @@
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E225" s="5" t="inlineStr">
@@ -14917,13 +14917,13 @@
         <v>1</v>
       </c>
       <c r="N225" s="5" t="n">
-        <v>7.27</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_003</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B226" s="5" t="n">
@@ -14931,12 +14931,12 @@
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E226" s="5" t="inlineStr">
@@ -14977,13 +14977,13 @@
         <v>1</v>
       </c>
       <c r="N226" s="5" t="n">
-        <v>7.27</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_001</t>
+          <t>filter_string_kg2_001</t>
         </is>
       </c>
       <c r="B227" s="5" t="n">
@@ -14991,12 +14991,12 @@
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E227" s="5" t="inlineStr">
@@ -15037,13 +15037,13 @@
         <v>1</v>
       </c>
       <c r="N227" s="5" t="n">
-        <v>7.64</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_001</t>
+          <t>filter_string_kg2_001</t>
         </is>
       </c>
       <c r="B228" s="5" t="n">
@@ -15051,12 +15051,12 @@
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
@@ -15097,13 +15097,13 @@
         <v>1</v>
       </c>
       <c r="N228" s="5" t="n">
-        <v>7.65</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_001</t>
+          <t>filter_string_kg2_001</t>
         </is>
       </c>
       <c r="B229" s="5" t="n">
@@ -15111,12 +15111,12 @@
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E229" s="5" t="inlineStr">
@@ -15157,13 +15157,13 @@
         <v>1</v>
       </c>
       <c r="N229" s="5" t="n">
-        <v>7.61</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_002</t>
+          <t>filter_string_kg2_002</t>
         </is>
       </c>
       <c r="B230" s="5" t="n">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="C230" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E230" s="5" t="inlineStr">
@@ -15210,20 +15210,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L230" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M230" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L230" s="5" t="n"/>
+      <c r="M230" s="5" t="n"/>
       <c r="N230" s="5" t="n">
-        <v>8.18</v>
+        <v>14.52</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_002</t>
+          <t>filter_string_kg2_002</t>
         </is>
       </c>
       <c r="B231" s="5" t="n">
@@ -15231,12 +15227,12 @@
       </c>
       <c r="C231" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E231" s="5" t="inlineStr">
@@ -15270,20 +15266,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L231" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M231" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L231" s="5" t="n"/>
+      <c r="M231" s="5" t="n"/>
       <c r="N231" s="5" t="n">
-        <v>11.49</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_002</t>
+          <t>filter_string_kg2_002</t>
         </is>
       </c>
       <c r="B232" s="5" t="n">
@@ -15291,12 +15283,12 @@
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E232" s="5" t="inlineStr">
@@ -15330,20 +15322,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L232" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M232" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L232" s="5" t="n"/>
+      <c r="M232" s="5" t="n"/>
       <c r="N232" s="5" t="n">
-        <v>11.14</v>
+        <v>10.88</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_003</t>
+          <t>ranking_kg2_001</t>
         </is>
       </c>
       <c r="B233" s="5" t="n">
@@ -15351,12 +15339,12 @@
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E233" s="5" t="inlineStr">
@@ -15397,13 +15385,13 @@
         <v>1</v>
       </c>
       <c r="N233" s="5" t="n">
-        <v>7.94</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_003</t>
+          <t>ranking_kg2_001</t>
         </is>
       </c>
       <c r="B234" s="5" t="n">
@@ -15411,12 +15399,12 @@
       </c>
       <c r="C234" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
@@ -15457,13 +15445,13 @@
         <v>1</v>
       </c>
       <c r="N234" s="5" t="n">
-        <v>7.93</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_003</t>
+          <t>ranking_kg2_001</t>
         </is>
       </c>
       <c r="B235" s="5" t="n">
@@ -15471,12 +15459,12 @@
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E235" s="5" t="inlineStr">
@@ -15517,13 +15505,13 @@
         <v>1</v>
       </c>
       <c r="N235" s="5" t="n">
-        <v>7.63</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_001</t>
+          <t>ranking_kg2_002</t>
         </is>
       </c>
       <c r="B236" s="5" t="n">
@@ -15531,7 +15519,7 @@
       </c>
       <c r="C236" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D236" s="5" t="inlineStr">
@@ -15577,13 +15565,13 @@
         <v>1</v>
       </c>
       <c r="N236" s="5" t="n">
-        <v>9.98</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_001</t>
+          <t>ranking_kg2_002</t>
         </is>
       </c>
       <c r="B237" s="5" t="n">
@@ -15591,7 +15579,7 @@
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D237" s="5" t="inlineStr">
@@ -15637,13 +15625,13 @@
         <v>1</v>
       </c>
       <c r="N237" s="5" t="n">
-        <v>12.4</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_001</t>
+          <t>ranking_kg2_002</t>
         </is>
       </c>
       <c r="B238" s="5" t="n">
@@ -15651,7 +15639,7 @@
       </c>
       <c r="C238" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D238" s="5" t="inlineStr">
@@ -15697,13 +15685,13 @@
         <v>1</v>
       </c>
       <c r="N238" s="5" t="n">
-        <v>9.48</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>ranking_kg2_003</t>
         </is>
       </c>
       <c r="B239" s="5" t="n">
@@ -15711,7 +15699,7 @@
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D239" s="5" t="inlineStr">
@@ -15751,19 +15739,19 @@
         </is>
       </c>
       <c r="L239" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M239" s="5" t="n">
-        <v>0.7692</v>
+        <v>1</v>
       </c>
       <c r="N239" s="5" t="n">
-        <v>7.51</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>ranking_kg2_003</t>
         </is>
       </c>
       <c r="B240" s="5" t="n">
@@ -15771,7 +15759,7 @@
       </c>
       <c r="C240" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D240" s="5" t="inlineStr">
@@ -15811,19 +15799,19 @@
         </is>
       </c>
       <c r="L240" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M240" s="5" t="n">
-        <v>0.7692</v>
+        <v>1</v>
       </c>
       <c r="N240" s="5" t="n">
-        <v>8.029999999999999</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>ranking_kg2_003</t>
         </is>
       </c>
       <c r="B241" s="5" t="n">
@@ -15831,7 +15819,7 @@
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D241" s="5" t="inlineStr">
@@ -15871,19 +15859,19 @@
         </is>
       </c>
       <c r="L241" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M241" s="5" t="n">
-        <v>0.7692</v>
+        <v>1</v>
       </c>
       <c r="N241" s="5" t="n">
-        <v>8.640000000000001</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B242" s="5" t="n">
@@ -15891,7 +15879,7 @@
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D242" s="5" t="inlineStr">
@@ -15937,13 +15925,13 @@
         <v>1</v>
       </c>
       <c r="N242" s="5" t="n">
-        <v>9.23</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B243" s="5" t="n">
@@ -15951,7 +15939,7 @@
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D243" s="5" t="inlineStr">
@@ -15997,13 +15985,13 @@
         <v>1</v>
       </c>
       <c r="N243" s="5" t="n">
-        <v>9.27</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B244" s="5" t="n">
@@ -16011,7 +15999,7 @@
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D244" s="5" t="inlineStr">
@@ -16057,13 +16045,13 @@
         <v>1</v>
       </c>
       <c r="N244" s="5" t="n">
-        <v>9.970000000000001</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_001</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B245" s="5" t="n">
@@ -16071,7 +16059,7 @@
       </c>
       <c r="C245" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D245" s="5" t="inlineStr">
@@ -16117,13 +16105,13 @@
         <v>1</v>
       </c>
       <c r="N245" s="5" t="n">
-        <v>8.59</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_001</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B246" s="5" t="n">
@@ -16131,7 +16119,7 @@
       </c>
       <c r="C246" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D246" s="5" t="inlineStr">
@@ -16177,13 +16165,13 @@
         <v>1</v>
       </c>
       <c r="N246" s="5" t="n">
-        <v>8.460000000000001</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_001</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B247" s="5" t="n">
@@ -16191,7 +16179,7 @@
       </c>
       <c r="C247" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D247" s="5" t="inlineStr">
@@ -16237,27 +16225,25 @@
         <v>1</v>
       </c>
       <c r="N247" s="5" t="n">
-        <v>8.859999999999999</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_002</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B248" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
-        </is>
-      </c>
-      <c r="D248" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D248" s="5" t="n">
+        <v/>
       </c>
       <c r="E248" s="5" t="inlineStr">
         <is>
@@ -16271,19 +16257,19 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I248" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J248" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K248" s="5" t="inlineStr">
         <is>
@@ -16293,27 +16279,25 @@
       <c r="L248" s="5" t="n"/>
       <c r="M248" s="5" t="n"/>
       <c r="N248" s="5" t="n">
-        <v>14.52</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_002</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B249" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
-        </is>
-      </c>
-      <c r="D249" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D249" s="5" t="n">
+        <v/>
       </c>
       <c r="E249" s="5" t="inlineStr">
         <is>
@@ -16327,19 +16311,19 @@
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H249" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I249" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J249" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K249" s="5" t="inlineStr">
         <is>
@@ -16349,27 +16333,25 @@
       <c r="L249" s="5" t="n"/>
       <c r="M249" s="5" t="n"/>
       <c r="N249" s="5" t="n">
-        <v>11.11</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_002</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B250" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
-        </is>
-      </c>
-      <c r="D250" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D250" s="5" t="n">
+        <v/>
       </c>
       <c r="E250" s="5" t="inlineStr">
         <is>
@@ -16383,19 +16365,19 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I250" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J250" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K250" s="5" t="inlineStr">
         <is>
@@ -16405,27 +16387,25 @@
       <c r="L250" s="5" t="n"/>
       <c r="M250" s="5" t="n"/>
       <c r="N250" s="5" t="n">
-        <v>10.88</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B251" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C251" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
-        </is>
-      </c>
-      <c r="D251" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D251" s="5" t="n">
+        <v/>
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
@@ -16439,53 +16419,47 @@
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H251" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I251" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J251" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K251" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L251" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M251" s="5" t="n">
-        <v>0.7368</v>
-      </c>
+      <c r="L251" s="5" t="n"/>
+      <c r="M251" s="5" t="n"/>
       <c r="N251" s="5" t="n">
-        <v>8.890000000000001</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B252" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C252" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
-        </is>
-      </c>
-      <c r="D252" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D252" s="5" t="n">
+        <v/>
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
@@ -16499,53 +16473,47 @@
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H252" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I252" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J252" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K252" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L252" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M252" s="5" t="n">
-        <v>0.7368</v>
-      </c>
+      <c r="L252" s="5" t="n"/>
+      <c r="M252" s="5" t="n"/>
       <c r="N252" s="5" t="n">
-        <v>8.779999999999999</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B253" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
-        </is>
-      </c>
-      <c r="D253" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D253" s="5" t="n">
+        <v/>
       </c>
       <c r="E253" s="5" t="inlineStr">
         <is>
@@ -16559,53 +16527,47 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I253" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J253" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K253" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L253" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M253" s="5" t="n">
-        <v>0.7368</v>
-      </c>
+          <t>mapping_failure</t>
+        </is>
+      </c>
+      <c r="L253" s="5" t="n"/>
+      <c r="M253" s="5" t="n"/>
       <c r="N253" s="5" t="n">
-        <v>8.77</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_001</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B254" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
-        </is>
-      </c>
-      <c r="D254" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D254" s="5" t="n">
+        <v/>
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
@@ -16619,53 +16581,47 @@
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H254" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I254" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J254" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K254" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L254" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M254" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L254" s="5" t="n"/>
+      <c r="M254" s="5" t="n"/>
       <c r="N254" s="5" t="n">
-        <v>6.9</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_001</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B255" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
-        </is>
-      </c>
-      <c r="D255" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D255" s="5" t="n">
+        <v/>
       </c>
       <c r="E255" s="5" t="inlineStr">
         <is>
@@ -16679,53 +16635,47 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I255" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J255" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K255" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L255" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M255" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L255" s="5" t="n"/>
+      <c r="M255" s="5" t="n"/>
       <c r="N255" s="5" t="n">
-        <v>6.82</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_001</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B256" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C256" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
-        </is>
-      </c>
-      <c r="D256" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D256" s="5" t="n">
+        <v/>
       </c>
       <c r="E256" s="5" t="inlineStr">
         <is>
@@ -16739,52 +16689,48 @@
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H256" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I256" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J256" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K256" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L256" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M256" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L256" s="5" t="n"/>
+      <c r="M256" s="5" t="n"/>
       <c r="N256" s="5" t="n">
-        <v>6.85</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_002</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B257" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E257" s="5" t="inlineStr">
@@ -16799,12 +16745,12 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I257" s="5" t="b">
@@ -16825,26 +16771,26 @@
         <v>1</v>
       </c>
       <c r="N257" s="5" t="n">
-        <v>6.61</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_002</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B258" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E258" s="5" t="inlineStr">
@@ -16859,12 +16805,12 @@
       </c>
       <c r="G258" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H258" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I258" s="5" t="b">
@@ -16885,26 +16831,26 @@
         <v>1</v>
       </c>
       <c r="N258" s="5" t="n">
-        <v>6.82</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_002</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B259" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C259" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E259" s="5" t="inlineStr">
@@ -16919,12 +16865,12 @@
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H259" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I259" s="5" t="b">
@@ -16945,26 +16891,26 @@
         <v>1</v>
       </c>
       <c r="N259" s="5" t="n">
-        <v>6.69</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_003</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B260" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E260" s="5" t="inlineStr">
@@ -16979,12 +16925,12 @@
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H260" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I260" s="5" t="b">
@@ -17005,26 +16951,26 @@
         <v>1</v>
       </c>
       <c r="N260" s="5" t="n">
-        <v>6.95</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_003</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B261" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E261" s="5" t="inlineStr">
@@ -17039,52 +16985,48 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I261" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J261" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K261" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L261" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M261" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L261" s="5" t="n"/>
+      <c r="M261" s="5" t="n"/>
       <c r="N261" s="5" t="n">
-        <v>6.88</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_003</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B262" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E262" s="5" t="inlineStr">
@@ -17099,12 +17041,12 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I262" s="5" t="b">
@@ -17125,26 +17067,26 @@
         <v>1</v>
       </c>
       <c r="N262" s="5" t="n">
-        <v>6.92</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B263" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C263" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E263" s="5" t="inlineStr">
@@ -17159,12 +17101,12 @@
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H263" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I263" s="5" t="b">
@@ -17185,26 +17127,26 @@
         <v>1</v>
       </c>
       <c r="N263" s="5" t="n">
-        <v>4.34</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B264" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E264" s="5" t="inlineStr">
@@ -17219,12 +17161,12 @@
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H264" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I264" s="5" t="b">
@@ -17245,26 +17187,26 @@
         <v>1</v>
       </c>
       <c r="N264" s="5" t="n">
-        <v>3.62</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B265" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E265" s="5" t="inlineStr">
@@ -17279,12 +17221,12 @@
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H265" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I265" s="5" t="b">
@@ -17305,26 +17247,26 @@
         <v>1</v>
       </c>
       <c r="N265" s="5" t="n">
-        <v>4.4</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B266" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
@@ -17339,12 +17281,12 @@
       </c>
       <c r="G266" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H266" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I266" s="5" t="b">
@@ -17365,26 +17307,26 @@
         <v>1</v>
       </c>
       <c r="N266" s="5" t="n">
-        <v>3.49</v>
+        <v>16.49</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B267" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E267" s="5" t="inlineStr">
@@ -17399,12 +17341,12 @@
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H267" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I267" s="5" t="b">
@@ -17425,26 +17367,26 @@
         <v>1</v>
       </c>
       <c r="N267" s="5" t="n">
-        <v>4.45</v>
+        <v>17.18</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B268" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
@@ -17459,12 +17401,12 @@
       </c>
       <c r="G268" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H268" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I268" s="5" t="b">
@@ -17479,32 +17421,32 @@
         </is>
       </c>
       <c r="L268" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M268" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N268" s="5" t="n">
-        <v>10.46</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B269" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E269" s="5" t="inlineStr">
@@ -17519,12 +17461,12 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I269" s="5" t="b">
@@ -17545,26 +17487,26 @@
         <v>1</v>
       </c>
       <c r="N269" s="5" t="n">
-        <v>4.17</v>
+        <v>26.92</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B270" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
@@ -17579,12 +17521,12 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I270" s="5" t="b">
@@ -17605,26 +17547,26 @@
         <v>1</v>
       </c>
       <c r="N270" s="5" t="n">
-        <v>3.67</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B271" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
@@ -17639,12 +17581,12 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I271" s="5" t="b">
@@ -17665,13 +17607,13 @@
         <v>1</v>
       </c>
       <c r="N271" s="5" t="n">
-        <v>3.61</v>
+        <v>19.47</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B272" s="5" t="n">
@@ -17679,11 +17621,13 @@
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D272" s="5" t="n">
-        <v/>
+          <t>typo_fuzzy</t>
+        </is>
+      </c>
+      <c r="D272" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
         <is>
@@ -17697,35 +17641,39 @@
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H272" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I272" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J272" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K272" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L272" s="5" t="n"/>
-      <c r="M272" s="5" t="n"/>
+      <c r="L272" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M272" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N272" s="5" t="n">
-        <v>3.89</v>
+        <v>21.28</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B273" s="5" t="n">
@@ -17733,11 +17681,13 @@
       </c>
       <c r="C273" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D273" s="5" t="n">
-        <v/>
+          <t>typo_fuzzy</t>
+        </is>
+      </c>
+      <c r="D273" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E273" s="5" t="inlineStr">
         <is>
@@ -17751,35 +17701,39 @@
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H273" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I273" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J273" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K273" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L273" s="5" t="n"/>
-      <c r="M273" s="5" t="n"/>
+      <c r="L273" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M273" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N273" s="5" t="n">
-        <v>3.34</v>
+        <v>22.32</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B274" s="5" t="n">
@@ -17787,11 +17741,13 @@
       </c>
       <c r="C274" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D274" s="5" t="n">
-        <v/>
+          <t>typo_fuzzy</t>
+        </is>
+      </c>
+      <c r="D274" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E274" s="5" t="inlineStr">
         <is>
@@ -17805,35 +17761,39 @@
       </c>
       <c r="G274" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H274" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I274" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J274" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K274" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L274" s="5" t="n"/>
-      <c r="M274" s="5" t="n"/>
+      <c r="L274" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M274" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N274" s="5" t="n">
-        <v>3.8</v>
+        <v>21.36</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B275" s="5" t="n">
@@ -17841,11 +17801,13 @@
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D275" s="5" t="n">
-        <v/>
+          <t>multilingual_edge</t>
+        </is>
+      </c>
+      <c r="D275" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E275" s="5" t="inlineStr">
         <is>
@@ -17859,35 +17821,39 @@
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H275" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I275" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J275" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K275" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L275" s="5" t="n"/>
-      <c r="M275" s="5" t="n"/>
+      <c r="L275" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M275" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N275" s="5" t="n">
-        <v>7.1</v>
+        <v>16.55</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B276" s="5" t="n">
@@ -17895,11 +17861,13 @@
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D276" s="5" t="n">
-        <v/>
+          <t>multilingual_edge</t>
+        </is>
+      </c>
+      <c r="D276" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
@@ -17913,35 +17881,39 @@
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H276" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I276" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J276" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K276" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L276" s="5" t="n"/>
-      <c r="M276" s="5" t="n"/>
+      <c r="L276" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M276" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N276" s="5" t="n">
-        <v>7.48</v>
+        <v>20.76</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B277" s="5" t="n">
@@ -17949,11 +17921,13 @@
       </c>
       <c r="C277" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D277" s="5" t="n">
-        <v/>
+          <t>multilingual_edge</t>
+        </is>
+      </c>
+      <c r="D277" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E277" s="5" t="inlineStr">
         <is>
@@ -17967,35 +17941,39 @@
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H277" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I277" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J277" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K277" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L277" s="5" t="n"/>
-      <c r="M277" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L277" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M277" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N277" s="5" t="n">
-        <v>4.99</v>
+        <v>16.66</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B278" s="5" t="n">
@@ -18003,11 +17981,13 @@
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D278" s="5" t="n">
-        <v/>
+          <t>multilingual_edge</t>
+        </is>
+      </c>
+      <c r="D278" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E278" s="5" t="inlineStr">
         <is>
@@ -18021,35 +18001,39 @@
       </c>
       <c r="G278" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H278" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I278" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J278" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K278" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L278" s="5" t="n"/>
-      <c r="M278" s="5" t="n"/>
+      <c r="L278" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M278" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N278" s="5" t="n">
-        <v>3.28</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B279" s="5" t="n">
@@ -18057,11 +18041,13 @@
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D279" s="5" t="n">
-        <v/>
+          <t>multilingual_edge</t>
+        </is>
+      </c>
+      <c r="D279" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E279" s="5" t="inlineStr">
         <is>
@@ -18075,35 +18061,39 @@
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H279" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I279" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J279" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K279" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L279" s="5" t="n"/>
-      <c r="M279" s="5" t="n"/>
+      <c r="L279" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M279" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N279" s="5" t="n">
-        <v>3.38</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B280" s="5" t="n">
@@ -18111,11 +18101,13 @@
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D280" s="5" t="n">
-        <v/>
+          <t>multilingual_edge</t>
+        </is>
+      </c>
+      <c r="D280" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
@@ -18129,35 +18121,39 @@
       </c>
       <c r="G280" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H280" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I280" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J280" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K280" s="5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="L280" s="5" t="n"/>
-      <c r="M280" s="5" t="n"/>
+      <c r="L280" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M280" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N280" s="5" t="n">
-        <v>3.33</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B281" s="5" t="n">
@@ -18165,7 +18161,7 @@
       </c>
       <c r="C281" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D281" s="5" t="inlineStr">
@@ -18185,12 +18181,12 @@
       </c>
       <c r="G281" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H281" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I281" s="5" t="b">
@@ -18204,20 +18200,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L281" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M281" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L281" s="5" t="n"/>
+      <c r="M281" s="5" t="n"/>
       <c r="N281" s="5" t="n">
-        <v>7.1</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B282" s="5" t="n">
@@ -18225,7 +18217,7 @@
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D282" s="5" t="inlineStr">
@@ -18245,12 +18237,12 @@
       </c>
       <c r="G282" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H282" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I282" s="5" t="b">
@@ -18264,20 +18256,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L282" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M282" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L282" s="5" t="n"/>
+      <c r="M282" s="5" t="n"/>
       <c r="N282" s="5" t="n">
-        <v>7.12</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B283" s="5" t="n">
@@ -18285,7 +18273,7 @@
       </c>
       <c r="C283" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D283" s="5" t="inlineStr">
@@ -18305,12 +18293,12 @@
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H283" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I283" s="5" t="b">
@@ -18324,20 +18312,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L283" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M283" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L283" s="5" t="n"/>
+      <c r="M283" s="5" t="n"/>
       <c r="N283" s="5" t="n">
-        <v>3.92</v>
+        <v>14.34</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B284" s="5" t="n">
@@ -18345,7 +18329,7 @@
       </c>
       <c r="C284" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D284" s="5" t="inlineStr">
@@ -18365,12 +18349,12 @@
       </c>
       <c r="G284" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H284" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I284" s="5" t="b">
@@ -18391,13 +18375,13 @@
         <v>1</v>
       </c>
       <c r="N284" s="5" t="n">
-        <v>6.58</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B285" s="5" t="n">
@@ -18405,7 +18389,7 @@
       </c>
       <c r="C285" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D285" s="5" t="inlineStr">
@@ -18425,12 +18409,12 @@
       </c>
       <c r="G285" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H285" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I285" s="5" t="b">
@@ -18445,19 +18429,19 @@
         </is>
       </c>
       <c r="L285" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M285" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N285" s="5" t="n">
-        <v>7.61</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B286" s="5" t="n">
@@ -18465,7 +18449,7 @@
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D286" s="5" t="inlineStr">
@@ -18485,12 +18469,12 @@
       </c>
       <c r="G286" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H286" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I286" s="5" t="b">
@@ -18505,19 +18489,19 @@
         </is>
       </c>
       <c r="L286" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M286" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N286" s="5" t="n">
-        <v>4.12</v>
+        <v>12.83</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B287" s="5" t="n">
@@ -18525,7 +18509,7 @@
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D287" s="5" t="inlineStr">
@@ -18545,12 +18529,12 @@
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H287" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I287" s="5" t="b">
@@ -18564,20 +18548,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L287" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M287" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L287" s="5" t="n"/>
+      <c r="M287" s="5" t="n"/>
       <c r="N287" s="5" t="n">
-        <v>7.1</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B288" s="5" t="n">
@@ -18585,7 +18565,7 @@
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D288" s="5" t="inlineStr">
@@ -18605,35 +18585,35 @@
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H288" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I288" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J288" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K288" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L288" s="5" t="n"/>
       <c r="M288" s="5" t="n"/>
       <c r="N288" s="5" t="n">
-        <v>7.05</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B289" s="5" t="n">
@@ -18641,7 +18621,7 @@
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D289" s="5" t="inlineStr">
@@ -18661,12 +18641,12 @@
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H289" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I289" s="5" t="b">
@@ -18680,20 +18660,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L289" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M289" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L289" s="5" t="n"/>
+      <c r="M289" s="5" t="n"/>
       <c r="N289" s="5" t="n">
-        <v>3.92</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B290" s="5" t="n">
@@ -18701,7 +18677,7 @@
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D290" s="5" t="inlineStr">
@@ -18721,12 +18697,12 @@
       </c>
       <c r="G290" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H290" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I290" s="5" t="b">
@@ -18740,20 +18716,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L290" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M290" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L290" s="5" t="n"/>
+      <c r="M290" s="5" t="n"/>
       <c r="N290" s="5" t="n">
-        <v>8.23</v>
+        <v>13.03</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B291" s="5" t="n">
@@ -18761,7 +18733,7 @@
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
@@ -18781,12 +18753,12 @@
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H291" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I291" s="5" t="b">
@@ -18800,20 +18772,16 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L291" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M291" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L291" s="5" t="n"/>
+      <c r="M291" s="5" t="n"/>
       <c r="N291" s="5" t="n">
-        <v>8.1</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B292" s="5" t="n">
@@ -18821,7 +18789,7 @@
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
@@ -18841,12 +18809,12 @@
       </c>
       <c r="G292" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H292" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I292" s="5" t="b">
@@ -18860,33 +18828,29 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L292" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M292" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="L292" s="5" t="n"/>
+      <c r="M292" s="5" t="n"/>
       <c r="N292" s="5" t="n">
-        <v>4.61</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B293" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C293" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E293" s="5" t="inlineStr">
@@ -18901,7 +18865,7 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
@@ -18927,41 +18891,41 @@
         <v>1</v>
       </c>
       <c r="N293" s="5" t="n">
-        <v>16.49</v>
+        <v>35.31</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B294" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C294" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E294" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F294" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H294" s="5" t="inlineStr">
@@ -18987,41 +18951,41 @@
         <v>1</v>
       </c>
       <c r="N294" s="5" t="n">
-        <v>17.18</v>
+        <v>16.82</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B295" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C295" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E295" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F295" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
@@ -19047,31 +19011,31 @@
         <v>1</v>
       </c>
       <c r="N295" s="5" t="n">
-        <v>16.5</v>
+        <v>16.51</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B296" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C296" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E296" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F296" s="5" t="inlineStr">
@@ -19081,12 +19045,12 @@
       </c>
       <c r="G296" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H296" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I296" s="5" t="b">
@@ -19107,26 +19071,26 @@
         <v>1</v>
       </c>
       <c r="N296" s="5" t="n">
-        <v>26.92</v>
+        <v>20.41</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B297" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C297" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E297" s="5" t="inlineStr">
@@ -19136,17 +19100,17 @@
       </c>
       <c r="F297" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I297" s="5" t="b">
@@ -19167,46 +19131,46 @@
         <v>1</v>
       </c>
       <c r="N297" s="5" t="n">
-        <v>19.44</v>
+        <v>18.71</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B298" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C298" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D298" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E298" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F298" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G298" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H298" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I298" s="5" t="b">
@@ -19227,31 +19191,31 @@
         <v>1</v>
       </c>
       <c r="N298" s="5" t="n">
-        <v>19.47</v>
+        <v>18.72</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B299" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C299" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D299" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E299" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F299" s="5" t="inlineStr">
@@ -19261,7 +19225,7 @@
       </c>
       <c r="G299" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H299" s="5" t="inlineStr">
@@ -19273,55 +19237,55 @@
         <v>1</v>
       </c>
       <c r="J299" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K299" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L299" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M299" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N299" s="5" t="n">
-        <v>21.28</v>
+        <v>18.04</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B300" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C300" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D300" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E300" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F300" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G300" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H300" s="5" t="inlineStr">
@@ -19333,40 +19297,40 @@
         <v>1</v>
       </c>
       <c r="J300" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K300" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L300" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M300" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N300" s="5" t="n">
-        <v>22.32</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B301" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D301" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E301" s="5" t="inlineStr">
@@ -19376,12 +19340,12 @@
       </c>
       <c r="F301" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -19393,40 +19357,40 @@
         <v>1</v>
       </c>
       <c r="J301" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K301" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L301" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M301" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N301" s="5" t="n">
-        <v>21.36</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>cross_kg_005</t>
         </is>
       </c>
       <c r="B302" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C302" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D302" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E302" s="5" t="inlineStr">
@@ -19441,12 +19405,12 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I302" s="5" t="b">
@@ -19467,26 +19431,26 @@
         <v>1</v>
       </c>
       <c r="N302" s="5" t="n">
-        <v>16.55</v>
+        <v>22.65</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>cross_kg_005</t>
         </is>
       </c>
       <c r="B303" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C303" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E303" s="5" t="inlineStr">
@@ -19501,12 +19465,12 @@
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H303" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I303" s="5" t="b">
@@ -19527,26 +19491,26 @@
         <v>1</v>
       </c>
       <c r="N303" s="5" t="n">
-        <v>20.76</v>
+        <v>23.76</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>cross_kg_005</t>
         </is>
       </c>
       <c r="B304" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C304" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D304" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E304" s="5" t="inlineStr">
@@ -19561,12 +19525,12 @@
       </c>
       <c r="G304" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H304" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I304" s="5" t="b">
@@ -19587,26 +19551,26 @@
         <v>1</v>
       </c>
       <c r="N304" s="5" t="n">
-        <v>16.66</v>
+        <v>22.97</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>cross_kg_009</t>
         </is>
       </c>
       <c r="B305" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C305" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D305" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E305" s="5" t="inlineStr">
@@ -19621,12 +19585,12 @@
       </c>
       <c r="G305" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H305" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I305" s="5" t="b">
@@ -19647,26 +19611,26 @@
         <v>1</v>
       </c>
       <c r="N305" s="5" t="n">
-        <v>16.33</v>
+        <v>19.47</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>cross_kg_009</t>
         </is>
       </c>
       <c r="B306" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C306" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D306" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E306" s="5" t="inlineStr">
@@ -19681,12 +19645,12 @@
       </c>
       <c r="G306" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H306" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I306" s="5" t="b">
@@ -19707,26 +19671,26 @@
         <v>1</v>
       </c>
       <c r="N306" s="5" t="n">
-        <v>18.7</v>
+        <v>26.07</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>cross_kg_009</t>
         </is>
       </c>
       <c r="B307" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C307" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D307" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E307" s="5" t="inlineStr">
@@ -19741,12 +19705,12 @@
       </c>
       <c r="G307" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H307" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I307" s="5" t="b">
@@ -19761,32 +19725,32 @@
         </is>
       </c>
       <c r="L307" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M307" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N307" s="5" t="n">
-        <v>9.35</v>
+        <v>23.25</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>count_kg1_001</t>
         </is>
       </c>
       <c r="B308" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C308" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D308" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E308" s="5" t="inlineStr">
@@ -19801,52 +19765,52 @@
       </c>
       <c r="G308" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H308" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I308" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J308" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K308" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>sparql_build_failure</t>
         </is>
       </c>
       <c r="L308" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M308" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N308" s="5" t="n">
-        <v>7.16</v>
+        <v>12.69</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>count_kg1_001</t>
         </is>
       </c>
       <c r="B309" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C309" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D309" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E309" s="5" t="inlineStr">
@@ -19861,23 +19825,23 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I309" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J309" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K309" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>sparql_build_failure</t>
         </is>
       </c>
       <c r="L309" s="5" t="b">
@@ -19887,26 +19851,26 @@
         <v>0</v>
       </c>
       <c r="N309" s="5" t="n">
-        <v>7.43</v>
+        <v>9.210000000000001</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>count_kg1_001</t>
         </is>
       </c>
       <c r="B310" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C310" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D310" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E310" s="5" t="inlineStr">
@@ -19921,12 +19885,12 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I310" s="5" t="b">
@@ -19941,32 +19905,32 @@
         </is>
       </c>
       <c r="L310" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M310" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N310" s="5" t="n">
-        <v>4.21</v>
+        <v>8.98</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B311" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C311" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D311" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E311" s="5" t="inlineStr">
@@ -19981,12 +19945,12 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I311" s="5" t="b">
@@ -20007,26 +19971,26 @@
         <v>1</v>
       </c>
       <c r="N311" s="5" t="n">
-        <v>17.3</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B312" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C312" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D312" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E312" s="5" t="inlineStr">
@@ -20041,12 +20005,12 @@
       </c>
       <c r="G312" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H312" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I312" s="5" t="b">
@@ -20067,26 +20031,26 @@
         <v>1</v>
       </c>
       <c r="N312" s="5" t="n">
-        <v>18.6</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B313" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C313" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E313" s="5" t="inlineStr">
@@ -20101,12 +20065,12 @@
       </c>
       <c r="G313" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H313" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I313" s="5" t="b">
@@ -20127,26 +20091,26 @@
         <v>1</v>
       </c>
       <c r="N313" s="5" t="n">
-        <v>16.8</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B314" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C314" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D314" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E314" s="5" t="inlineStr">
@@ -20161,12 +20125,12 @@
       </c>
       <c r="G314" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H314" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I314" s="5" t="b">
@@ -20180,29 +20144,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L314" s="5" t="n"/>
-      <c r="M314" s="5" t="n"/>
+      <c r="L314" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M314" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N314" s="5" t="n">
-        <v>10.68</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B315" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C315" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D315" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E315" s="5" t="inlineStr">
@@ -20217,12 +20185,12 @@
       </c>
       <c r="G315" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H315" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I315" s="5" t="b">
@@ -20236,29 +20204,33 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L315" s="5" t="n"/>
-      <c r="M315" s="5" t="n"/>
+      <c r="L315" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M315" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N315" s="5" t="n">
-        <v>12.47</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B316" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C316" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D316" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E316" s="5" t="inlineStr">
@@ -20273,12 +20245,12 @@
       </c>
       <c r="G316" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H316" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I316" s="5" t="b">
@@ -20292,16 +20264,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L316" s="5" t="n"/>
-      <c r="M316" s="5" t="n"/>
+      <c r="L316" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M316" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N316" s="5" t="n">
-        <v>14.34</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B317" s="5" t="n">
@@ -20309,7 +20285,7 @@
       </c>
       <c r="C317" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D317" s="5" t="inlineStr">
@@ -20329,12 +20305,12 @@
       </c>
       <c r="G317" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H317" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I317" s="5" t="b">
@@ -20355,13 +20331,13 @@
         <v>1</v>
       </c>
       <c r="N317" s="5" t="n">
-        <v>12.05</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B318" s="5" t="n">
@@ -20369,7 +20345,7 @@
       </c>
       <c r="C318" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D318" s="5" t="inlineStr">
@@ -20389,12 +20365,12 @@
       </c>
       <c r="G318" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H318" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I318" s="5" t="b">
@@ -20415,13 +20391,13 @@
         <v>1</v>
       </c>
       <c r="N318" s="5" t="n">
-        <v>12.24</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B319" s="5" t="n">
@@ -20429,7 +20405,7 @@
       </c>
       <c r="C319" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D319" s="5" t="inlineStr">
@@ -20449,12 +20425,12 @@
       </c>
       <c r="G319" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H319" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I319" s="5" t="b">
@@ -20475,13 +20451,13 @@
         <v>1</v>
       </c>
       <c r="N319" s="5" t="n">
-        <v>12.83</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B320" s="5" t="n">
@@ -20489,7 +20465,7 @@
       </c>
       <c r="C320" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D320" s="5" t="inlineStr">
@@ -20514,7 +20490,7 @@
       </c>
       <c r="H320" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I320" s="5" t="b">
@@ -20528,16 +20504,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L320" s="5" t="n"/>
-      <c r="M320" s="5" t="n"/>
+      <c r="L320" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M320" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N320" s="5" t="n">
-        <v>11.92</v>
+        <v>18.94</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B321" s="5" t="n">
@@ -20545,7 +20525,7 @@
       </c>
       <c r="C321" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D321" s="5" t="inlineStr">
@@ -20570,7 +20550,7 @@
       </c>
       <c r="H321" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I321" s="5" t="b">
@@ -20581,19 +20561,23 @@
       </c>
       <c r="K321" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L321" s="5" t="n"/>
-      <c r="M321" s="5" t="n"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L321" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M321" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N321" s="5" t="n">
-        <v>12.6</v>
+        <v>21.38</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B322" s="5" t="n">
@@ -20601,7 +20585,7 @@
       </c>
       <c r="C322" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D322" s="5" t="inlineStr">
@@ -20626,7 +20610,7 @@
       </c>
       <c r="H322" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I322" s="5" t="b">
@@ -20640,16 +20624,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L322" s="5" t="n"/>
-      <c r="M322" s="5" t="n"/>
+      <c r="L322" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M322" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N322" s="5" t="n">
-        <v>13.69</v>
+        <v>14.78</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B323" s="5" t="n">
@@ -20657,7 +20645,7 @@
       </c>
       <c r="C323" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D323" s="5" t="inlineStr">
@@ -20682,7 +20670,7 @@
       </c>
       <c r="H323" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I323" s="5" t="b">
@@ -20696,16 +20684,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L323" s="5" t="n"/>
-      <c r="M323" s="5" t="n"/>
+      <c r="L323" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M323" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N323" s="5" t="n">
-        <v>13.03</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B324" s="5" t="n">
@@ -20713,7 +20705,7 @@
       </c>
       <c r="C324" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D324" s="5" t="inlineStr">
@@ -20738,7 +20730,7 @@
       </c>
       <c r="H324" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I324" s="5" t="b">
@@ -20752,16 +20744,20 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L324" s="5" t="n"/>
-      <c r="M324" s="5" t="n"/>
+      <c r="L324" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M324" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N324" s="5" t="n">
-        <v>13.16</v>
+        <v>9.029999999999999</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B325" s="5" t="n">
@@ -20769,7 +20765,7 @@
       </c>
       <c r="C325" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D325" s="5" t="inlineStr">
@@ -20794,7 +20790,7 @@
       </c>
       <c r="H325" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I325" s="5" t="b">
@@ -20808,10 +20804,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L325" s="5" t="n"/>
-      <c r="M325" s="5" t="n"/>
+      <c r="L325" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M325" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N325" s="5" t="n">
-        <v>13.05</v>
+        <v>5.17</v>
       </c>
     </row>
   </sheetData>

--- a/NL2SPARQL_Evaluation_Results.xlsx
+++ b/NL2SPARQL_Evaluation_Results.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Raw" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw'!$A$1:$N$325</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw'!$A$1:$O$325</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -567,11 +567,11 @@
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!E2:E325,"en"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!E2:E325,"en"),"")</f>
         <v/>
       </c>
       <c r="G6" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!E2:E325,"en"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!E2:E325,"en"),"")</f>
         <v/>
       </c>
     </row>
@@ -598,11 +598,11 @@
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!E2:E325,"fr"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!E2:E325,"fr"),"")</f>
         <v/>
       </c>
       <c r="G7" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!E2:E325,"fr"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!E2:E325,"fr"),"")</f>
         <v/>
       </c>
     </row>
@@ -629,11 +629,11 @@
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!E2:E325,"ar"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!E2:E325,"ar"),"")</f>
         <v/>
       </c>
       <c r="G8" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!E2:E325,"ar"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!E2:E325,"ar"),"")</f>
         <v/>
       </c>
     </row>
@@ -704,11 +704,11 @@
         <v/>
       </c>
       <c r="F12" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!F2:F325,"zero-shot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!F2:F325,"zero-shot"),"")</f>
         <v/>
       </c>
       <c r="G12" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!F2:F325,"zero-shot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!F2:F325,"zero-shot"),"")</f>
         <v/>
       </c>
     </row>
@@ -735,11 +735,11 @@
         <v/>
       </c>
       <c r="F13" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!F2:F325,"few-shot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!F2:F325,"few-shot"),"")</f>
         <v/>
       </c>
       <c r="G13" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!F2:F325,"few-shot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!F2:F325,"few-shot"),"")</f>
         <v/>
       </c>
     </row>
@@ -766,11 +766,11 @@
         <v/>
       </c>
       <c r="F14" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!F2:F325,"cot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!F2:F325,"cot"),"")</f>
         <v/>
       </c>
       <c r="G14" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!F2:F325,"cot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!F2:F325,"cot"),"")</f>
         <v/>
       </c>
     </row>
@@ -839,11 +839,11 @@
         <v/>
       </c>
       <c r="F18" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!B2:B325,"1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!B2:B325,"1"),"")</f>
         <v/>
       </c>
       <c r="G18" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!B2:B325,"1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!B2:B325,"1"),"")</f>
         <v/>
       </c>
     </row>
@@ -868,11 +868,11 @@
         <v/>
       </c>
       <c r="F19" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!B2:B325,"2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!B2:B325,"2"),"")</f>
         <v/>
       </c>
       <c r="G19" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!B2:B325,"2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!B2:B325,"2"),"")</f>
         <v/>
       </c>
     </row>
@@ -897,11 +897,11 @@
         <v/>
       </c>
       <c r="F20" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!B2:B325,"3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!B2:B325,"3"),"")</f>
         <v/>
       </c>
       <c r="G20" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!B2:B325,"3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!B2:B325,"3"),"")</f>
         <v/>
       </c>
     </row>
@@ -972,11 +972,11 @@
         <v/>
       </c>
       <c r="F24" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"single_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"single_kg1"),"")</f>
         <v/>
       </c>
       <c r="G24" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"single_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!C2:C325,"single_kg1"),"")</f>
         <v/>
       </c>
     </row>
@@ -1003,11 +1003,11 @@
         <v/>
       </c>
       <c r="F25" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"single_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"single_kg2"),"")</f>
         <v/>
       </c>
       <c r="G25" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"single_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!C2:C325,"single_kg2"),"")</f>
         <v/>
       </c>
     </row>
@@ -1034,11 +1034,11 @@
         <v/>
       </c>
       <c r="F26" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"cross_kg"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"cross_kg"),"")</f>
         <v/>
       </c>
       <c r="G26" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"cross_kg"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!C2:C325,"cross_kg"),"")</f>
         <v/>
       </c>
     </row>
@@ -1065,11 +1065,11 @@
         <v/>
       </c>
       <c r="F27" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"open_kg"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"open_kg"),"")</f>
         <v/>
       </c>
       <c r="G27" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"open_kg"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!C2:C325,"open_kg"),"")</f>
         <v/>
       </c>
     </row>
@@ -1096,11 +1096,11 @@
         <v/>
       </c>
       <c r="F28" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"count_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"count_kg1"),"")</f>
         <v/>
       </c>
       <c r="G28" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"count_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!C2:C325,"count_kg1"),"")</f>
         <v/>
       </c>
     </row>
@@ -1127,11 +1127,11 @@
         <v/>
       </c>
       <c r="F29" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"filter_numeric_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"filter_numeric_kg1"),"")</f>
         <v/>
       </c>
       <c r="G29" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"filter_numeric_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!C2:C325,"filter_numeric_kg1"),"")</f>
         <v/>
       </c>
     </row>
@@ -1158,11 +1158,11 @@
         <v/>
       </c>
       <c r="F30" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"filter_numeric_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"filter_numeric_kg2"),"")</f>
         <v/>
       </c>
       <c r="G30" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"filter_numeric_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!C2:C325,"filter_numeric_kg2"),"")</f>
         <v/>
       </c>
     </row>
@@ -1189,11 +1189,11 @@
         <v/>
       </c>
       <c r="F31" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"filter_string_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"filter_string_kg2"),"")</f>
         <v/>
       </c>
       <c r="G31" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"filter_string_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!C2:C325,"filter_string_kg2"),"")</f>
         <v/>
       </c>
     </row>
@@ -1220,11 +1220,11 @@
         <v/>
       </c>
       <c r="F32" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"ranking_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"ranking_kg2"),"")</f>
         <v/>
       </c>
       <c r="G32" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"ranking_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!C2:C325,"ranking_kg2"),"")</f>
         <v/>
       </c>
     </row>
@@ -1251,11 +1251,11 @@
         <v/>
       </c>
       <c r="F33" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"compare_two_airports"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"compare_two_airports"),"")</f>
         <v/>
       </c>
       <c r="G33" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"compare_two_airports"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!C2:C325,"compare_two_airports"),"")</f>
         <v/>
       </c>
     </row>
@@ -1282,11 +1282,11 @@
         <v/>
       </c>
       <c r="F34" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"out_of_scope"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"out_of_scope"),"")</f>
         <v/>
       </c>
       <c r="G34" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"out_of_scope"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!C2:C325,"out_of_scope"),"")</f>
         <v/>
       </c>
     </row>
@@ -1313,11 +1313,11 @@
         <v/>
       </c>
       <c r="F35" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"ask_query"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"ask_query"),"")</f>
         <v/>
       </c>
       <c r="G35" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"ask_query"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!C2:C325,"ask_query"),"")</f>
         <v/>
       </c>
     </row>
@@ -1344,11 +1344,11 @@
         <v/>
       </c>
       <c r="F36" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"typo_fuzzy"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"typo_fuzzy"),"")</f>
         <v/>
       </c>
       <c r="G36" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"typo_fuzzy"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!C2:C325,"typo_fuzzy"),"")</f>
         <v/>
       </c>
     </row>
@@ -1375,11 +1375,11 @@
         <v/>
       </c>
       <c r="F37" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"multilingual_edge"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"multilingual_edge"),"")</f>
         <v/>
       </c>
       <c r="G37" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"multilingual_edge"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!C2:C325,"multilingual_edge"),"")</f>
         <v/>
       </c>
     </row>
@@ -1406,11 +1406,11 @@
         <v/>
       </c>
       <c r="F38" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!L2:L325,Raw!C2:C325,"property_ambiguity"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"property_ambiguity"),"")</f>
         <v/>
       </c>
       <c r="G38" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M325,Raw!C2:C325,"property_ambiguity"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N325,Raw!C2:C325,"property_ambiguity"),"")</f>
         <v/>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N325"/>
+  <dimension ref="A1:O325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1442,6 +1442,7 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1502,15 +1503,20 @@
       </c>
       <c r="L1" s="4" t="inlineStr">
         <is>
+          <t>error_detail</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
           <t>exact_match</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>duration_s</t>
         </is>
@@ -1566,13 +1572,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L2" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M2" s="5" t="n">
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" s="5" t="n">
         <v>32.85</v>
       </c>
     </row>
@@ -1626,13 +1633,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L3" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5" t="n">
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="5" t="n">
         <v>15.29</v>
       </c>
     </row>
@@ -1686,13 +1694,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L4" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5" t="n">
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="5" t="n">
         <v>15.8</v>
       </c>
     </row>
@@ -1746,13 +1755,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L5" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" s="5" t="n">
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="5" t="n">
         <v>17.31</v>
       </c>
     </row>
@@ -1806,13 +1816,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L6" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" s="5" t="n">
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="5" t="n">
         <v>16.14</v>
       </c>
     </row>
@@ -1866,13 +1877,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L7" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="5" t="n">
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="5" t="n">
         <v>16.68</v>
       </c>
     </row>
@@ -1926,13 +1938,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L8" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" s="5" t="n">
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="5" t="n">
         <v>18.29</v>
       </c>
     </row>
@@ -1986,13 +1999,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L9" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" s="5" t="n">
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="5" t="n">
         <v>17.92</v>
       </c>
     </row>
@@ -2046,13 +2060,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L10" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" s="5" t="n">
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="5" t="n">
         <v>17.11</v>
       </c>
     </row>
@@ -2106,13 +2121,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L11" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M11" s="5" t="n">
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="5" t="n">
         <v>16.09</v>
       </c>
     </row>
@@ -2166,13 +2182,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M12" s="5" t="n">
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="5" t="n">
         <v>14.01</v>
       </c>
     </row>
@@ -2226,13 +2243,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L13" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M13" s="5" t="n">
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="5" t="n">
         <v>14.68</v>
       </c>
     </row>
@@ -2286,13 +2304,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M14" s="5" t="n">
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" s="5" t="n">
         <v>15.88</v>
       </c>
     </row>
@@ -2346,13 +2365,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M15" s="5" t="n">
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="5" t="n">
         <v>14.79</v>
       </c>
     </row>
@@ -2406,13 +2426,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L16" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M16" s="5" t="n">
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="5" t="n">
         <v>15.53</v>
       </c>
     </row>
@@ -2466,13 +2487,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L17" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M17" s="5" t="n">
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="5" t="n">
         <v>16.08</v>
       </c>
     </row>
@@ -2526,13 +2548,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M18" s="5" t="n">
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="5" t="n">
         <v>14.9</v>
       </c>
     </row>
@@ -2586,13 +2609,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L19" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M19" s="5" t="n">
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="5" t="n">
         <v>15.53</v>
       </c>
     </row>
@@ -2646,13 +2670,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L20" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M20" s="5" t="n">
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" s="5" t="n">
         <v>17.59</v>
       </c>
     </row>
@@ -2706,13 +2731,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L21" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M21" s="5" t="n">
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="5" t="n">
         <v>15.12</v>
       </c>
     </row>
@@ -2766,13 +2792,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L22" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M22" s="5" t="n">
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="5" t="n">
         <v>15.83</v>
       </c>
     </row>
@@ -2826,13 +2853,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L23" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M23" s="5" t="n">
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="5" t="n">
         <v>16.99</v>
       </c>
     </row>
@@ -2886,13 +2914,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L24" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M24" s="5" t="n">
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" s="5" t="n">
         <v>16.88</v>
       </c>
     </row>
@@ -2946,13 +2975,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L25" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M25" s="5" t="n">
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="5" t="n">
         <v>17.28</v>
       </c>
     </row>
@@ -3006,13 +3036,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L26" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M26" s="5" t="n">
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" s="5" t="n">
         <v>18.7</v>
       </c>
     </row>
@@ -3066,13 +3097,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L27" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M27" s="5" t="n">
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="5" t="n">
         <v>17.91</v>
       </c>
     </row>
@@ -3126,13 +3158,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M28" s="5" t="n">
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" s="5" t="n">
         <v>18.02</v>
       </c>
     </row>
@@ -3186,13 +3219,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L29" s="5" t="b">
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="M29" s="5" t="n">
+      <c r="N29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N29" s="5" t="n">
+      <c r="O29" s="5" t="n">
         <v>20.93</v>
       </c>
     </row>
@@ -3246,13 +3280,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L30" s="5" t="b">
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="M30" s="5" t="n">
+      <c r="N30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N30" s="5" t="n">
+      <c r="O30" s="5" t="n">
         <v>19.64</v>
       </c>
     </row>
@@ -3306,13 +3341,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L31" s="5" t="b">
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="M31" s="5" t="n">
+      <c r="N31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N31" s="5" t="n">
+      <c r="O31" s="5" t="n">
         <v>20.12</v>
       </c>
     </row>
@@ -3366,13 +3402,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L32" s="5" t="b">
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="M32" s="5" t="n">
+      <c r="N32" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N32" s="5" t="n">
+      <c r="O32" s="5" t="n">
         <v>21.36</v>
       </c>
     </row>
@@ -3426,13 +3463,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L33" s="5" t="b">
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="M33" s="5" t="n">
+      <c r="N33" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N33" s="5" t="n">
+      <c r="O33" s="5" t="n">
         <v>20.18</v>
       </c>
     </row>
@@ -3486,13 +3524,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L34" s="5" t="b">
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="M34" s="5" t="n">
+      <c r="N34" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N34" s="5" t="n">
+      <c r="O34" s="5" t="n">
         <v>20.81</v>
       </c>
     </row>
@@ -3546,13 +3585,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L35" s="5" t="b">
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="M35" s="5" t="n">
+      <c r="N35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N35" s="5" t="n">
+      <c r="O35" s="5" t="n">
         <v>21.74</v>
       </c>
     </row>
@@ -3606,13 +3646,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L36" s="5" t="b">
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="M36" s="5" t="n">
+      <c r="N36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N36" s="5" t="n">
+      <c r="O36" s="5" t="n">
         <v>20.67</v>
       </c>
     </row>
@@ -3666,13 +3707,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L37" s="5" t="b">
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="M37" s="5" t="n">
+      <c r="N37" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N37" s="5" t="n">
+      <c r="O37" s="5" t="n">
         <v>21.06</v>
       </c>
     </row>
@@ -3726,13 +3768,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L38" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M38" s="5" t="n">
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" s="5" t="n">
         <v>21.32</v>
       </c>
     </row>
@@ -3786,13 +3829,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L39" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M39" s="5" t="n">
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" s="5" t="n">
         <v>19.7</v>
       </c>
     </row>
@@ -3846,13 +3890,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M40" s="5" t="n">
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" s="5" t="n">
         <v>20.35</v>
       </c>
     </row>
@@ -3906,13 +3951,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L41" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M41" s="5" t="n">
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" s="5" t="n">
         <v>22.87</v>
       </c>
     </row>
@@ -3966,13 +4012,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L42" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M42" s="5" t="n">
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" s="5" t="n">
         <v>22.03</v>
       </c>
     </row>
@@ -4026,13 +4073,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L43" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M43" s="5" t="n">
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" s="5" t="n">
         <v>22.45</v>
       </c>
     </row>
@@ -4086,13 +4134,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M44" s="5" t="n">
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N44" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" s="5" t="n">
         <v>23.19</v>
       </c>
     </row>
@@ -4146,13 +4195,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M45" s="5" t="n">
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" s="5" t="n">
         <v>22.2</v>
       </c>
     </row>
@@ -4206,13 +4256,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L46" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M46" s="5" t="n">
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" s="5" t="n">
         <v>22.61</v>
       </c>
     </row>
@@ -4266,13 +4317,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L47" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M47" s="5" t="n">
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" s="5" t="n">
         <v>16.03</v>
       </c>
     </row>
@@ -4326,13 +4378,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L48" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M48" s="5" t="n">
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N48" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" s="5" t="n">
         <v>13.82</v>
       </c>
     </row>
@@ -4386,13 +4439,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L49" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M49" s="5" t="n">
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" s="5" t="n">
         <v>14.83</v>
       </c>
     </row>
@@ -4446,13 +4500,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L50" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M50" s="5" t="n">
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N50" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" s="5" t="n">
         <v>18.1</v>
       </c>
     </row>
@@ -4506,13 +4561,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L51" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M51" s="5" t="n">
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" s="5" t="n">
         <v>17.52</v>
       </c>
     </row>
@@ -4566,13 +4622,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L52" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M52" s="5" t="n">
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" s="5" t="n">
         <v>17.62</v>
       </c>
     </row>
@@ -4626,13 +4683,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L53" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M53" s="5" t="n">
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" s="5" t="n">
         <v>18.92</v>
       </c>
     </row>
@@ -4686,13 +4744,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L54" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M54" s="5" t="n">
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" s="5" t="n">
         <v>17.34</v>
       </c>
     </row>
@@ -4746,13 +4805,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L55" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M55" s="5" t="n">
+      <c r="L55" s="5" t="n"/>
+      <c r="M55" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" s="5" t="n">
         <v>17.07</v>
       </c>
     </row>
@@ -4806,13 +4866,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L56" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M56" s="5" t="n">
+      <c r="L56" s="5" t="n"/>
+      <c r="M56" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N56" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" s="5" t="n">
         <v>16.26</v>
       </c>
     </row>
@@ -4866,13 +4927,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L57" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M57" s="5" t="n">
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" s="5" t="n">
         <v>14.41</v>
       </c>
     </row>
@@ -4926,13 +4988,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L58" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M58" s="5" t="n">
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" s="5" t="n">
         <v>15.21</v>
       </c>
     </row>
@@ -4986,13 +5049,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L59" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M59" s="5" t="n">
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" s="5" t="n">
         <v>17.07</v>
       </c>
     </row>
@@ -5046,13 +5110,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L60" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M60" s="5" t="n">
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" s="5" t="n">
         <v>15.88</v>
       </c>
     </row>
@@ -5106,13 +5171,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L61" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M61" s="5" t="n">
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N61" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" s="5" t="n">
         <v>16.5</v>
       </c>
     </row>
@@ -5166,13 +5232,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L62" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M62" s="5" t="n">
+      <c r="L62" s="5" t="n"/>
+      <c r="M62" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" s="5" t="n">
         <v>17.3</v>
       </c>
     </row>
@@ -5226,13 +5293,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L63" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M63" s="5" t="n">
+      <c r="L63" s="5" t="n"/>
+      <c r="M63" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" s="5" t="n">
         <v>16.58</v>
       </c>
     </row>
@@ -5286,13 +5354,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L64" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M64" s="5" t="n">
+      <c r="L64" s="5" t="n"/>
+      <c r="M64" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N64" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O64" s="5" t="n">
         <v>17.23</v>
       </c>
     </row>
@@ -5346,13 +5415,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L65" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M65" s="5" t="n">
+      <c r="L65" s="5" t="n"/>
+      <c r="M65" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O65" s="5" t="n">
         <v>16.54</v>
       </c>
     </row>
@@ -5406,13 +5476,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L66" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M66" s="5" t="n">
+      <c r="L66" s="5" t="n"/>
+      <c r="M66" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N66" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O66" s="5" t="n">
         <v>14.23</v>
       </c>
     </row>
@@ -5466,13 +5537,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L67" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M67" s="5" t="n">
+      <c r="L67" s="5" t="n"/>
+      <c r="M67" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N67" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O67" s="5" t="n">
         <v>15.06</v>
       </c>
     </row>
@@ -5526,13 +5598,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L68" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M68" s="5" t="n">
+      <c r="L68" s="5" t="n"/>
+      <c r="M68" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N68" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O68" s="5" t="n">
         <v>16.85</v>
       </c>
     </row>
@@ -5586,13 +5659,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L69" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M69" s="5" t="n">
+      <c r="L69" s="5" t="n"/>
+      <c r="M69" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N69" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O69" s="5" t="n">
         <v>15.87</v>
       </c>
     </row>
@@ -5646,13 +5720,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L70" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M70" s="5" t="n">
+      <c r="L70" s="5" t="n"/>
+      <c r="M70" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N70" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O70" s="5" t="n">
         <v>16.41</v>
       </c>
     </row>
@@ -5706,13 +5781,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L71" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M71" s="5" t="n">
+      <c r="L71" s="5" t="n"/>
+      <c r="M71" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N71" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" s="5" t="n">
         <v>17.07</v>
       </c>
     </row>
@@ -5766,13 +5842,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L72" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M72" s="5" t="n">
+      <c r="L72" s="5" t="n"/>
+      <c r="M72" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N72" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O72" s="5" t="n">
         <v>16.11</v>
       </c>
     </row>
@@ -5826,13 +5903,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L73" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M73" s="5" t="n">
+      <c r="L73" s="5" t="n"/>
+      <c r="M73" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N73" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O73" s="5" t="n">
         <v>16.98</v>
       </c>
     </row>
@@ -5886,13 +5964,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L74" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M74" s="5" t="n">
+      <c r="L74" s="5" t="n"/>
+      <c r="M74" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O74" s="5" t="n">
         <v>16.23</v>
       </c>
     </row>
@@ -5946,13 +6025,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L75" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M75" s="5" t="n">
+      <c r="L75" s="5" t="n"/>
+      <c r="M75" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N75" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" s="5" t="n">
         <v>13.99</v>
       </c>
     </row>
@@ -6006,13 +6086,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L76" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M76" s="5" t="n">
+      <c r="L76" s="5" t="n"/>
+      <c r="M76" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N76" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" s="5" t="n">
         <v>14.87</v>
       </c>
     </row>
@@ -6066,13 +6147,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L77" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M77" s="5" t="n">
+      <c r="L77" s="5" t="n"/>
+      <c r="M77" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O77" s="5" t="n">
         <v>16.6</v>
       </c>
     </row>
@@ -6126,13 +6208,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L78" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M78" s="5" t="n">
+      <c r="L78" s="5" t="n"/>
+      <c r="M78" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N78" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O78" s="5" t="n">
         <v>15.04</v>
       </c>
     </row>
@@ -6186,13 +6269,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L79" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M79" s="5" t="n">
+      <c r="L79" s="5" t="n"/>
+      <c r="M79" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N79" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" s="5" t="n">
         <v>15.25</v>
       </c>
     </row>
@@ -6246,13 +6330,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L80" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M80" s="5" t="n">
+      <c r="L80" s="5" t="n"/>
+      <c r="M80" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N80" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" s="5" t="n">
         <v>16.18</v>
       </c>
     </row>
@@ -6306,13 +6391,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L81" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M81" s="5" t="n">
+      <c r="L81" s="5" t="n"/>
+      <c r="M81" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N81" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" s="5" t="n">
         <v>15.32</v>
       </c>
     </row>
@@ -6366,13 +6452,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L82" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M82" s="5" t="n">
+      <c r="L82" s="5" t="n"/>
+      <c r="M82" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N82" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" s="5" t="n">
         <v>15.81</v>
       </c>
     </row>
@@ -6426,13 +6513,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L83" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M83" s="5" t="n">
+      <c r="L83" s="5" t="n"/>
+      <c r="M83" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N83" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O83" s="5" t="n">
         <v>16.96</v>
       </c>
     </row>
@@ -6486,13 +6574,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L84" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M84" s="5" t="n">
+      <c r="L84" s="5" t="n"/>
+      <c r="M84" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N84" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O84" s="5" t="n">
         <v>16.31</v>
       </c>
     </row>
@@ -6546,13 +6635,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L85" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M85" s="5" t="n">
+      <c r="L85" s="5" t="n"/>
+      <c r="M85" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N85" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O85" s="5" t="n">
         <v>16.63</v>
       </c>
     </row>
@@ -6606,13 +6696,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L86" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M86" s="5" t="n">
+      <c r="L86" s="5" t="n"/>
+      <c r="M86" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N86" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O86" s="5" t="n">
         <v>19.67</v>
       </c>
     </row>
@@ -6666,13 +6757,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L87" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M87" s="5" t="n">
+      <c r="L87" s="5" t="n"/>
+      <c r="M87" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N87" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" s="5" t="n">
         <v>17.21</v>
       </c>
     </row>
@@ -6726,13 +6818,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L88" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M88" s="5" t="n">
+      <c r="L88" s="5" t="n"/>
+      <c r="M88" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N88" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" s="5" t="n">
         <v>17.77</v>
       </c>
     </row>
@@ -6786,13 +6879,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L89" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M89" s="5" t="n">
+      <c r="L89" s="5" t="n"/>
+      <c r="M89" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N89" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O89" s="5" t="n">
         <v>19.12</v>
       </c>
     </row>
@@ -6846,13 +6940,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L90" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M90" s="5" t="n">
+      <c r="L90" s="5" t="n"/>
+      <c r="M90" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N90" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O90" s="5" t="n">
         <v>16.66</v>
       </c>
     </row>
@@ -6906,13 +7001,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L91" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M91" s="5" t="n">
+      <c r="L91" s="5" t="n"/>
+      <c r="M91" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N91" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O91" s="5" t="n">
         <v>17.08</v>
       </c>
     </row>
@@ -6966,13 +7062,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L92" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M92" s="5" t="n">
+      <c r="L92" s="5" t="n"/>
+      <c r="M92" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N92" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O92" s="5" t="n">
         <v>18.47</v>
       </c>
     </row>
@@ -7026,13 +7123,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L93" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M93" s="5" t="n">
+      <c r="L93" s="5" t="n"/>
+      <c r="M93" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N93" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O93" s="5" t="n">
         <v>16.44</v>
       </c>
     </row>
@@ -7086,13 +7184,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L94" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M94" s="5" t="n">
+      <c r="L94" s="5" t="n"/>
+      <c r="M94" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N94" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O94" s="5" t="n">
         <v>16.95</v>
       </c>
     </row>
@@ -7146,13 +7245,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L95" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M95" s="5" t="n">
+      <c r="L95" s="5" t="n"/>
+      <c r="M95" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N95" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O95" s="5" t="n">
         <v>19.68</v>
       </c>
     </row>
@@ -7206,13 +7306,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L96" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M96" s="5" t="n">
+      <c r="L96" s="5" t="n"/>
+      <c r="M96" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N96" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O96" s="5" t="n">
         <v>17.3</v>
       </c>
     </row>
@@ -7266,13 +7367,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L97" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M97" s="5" t="n">
+      <c r="L97" s="5" t="n"/>
+      <c r="M97" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N97" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O97" s="5" t="n">
         <v>17.83</v>
       </c>
     </row>
@@ -7326,13 +7428,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L98" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M98" s="5" t="n">
+      <c r="L98" s="5" t="n"/>
+      <c r="M98" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N98" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O98" s="5" t="n">
         <v>18.68</v>
       </c>
     </row>
@@ -7386,13 +7489,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L99" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M99" s="5" t="n">
+      <c r="L99" s="5" t="n"/>
+      <c r="M99" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N99" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O99" s="5" t="n">
         <v>17.13</v>
       </c>
     </row>
@@ -7446,13 +7550,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L100" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M100" s="5" t="n">
+      <c r="L100" s="5" t="n"/>
+      <c r="M100" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N100" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O100" s="5" t="n">
         <v>18.28</v>
       </c>
     </row>
@@ -7506,13 +7611,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L101" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M101" s="5" t="n">
+      <c r="L101" s="5" t="n"/>
+      <c r="M101" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N101" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O101" s="5" t="n">
         <v>22.01</v>
       </c>
     </row>
@@ -7566,13 +7672,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L102" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M102" s="5" t="n">
+      <c r="L102" s="5" t="n"/>
+      <c r="M102" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N102" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O102" s="5" t="n">
         <v>20.32</v>
       </c>
     </row>
@@ -7626,13 +7733,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L103" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M103" s="5" t="n">
+      <c r="L103" s="5" t="n"/>
+      <c r="M103" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N103" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O103" s="5" t="n">
         <v>20.81</v>
       </c>
     </row>
@@ -7686,13 +7794,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L104" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M104" s="5" t="n">
+      <c r="L104" s="5" t="n"/>
+      <c r="M104" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N104" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O104" s="5" t="n">
         <v>23.28</v>
       </c>
     </row>
@@ -7746,13 +7855,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L105" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M105" s="5" t="n">
+      <c r="L105" s="5" t="n"/>
+      <c r="M105" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N105" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O105" s="5" t="n">
         <v>21.54</v>
       </c>
     </row>
@@ -7806,13 +7916,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L106" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M106" s="5" t="n">
+      <c r="L106" s="5" t="n"/>
+      <c r="M106" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N106" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O106" s="5" t="n">
         <v>22.35</v>
       </c>
     </row>
@@ -7866,13 +7977,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L107" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M107" s="5" t="n">
+      <c r="L107" s="5" t="n"/>
+      <c r="M107" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N107" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O107" s="5" t="n">
         <v>24.45</v>
       </c>
     </row>
@@ -7926,13 +8038,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L108" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M108" s="5" t="n">
+      <c r="L108" s="5" t="n"/>
+      <c r="M108" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N108" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O108" s="5" t="n">
         <v>22</v>
       </c>
     </row>
@@ -7986,13 +8099,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L109" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M109" s="5" t="n">
+      <c r="L109" s="5" t="n"/>
+      <c r="M109" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N109" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O109" s="5" t="n">
         <v>24.36</v>
       </c>
     </row>
@@ -8046,13 +8160,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L110" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M110" s="5" t="n">
+      <c r="L110" s="5" t="n"/>
+      <c r="M110" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N110" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O110" s="5" t="n">
         <v>23.6</v>
       </c>
     </row>
@@ -8106,13 +8221,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L111" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M111" s="5" t="n">
+      <c r="L111" s="5" t="n"/>
+      <c r="M111" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N111" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O111" s="5" t="n">
         <v>22.03</v>
       </c>
     </row>
@@ -8166,13 +8282,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L112" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M112" s="5" t="n">
+      <c r="L112" s="5" t="n"/>
+      <c r="M112" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N112" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O112" s="5" t="n">
         <v>21.87</v>
       </c>
     </row>
@@ -8226,13 +8343,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L113" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M113" s="5" t="n">
+      <c r="L113" s="5" t="n"/>
+      <c r="M113" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N113" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O113" s="5" t="n">
         <v>25.94</v>
       </c>
     </row>
@@ -8286,13 +8404,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L114" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M114" s="5" t="n">
+      <c r="L114" s="5" t="n"/>
+      <c r="M114" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N114" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O114" s="5" t="n">
         <v>23.03</v>
       </c>
     </row>
@@ -8346,13 +8465,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L115" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M115" s="5" t="n">
+      <c r="L115" s="5" t="n"/>
+      <c r="M115" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N115" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O115" s="5" t="n">
         <v>23.42</v>
       </c>
     </row>
@@ -8406,13 +8526,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L116" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M116" s="5" t="n">
+      <c r="L116" s="5" t="n"/>
+      <c r="M116" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N116" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O116" s="5" t="n">
         <v>24.88</v>
       </c>
     </row>
@@ -8466,13 +8587,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L117" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M117" s="5" t="n">
+      <c r="L117" s="5" t="n"/>
+      <c r="M117" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N117" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O117" s="5" t="n">
         <v>25.35</v>
       </c>
     </row>
@@ -8526,13 +8648,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L118" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M118" s="5" t="n">
+      <c r="L118" s="5" t="n"/>
+      <c r="M118" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N118" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O118" s="5" t="n">
         <v>21.63</v>
       </c>
     </row>
@@ -8586,13 +8709,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L119" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M119" s="5" t="n">
+      <c r="L119" s="5" t="n"/>
+      <c r="M119" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N119" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O119" s="5" t="n">
         <v>23.29</v>
       </c>
     </row>
@@ -8646,13 +8770,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L120" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M120" s="5" t="n">
+      <c r="L120" s="5" t="n"/>
+      <c r="M120" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N120" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O120" s="5" t="n">
         <v>20.12</v>
       </c>
     </row>
@@ -8706,13 +8831,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L121" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M121" s="5" t="n">
+      <c r="L121" s="5" t="n"/>
+      <c r="M121" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N121" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O121" s="5" t="n">
         <v>21.15</v>
       </c>
     </row>
@@ -8766,13 +8892,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L122" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M122" s="5" t="n">
+      <c r="L122" s="5" t="n"/>
+      <c r="M122" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N122" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O122" s="5" t="n">
         <v>25.07</v>
       </c>
     </row>
@@ -8826,13 +8953,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L123" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M123" s="5" t="n">
+      <c r="L123" s="5" t="n"/>
+      <c r="M123" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N123" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O123" s="5" t="n">
         <v>21.12</v>
       </c>
     </row>
@@ -8886,13 +9014,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L124" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M124" s="5" t="n">
+      <c r="L124" s="5" t="n"/>
+      <c r="M124" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N124" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O124" s="5" t="n">
         <v>21.83</v>
       </c>
     </row>
@@ -8946,13 +9075,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L125" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M125" s="5" t="n">
+      <c r="L125" s="5" t="n"/>
+      <c r="M125" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N125" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O125" s="5" t="n">
         <v>24.21</v>
       </c>
     </row>
@@ -9006,13 +9136,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L126" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M126" s="5" t="n">
+      <c r="L126" s="5" t="n"/>
+      <c r="M126" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N126" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O126" s="5" t="n">
         <v>21.47</v>
       </c>
     </row>
@@ -9066,13 +9197,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L127" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M127" s="5" t="n">
+      <c r="L127" s="5" t="n"/>
+      <c r="M127" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N127" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O127" s="5" t="n">
         <v>22.13</v>
       </c>
     </row>
@@ -9126,13 +9258,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L128" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M128" s="5" t="n">
+      <c r="L128" s="5" t="n"/>
+      <c r="M128" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N128" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O128" s="5" t="n">
         <v>18</v>
       </c>
     </row>
@@ -9186,13 +9319,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L129" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M129" s="5" t="n">
+      <c r="L129" s="5" t="n"/>
+      <c r="M129" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N129" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O129" s="5" t="n">
         <v>15.54</v>
       </c>
     </row>
@@ -9246,13 +9380,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L130" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M130" s="5" t="n">
+      <c r="L130" s="5" t="n"/>
+      <c r="M130" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N130" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O130" s="5" t="n">
         <v>16.26</v>
       </c>
     </row>
@@ -9306,13 +9441,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L131" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M131" s="5" t="n">
+      <c r="L131" s="5" t="n"/>
+      <c r="M131" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N131" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O131" s="5" t="n">
         <v>20.99</v>
       </c>
     </row>
@@ -9366,13 +9502,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L132" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M132" s="5" t="n">
+      <c r="L132" s="5" t="n"/>
+      <c r="M132" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N132" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O132" s="5" t="n">
         <v>17.33</v>
       </c>
     </row>
@@ -9426,13 +9563,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L133" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M133" s="5" t="n">
+      <c r="L133" s="5" t="n"/>
+      <c r="M133" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N133" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O133" s="5" t="n">
         <v>17.82</v>
       </c>
     </row>
@@ -9486,13 +9624,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L134" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M134" s="5" t="n">
+      <c r="L134" s="5" t="n"/>
+      <c r="M134" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N134" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O134" s="5" t="n">
         <v>19.31</v>
       </c>
     </row>
@@ -9546,13 +9685,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L135" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M135" s="5" t="n">
+      <c r="L135" s="5" t="n"/>
+      <c r="M135" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N135" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O135" s="5" t="n">
         <v>15.85</v>
       </c>
     </row>
@@ -9606,13 +9746,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L136" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M136" s="5" t="n">
+      <c r="L136" s="5" t="n"/>
+      <c r="M136" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N136" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O136" s="5" t="n">
         <v>16.03</v>
       </c>
     </row>
@@ -9666,13 +9807,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L137" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M137" s="5" t="n">
+      <c r="L137" s="5" t="n"/>
+      <c r="M137" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N137" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O137" s="5" t="n">
         <v>22.61</v>
       </c>
     </row>
@@ -9726,13 +9868,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L138" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M138" s="5" t="n">
+      <c r="L138" s="5" t="n"/>
+      <c r="M138" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O138" s="5" t="n">
         <v>21.67</v>
       </c>
     </row>
@@ -9786,13 +9929,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L139" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M139" s="5" t="n">
+      <c r="L139" s="5" t="n"/>
+      <c r="M139" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N139" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O139" s="5" t="n">
         <v>20.82</v>
       </c>
     </row>
@@ -9846,13 +9990,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L140" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M140" s="5" t="n">
+      <c r="L140" s="5" t="n"/>
+      <c r="M140" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N140" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O140" s="5" t="n">
         <v>23.48</v>
       </c>
     </row>
@@ -9906,13 +10051,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L141" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M141" s="5" t="n">
+      <c r="L141" s="5" t="n"/>
+      <c r="M141" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N141" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O141" s="5" t="n">
         <v>20.7</v>
       </c>
     </row>
@@ -9966,13 +10112,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L142" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M142" s="5" t="n">
+      <c r="L142" s="5" t="n"/>
+      <c r="M142" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N142" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O142" s="5" t="n">
         <v>21.28</v>
       </c>
     </row>
@@ -10026,13 +10173,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L143" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M143" s="5" t="n">
+      <c r="L143" s="5" t="n"/>
+      <c r="M143" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N143" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O143" s="5" t="n">
         <v>24.89</v>
       </c>
     </row>
@@ -10086,13 +10234,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L144" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M144" s="5" t="n">
+      <c r="L144" s="5" t="n"/>
+      <c r="M144" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N144" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O144" s="5" t="n">
         <v>21.65</v>
       </c>
     </row>
@@ -10146,13 +10295,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L145" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M145" s="5" t="n">
+      <c r="L145" s="5" t="n"/>
+      <c r="M145" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N145" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O145" s="5" t="n">
         <v>22.22</v>
       </c>
     </row>
@@ -10206,13 +10356,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L146" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M146" s="5" t="n">
+      <c r="L146" s="5" t="n"/>
+      <c r="M146" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N146" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O146" s="5" t="n">
         <v>18.67</v>
       </c>
     </row>
@@ -10266,13 +10417,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L147" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M147" s="5" t="n">
+      <c r="L147" s="5" t="n"/>
+      <c r="M147" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N147" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O147" s="5" t="n">
         <v>15.99</v>
       </c>
     </row>
@@ -10326,13 +10478,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L148" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M148" s="5" t="n">
+      <c r="L148" s="5" t="n"/>
+      <c r="M148" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N148" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O148" s="5" t="n">
         <v>16.14</v>
       </c>
     </row>
@@ -10386,13 +10539,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L149" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M149" s="5" t="n">
+      <c r="L149" s="5" t="n"/>
+      <c r="M149" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N149" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O149" s="5" t="n">
         <v>20.41</v>
       </c>
     </row>
@@ -10446,13 +10600,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L150" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M150" s="5" t="n">
+      <c r="L150" s="5" t="n"/>
+      <c r="M150" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N150" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O150" s="5" t="n">
         <v>17.59</v>
       </c>
     </row>
@@ -10506,13 +10661,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L151" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M151" s="5" t="n">
+      <c r="L151" s="5" t="n"/>
+      <c r="M151" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N151" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O151" s="5" t="n">
         <v>18.07</v>
       </c>
     </row>
@@ -10566,13 +10722,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L152" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M152" s="5" t="n">
+      <c r="L152" s="5" t="n"/>
+      <c r="M152" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N152" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O152" s="5" t="n">
         <v>18.77</v>
       </c>
     </row>
@@ -10626,13 +10783,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L153" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M153" s="5" t="n">
+      <c r="L153" s="5" t="n"/>
+      <c r="M153" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N153" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O153" s="5" t="n">
         <v>16.34</v>
       </c>
     </row>
@@ -10686,13 +10844,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L154" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M154" s="5" t="n">
+      <c r="L154" s="5" t="n"/>
+      <c r="M154" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N154" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O154" s="5" t="n">
         <v>16.71</v>
       </c>
     </row>
@@ -10746,13 +10905,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L155" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M155" s="5" t="n">
+      <c r="L155" s="5" t="n"/>
+      <c r="M155" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N155" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O155" s="5" t="n">
         <v>20.6</v>
       </c>
     </row>
@@ -10806,13 +10966,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L156" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M156" s="5" t="n">
+      <c r="L156" s="5" t="n"/>
+      <c r="M156" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N156" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O156" s="5" t="n">
         <v>20.58</v>
       </c>
     </row>
@@ -10866,13 +11027,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L157" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M157" s="5" t="n">
+      <c r="L157" s="5" t="n"/>
+      <c r="M157" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N157" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O157" s="5" t="n">
         <v>21</v>
       </c>
     </row>
@@ -10926,13 +11088,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L158" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M158" s="5" t="n">
+      <c r="L158" s="5" t="n"/>
+      <c r="M158" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N158" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O158" s="5" t="n">
         <v>15.76</v>
       </c>
     </row>
@@ -10986,13 +11149,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L159" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M159" s="5" t="n">
+      <c r="L159" s="5" t="n"/>
+      <c r="M159" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N159" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O159" s="5" t="n">
         <v>14.51</v>
       </c>
     </row>
@@ -11046,13 +11210,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L160" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M160" s="5" t="n">
+      <c r="L160" s="5" t="n"/>
+      <c r="M160" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N160" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O160" s="5" t="n">
         <v>14.31</v>
       </c>
     </row>
@@ -11106,13 +11271,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L161" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M161" s="5" t="n">
+      <c r="L161" s="5" t="n"/>
+      <c r="M161" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N161" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O161" s="5" t="n">
         <v>14.87</v>
       </c>
     </row>
@@ -11166,13 +11332,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L162" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M162" s="5" t="n">
+      <c r="L162" s="5" t="n"/>
+      <c r="M162" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N162" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O162" s="5" t="n">
         <v>19.16</v>
       </c>
     </row>
@@ -11226,13 +11393,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L163" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M163" s="5" t="n">
+      <c r="L163" s="5" t="n"/>
+      <c r="M163" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N163" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O163" s="5" t="n">
         <v>15.12</v>
       </c>
     </row>
@@ -11286,13 +11454,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L164" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M164" s="5" t="n">
+      <c r="L164" s="5" t="n"/>
+      <c r="M164" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N164" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O164" s="5" t="n">
         <v>17.76</v>
       </c>
     </row>
@@ -11346,13 +11515,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L165" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M165" s="5" t="n">
+      <c r="L165" s="5" t="n"/>
+      <c r="M165" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N165" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O165" s="5" t="n">
         <v>18.48</v>
       </c>
     </row>
@@ -11406,13 +11576,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L166" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M166" s="5" t="n">
+      <c r="L166" s="5" t="n"/>
+      <c r="M166" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N166" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O166" s="5" t="n">
         <v>14.93</v>
       </c>
     </row>
@@ -11466,13 +11637,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L167" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M167" s="5" t="n">
+      <c r="L167" s="5" t="n"/>
+      <c r="M167" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N167" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O167" s="5" t="n">
         <v>13.91</v>
       </c>
     </row>
@@ -11526,13 +11698,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L168" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M168" s="5" t="n">
+      <c r="L168" s="5" t="n"/>
+      <c r="M168" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N168" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O168" s="5" t="n">
         <v>14.42</v>
       </c>
     </row>
@@ -11586,13 +11759,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L169" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M169" s="5" t="n">
+      <c r="L169" s="5" t="n"/>
+      <c r="M169" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N169" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O169" s="5" t="n">
         <v>18.99</v>
       </c>
     </row>
@@ -11646,13 +11820,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L170" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M170" s="5" t="n">
+      <c r="L170" s="5" t="n"/>
+      <c r="M170" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N170" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O170" s="5" t="n">
         <v>15.71</v>
       </c>
     </row>
@@ -11706,13 +11881,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L171" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M171" s="5" t="n">
+      <c r="L171" s="5" t="n"/>
+      <c r="M171" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N171" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O171" s="5" t="n">
         <v>20.66</v>
       </c>
     </row>
@@ -11766,13 +11942,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L172" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M172" s="5" t="n">
+      <c r="L172" s="5" t="n"/>
+      <c r="M172" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N172" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O172" s="5" t="n">
         <v>15.22</v>
       </c>
     </row>
@@ -11826,13 +12003,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L173" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M173" s="5" t="n">
+      <c r="L173" s="5" t="n"/>
+      <c r="M173" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N173" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O173" s="5" t="n">
         <v>18.21</v>
       </c>
     </row>
@@ -11886,13 +12064,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L174" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M174" s="5" t="n">
+      <c r="L174" s="5" t="n"/>
+      <c r="M174" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N174" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O174" s="5" t="n">
         <v>18.97</v>
       </c>
     </row>
@@ -11946,13 +12125,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L175" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M175" s="5" t="n">
+      <c r="L175" s="5" t="n"/>
+      <c r="M175" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N175" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O175" s="5" t="n">
         <v>15.86</v>
       </c>
     </row>
@@ -12006,13 +12186,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L176" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M176" s="5" t="n">
+      <c r="L176" s="5" t="n"/>
+      <c r="M176" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N176" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O176" s="5" t="n">
         <v>13.62</v>
       </c>
     </row>
@@ -12066,13 +12247,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L177" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M177" s="5" t="n">
+      <c r="L177" s="5" t="n"/>
+      <c r="M177" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N177" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O177" s="5" t="n">
         <v>14.52</v>
       </c>
     </row>
@@ -12126,13 +12308,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L178" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M178" s="5" t="n">
+      <c r="L178" s="5" t="n"/>
+      <c r="M178" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N178" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O178" s="5" t="n">
         <v>14.79</v>
       </c>
     </row>
@@ -12186,13 +12369,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L179" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M179" s="5" t="n">
+      <c r="L179" s="5" t="n"/>
+      <c r="M179" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N179" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O179" s="5" t="n">
         <v>14.66</v>
       </c>
     </row>
@@ -12246,13 +12430,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L180" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M180" s="5" t="n">
+      <c r="L180" s="5" t="n"/>
+      <c r="M180" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N180" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O180" s="5" t="n">
         <v>16.25</v>
       </c>
     </row>
@@ -12306,13 +12491,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L181" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M181" s="5" t="n">
+      <c r="L181" s="5" t="n"/>
+      <c r="M181" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N181" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O181" s="5" t="n">
         <v>15.25</v>
       </c>
     </row>
@@ -12366,13 +12552,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L182" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M182" s="5" t="n">
+      <c r="L182" s="5" t="n"/>
+      <c r="M182" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N182" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O182" s="5" t="n">
         <v>14.31</v>
       </c>
     </row>
@@ -12426,13 +12613,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L183" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M183" s="5" t="n">
+      <c r="L183" s="5" t="n"/>
+      <c r="M183" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N183" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O183" s="5" t="n">
         <v>15.12</v>
       </c>
     </row>
@@ -12486,13 +12674,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L184" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M184" s="5" t="n">
+      <c r="L184" s="5" t="n"/>
+      <c r="M184" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N184" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O184" s="5" t="n">
         <v>14.99</v>
       </c>
     </row>
@@ -12548,7 +12737,8 @@
       </c>
       <c r="L185" s="5" t="n"/>
       <c r="M185" s="5" t="n"/>
-      <c r="N185" s="5" t="n">
+      <c r="N185" s="5" t="n"/>
+      <c r="O185" s="5" t="n">
         <v>24.09</v>
       </c>
     </row>
@@ -12604,7 +12794,8 @@
       </c>
       <c r="L186" s="5" t="n"/>
       <c r="M186" s="5" t="n"/>
-      <c r="N186" s="5" t="n">
+      <c r="N186" s="5" t="n"/>
+      <c r="O186" s="5" t="n">
         <v>23.4</v>
       </c>
     </row>
@@ -12660,7 +12851,8 @@
       </c>
       <c r="L187" s="5" t="n"/>
       <c r="M187" s="5" t="n"/>
-      <c r="N187" s="5" t="n">
+      <c r="N187" s="5" t="n"/>
+      <c r="O187" s="5" t="n">
         <v>22.25</v>
       </c>
     </row>
@@ -12714,13 +12906,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L188" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M188" s="5" t="n">
+      <c r="L188" s="5" t="n"/>
+      <c r="M188" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N188" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O188" s="5" t="n">
         <v>31.98</v>
       </c>
     </row>
@@ -12774,13 +12967,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L189" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M189" s="5" t="n">
+      <c r="L189" s="5" t="n"/>
+      <c r="M189" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N189" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O189" s="5" t="n">
         <v>31.6</v>
       </c>
     </row>
@@ -12834,13 +13028,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L190" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M190" s="5" t="n">
+      <c r="L190" s="5" t="n"/>
+      <c r="M190" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N190" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O190" s="5" t="n">
         <v>28.32</v>
       </c>
     </row>
@@ -12894,13 +13089,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L191" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M191" s="5" t="n">
+      <c r="L191" s="5" t="n"/>
+      <c r="M191" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N191" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O191" s="5" t="n">
         <v>16.66</v>
       </c>
     </row>
@@ -12954,13 +13150,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L192" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M192" s="5" t="n">
+      <c r="L192" s="5" t="n"/>
+      <c r="M192" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N192" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O192" s="5" t="n">
         <v>16.45</v>
       </c>
     </row>
@@ -13014,13 +13211,14 @@
           <t>execution_failure</t>
         </is>
       </c>
-      <c r="L193" s="5" t="b">
+      <c r="L193" s="5" t="n"/>
+      <c r="M193" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="M193" s="5" t="n">
+      <c r="N193" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N193" s="5" t="n">
+      <c r="O193" s="5" t="n">
         <v>21.42</v>
       </c>
     </row>
@@ -13074,13 +13272,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L194" s="5" t="b">
+      <c r="L194" s="5" t="n"/>
+      <c r="M194" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="M194" s="5" t="n">
+      <c r="N194" s="5" t="n">
         <v>0.6667</v>
       </c>
-      <c r="N194" s="5" t="n">
+      <c r="O194" s="5" t="n">
         <v>30.16</v>
       </c>
     </row>
@@ -13134,13 +13333,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L195" s="5" t="b">
+      <c r="L195" s="5" t="n"/>
+      <c r="M195" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="M195" s="5" t="n">
+      <c r="N195" s="5" t="n">
         <v>0.6667</v>
       </c>
-      <c r="N195" s="5" t="n">
+      <c r="O195" s="5" t="n">
         <v>26.96</v>
       </c>
     </row>
@@ -13194,13 +13394,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L196" s="5" t="b">
+      <c r="L196" s="5" t="n"/>
+      <c r="M196" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="M196" s="5" t="n">
+      <c r="N196" s="5" t="n">
         <v>0.6667</v>
       </c>
-      <c r="N196" s="5" t="n">
+      <c r="O196" s="5" t="n">
         <v>26.8</v>
       </c>
     </row>
@@ -13256,7 +13457,8 @@
       </c>
       <c r="L197" s="5" t="n"/>
       <c r="M197" s="5" t="n"/>
-      <c r="N197" s="5" t="n">
+      <c r="N197" s="5" t="n"/>
+      <c r="O197" s="5" t="n">
         <v>9.82</v>
       </c>
     </row>
@@ -13312,7 +13514,8 @@
       </c>
       <c r="L198" s="5" t="n"/>
       <c r="M198" s="5" t="n"/>
-      <c r="N198" s="5" t="n">
+      <c r="N198" s="5" t="n"/>
+      <c r="O198" s="5" t="n">
         <v>11.1</v>
       </c>
     </row>
@@ -13368,7 +13571,8 @@
       </c>
       <c r="L199" s="5" t="n"/>
       <c r="M199" s="5" t="n"/>
-      <c r="N199" s="5" t="n">
+      <c r="N199" s="5" t="n"/>
+      <c r="O199" s="5" t="n">
         <v>36.26</v>
       </c>
     </row>
@@ -13424,7 +13628,8 @@
       </c>
       <c r="L200" s="5" t="n"/>
       <c r="M200" s="5" t="n"/>
-      <c r="N200" s="5" t="n">
+      <c r="N200" s="5" t="n"/>
+      <c r="O200" s="5" t="n">
         <v>22.57</v>
       </c>
     </row>
@@ -13480,7 +13685,8 @@
       </c>
       <c r="L201" s="5" t="n"/>
       <c r="M201" s="5" t="n"/>
-      <c r="N201" s="5" t="n">
+      <c r="N201" s="5" t="n"/>
+      <c r="O201" s="5" t="n">
         <v>21.96</v>
       </c>
     </row>
@@ -13536,7 +13742,8 @@
       </c>
       <c r="L202" s="5" t="n"/>
       <c r="M202" s="5" t="n"/>
-      <c r="N202" s="5" t="n">
+      <c r="N202" s="5" t="n"/>
+      <c r="O202" s="5" t="n">
         <v>21.9</v>
       </c>
     </row>
@@ -13590,13 +13797,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L203" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M203" s="5" t="n">
+      <c r="L203" s="5" t="n"/>
+      <c r="M203" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N203" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O203" s="5" t="n">
         <v>10.08</v>
       </c>
     </row>
@@ -13650,13 +13858,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L204" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M204" s="5" t="n">
+      <c r="L204" s="5" t="n"/>
+      <c r="M204" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N204" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O204" s="5" t="n">
         <v>7.59</v>
       </c>
     </row>
@@ -13710,13 +13919,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L205" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M205" s="5" t="n">
+      <c r="L205" s="5" t="n"/>
+      <c r="M205" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N205" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O205" s="5" t="n">
         <v>7.26</v>
       </c>
     </row>
@@ -13770,13 +13980,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L206" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M206" s="5" t="n">
+      <c r="L206" s="5" t="n"/>
+      <c r="M206" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N206" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O206" s="5" t="n">
         <v>7.41</v>
       </c>
     </row>
@@ -13830,13 +14041,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L207" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M207" s="5" t="n">
+      <c r="L207" s="5" t="n"/>
+      <c r="M207" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N207" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O207" s="5" t="n">
         <v>7.27</v>
       </c>
     </row>
@@ -13890,13 +14102,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L208" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M208" s="5" t="n">
+      <c r="L208" s="5" t="n"/>
+      <c r="M208" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N208" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O208" s="5" t="n">
         <v>7.27</v>
       </c>
     </row>
@@ -13950,13 +14163,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L209" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M209" s="5" t="n">
+      <c r="L209" s="5" t="n"/>
+      <c r="M209" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N209" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O209" s="5" t="n">
         <v>7.64</v>
       </c>
     </row>
@@ -14010,13 +14224,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L210" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M210" s="5" t="n">
+      <c r="L210" s="5" t="n"/>
+      <c r="M210" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N210" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O210" s="5" t="n">
         <v>7.65</v>
       </c>
     </row>
@@ -14070,13 +14285,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L211" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M211" s="5" t="n">
+      <c r="L211" s="5" t="n"/>
+      <c r="M211" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N211" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O211" s="5" t="n">
         <v>7.61</v>
       </c>
     </row>
@@ -14130,13 +14346,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L212" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M212" s="5" t="n">
+      <c r="L212" s="5" t="n"/>
+      <c r="M212" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N212" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O212" s="5" t="n">
         <v>8.18</v>
       </c>
     </row>
@@ -14190,13 +14407,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L213" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M213" s="5" t="n">
+      <c r="L213" s="5" t="n"/>
+      <c r="M213" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N213" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O213" s="5" t="n">
         <v>11.49</v>
       </c>
     </row>
@@ -14250,13 +14468,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L214" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M214" s="5" t="n">
+      <c r="L214" s="5" t="n"/>
+      <c r="M214" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N214" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O214" s="5" t="n">
         <v>11.14</v>
       </c>
     </row>
@@ -14310,13 +14529,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L215" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M215" s="5" t="n">
+      <c r="L215" s="5" t="n"/>
+      <c r="M215" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N215" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O215" s="5" t="n">
         <v>7.94</v>
       </c>
     </row>
@@ -14370,13 +14590,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L216" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M216" s="5" t="n">
+      <c r="L216" s="5" t="n"/>
+      <c r="M216" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N216" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O216" s="5" t="n">
         <v>7.93</v>
       </c>
     </row>
@@ -14430,13 +14651,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L217" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M217" s="5" t="n">
+      <c r="L217" s="5" t="n"/>
+      <c r="M217" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N217" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O217" s="5" t="n">
         <v>7.63</v>
       </c>
     </row>
@@ -14490,13 +14712,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L218" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M218" s="5" t="n">
+      <c r="L218" s="5" t="n"/>
+      <c r="M218" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N218" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O218" s="5" t="n">
         <v>9.98</v>
       </c>
     </row>
@@ -14550,13 +14773,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L219" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M219" s="5" t="n">
+      <c r="L219" s="5" t="n"/>
+      <c r="M219" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N219" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O219" s="5" t="n">
         <v>12.4</v>
       </c>
     </row>
@@ -14610,13 +14834,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L220" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M220" s="5" t="n">
+      <c r="L220" s="5" t="n"/>
+      <c r="M220" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N220" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O220" s="5" t="n">
         <v>9.48</v>
       </c>
     </row>
@@ -14670,13 +14895,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L221" s="5" t="b">
+      <c r="L221" s="5" t="n"/>
+      <c r="M221" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="M221" s="5" t="n">
+      <c r="N221" s="5" t="n">
         <v>0.7692</v>
       </c>
-      <c r="N221" s="5" t="n">
+      <c r="O221" s="5" t="n">
         <v>7.51</v>
       </c>
     </row>
@@ -14730,13 +14956,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L222" s="5" t="b">
+      <c r="L222" s="5" t="n"/>
+      <c r="M222" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="M222" s="5" t="n">
+      <c r="N222" s="5" t="n">
         <v>0.7692</v>
       </c>
-      <c r="N222" s="5" t="n">
+      <c r="O222" s="5" t="n">
         <v>8.029999999999999</v>
       </c>
     </row>
@@ -14790,13 +15017,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L223" s="5" t="b">
+      <c r="L223" s="5" t="n"/>
+      <c r="M223" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="M223" s="5" t="n">
+      <c r="N223" s="5" t="n">
         <v>0.7692</v>
       </c>
-      <c r="N223" s="5" t="n">
+      <c r="O223" s="5" t="n">
         <v>8.640000000000001</v>
       </c>
     </row>
@@ -14850,13 +15078,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L224" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M224" s="5" t="n">
+      <c r="L224" s="5" t="n"/>
+      <c r="M224" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N224" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O224" s="5" t="n">
         <v>9.23</v>
       </c>
     </row>
@@ -14910,13 +15139,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L225" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M225" s="5" t="n">
+      <c r="L225" s="5" t="n"/>
+      <c r="M225" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N225" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O225" s="5" t="n">
         <v>9.27</v>
       </c>
     </row>
@@ -14970,13 +15200,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L226" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M226" s="5" t="n">
+      <c r="L226" s="5" t="n"/>
+      <c r="M226" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N226" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O226" s="5" t="n">
         <v>9.970000000000001</v>
       </c>
     </row>
@@ -15030,13 +15261,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L227" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M227" s="5" t="n">
+      <c r="L227" s="5" t="n"/>
+      <c r="M227" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N227" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O227" s="5" t="n">
         <v>8.59</v>
       </c>
     </row>
@@ -15090,13 +15322,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L228" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M228" s="5" t="n">
+      <c r="L228" s="5" t="n"/>
+      <c r="M228" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N228" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O228" s="5" t="n">
         <v>8.460000000000001</v>
       </c>
     </row>
@@ -15150,13 +15383,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L229" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M229" s="5" t="n">
+      <c r="L229" s="5" t="n"/>
+      <c r="M229" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N229" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O229" s="5" t="n">
         <v>8.859999999999999</v>
       </c>
     </row>
@@ -15212,7 +15446,8 @@
       </c>
       <c r="L230" s="5" t="n"/>
       <c r="M230" s="5" t="n"/>
-      <c r="N230" s="5" t="n">
+      <c r="N230" s="5" t="n"/>
+      <c r="O230" s="5" t="n">
         <v>14.52</v>
       </c>
     </row>
@@ -15268,7 +15503,8 @@
       </c>
       <c r="L231" s="5" t="n"/>
       <c r="M231" s="5" t="n"/>
-      <c r="N231" s="5" t="n">
+      <c r="N231" s="5" t="n"/>
+      <c r="O231" s="5" t="n">
         <v>11.11</v>
       </c>
     </row>
@@ -15324,7 +15560,8 @@
       </c>
       <c r="L232" s="5" t="n"/>
       <c r="M232" s="5" t="n"/>
-      <c r="N232" s="5" t="n">
+      <c r="N232" s="5" t="n"/>
+      <c r="O232" s="5" t="n">
         <v>10.88</v>
       </c>
     </row>
@@ -15378,13 +15615,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L233" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M233" s="5" t="n">
+      <c r="L233" s="5" t="n"/>
+      <c r="M233" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N233" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O233" s="5" t="n">
         <v>6.9</v>
       </c>
     </row>
@@ -15438,13 +15676,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L234" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M234" s="5" t="n">
+      <c r="L234" s="5" t="n"/>
+      <c r="M234" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N234" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O234" s="5" t="n">
         <v>6.82</v>
       </c>
     </row>
@@ -15498,13 +15737,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L235" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M235" s="5" t="n">
+      <c r="L235" s="5" t="n"/>
+      <c r="M235" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N235" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O235" s="5" t="n">
         <v>6.85</v>
       </c>
     </row>
@@ -15558,13 +15798,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L236" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M236" s="5" t="n">
+      <c r="L236" s="5" t="n"/>
+      <c r="M236" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N236" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O236" s="5" t="n">
         <v>6.61</v>
       </c>
     </row>
@@ -15618,13 +15859,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L237" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M237" s="5" t="n">
+      <c r="L237" s="5" t="n"/>
+      <c r="M237" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N237" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O237" s="5" t="n">
         <v>6.82</v>
       </c>
     </row>
@@ -15678,13 +15920,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L238" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M238" s="5" t="n">
+      <c r="L238" s="5" t="n"/>
+      <c r="M238" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N238" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O238" s="5" t="n">
         <v>6.69</v>
       </c>
     </row>
@@ -15738,13 +15981,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L239" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M239" s="5" t="n">
+      <c r="L239" s="5" t="n"/>
+      <c r="M239" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N239" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O239" s="5" t="n">
         <v>6.95</v>
       </c>
     </row>
@@ -15798,13 +16042,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L240" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M240" s="5" t="n">
+      <c r="L240" s="5" t="n"/>
+      <c r="M240" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N240" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O240" s="5" t="n">
         <v>6.88</v>
       </c>
     </row>
@@ -15858,13 +16103,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L241" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M241" s="5" t="n">
+      <c r="L241" s="5" t="n"/>
+      <c r="M241" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N241" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O241" s="5" t="n">
         <v>6.92</v>
       </c>
     </row>
@@ -15918,13 +16164,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L242" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M242" s="5" t="n">
+      <c r="L242" s="5" t="n"/>
+      <c r="M242" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N242" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O242" s="5" t="n">
         <v>4.34</v>
       </c>
     </row>
@@ -15978,13 +16225,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L243" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M243" s="5" t="n">
+      <c r="L243" s="5" t="n"/>
+      <c r="M243" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N243" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O243" s="5" t="n">
         <v>3.62</v>
       </c>
     </row>
@@ -16038,13 +16286,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L244" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M244" s="5" t="n">
+      <c r="L244" s="5" t="n"/>
+      <c r="M244" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N244" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O244" s="5" t="n">
         <v>4.4</v>
       </c>
     </row>
@@ -16098,13 +16347,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L245" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M245" s="5" t="n">
+      <c r="L245" s="5" t="n"/>
+      <c r="M245" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N245" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O245" s="5" t="n">
         <v>4.17</v>
       </c>
     </row>
@@ -16158,13 +16408,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L246" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M246" s="5" t="n">
+      <c r="L246" s="5" t="n"/>
+      <c r="M246" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N246" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O246" s="5" t="n">
         <v>3.67</v>
       </c>
     </row>
@@ -16218,13 +16469,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L247" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M247" s="5" t="n">
+      <c r="L247" s="5" t="n"/>
+      <c r="M247" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N247" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O247" s="5" t="n">
         <v>3.61</v>
       </c>
     </row>
@@ -16278,7 +16530,8 @@
       </c>
       <c r="L248" s="5" t="n"/>
       <c r="M248" s="5" t="n"/>
-      <c r="N248" s="5" t="n">
+      <c r="N248" s="5" t="n"/>
+      <c r="O248" s="5" t="n">
         <v>3.89</v>
       </c>
     </row>
@@ -16332,7 +16585,8 @@
       </c>
       <c r="L249" s="5" t="n"/>
       <c r="M249" s="5" t="n"/>
-      <c r="N249" s="5" t="n">
+      <c r="N249" s="5" t="n"/>
+      <c r="O249" s="5" t="n">
         <v>3.34</v>
       </c>
     </row>
@@ -16386,7 +16640,8 @@
       </c>
       <c r="L250" s="5" t="n"/>
       <c r="M250" s="5" t="n"/>
-      <c r="N250" s="5" t="n">
+      <c r="N250" s="5" t="n"/>
+      <c r="O250" s="5" t="n">
         <v>3.8</v>
       </c>
     </row>
@@ -16440,7 +16695,8 @@
       </c>
       <c r="L251" s="5" t="n"/>
       <c r="M251" s="5" t="n"/>
-      <c r="N251" s="5" t="n">
+      <c r="N251" s="5" t="n"/>
+      <c r="O251" s="5" t="n">
         <v>7.1</v>
       </c>
     </row>
@@ -16494,7 +16750,8 @@
       </c>
       <c r="L252" s="5" t="n"/>
       <c r="M252" s="5" t="n"/>
-      <c r="N252" s="5" t="n">
+      <c r="N252" s="5" t="n"/>
+      <c r="O252" s="5" t="n">
         <v>7.48</v>
       </c>
     </row>
@@ -16548,7 +16805,8 @@
       </c>
       <c r="L253" s="5" t="n"/>
       <c r="M253" s="5" t="n"/>
-      <c r="N253" s="5" t="n">
+      <c r="N253" s="5" t="n"/>
+      <c r="O253" s="5" t="n">
         <v>4.99</v>
       </c>
     </row>
@@ -16602,7 +16860,8 @@
       </c>
       <c r="L254" s="5" t="n"/>
       <c r="M254" s="5" t="n"/>
-      <c r="N254" s="5" t="n">
+      <c r="N254" s="5" t="n"/>
+      <c r="O254" s="5" t="n">
         <v>3.28</v>
       </c>
     </row>
@@ -16656,7 +16915,8 @@
       </c>
       <c r="L255" s="5" t="n"/>
       <c r="M255" s="5" t="n"/>
-      <c r="N255" s="5" t="n">
+      <c r="N255" s="5" t="n"/>
+      <c r="O255" s="5" t="n">
         <v>3.38</v>
       </c>
     </row>
@@ -16710,7 +16970,8 @@
       </c>
       <c r="L256" s="5" t="n"/>
       <c r="M256" s="5" t="n"/>
-      <c r="N256" s="5" t="n">
+      <c r="N256" s="5" t="n"/>
+      <c r="O256" s="5" t="n">
         <v>3.33</v>
       </c>
     </row>
@@ -16764,13 +17025,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L257" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M257" s="5" t="n">
+      <c r="L257" s="5" t="n"/>
+      <c r="M257" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N257" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O257" s="5" t="n">
         <v>7.1</v>
       </c>
     </row>
@@ -16824,13 +17086,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L258" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M258" s="5" t="n">
+      <c r="L258" s="5" t="n"/>
+      <c r="M258" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N258" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O258" s="5" t="n">
         <v>7.12</v>
       </c>
     </row>
@@ -16884,13 +17147,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L259" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M259" s="5" t="n">
+      <c r="L259" s="5" t="n"/>
+      <c r="M259" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N259" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O259" s="5" t="n">
         <v>3.92</v>
       </c>
     </row>
@@ -16944,13 +17208,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L260" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M260" s="5" t="n">
+      <c r="L260" s="5" t="n"/>
+      <c r="M260" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N260" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O260" s="5" t="n">
         <v>7.1</v>
       </c>
     </row>
@@ -17006,7 +17271,8 @@
       </c>
       <c r="L261" s="5" t="n"/>
       <c r="M261" s="5" t="n"/>
-      <c r="N261" s="5" t="n">
+      <c r="N261" s="5" t="n"/>
+      <c r="O261" s="5" t="n">
         <v>7.05</v>
       </c>
     </row>
@@ -17060,13 +17326,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L262" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M262" s="5" t="n">
+      <c r="L262" s="5" t="n"/>
+      <c r="M262" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N262" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O262" s="5" t="n">
         <v>3.92</v>
       </c>
     </row>
@@ -17120,13 +17387,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L263" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M263" s="5" t="n">
+      <c r="L263" s="5" t="n"/>
+      <c r="M263" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N263" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O263" s="5" t="n">
         <v>8.23</v>
       </c>
     </row>
@@ -17180,13 +17448,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L264" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M264" s="5" t="n">
+      <c r="L264" s="5" t="n"/>
+      <c r="M264" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N264" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O264" s="5" t="n">
         <v>8.1</v>
       </c>
     </row>
@@ -17240,13 +17509,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L265" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M265" s="5" t="n">
+      <c r="L265" s="5" t="n"/>
+      <c r="M265" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N265" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O265" s="5" t="n">
         <v>4.61</v>
       </c>
     </row>
@@ -17300,13 +17570,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L266" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M266" s="5" t="n">
+      <c r="L266" s="5" t="n"/>
+      <c r="M266" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N266" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O266" s="5" t="n">
         <v>16.49</v>
       </c>
     </row>
@@ -17360,13 +17631,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L267" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M267" s="5" t="n">
+      <c r="L267" s="5" t="n"/>
+      <c r="M267" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N267" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O267" s="5" t="n">
         <v>17.18</v>
       </c>
     </row>
@@ -17420,13 +17692,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L268" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M268" s="5" t="n">
+      <c r="L268" s="5" t="n"/>
+      <c r="M268" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N268" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O268" s="5" t="n">
         <v>16.5</v>
       </c>
     </row>
@@ -17480,13 +17753,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L269" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M269" s="5" t="n">
+      <c r="L269" s="5" t="n"/>
+      <c r="M269" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N269" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O269" s="5" t="n">
         <v>26.92</v>
       </c>
     </row>
@@ -17540,13 +17814,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L270" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M270" s="5" t="n">
+      <c r="L270" s="5" t="n"/>
+      <c r="M270" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N270" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O270" s="5" t="n">
         <v>19.44</v>
       </c>
     </row>
@@ -17600,13 +17875,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L271" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M271" s="5" t="n">
+      <c r="L271" s="5" t="n"/>
+      <c r="M271" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N271" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O271" s="5" t="n">
         <v>19.47</v>
       </c>
     </row>
@@ -17660,13 +17936,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L272" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M272" s="5" t="n">
+      <c r="L272" s="5" t="n"/>
+      <c r="M272" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N272" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O272" s="5" t="n">
         <v>21.28</v>
       </c>
     </row>
@@ -17720,13 +17997,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L273" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M273" s="5" t="n">
+      <c r="L273" s="5" t="n"/>
+      <c r="M273" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N273" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O273" s="5" t="n">
         <v>22.32</v>
       </c>
     </row>
@@ -17780,13 +18058,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L274" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M274" s="5" t="n">
+      <c r="L274" s="5" t="n"/>
+      <c r="M274" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N274" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O274" s="5" t="n">
         <v>21.36</v>
       </c>
     </row>
@@ -17840,13 +18119,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L275" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M275" s="5" t="n">
+      <c r="L275" s="5" t="n"/>
+      <c r="M275" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N275" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O275" s="5" t="n">
         <v>16.55</v>
       </c>
     </row>
@@ -17900,13 +18180,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L276" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M276" s="5" t="n">
+      <c r="L276" s="5" t="n"/>
+      <c r="M276" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N276" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O276" s="5" t="n">
         <v>20.76</v>
       </c>
     </row>
@@ -17960,13 +18241,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L277" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M277" s="5" t="n">
+      <c r="L277" s="5" t="n"/>
+      <c r="M277" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N277" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O277" s="5" t="n">
         <v>16.66</v>
       </c>
     </row>
@@ -18020,13 +18302,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L278" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M278" s="5" t="n">
+      <c r="L278" s="5" t="n"/>
+      <c r="M278" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N278" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O278" s="5" t="n">
         <v>17.3</v>
       </c>
     </row>
@@ -18080,13 +18363,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L279" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M279" s="5" t="n">
+      <c r="L279" s="5" t="n"/>
+      <c r="M279" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N279" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O279" s="5" t="n">
         <v>18.6</v>
       </c>
     </row>
@@ -18140,13 +18424,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L280" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M280" s="5" t="n">
+      <c r="L280" s="5" t="n"/>
+      <c r="M280" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N280" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O280" s="5" t="n">
         <v>16.8</v>
       </c>
     </row>
@@ -18202,7 +18487,8 @@
       </c>
       <c r="L281" s="5" t="n"/>
       <c r="M281" s="5" t="n"/>
-      <c r="N281" s="5" t="n">
+      <c r="N281" s="5" t="n"/>
+      <c r="O281" s="5" t="n">
         <v>10.68</v>
       </c>
     </row>
@@ -18258,7 +18544,8 @@
       </c>
       <c r="L282" s="5" t="n"/>
       <c r="M282" s="5" t="n"/>
-      <c r="N282" s="5" t="n">
+      <c r="N282" s="5" t="n"/>
+      <c r="O282" s="5" t="n">
         <v>12.47</v>
       </c>
     </row>
@@ -18314,7 +18601,8 @@
       </c>
       <c r="L283" s="5" t="n"/>
       <c r="M283" s="5" t="n"/>
-      <c r="N283" s="5" t="n">
+      <c r="N283" s="5" t="n"/>
+      <c r="O283" s="5" t="n">
         <v>14.34</v>
       </c>
     </row>
@@ -18368,13 +18656,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L284" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M284" s="5" t="n">
+      <c r="L284" s="5" t="n"/>
+      <c r="M284" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N284" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O284" s="5" t="n">
         <v>12.05</v>
       </c>
     </row>
@@ -18428,13 +18717,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L285" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M285" s="5" t="n">
+      <c r="L285" s="5" t="n"/>
+      <c r="M285" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N285" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O285" s="5" t="n">
         <v>12.24</v>
       </c>
     </row>
@@ -18488,13 +18778,14 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L286" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M286" s="5" t="n">
+      <c r="L286" s="5" t="n"/>
+      <c r="M286" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N286" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O286" s="5" t="n">
         <v>12.83</v>
       </c>
     </row>
@@ -18550,7 +18841,8 @@
       </c>
       <c r="L287" s="5" t="n"/>
       <c r="M287" s="5" t="n"/>
-      <c r="N287" s="5" t="n">
+      <c r="N287" s="5" t="n"/>
+      <c r="O287" s="5" t="n">
         <v>11.92</v>
       </c>
     </row>
@@ -18606,7 +18898,8 @@
       </c>
       <c r="L288" s="5" t="n"/>
       <c r="M288" s="5" t="n"/>
-      <c r="N288" s="5" t="n">
+      <c r="N288" s="5" t="n"/>
+      <c r="O288" s="5" t="n">
         <v>12.6</v>
       </c>
     </row>
@@ -18662,7 +18955,8 @@
       </c>
       <c r="L289" s="5" t="n"/>
       <c r="M289" s="5" t="n"/>
-      <c r="N289" s="5" t="n">
+      <c r="N289" s="5" t="n"/>
+      <c r="O289" s="5" t="n">
         <v>13.69</v>
       </c>
     </row>
@@ -18718,7 +19012,8 @@
       </c>
       <c r="L290" s="5" t="n"/>
       <c r="M290" s="5" t="n"/>
-      <c r="N290" s="5" t="n">
+      <c r="N290" s="5" t="n"/>
+      <c r="O290" s="5" t="n">
         <v>13.03</v>
       </c>
     </row>
@@ -18774,7 +19069,8 @@
       </c>
       <c r="L291" s="5" t="n"/>
       <c r="M291" s="5" t="n"/>
-      <c r="N291" s="5" t="n">
+      <c r="N291" s="5" t="n"/>
+      <c r="O291" s="5" t="n">
         <v>13.16</v>
       </c>
     </row>
@@ -18830,14 +19126,15 @@
       </c>
       <c r="L292" s="5" t="n"/>
       <c r="M292" s="5" t="n"/>
-      <c r="N292" s="5" t="n">
+      <c r="N292" s="5" t="n"/>
+      <c r="O292" s="5" t="n">
         <v>13.05</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>cross_kg_005</t>
         </is>
       </c>
       <c r="B293" s="5" t="n">
@@ -18845,12 +19142,12 @@
       </c>
       <c r="C293" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E293" s="5" t="inlineStr">
@@ -18865,12 +19162,12 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I293" s="5" t="b">
@@ -18884,20 +19181,21 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L293" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M293" s="5" t="n">
+      <c r="L293" s="5" t="n"/>
+      <c r="M293" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N293" s="5" t="n">
-        <v>35.31</v>
+        <v>1</v>
+      </c>
+      <c r="O293" s="5" t="n">
+        <v>22.65</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>cross_kg_005</t>
         </is>
       </c>
       <c r="B294" s="5" t="n">
@@ -18905,32 +19203,32 @@
       </c>
       <c r="C294" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E294" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F294" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H294" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I294" s="5" t="b">
@@ -18944,20 +19242,21 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L294" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M294" s="5" t="n">
+      <c r="L294" s="5" t="n"/>
+      <c r="M294" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N294" s="5" t="n">
-        <v>16.82</v>
+        <v>1</v>
+      </c>
+      <c r="O294" s="5" t="n">
+        <v>23.76</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>cross_kg_005</t>
         </is>
       </c>
       <c r="B295" s="5" t="n">
@@ -18965,32 +19264,32 @@
       </c>
       <c r="C295" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E295" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F295" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I295" s="5" t="b">
@@ -19004,20 +19303,21 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L295" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M295" s="5" t="n">
+      <c r="L295" s="5" t="n"/>
+      <c r="M295" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N295" s="5" t="n">
-        <v>16.51</v>
+        <v>1</v>
+      </c>
+      <c r="O295" s="5" t="n">
+        <v>22.97</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>cross_kg_009</t>
         </is>
       </c>
       <c r="B296" s="5" t="n">
@@ -19025,17 +19325,17 @@
       </c>
       <c r="C296" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E296" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F296" s="5" t="inlineStr">
@@ -19045,12 +19345,12 @@
       </c>
       <c r="G296" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H296" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I296" s="5" t="b">
@@ -19064,20 +19364,21 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L296" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M296" s="5" t="n">
+      <c r="L296" s="5" t="n"/>
+      <c r="M296" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N296" s="5" t="n">
-        <v>20.41</v>
+        <v>1</v>
+      </c>
+      <c r="O296" s="5" t="n">
+        <v>19.47</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>cross_kg_009</t>
         </is>
       </c>
       <c r="B297" s="5" t="n">
@@ -19085,12 +19386,12 @@
       </c>
       <c r="C297" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E297" s="5" t="inlineStr">
@@ -19100,17 +19401,17 @@
       </c>
       <c r="F297" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I297" s="5" t="b">
@@ -19124,20 +19425,21 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L297" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M297" s="5" t="n">
+      <c r="L297" s="5" t="n"/>
+      <c r="M297" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N297" s="5" t="n">
-        <v>18.71</v>
+        <v>1</v>
+      </c>
+      <c r="O297" s="5" t="n">
+        <v>26.07</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>cross_kg_009</t>
         </is>
       </c>
       <c r="B298" s="5" t="n">
@@ -19145,32 +19447,32 @@
       </c>
       <c r="C298" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D298" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E298" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F298" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G298" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H298" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I298" s="5" t="b">
@@ -19184,28 +19486,29 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L298" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M298" s="5" t="n">
+      <c r="L298" s="5" t="n"/>
+      <c r="M298" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N298" s="5" t="n">
-        <v>18.72</v>
+        <v>1</v>
+      </c>
+      <c r="O298" s="5" t="n">
+        <v>23.25</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B299" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C299" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D299" s="5" t="inlineStr">
@@ -19215,7 +19518,7 @@
       </c>
       <c r="E299" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F299" s="5" t="inlineStr">
@@ -19225,47 +19528,48 @@
       </c>
       <c r="G299" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H299" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I299" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J299" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K299" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L299" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M299" s="5" t="n">
-        <v>0</v>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L299" s="5" t="n"/>
+      <c r="M299" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="N299" s="5" t="n">
-        <v>18.04</v>
+        <v>1</v>
+      </c>
+      <c r="O299" s="5" t="n">
+        <v>13.57</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B300" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C300" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D300" s="5" t="inlineStr">
@@ -19275,57 +19579,58 @@
       </c>
       <c r="E300" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F300" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G300" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H300" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I300" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J300" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K300" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L300" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M300" s="5" t="n">
-        <v>0</v>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L300" s="5" t="n"/>
+      <c r="M300" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="N300" s="5" t="n">
-        <v>5.74</v>
+        <v>1</v>
+      </c>
+      <c r="O300" s="5" t="n">
+        <v>10.24</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B301" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D301" s="5" t="inlineStr">
@@ -19340,57 +19645,58 @@
       </c>
       <c r="F301" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I301" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J301" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K301" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L301" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M301" s="5" t="n">
-        <v>0</v>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L301" s="5" t="n"/>
+      <c r="M301" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="N301" s="5" t="n">
-        <v>4.9</v>
+        <v>1</v>
+      </c>
+      <c r="O301" s="5" t="n">
+        <v>10.42</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_005</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B302" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C302" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D302" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E302" s="5" t="inlineStr">
@@ -19405,12 +19711,12 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I302" s="5" t="b">
@@ -19424,33 +19730,34 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L302" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M302" s="5" t="n">
+      <c r="L302" s="5" t="n"/>
+      <c r="M302" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N302" s="5" t="n">
-        <v>22.65</v>
+        <v>1</v>
+      </c>
+      <c r="O302" s="5" t="n">
+        <v>3.81</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_005</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B303" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C303" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E303" s="5" t="inlineStr">
@@ -19465,12 +19772,12 @@
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H303" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I303" s="5" t="b">
@@ -19484,33 +19791,34 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L303" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M303" s="5" t="n">
+      <c r="L303" s="5" t="n"/>
+      <c r="M303" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N303" s="5" t="n">
-        <v>23.76</v>
+        <v>1</v>
+      </c>
+      <c r="O303" s="5" t="n">
+        <v>5.16</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_005</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B304" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C304" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D304" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E304" s="5" t="inlineStr">
@@ -19525,12 +19833,12 @@
       </c>
       <c r="G304" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H304" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I304" s="5" t="b">
@@ -19544,33 +19852,34 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L304" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M304" s="5" t="n">
-        <v>1</v>
+      <c r="L304" s="5" t="n"/>
+      <c r="M304" s="5" t="b">
+        <v>0</v>
       </c>
       <c r="N304" s="5" t="n">
-        <v>22.97</v>
+        <v>0</v>
+      </c>
+      <c r="O304" s="5" t="n">
+        <v>13.07</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_009</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B305" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C305" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D305" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E305" s="5" t="inlineStr">
@@ -19585,12 +19894,12 @@
       </c>
       <c r="G305" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H305" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I305" s="5" t="b">
@@ -19604,33 +19913,34 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L305" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M305" s="5" t="n">
+      <c r="L305" s="5" t="n"/>
+      <c r="M305" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N305" s="5" t="n">
-        <v>19.47</v>
+        <v>1</v>
+      </c>
+      <c r="O305" s="5" t="n">
+        <v>7.85</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_009</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B306" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C306" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D306" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E306" s="5" t="inlineStr">
@@ -19645,12 +19955,12 @@
       </c>
       <c r="G306" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H306" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I306" s="5" t="b">
@@ -19664,33 +19974,34 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L306" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M306" s="5" t="n">
+      <c r="L306" s="5" t="n"/>
+      <c r="M306" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N306" s="5" t="n">
-        <v>26.07</v>
+        <v>1</v>
+      </c>
+      <c r="O306" s="5" t="n">
+        <v>8.73</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_009</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B307" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C307" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D307" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E307" s="5" t="inlineStr">
@@ -19705,12 +20016,12 @@
       </c>
       <c r="G307" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H307" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I307" s="5" t="b">
@@ -19724,33 +20035,34 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L307" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M307" s="5" t="n">
+      <c r="L307" s="5" t="n"/>
+      <c r="M307" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N307" s="5" t="n">
-        <v>23.25</v>
+        <v>1</v>
+      </c>
+      <c r="O307" s="5" t="n">
+        <v>4.92</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_001</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B308" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C308" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D308" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E308" s="5" t="inlineStr">
@@ -19765,52 +20077,53 @@
       </c>
       <c r="G308" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H308" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I308" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J308" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K308" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L308" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M308" s="5" t="n">
-        <v>0</v>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L308" s="5" t="n"/>
+      <c r="M308" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="N308" s="5" t="n">
-        <v>12.69</v>
+        <v>1</v>
+      </c>
+      <c r="O308" s="5" t="n">
+        <v>18.94</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_001</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B309" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C309" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D309" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E309" s="5" t="inlineStr">
@@ -19825,52 +20138,53 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I309" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J309" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K309" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L309" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M309" s="5" t="n">
-        <v>0</v>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L309" s="5" t="n"/>
+      <c r="M309" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="N309" s="5" t="n">
-        <v>9.210000000000001</v>
+        <v>1</v>
+      </c>
+      <c r="O309" s="5" t="n">
+        <v>21.38</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_001</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B310" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C310" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D310" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E310" s="5" t="inlineStr">
@@ -19885,14 +20199,14 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
+          <t>VARIES</t>
+        </is>
+      </c>
+      <c r="H310" s="5" t="inlineStr">
+        <is>
           <t>template</t>
         </is>
       </c>
-      <c r="H310" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
       <c r="I310" s="5" t="b">
         <v>1</v>
       </c>
@@ -19904,33 +20218,34 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L310" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M310" s="5" t="n">
-        <v>1</v>
+      <c r="L310" s="5" t="n"/>
+      <c r="M310" s="5" t="b">
+        <v>0</v>
       </c>
       <c r="N310" s="5" t="n">
-        <v>8.98</v>
+        <v>0</v>
+      </c>
+      <c r="O310" s="5" t="n">
+        <v>14.78</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B311" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C311" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D311" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E311" s="5" t="inlineStr">
@@ -19945,12 +20260,12 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I311" s="5" t="b">
@@ -19964,33 +20279,34 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L311" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M311" s="5" t="n">
+      <c r="L311" s="5" t="n"/>
+      <c r="M311" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N311" s="5" t="n">
-        <v>13.57</v>
+        <v>1</v>
+      </c>
+      <c r="O311" s="5" t="n">
+        <v>7.87</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B312" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C312" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D312" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E312" s="5" t="inlineStr">
@@ -20005,12 +20321,12 @@
       </c>
       <c r="G312" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H312" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I312" s="5" t="b">
@@ -20024,33 +20340,34 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L312" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M312" s="5" t="n">
+      <c r="L312" s="5" t="n"/>
+      <c r="M312" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N312" s="5" t="n">
-        <v>10.24</v>
+        <v>1</v>
+      </c>
+      <c r="O312" s="5" t="n">
+        <v>9.029999999999999</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B313" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C313" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E313" s="5" t="inlineStr">
@@ -20065,12 +20382,12 @@
       </c>
       <c r="G313" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H313" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I313" s="5" t="b">
@@ -20084,28 +20401,29 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L313" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M313" s="5" t="n">
+      <c r="L313" s="5" t="n"/>
+      <c r="M313" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N313" s="5" t="n">
-        <v>10.42</v>
+        <v>1</v>
+      </c>
+      <c r="O313" s="5" t="n">
+        <v>5.17</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B314" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C314" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D314" s="5" t="inlineStr">
@@ -20125,12 +20443,12 @@
       </c>
       <c r="G314" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H314" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I314" s="5" t="b">
@@ -20144,28 +20462,29 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L314" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M314" s="5" t="n">
+      <c r="L314" s="5" t="n"/>
+      <c r="M314" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N314" s="5" t="n">
-        <v>3.81</v>
+        <v>1</v>
+      </c>
+      <c r="O314" s="5" t="n">
+        <v>19.5</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B315" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C315" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D315" s="5" t="inlineStr">
@@ -20175,22 +20494,22 @@
       </c>
       <c r="E315" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F315" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G315" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H315" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I315" s="5" t="b">
@@ -20204,28 +20523,29 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L315" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M315" s="5" t="n">
+      <c r="L315" s="5" t="n"/>
+      <c r="M315" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N315" s="5" t="n">
-        <v>5.16</v>
+        <v>1</v>
+      </c>
+      <c r="O315" s="5" t="n">
+        <v>16.45</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B316" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C316" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D316" s="5" t="inlineStr">
@@ -20235,22 +20555,22 @@
       </c>
       <c r="E316" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F316" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G316" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H316" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I316" s="5" t="b">
@@ -20264,38 +20584,39 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L316" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M316" s="5" t="n">
-        <v>0</v>
+      <c r="L316" s="5" t="n"/>
+      <c r="M316" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="N316" s="5" t="n">
-        <v>13.07</v>
+        <v>1</v>
+      </c>
+      <c r="O316" s="5" t="n">
+        <v>16.76</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B317" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C317" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D317" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E317" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F317" s="5" t="inlineStr">
@@ -20305,12 +20626,12 @@
       </c>
       <c r="G317" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H317" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I317" s="5" t="b">
@@ -20324,33 +20645,34 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L317" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M317" s="5" t="n">
+      <c r="L317" s="5" t="n"/>
+      <c r="M317" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N317" s="5" t="n">
-        <v>7.85</v>
+        <v>1</v>
+      </c>
+      <c r="O317" s="5" t="n">
+        <v>20.52</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B318" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C318" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D318" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E318" s="5" t="inlineStr">
@@ -20360,17 +20682,17 @@
       </c>
       <c r="F318" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G318" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H318" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I318" s="5" t="b">
@@ -20384,53 +20706,54 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L318" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M318" s="5" t="n">
+      <c r="L318" s="5" t="n"/>
+      <c r="M318" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N318" s="5" t="n">
-        <v>8.73</v>
+        <v>1</v>
+      </c>
+      <c r="O318" s="5" t="n">
+        <v>18.23</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B319" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C319" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E319" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F319" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G319" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H319" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I319" s="5" t="b">
@@ -20444,38 +20767,39 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L319" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M319" s="5" t="n">
+      <c r="L319" s="5" t="n"/>
+      <c r="M319" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N319" s="5" t="n">
-        <v>4.92</v>
+        <v>1</v>
+      </c>
+      <c r="O319" s="5" t="n">
+        <v>18.17</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B320" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C320" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D320" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E320" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F320" s="5" t="inlineStr">
@@ -20485,7 +20809,7 @@
       </c>
       <c r="G320" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H320" s="5" t="inlineStr">
@@ -20504,48 +20828,49 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L320" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M320" s="5" t="n">
+      <c r="L320" s="5" t="n"/>
+      <c r="M320" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N320" s="5" t="n">
-        <v>18.94</v>
+        <v>1</v>
+      </c>
+      <c r="O320" s="5" t="n">
+        <v>20.49</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B321" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C321" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D321" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E321" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F321" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G321" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H321" s="5" t="inlineStr">
@@ -20564,33 +20889,34 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L321" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M321" s="5" t="n">
+      <c r="L321" s="5" t="n"/>
+      <c r="M321" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N321" s="5" t="n">
-        <v>21.38</v>
+        <v>1</v>
+      </c>
+      <c r="O321" s="5" t="n">
+        <v>17.83</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B322" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C322" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D322" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E322" s="5" t="inlineStr">
@@ -20600,17 +20926,17 @@
       </c>
       <c r="F322" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G322" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H322" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I322" s="5" t="b">
@@ -20624,33 +20950,34 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L322" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M322" s="5" t="n">
-        <v>0</v>
+      <c r="L322" s="5" t="n"/>
+      <c r="M322" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="N322" s="5" t="n">
-        <v>14.78</v>
+        <v>1</v>
+      </c>
+      <c r="O322" s="5" t="n">
+        <v>17.58</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>count_kg1_001</t>
         </is>
       </c>
       <c r="B323" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C323" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E323" s="5" t="inlineStr">
@@ -20665,12 +20992,12 @@
       </c>
       <c r="G323" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H323" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I323" s="5" t="b">
@@ -20684,33 +21011,34 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L323" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M323" s="5" t="n">
+      <c r="L323" s="5" t="n"/>
+      <c r="M323" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N323" s="5" t="n">
-        <v>7.87</v>
+        <v>1</v>
+      </c>
+      <c r="O323" s="5" t="n">
+        <v>9.44</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>count_kg1_001</t>
         </is>
       </c>
       <c r="B324" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C324" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D324" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E324" s="5" t="inlineStr">
@@ -20725,12 +21053,12 @@
       </c>
       <c r="G324" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H324" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I324" s="5" t="b">
@@ -20744,33 +21072,34 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L324" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M324" s="5" t="n">
+      <c r="L324" s="5" t="n"/>
+      <c r="M324" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N324" s="5" t="n">
-        <v>9.029999999999999</v>
+        <v>1</v>
+      </c>
+      <c r="O324" s="5" t="n">
+        <v>9.07</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>count_kg1_001</t>
         </is>
       </c>
       <c r="B325" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C325" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E325" s="5" t="inlineStr">
@@ -20785,12 +21114,12 @@
       </c>
       <c r="G325" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H325" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I325" s="5" t="b">
@@ -20804,18 +21133,19 @@
           <t>success</t>
         </is>
       </c>
-      <c r="L325" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M325" s="5" t="n">
+      <c r="L325" s="5" t="n"/>
+      <c r="M325" s="5" t="b">
         <v>1</v>
       </c>
       <c r="N325" s="5" t="n">
-        <v>5.17</v>
+        <v>1</v>
+      </c>
+      <c r="O325" s="5" t="n">
+        <v>8.92</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N325"/>
+  <autoFilter ref="A1:O325"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/NL2SPARQL_Evaluation_Results.xlsx
+++ b/NL2SPARQL_Evaluation_Results.xlsx
@@ -12688,7 +12688,7 @@
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>open_kg_001</t>
+          <t>open_kg_002</t>
         </is>
       </c>
       <c r="B185" s="5" t="n">
@@ -12732,20 +12732,24 @@
       </c>
       <c r="K185" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L185" s="5" t="n"/>
-      <c r="M185" s="5" t="n"/>
-      <c r="N185" s="5" t="n"/>
+      <c r="M185" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N185" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O185" s="5" t="n">
-        <v>24.09</v>
+        <v>31.98</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
         <is>
-          <t>open_kg_001</t>
+          <t>open_kg_002</t>
         </is>
       </c>
       <c r="B186" s="5" t="n">
@@ -12793,16 +12797,20 @@
         </is>
       </c>
       <c r="L186" s="5" t="n"/>
-      <c r="M186" s="5" t="n"/>
-      <c r="N186" s="5" t="n"/>
+      <c r="M186" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N186" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O186" s="5" t="n">
-        <v>23.4</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>open_kg_001</t>
+          <t>open_kg_002</t>
         </is>
       </c>
       <c r="B187" s="5" t="n">
@@ -12850,29 +12858,33 @@
         </is>
       </c>
       <c r="L187" s="5" t="n"/>
-      <c r="M187" s="5" t="n"/>
-      <c r="N187" s="5" t="n"/>
+      <c r="M187" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N187" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O187" s="5" t="n">
-        <v>22.25</v>
+        <v>28.32</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
         <is>
-          <t>open_kg_002</t>
+          <t>count_kg1_002</t>
         </is>
       </c>
       <c r="B188" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
@@ -12887,12 +12899,12 @@
       </c>
       <c r="G188" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H188" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I188" s="5" t="b">
@@ -12914,26 +12926,26 @@
         <v>1</v>
       </c>
       <c r="O188" s="5" t="n">
-        <v>31.98</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>open_kg_002</t>
+          <t>count_kg1_002</t>
         </is>
       </c>
       <c r="B189" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E189" s="5" t="inlineStr">
@@ -12948,12 +12960,12 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I189" s="5" t="b">
@@ -12975,26 +12987,26 @@
         <v>1</v>
       </c>
       <c r="O189" s="5" t="n">
-        <v>31.6</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
         <is>
-          <t>open_kg_002</t>
+          <t>count_kg1_002</t>
         </is>
       </c>
       <c r="B190" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
@@ -13009,12 +13021,12 @@
       </c>
       <c r="G190" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H190" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I190" s="5" t="b">
@@ -13036,26 +13048,26 @@
         <v>1</v>
       </c>
       <c r="O190" s="5" t="n">
-        <v>28.32</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>open_kg_003</t>
+          <t>count_kg1_003</t>
         </is>
       </c>
       <c r="B191" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E191" s="5" t="inlineStr">
@@ -13070,12 +13082,12 @@
       </c>
       <c r="G191" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H191" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I191" s="5" t="b">
@@ -13097,26 +13109,26 @@
         <v>1</v>
       </c>
       <c r="O191" s="5" t="n">
-        <v>16.66</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
         <is>
-          <t>open_kg_003</t>
+          <t>count_kg1_003</t>
         </is>
       </c>
       <c r="B192" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
@@ -13131,12 +13143,12 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I192" s="5" t="b">
@@ -13158,26 +13170,26 @@
         <v>1</v>
       </c>
       <c r="O192" s="5" t="n">
-        <v>16.45</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>open_kg_003</t>
+          <t>count_kg1_003</t>
         </is>
       </c>
       <c r="B193" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E193" s="5" t="inlineStr">
@@ -13192,12 +13204,12 @@
       </c>
       <c r="G193" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H193" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I193" s="5" t="b">
@@ -13208,37 +13220,37 @@
       </c>
       <c r="K193" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L193" s="5" t="n"/>
       <c r="M193" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N193" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O193" s="5" t="n">
-        <v>21.42</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
         <is>
-          <t>open_kg_004</t>
+          <t>filter_numeric_kg1_001</t>
         </is>
       </c>
       <c r="B194" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
@@ -13253,12 +13265,12 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I194" s="5" t="b">
@@ -13274,32 +13286,32 @@
       </c>
       <c r="L194" s="5" t="n"/>
       <c r="M194" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N194" s="5" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="O194" s="5" t="n">
-        <v>30.16</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>open_kg_004</t>
+          <t>filter_numeric_kg1_001</t>
         </is>
       </c>
       <c r="B195" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E195" s="5" t="inlineStr">
@@ -13314,12 +13326,12 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I195" s="5" t="b">
@@ -13335,32 +13347,32 @@
       </c>
       <c r="L195" s="5" t="n"/>
       <c r="M195" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N195" s="5" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="O195" s="5" t="n">
-        <v>26.96</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
         <is>
-          <t>open_kg_004</t>
+          <t>filter_numeric_kg1_001</t>
         </is>
       </c>
       <c r="B196" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
@@ -13375,12 +13387,12 @@
       </c>
       <c r="G196" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H196" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I196" s="5" t="b">
@@ -13396,32 +13408,32 @@
       </c>
       <c r="L196" s="5" t="n"/>
       <c r="M196" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N196" s="5" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="O196" s="5" t="n">
-        <v>26.8</v>
+        <v>7.61</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>open_kg_005</t>
+          <t>filter_numeric_kg1_002</t>
         </is>
       </c>
       <c r="B197" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E197" s="5" t="inlineStr">
@@ -13436,7 +13448,7 @@
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H197" s="5" t="inlineStr">
@@ -13445,40 +13457,44 @@
         </is>
       </c>
       <c r="I197" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J197" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K197" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L197" s="5" t="n"/>
-      <c r="M197" s="5" t="n"/>
-      <c r="N197" s="5" t="n"/>
+      <c r="M197" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N197" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O197" s="5" t="n">
-        <v>9.82</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
         <is>
-          <t>open_kg_005</t>
+          <t>filter_numeric_kg1_002</t>
         </is>
       </c>
       <c r="B198" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D198" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
@@ -13493,7 +13509,7 @@
       </c>
       <c r="G198" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H198" s="5" t="inlineStr">
@@ -13502,40 +13518,44 @@
         </is>
       </c>
       <c r="I198" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J198" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K198" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L198" s="5" t="n"/>
-      <c r="M198" s="5" t="n"/>
-      <c r="N198" s="5" t="n"/>
+      <c r="M198" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N198" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O198" s="5" t="n">
-        <v>11.1</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
         <is>
-          <t>open_kg_005</t>
+          <t>filter_numeric_kg1_002</t>
         </is>
       </c>
       <c r="B199" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
@@ -13550,12 +13570,12 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I199" s="5" t="b">
@@ -13570,29 +13590,33 @@
         </is>
       </c>
       <c r="L199" s="5" t="n"/>
-      <c r="M199" s="5" t="n"/>
-      <c r="N199" s="5" t="n"/>
+      <c r="M199" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N199" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O199" s="5" t="n">
-        <v>36.26</v>
+        <v>11.14</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
         <is>
-          <t>open_kg_006</t>
+          <t>filter_numeric_kg1_003</t>
         </is>
       </c>
       <c r="B200" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
@@ -13607,12 +13631,12 @@
       </c>
       <c r="G200" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H200" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I200" s="5" t="b">
@@ -13623,33 +13647,37 @@
       </c>
       <c r="K200" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L200" s="5" t="n"/>
-      <c r="M200" s="5" t="n"/>
-      <c r="N200" s="5" t="n"/>
+      <c r="M200" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N200" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O200" s="5" t="n">
-        <v>22.57</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>open_kg_006</t>
+          <t>filter_numeric_kg1_003</t>
         </is>
       </c>
       <c r="B201" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C201" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
@@ -13664,12 +13692,12 @@
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H201" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I201" s="5" t="b">
@@ -13684,29 +13712,33 @@
         </is>
       </c>
       <c r="L201" s="5" t="n"/>
-      <c r="M201" s="5" t="n"/>
-      <c r="N201" s="5" t="n"/>
+      <c r="M201" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N201" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O201" s="5" t="n">
-        <v>21.96</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
         <is>
-          <t>open_kg_006</t>
+          <t>filter_numeric_kg1_003</t>
         </is>
       </c>
       <c r="B202" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="D202" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
@@ -13721,12 +13753,12 @@
       </c>
       <c r="G202" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H202" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I202" s="5" t="b">
@@ -13741,16 +13773,20 @@
         </is>
       </c>
       <c r="L202" s="5" t="n"/>
-      <c r="M202" s="5" t="n"/>
-      <c r="N202" s="5" t="n"/>
+      <c r="M202" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N202" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O202" s="5" t="n">
-        <v>21.9</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_002</t>
+          <t>filter_numeric_kg2_001</t>
         </is>
       </c>
       <c r="B203" s="5" t="n">
@@ -13758,12 +13794,12 @@
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
@@ -13805,13 +13841,13 @@
         <v>1</v>
       </c>
       <c r="O203" s="5" t="n">
-        <v>10.08</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_002</t>
+          <t>filter_numeric_kg2_001</t>
         </is>
       </c>
       <c r="B204" s="5" t="n">
@@ -13819,12 +13855,12 @@
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
@@ -13866,13 +13902,13 @@
         <v>1</v>
       </c>
       <c r="O204" s="5" t="n">
-        <v>7.59</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_002</t>
+          <t>filter_numeric_kg2_001</t>
         </is>
       </c>
       <c r="B205" s="5" t="n">
@@ -13880,12 +13916,12 @@
       </c>
       <c r="C205" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr">
@@ -13927,13 +13963,13 @@
         <v>1</v>
       </c>
       <c r="O205" s="5" t="n">
-        <v>7.26</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_003</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B206" s="5" t="n">
@@ -13941,12 +13977,12 @@
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
@@ -13982,19 +14018,19 @@
       </c>
       <c r="L206" s="5" t="n"/>
       <c r="M206" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N206" s="5" t="n">
-        <v>1</v>
+        <v>0.7692</v>
       </c>
       <c r="O206" s="5" t="n">
-        <v>7.41</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_003</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B207" s="5" t="n">
@@ -14002,12 +14038,12 @@
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E207" s="5" t="inlineStr">
@@ -14043,19 +14079,19 @@
       </c>
       <c r="L207" s="5" t="n"/>
       <c r="M207" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N207" s="5" t="n">
-        <v>1</v>
+        <v>0.7692</v>
       </c>
       <c r="O207" s="5" t="n">
-        <v>7.27</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_003</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B208" s="5" t="n">
@@ -14063,12 +14099,12 @@
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
@@ -14104,19 +14140,19 @@
       </c>
       <c r="L208" s="5" t="n"/>
       <c r="M208" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N208" s="5" t="n">
-        <v>1</v>
+        <v>0.7692</v>
       </c>
       <c r="O208" s="5" t="n">
-        <v>7.27</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_001</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B209" s="5" t="n">
@@ -14124,12 +14160,12 @@
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E209" s="5" t="inlineStr">
@@ -14171,13 +14207,13 @@
         <v>1</v>
       </c>
       <c r="O209" s="5" t="n">
-        <v>7.64</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_001</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B210" s="5" t="n">
@@ -14185,12 +14221,12 @@
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
@@ -14232,13 +14268,13 @@
         <v>1</v>
       </c>
       <c r="O210" s="5" t="n">
-        <v>7.65</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_001</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B211" s="5" t="n">
@@ -14246,12 +14282,12 @@
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E211" s="5" t="inlineStr">
@@ -14293,13 +14329,13 @@
         <v>1</v>
       </c>
       <c r="O211" s="5" t="n">
-        <v>7.61</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_002</t>
+          <t>filter_string_kg2_001</t>
         </is>
       </c>
       <c r="B212" s="5" t="n">
@@ -14307,12 +14343,12 @@
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
@@ -14354,13 +14390,13 @@
         <v>1</v>
       </c>
       <c r="O212" s="5" t="n">
-        <v>8.18</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_002</t>
+          <t>filter_string_kg2_001</t>
         </is>
       </c>
       <c r="B213" s="5" t="n">
@@ -14368,12 +14404,12 @@
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E213" s="5" t="inlineStr">
@@ -14415,13 +14451,13 @@
         <v>1</v>
       </c>
       <c r="O213" s="5" t="n">
-        <v>11.49</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_002</t>
+          <t>filter_string_kg2_001</t>
         </is>
       </c>
       <c r="B214" s="5" t="n">
@@ -14429,12 +14465,12 @@
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
@@ -14476,13 +14512,13 @@
         <v>1</v>
       </c>
       <c r="O214" s="5" t="n">
-        <v>11.14</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_003</t>
+          <t>filter_string_kg2_002</t>
         </is>
       </c>
       <c r="B215" s="5" t="n">
@@ -14490,12 +14526,12 @@
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E215" s="5" t="inlineStr">
@@ -14530,20 +14566,16 @@
         </is>
       </c>
       <c r="L215" s="5" t="n"/>
-      <c r="M215" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N215" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M215" s="5" t="n"/>
+      <c r="N215" s="5" t="n"/>
       <c r="O215" s="5" t="n">
-        <v>7.94</v>
+        <v>14.52</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_003</t>
+          <t>filter_string_kg2_002</t>
         </is>
       </c>
       <c r="B216" s="5" t="n">
@@ -14551,12 +14583,12 @@
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
@@ -14591,20 +14623,16 @@
         </is>
       </c>
       <c r="L216" s="5" t="n"/>
-      <c r="M216" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N216" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M216" s="5" t="n"/>
+      <c r="N216" s="5" t="n"/>
       <c r="O216" s="5" t="n">
-        <v>7.93</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1_003</t>
+          <t>filter_string_kg2_002</t>
         </is>
       </c>
       <c r="B217" s="5" t="n">
@@ -14612,12 +14640,12 @@
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E217" s="5" t="inlineStr">
@@ -14652,20 +14680,16 @@
         </is>
       </c>
       <c r="L217" s="5" t="n"/>
-      <c r="M217" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N217" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M217" s="5" t="n"/>
+      <c r="N217" s="5" t="n"/>
       <c r="O217" s="5" t="n">
-        <v>7.63</v>
+        <v>10.88</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_001</t>
+          <t>ranking_kg2_001</t>
         </is>
       </c>
       <c r="B218" s="5" t="n">
@@ -14673,7 +14697,7 @@
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D218" s="5" t="inlineStr">
@@ -14720,13 +14744,13 @@
         <v>1</v>
       </c>
       <c r="O218" s="5" t="n">
-        <v>9.98</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_001</t>
+          <t>ranking_kg2_001</t>
         </is>
       </c>
       <c r="B219" s="5" t="n">
@@ -14734,7 +14758,7 @@
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D219" s="5" t="inlineStr">
@@ -14781,13 +14805,13 @@
         <v>1</v>
       </c>
       <c r="O219" s="5" t="n">
-        <v>12.4</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_001</t>
+          <t>ranking_kg2_001</t>
         </is>
       </c>
       <c r="B220" s="5" t="n">
@@ -14795,7 +14819,7 @@
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D220" s="5" t="inlineStr">
@@ -14842,13 +14866,13 @@
         <v>1</v>
       </c>
       <c r="O220" s="5" t="n">
-        <v>9.48</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>ranking_kg2_002</t>
         </is>
       </c>
       <c r="B221" s="5" t="n">
@@ -14856,7 +14880,7 @@
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D221" s="5" t="inlineStr">
@@ -14897,19 +14921,19 @@
       </c>
       <c r="L221" s="5" t="n"/>
       <c r="M221" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N221" s="5" t="n">
-        <v>0.7692</v>
+        <v>1</v>
       </c>
       <c r="O221" s="5" t="n">
-        <v>7.51</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>ranking_kg2_002</t>
         </is>
       </c>
       <c r="B222" s="5" t="n">
@@ -14917,7 +14941,7 @@
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
@@ -14958,19 +14982,19 @@
       </c>
       <c r="L222" s="5" t="n"/>
       <c r="M222" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N222" s="5" t="n">
-        <v>0.7692</v>
+        <v>1</v>
       </c>
       <c r="O222" s="5" t="n">
-        <v>8.029999999999999</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>ranking_kg2_002</t>
         </is>
       </c>
       <c r="B223" s="5" t="n">
@@ -14978,7 +15002,7 @@
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D223" s="5" t="inlineStr">
@@ -15019,19 +15043,19 @@
       </c>
       <c r="L223" s="5" t="n"/>
       <c r="M223" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N223" s="5" t="n">
-        <v>0.7692</v>
+        <v>1</v>
       </c>
       <c r="O223" s="5" t="n">
-        <v>8.640000000000001</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>ranking_kg2_003</t>
         </is>
       </c>
       <c r="B224" s="5" t="n">
@@ -15039,7 +15063,7 @@
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D224" s="5" t="inlineStr">
@@ -15086,13 +15110,13 @@
         <v>1</v>
       </c>
       <c r="O224" s="5" t="n">
-        <v>9.23</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>ranking_kg2_003</t>
         </is>
       </c>
       <c r="B225" s="5" t="n">
@@ -15100,7 +15124,7 @@
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D225" s="5" t="inlineStr">
@@ -15147,13 +15171,13 @@
         <v>1</v>
       </c>
       <c r="O225" s="5" t="n">
-        <v>9.27</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>ranking_kg2_003</t>
         </is>
       </c>
       <c r="B226" s="5" t="n">
@@ -15161,7 +15185,7 @@
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D226" s="5" t="inlineStr">
@@ -15208,13 +15232,13 @@
         <v>1</v>
       </c>
       <c r="O226" s="5" t="n">
-        <v>9.970000000000001</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_001</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B227" s="5" t="n">
@@ -15222,7 +15246,7 @@
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D227" s="5" t="inlineStr">
@@ -15269,13 +15293,13 @@
         <v>1</v>
       </c>
       <c r="O227" s="5" t="n">
-        <v>8.59</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_001</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B228" s="5" t="n">
@@ -15283,7 +15307,7 @@
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D228" s="5" t="inlineStr">
@@ -15330,13 +15354,13 @@
         <v>1</v>
       </c>
       <c r="O228" s="5" t="n">
-        <v>8.460000000000001</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_001</t>
+          <t>compare_two_airports_001</t>
         </is>
       </c>
       <c r="B229" s="5" t="n">
@@ -15344,7 +15368,7 @@
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D229" s="5" t="inlineStr">
@@ -15391,13 +15415,13 @@
         <v>1</v>
       </c>
       <c r="O229" s="5" t="n">
-        <v>8.859999999999999</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_002</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B230" s="5" t="n">
@@ -15405,7 +15429,7 @@
       </c>
       <c r="C230" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D230" s="5" t="inlineStr">
@@ -15445,16 +15469,20 @@
         </is>
       </c>
       <c r="L230" s="5" t="n"/>
-      <c r="M230" s="5" t="n"/>
-      <c r="N230" s="5" t="n"/>
+      <c r="M230" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N230" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O230" s="5" t="n">
-        <v>14.52</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_002</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B231" s="5" t="n">
@@ -15462,7 +15490,7 @@
       </c>
       <c r="C231" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D231" s="5" t="inlineStr">
@@ -15502,16 +15530,20 @@
         </is>
       </c>
       <c r="L231" s="5" t="n"/>
-      <c r="M231" s="5" t="n"/>
-      <c r="N231" s="5" t="n"/>
+      <c r="M231" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N231" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O231" s="5" t="n">
-        <v>11.11</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_002</t>
+          <t>compare_two_airports_003</t>
         </is>
       </c>
       <c r="B232" s="5" t="n">
@@ -15519,7 +15551,7 @@
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D232" s="5" t="inlineStr">
@@ -15559,29 +15591,33 @@
         </is>
       </c>
       <c r="L232" s="5" t="n"/>
-      <c r="M232" s="5" t="n"/>
-      <c r="N232" s="5" t="n"/>
+      <c r="M232" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N232" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O232" s="5" t="n">
-        <v>10.88</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_001</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B233" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E233" s="5" t="inlineStr">
@@ -15596,12 +15632,12 @@
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H233" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I233" s="5" t="b">
@@ -15623,26 +15659,26 @@
         <v>1</v>
       </c>
       <c r="O233" s="5" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_001</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B234" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C234" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
@@ -15657,12 +15693,12 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I234" s="5" t="b">
@@ -15684,26 +15720,26 @@
         <v>1</v>
       </c>
       <c r="O234" s="5" t="n">
-        <v>6.82</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_001</t>
+          <t>ask_query_001</t>
         </is>
       </c>
       <c r="B235" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E235" s="5" t="inlineStr">
@@ -15718,12 +15754,12 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I235" s="5" t="b">
@@ -15745,26 +15781,26 @@
         <v>1</v>
       </c>
       <c r="O235" s="5" t="n">
-        <v>6.85</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_002</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B236" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C236" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E236" s="5" t="inlineStr">
@@ -15779,12 +15815,12 @@
       </c>
       <c r="G236" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H236" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I236" s="5" t="b">
@@ -15806,26 +15842,26 @@
         <v>1</v>
       </c>
       <c r="O236" s="5" t="n">
-        <v>6.61</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_002</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B237" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E237" s="5" t="inlineStr">
@@ -15840,19 +15876,19 @@
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H237" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I237" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J237" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K237" s="5" t="inlineStr">
         <is>
@@ -15860,33 +15896,29 @@
         </is>
       </c>
       <c r="L237" s="5" t="n"/>
-      <c r="M237" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N237" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M237" s="5" t="n"/>
+      <c r="N237" s="5" t="n"/>
       <c r="O237" s="5" t="n">
-        <v>6.82</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_002</t>
+          <t>ask_query_003</t>
         </is>
       </c>
       <c r="B238" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C238" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
@@ -15901,12 +15933,12 @@
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H238" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I238" s="5" t="b">
@@ -15928,26 +15960,26 @@
         <v>1</v>
       </c>
       <c r="O238" s="5" t="n">
-        <v>6.69</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_003</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B239" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E239" s="5" t="inlineStr">
@@ -15962,12 +15994,12 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I239" s="5" t="b">
@@ -15989,26 +16021,26 @@
         <v>1</v>
       </c>
       <c r="O239" s="5" t="n">
-        <v>6.95</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_003</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B240" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C240" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E240" s="5" t="inlineStr">
@@ -16023,12 +16055,12 @@
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H240" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I240" s="5" t="b">
@@ -16050,26 +16082,26 @@
         <v>1</v>
       </c>
       <c r="O240" s="5" t="n">
-        <v>6.88</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_003</t>
+          <t>ask_query_004</t>
         </is>
       </c>
       <c r="B241" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E241" s="5" t="inlineStr">
@@ -16084,12 +16116,12 @@
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H241" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I241" s="5" t="b">
@@ -16111,26 +16143,26 @@
         <v>1</v>
       </c>
       <c r="O241" s="5" t="n">
-        <v>6.92</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B242" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E242" s="5" t="inlineStr">
@@ -16145,12 +16177,12 @@
       </c>
       <c r="G242" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H242" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I242" s="5" t="b">
@@ -16172,26 +16204,26 @@
         <v>1</v>
       </c>
       <c r="O242" s="5" t="n">
-        <v>4.34</v>
+        <v>16.49</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B243" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E243" s="5" t="inlineStr">
@@ -16206,12 +16238,12 @@
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H243" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I243" s="5" t="b">
@@ -16233,26 +16265,26 @@
         <v>1</v>
       </c>
       <c r="O243" s="5" t="n">
-        <v>3.62</v>
+        <v>17.18</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_001</t>
+          <t>typo_fuzzy_001</t>
         </is>
       </c>
       <c r="B244" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E244" s="5" t="inlineStr">
@@ -16267,12 +16299,12 @@
       </c>
       <c r="G244" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H244" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I244" s="5" t="b">
@@ -16294,26 +16326,26 @@
         <v>1</v>
       </c>
       <c r="O244" s="5" t="n">
-        <v>4.4</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B245" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C245" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E245" s="5" t="inlineStr">
@@ -16328,12 +16360,12 @@
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H245" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I245" s="5" t="b">
@@ -16355,26 +16387,26 @@
         <v>1</v>
       </c>
       <c r="O245" s="5" t="n">
-        <v>4.17</v>
+        <v>26.92</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B246" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C246" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E246" s="5" t="inlineStr">
@@ -16389,12 +16421,12 @@
       </c>
       <c r="G246" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H246" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I246" s="5" t="b">
@@ -16416,26 +16448,26 @@
         <v>1</v>
       </c>
       <c r="O246" s="5" t="n">
-        <v>3.67</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_003</t>
+          <t>typo_fuzzy_002</t>
         </is>
       </c>
       <c r="B247" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C247" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>typo_fuzzy</t>
         </is>
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E247" s="5" t="inlineStr">
@@ -16450,12 +16482,12 @@
       </c>
       <c r="G247" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H247" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I247" s="5" t="b">
@@ -16477,13 +16509,13 @@
         <v>1</v>
       </c>
       <c r="O247" s="5" t="n">
-        <v>3.61</v>
+        <v>19.47</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B248" s="5" t="n">
@@ -16491,11 +16523,13 @@
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D248" s="5" t="n">
-        <v/>
+          <t>typo_fuzzy</t>
+        </is>
+      </c>
+      <c r="D248" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E248" s="5" t="inlineStr">
         <is>
@@ -16509,19 +16543,19 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I248" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J248" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K248" s="5" t="inlineStr">
         <is>
@@ -16529,16 +16563,20 @@
         </is>
       </c>
       <c r="L248" s="5" t="n"/>
-      <c r="M248" s="5" t="n"/>
-      <c r="N248" s="5" t="n"/>
+      <c r="M248" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N248" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O248" s="5" t="n">
-        <v>3.89</v>
+        <v>21.28</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B249" s="5" t="n">
@@ -16546,11 +16584,13 @@
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D249" s="5" t="n">
-        <v/>
+          <t>typo_fuzzy</t>
+        </is>
+      </c>
+      <c r="D249" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E249" s="5" t="inlineStr">
         <is>
@@ -16564,19 +16604,19 @@
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H249" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I249" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J249" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K249" s="5" t="inlineStr">
         <is>
@@ -16584,16 +16624,20 @@
         </is>
       </c>
       <c r="L249" s="5" t="n"/>
-      <c r="M249" s="5" t="n"/>
-      <c r="N249" s="5" t="n"/>
+      <c r="M249" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N249" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O249" s="5" t="n">
-        <v>3.34</v>
+        <v>22.32</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>typo_fuzzy_003</t>
         </is>
       </c>
       <c r="B250" s="5" t="n">
@@ -16601,11 +16645,13 @@
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D250" s="5" t="n">
-        <v/>
+          <t>typo_fuzzy</t>
+        </is>
+      </c>
+      <c r="D250" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E250" s="5" t="inlineStr">
         <is>
@@ -16619,19 +16665,19 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I250" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J250" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K250" s="5" t="inlineStr">
         <is>
@@ -16639,16 +16685,20 @@
         </is>
       </c>
       <c r="L250" s="5" t="n"/>
-      <c r="M250" s="5" t="n"/>
-      <c r="N250" s="5" t="n"/>
+      <c r="M250" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N250" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O250" s="5" t="n">
-        <v>3.8</v>
+        <v>21.36</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B251" s="5" t="n">
@@ -16656,11 +16706,13 @@
       </c>
       <c r="C251" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D251" s="5" t="n">
-        <v/>
+          <t>multilingual_edge</t>
+        </is>
+      </c>
+      <c r="D251" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
@@ -16674,19 +16726,19 @@
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H251" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I251" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J251" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K251" s="5" t="inlineStr">
         <is>
@@ -16694,16 +16746,20 @@
         </is>
       </c>
       <c r="L251" s="5" t="n"/>
-      <c r="M251" s="5" t="n"/>
-      <c r="N251" s="5" t="n"/>
+      <c r="M251" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N251" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O251" s="5" t="n">
-        <v>7.1</v>
+        <v>16.55</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B252" s="5" t="n">
@@ -16711,11 +16767,13 @@
       </c>
       <c r="C252" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D252" s="5" t="n">
-        <v/>
+          <t>multilingual_edge</t>
+        </is>
+      </c>
+      <c r="D252" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
@@ -16729,19 +16787,19 @@
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H252" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I252" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J252" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K252" s="5" t="inlineStr">
         <is>
@@ -16749,16 +16807,20 @@
         </is>
       </c>
       <c r="L252" s="5" t="n"/>
-      <c r="M252" s="5" t="n"/>
-      <c r="N252" s="5" t="n"/>
+      <c r="M252" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N252" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O252" s="5" t="n">
-        <v>7.48</v>
+        <v>20.76</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>multilingual_edge_001</t>
         </is>
       </c>
       <c r="B253" s="5" t="n">
@@ -16766,11 +16828,13 @@
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D253" s="5" t="n">
-        <v/>
+          <t>multilingual_edge</t>
+        </is>
+      </c>
+      <c r="D253" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E253" s="5" t="inlineStr">
         <is>
@@ -16784,36 +16848,40 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I253" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J253" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K253" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L253" s="5" t="n"/>
-      <c r="M253" s="5" t="n"/>
-      <c r="N253" s="5" t="n"/>
+      <c r="M253" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N253" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O253" s="5" t="n">
-        <v>4.99</v>
+        <v>16.66</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B254" s="5" t="n">
@@ -16821,11 +16889,13 @@
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D254" s="5" t="n">
-        <v/>
+          <t>multilingual_edge</t>
+        </is>
+      </c>
+      <c r="D254" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
@@ -16839,19 +16909,19 @@
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H254" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I254" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J254" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K254" s="5" t="inlineStr">
         <is>
@@ -16859,16 +16929,20 @@
         </is>
       </c>
       <c r="L254" s="5" t="n"/>
-      <c r="M254" s="5" t="n"/>
-      <c r="N254" s="5" t="n"/>
+      <c r="M254" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N254" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O254" s="5" t="n">
-        <v>3.28</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B255" s="5" t="n">
@@ -16876,11 +16950,13 @@
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D255" s="5" t="n">
-        <v/>
+          <t>multilingual_edge</t>
+        </is>
+      </c>
+      <c r="D255" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E255" s="5" t="inlineStr">
         <is>
@@ -16894,19 +16970,19 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I255" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J255" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K255" s="5" t="inlineStr">
         <is>
@@ -16914,16 +16990,20 @@
         </is>
       </c>
       <c r="L255" s="5" t="n"/>
-      <c r="M255" s="5" t="n"/>
-      <c r="N255" s="5" t="n"/>
+      <c r="M255" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N255" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O255" s="5" t="n">
-        <v>3.38</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>multilingual_edge_004</t>
         </is>
       </c>
       <c r="B256" s="5" t="n">
@@ -16931,11 +17011,13 @@
       </c>
       <c r="C256" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D256" s="5" t="n">
-        <v/>
+          <t>multilingual_edge</t>
+        </is>
+      </c>
+      <c r="D256" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E256" s="5" t="inlineStr">
         <is>
@@ -16949,19 +17031,19 @@
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H256" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I256" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J256" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K256" s="5" t="inlineStr">
         <is>
@@ -16969,16 +17051,20 @@
         </is>
       </c>
       <c r="L256" s="5" t="n"/>
-      <c r="M256" s="5" t="n"/>
-      <c r="N256" s="5" t="n"/>
+      <c r="M256" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N256" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O256" s="5" t="n">
-        <v>3.33</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B257" s="5" t="n">
@@ -16986,7 +17072,7 @@
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D257" s="5" t="inlineStr">
@@ -17006,12 +17092,12 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I257" s="5" t="b">
@@ -17026,20 +17112,16 @@
         </is>
       </c>
       <c r="L257" s="5" t="n"/>
-      <c r="M257" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N257" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M257" s="5" t="n"/>
+      <c r="N257" s="5" t="n"/>
       <c r="O257" s="5" t="n">
-        <v>7.1</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B258" s="5" t="n">
@@ -17047,7 +17129,7 @@
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
@@ -17067,12 +17149,12 @@
       </c>
       <c r="G258" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H258" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I258" s="5" t="b">
@@ -17087,20 +17169,16 @@
         </is>
       </c>
       <c r="L258" s="5" t="n"/>
-      <c r="M258" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N258" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M258" s="5" t="n"/>
+      <c r="N258" s="5" t="n"/>
       <c r="O258" s="5" t="n">
-        <v>7.12</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
         <is>
-          <t>ask_query_001</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B259" s="5" t="n">
@@ -17108,7 +17186,7 @@
       </c>
       <c r="C259" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D259" s="5" t="inlineStr">
@@ -17128,12 +17206,12 @@
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H259" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I259" s="5" t="b">
@@ -17148,20 +17226,16 @@
         </is>
       </c>
       <c r="L259" s="5" t="n"/>
-      <c r="M259" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N259" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M259" s="5" t="n"/>
+      <c r="N259" s="5" t="n"/>
       <c r="O259" s="5" t="n">
-        <v>3.92</v>
+        <v>14.34</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B260" s="5" t="n">
@@ -17169,7 +17243,7 @@
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D260" s="5" t="inlineStr">
@@ -17189,12 +17263,12 @@
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H260" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I260" s="5" t="b">
@@ -17216,13 +17290,13 @@
         <v>1</v>
       </c>
       <c r="O260" s="5" t="n">
-        <v>7.1</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B261" s="5" t="n">
@@ -17230,7 +17304,7 @@
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D261" s="5" t="inlineStr">
@@ -17250,19 +17324,19 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I261" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J261" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K261" s="5" t="inlineStr">
         <is>
@@ -17270,16 +17344,20 @@
         </is>
       </c>
       <c r="L261" s="5" t="n"/>
-      <c r="M261" s="5" t="n"/>
-      <c r="N261" s="5" t="n"/>
+      <c r="M261" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N261" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O261" s="5" t="n">
-        <v>7.05</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
         <is>
-          <t>ask_query_003</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B262" s="5" t="n">
@@ -17287,7 +17365,7 @@
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D262" s="5" t="inlineStr">
@@ -17307,12 +17385,12 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I262" s="5" t="b">
@@ -17334,13 +17412,13 @@
         <v>1</v>
       </c>
       <c r="O262" s="5" t="n">
-        <v>3.92</v>
+        <v>12.83</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B263" s="5" t="n">
@@ -17348,7 +17426,7 @@
       </c>
       <c r="C263" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D263" s="5" t="inlineStr">
@@ -17368,12 +17446,12 @@
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H263" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I263" s="5" t="b">
@@ -17388,20 +17466,16 @@
         </is>
       </c>
       <c r="L263" s="5" t="n"/>
-      <c r="M263" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N263" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M263" s="5" t="n"/>
+      <c r="N263" s="5" t="n"/>
       <c r="O263" s="5" t="n">
-        <v>8.23</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B264" s="5" t="n">
@@ -17409,7 +17483,7 @@
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D264" s="5" t="inlineStr">
@@ -17429,12 +17503,12 @@
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H264" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I264" s="5" t="b">
@@ -17445,24 +17519,20 @@
       </c>
       <c r="K264" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>execution_failure</t>
         </is>
       </c>
       <c r="L264" s="5" t="n"/>
-      <c r="M264" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N264" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M264" s="5" t="n"/>
+      <c r="N264" s="5" t="n"/>
       <c r="O264" s="5" t="n">
-        <v>8.1</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="5" t="inlineStr">
         <is>
-          <t>ask_query_004</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B265" s="5" t="n">
@@ -17470,7 +17540,7 @@
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D265" s="5" t="inlineStr">
@@ -17490,12 +17560,12 @@
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H265" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I265" s="5" t="b">
@@ -17510,20 +17580,16 @@
         </is>
       </c>
       <c r="L265" s="5" t="n"/>
-      <c r="M265" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N265" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M265" s="5" t="n"/>
+      <c r="N265" s="5" t="n"/>
       <c r="O265" s="5" t="n">
-        <v>4.61</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B266" s="5" t="n">
@@ -17531,7 +17597,7 @@
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D266" s="5" t="inlineStr">
@@ -17556,7 +17622,7 @@
       </c>
       <c r="H266" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I266" s="5" t="b">
@@ -17571,20 +17637,16 @@
         </is>
       </c>
       <c r="L266" s="5" t="n"/>
-      <c r="M266" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N266" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M266" s="5" t="n"/>
+      <c r="N266" s="5" t="n"/>
       <c r="O266" s="5" t="n">
-        <v>16.49</v>
+        <v>13.03</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B267" s="5" t="n">
@@ -17592,7 +17654,7 @@
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D267" s="5" t="inlineStr">
@@ -17617,7 +17679,7 @@
       </c>
       <c r="H267" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I267" s="5" t="b">
@@ -17632,20 +17694,16 @@
         </is>
       </c>
       <c r="L267" s="5" t="n"/>
-      <c r="M267" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N267" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M267" s="5" t="n"/>
+      <c r="N267" s="5" t="n"/>
       <c r="O267" s="5" t="n">
-        <v>17.18</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_001</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B268" s="5" t="n">
@@ -17653,7 +17711,7 @@
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D268" s="5" t="inlineStr">
@@ -17678,7 +17736,7 @@
       </c>
       <c r="H268" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I268" s="5" t="b">
@@ -17693,33 +17751,29 @@
         </is>
       </c>
       <c r="L268" s="5" t="n"/>
-      <c r="M268" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N268" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M268" s="5" t="n"/>
+      <c r="N268" s="5" t="n"/>
       <c r="O268" s="5" t="n">
-        <v>16.5</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>cross_kg_005</t>
         </is>
       </c>
       <c r="B269" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E269" s="5" t="inlineStr">
@@ -17734,12 +17788,12 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I269" s="5" t="b">
@@ -17761,26 +17815,26 @@
         <v>1</v>
       </c>
       <c r="O269" s="5" t="n">
-        <v>26.92</v>
+        <v>22.65</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>cross_kg_005</t>
         </is>
       </c>
       <c r="B270" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
@@ -17795,12 +17849,12 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I270" s="5" t="b">
@@ -17822,26 +17876,26 @@
         <v>1</v>
       </c>
       <c r="O270" s="5" t="n">
-        <v>19.44</v>
+        <v>23.76</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_002</t>
+          <t>cross_kg_005</t>
         </is>
       </c>
       <c r="B271" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
@@ -17856,12 +17910,12 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I271" s="5" t="b">
@@ -17883,26 +17937,26 @@
         <v>1</v>
       </c>
       <c r="O271" s="5" t="n">
-        <v>19.47</v>
+        <v>22.97</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>cross_kg_009</t>
         </is>
       </c>
       <c r="B272" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
@@ -17917,12 +17971,12 @@
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H272" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I272" s="5" t="b">
@@ -17944,26 +17998,26 @@
         <v>1</v>
       </c>
       <c r="O272" s="5" t="n">
-        <v>21.28</v>
+        <v>19.47</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>cross_kg_009</t>
         </is>
       </c>
       <c r="B273" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C273" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E273" s="5" t="inlineStr">
@@ -17978,12 +18032,12 @@
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H273" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I273" s="5" t="b">
@@ -18005,26 +18059,26 @@
         <v>1</v>
       </c>
       <c r="O273" s="5" t="n">
-        <v>22.32</v>
+        <v>26.07</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy_003</t>
+          <t>cross_kg_009</t>
         </is>
       </c>
       <c r="B274" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C274" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E274" s="5" t="inlineStr">
@@ -18039,12 +18093,12 @@
       </c>
       <c r="G274" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H274" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I274" s="5" t="b">
@@ -18066,26 +18120,26 @@
         <v>1</v>
       </c>
       <c r="O274" s="5" t="n">
-        <v>21.36</v>
+        <v>23.25</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B275" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E275" s="5" t="inlineStr">
@@ -18100,12 +18154,12 @@
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H275" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I275" s="5" t="b">
@@ -18127,26 +18181,26 @@
         <v>1</v>
       </c>
       <c r="O275" s="5" t="n">
-        <v>16.55</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B276" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E276" s="5" t="inlineStr">
@@ -18161,12 +18215,12 @@
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H276" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I276" s="5" t="b">
@@ -18188,26 +18242,26 @@
         <v>1</v>
       </c>
       <c r="O276" s="5" t="n">
-        <v>20.76</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_001</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B277" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C277" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E277" s="5" t="inlineStr">
@@ -18222,12 +18276,12 @@
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H277" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I277" s="5" t="b">
@@ -18249,26 +18303,26 @@
         <v>1</v>
       </c>
       <c r="O277" s="5" t="n">
-        <v>16.66</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B278" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E278" s="5" t="inlineStr">
@@ -18283,12 +18337,12 @@
       </c>
       <c r="G278" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H278" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I278" s="5" t="b">
@@ -18310,26 +18364,26 @@
         <v>1</v>
       </c>
       <c r="O278" s="5" t="n">
-        <v>17.3</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B279" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E279" s="5" t="inlineStr">
@@ -18344,12 +18398,12 @@
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H279" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I279" s="5" t="b">
@@ -18371,26 +18425,26 @@
         <v>1</v>
       </c>
       <c r="O279" s="5" t="n">
-        <v>18.6</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_004</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B280" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E280" s="5" t="inlineStr">
@@ -18405,12 +18459,12 @@
       </c>
       <c r="G280" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H280" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I280" s="5" t="b">
@@ -18426,19 +18480,19 @@
       </c>
       <c r="L280" s="5" t="n"/>
       <c r="M280" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N280" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O280" s="5" t="n">
-        <v>16.8</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B281" s="5" t="n">
@@ -18446,7 +18500,7 @@
       </c>
       <c r="C281" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D281" s="5" t="inlineStr">
@@ -18466,12 +18520,12 @@
       </c>
       <c r="G281" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H281" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I281" s="5" t="b">
@@ -18486,16 +18540,20 @@
         </is>
       </c>
       <c r="L281" s="5" t="n"/>
-      <c r="M281" s="5" t="n"/>
-      <c r="N281" s="5" t="n"/>
+      <c r="M281" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N281" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O281" s="5" t="n">
-        <v>10.68</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B282" s="5" t="n">
@@ -18503,7 +18561,7 @@
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D282" s="5" t="inlineStr">
@@ -18523,12 +18581,12 @@
       </c>
       <c r="G282" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H282" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I282" s="5" t="b">
@@ -18543,16 +18601,20 @@
         </is>
       </c>
       <c r="L282" s="5" t="n"/>
-      <c r="M282" s="5" t="n"/>
-      <c r="N282" s="5" t="n"/>
+      <c r="M282" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N282" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O282" s="5" t="n">
-        <v>12.47</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B283" s="5" t="n">
@@ -18560,7 +18622,7 @@
       </c>
       <c r="C283" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D283" s="5" t="inlineStr">
@@ -18580,12 +18642,12 @@
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H283" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I283" s="5" t="b">
@@ -18600,16 +18662,20 @@
         </is>
       </c>
       <c r="L283" s="5" t="n"/>
-      <c r="M283" s="5" t="n"/>
-      <c r="N283" s="5" t="n"/>
+      <c r="M283" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N283" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O283" s="5" t="n">
-        <v>14.34</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B284" s="5" t="n">
@@ -18617,7 +18683,7 @@
       </c>
       <c r="C284" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D284" s="5" t="inlineStr">
@@ -18642,7 +18708,7 @@
       </c>
       <c r="H284" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I284" s="5" t="b">
@@ -18664,13 +18730,13 @@
         <v>1</v>
       </c>
       <c r="O284" s="5" t="n">
-        <v>12.05</v>
+        <v>18.94</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B285" s="5" t="n">
@@ -18678,7 +18744,7 @@
       </c>
       <c r="C285" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D285" s="5" t="inlineStr">
@@ -18703,7 +18769,7 @@
       </c>
       <c r="H285" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I285" s="5" t="b">
@@ -18725,13 +18791,13 @@
         <v>1</v>
       </c>
       <c r="O285" s="5" t="n">
-        <v>12.24</v>
+        <v>21.38</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B286" s="5" t="n">
@@ -18739,7 +18805,7 @@
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D286" s="5" t="inlineStr">
@@ -18764,7 +18830,7 @@
       </c>
       <c r="H286" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I286" s="5" t="b">
@@ -18780,19 +18846,19 @@
       </c>
       <c r="L286" s="5" t="n"/>
       <c r="M286" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N286" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O286" s="5" t="n">
-        <v>12.83</v>
+        <v>14.78</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B287" s="5" t="n">
@@ -18800,7 +18866,7 @@
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D287" s="5" t="inlineStr">
@@ -18825,7 +18891,7 @@
       </c>
       <c r="H287" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I287" s="5" t="b">
@@ -18840,16 +18906,20 @@
         </is>
       </c>
       <c r="L287" s="5" t="n"/>
-      <c r="M287" s="5" t="n"/>
-      <c r="N287" s="5" t="n"/>
+      <c r="M287" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N287" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O287" s="5" t="n">
-        <v>11.92</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B288" s="5" t="n">
@@ -18857,7 +18927,7 @@
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D288" s="5" t="inlineStr">
@@ -18882,7 +18952,7 @@
       </c>
       <c r="H288" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I288" s="5" t="b">
@@ -18893,20 +18963,24 @@
       </c>
       <c r="K288" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L288" s="5" t="n"/>
-      <c r="M288" s="5" t="n"/>
-      <c r="N288" s="5" t="n"/>
+      <c r="M288" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N288" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O288" s="5" t="n">
-        <v>12.6</v>
+        <v>9.029999999999999</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B289" s="5" t="n">
@@ -18914,7 +18988,7 @@
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D289" s="5" t="inlineStr">
@@ -18939,7 +19013,7 @@
       </c>
       <c r="H289" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I289" s="5" t="b">
@@ -18954,29 +19028,33 @@
         </is>
       </c>
       <c r="L289" s="5" t="n"/>
-      <c r="M289" s="5" t="n"/>
-      <c r="N289" s="5" t="n"/>
+      <c r="M289" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N289" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O289" s="5" t="n">
-        <v>13.69</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B290" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E290" s="5" t="inlineStr">
@@ -18991,12 +19069,12 @@
       </c>
       <c r="G290" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H290" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I290" s="5" t="b">
@@ -19011,49 +19089,53 @@
         </is>
       </c>
       <c r="L290" s="5" t="n"/>
-      <c r="M290" s="5" t="n"/>
-      <c r="N290" s="5" t="n"/>
+      <c r="M290" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N290" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O290" s="5" t="n">
-        <v>13.03</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B291" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E291" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F291" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H291" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I291" s="5" t="b">
@@ -19068,49 +19150,53 @@
         </is>
       </c>
       <c r="L291" s="5" t="n"/>
-      <c r="M291" s="5" t="n"/>
-      <c r="N291" s="5" t="n"/>
+      <c r="M291" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N291" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O291" s="5" t="n">
-        <v>13.16</v>
+        <v>16.45</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B292" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E292" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F292" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H292" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I292" s="5" t="b">
@@ -19125,16 +19211,20 @@
         </is>
       </c>
       <c r="L292" s="5" t="n"/>
-      <c r="M292" s="5" t="n"/>
-      <c r="N292" s="5" t="n"/>
+      <c r="M292" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N292" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O292" s="5" t="n">
-        <v>13.05</v>
+        <v>16.76</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_005</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B293" s="5" t="n">
@@ -19142,17 +19232,17 @@
       </c>
       <c r="C293" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E293" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F293" s="5" t="inlineStr">
@@ -19162,12 +19252,12 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I293" s="5" t="b">
@@ -19189,13 +19279,13 @@
         <v>1</v>
       </c>
       <c r="O293" s="5" t="n">
-        <v>22.65</v>
+        <v>20.52</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_005</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B294" s="5" t="n">
@@ -19203,12 +19293,12 @@
       </c>
       <c r="C294" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E294" s="5" t="inlineStr">
@@ -19218,17 +19308,17 @@
       </c>
       <c r="F294" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H294" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I294" s="5" t="b">
@@ -19250,13 +19340,13 @@
         <v>1</v>
       </c>
       <c r="O294" s="5" t="n">
-        <v>23.76</v>
+        <v>18.23</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_005</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B295" s="5" t="n">
@@ -19264,32 +19354,32 @@
       </c>
       <c r="C295" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E295" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F295" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I295" s="5" t="b">
@@ -19311,13 +19401,13 @@
         <v>1</v>
       </c>
       <c r="O295" s="5" t="n">
-        <v>22.97</v>
+        <v>18.17</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_009</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B296" s="5" t="n">
@@ -19325,17 +19415,17 @@
       </c>
       <c r="C296" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E296" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F296" s="5" t="inlineStr">
@@ -19345,12 +19435,12 @@
       </c>
       <c r="G296" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H296" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I296" s="5" t="b">
@@ -19372,13 +19462,13 @@
         <v>1</v>
       </c>
       <c r="O296" s="5" t="n">
-        <v>19.47</v>
+        <v>20.49</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_009</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B297" s="5" t="n">
@@ -19386,32 +19476,32 @@
       </c>
       <c r="C297" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E297" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F297" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I297" s="5" t="b">
@@ -19433,13 +19523,13 @@
         <v>1</v>
       </c>
       <c r="O297" s="5" t="n">
-        <v>26.07</v>
+        <v>17.83</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_009</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B298" s="5" t="n">
@@ -19447,12 +19537,12 @@
       </c>
       <c r="C298" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D298" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E298" s="5" t="inlineStr">
@@ -19462,17 +19552,17 @@
       </c>
       <c r="F298" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G298" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H298" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I298" s="5" t="b">
@@ -19494,13 +19584,13 @@
         <v>1</v>
       </c>
       <c r="O298" s="5" t="n">
-        <v>23.25</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>count_kg1_001</t>
         </is>
       </c>
       <c r="B299" s="5" t="n">
@@ -19508,12 +19598,12 @@
       </c>
       <c r="C299" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D299" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E299" s="5" t="inlineStr">
@@ -19555,13 +19645,13 @@
         <v>1</v>
       </c>
       <c r="O299" s="5" t="n">
-        <v>13.57</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>count_kg1_001</t>
         </is>
       </c>
       <c r="B300" s="5" t="n">
@@ -19569,12 +19659,12 @@
       </c>
       <c r="C300" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D300" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E300" s="5" t="inlineStr">
@@ -19616,13 +19706,13 @@
         <v>1</v>
       </c>
       <c r="O300" s="5" t="n">
-        <v>10.24</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>count_kg1_001</t>
         </is>
       </c>
       <c r="B301" s="5" t="n">
@@ -19630,12 +19720,12 @@
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D301" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E301" s="5" t="inlineStr">
@@ -19677,26 +19767,26 @@
         <v>1</v>
       </c>
       <c r="O301" s="5" t="n">
-        <v>10.42</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>open_kg_004</t>
         </is>
       </c>
       <c r="B302" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C302" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D302" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E302" s="5" t="inlineStr">
@@ -19711,12 +19801,12 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I302" s="5" t="b">
@@ -19738,26 +19828,26 @@
         <v>1</v>
       </c>
       <c r="O302" s="5" t="n">
-        <v>3.81</v>
+        <v>30.85</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>open_kg_004</t>
         </is>
       </c>
       <c r="B303" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C303" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E303" s="5" t="inlineStr">
@@ -19772,12 +19862,12 @@
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H303" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I303" s="5" t="b">
@@ -19799,26 +19889,26 @@
         <v>1</v>
       </c>
       <c r="O303" s="5" t="n">
-        <v>5.16</v>
+        <v>30.75</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>open_kg_004</t>
         </is>
       </c>
       <c r="B304" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C304" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D304" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E304" s="5" t="inlineStr">
@@ -19833,12 +19923,12 @@
       </c>
       <c r="G304" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H304" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I304" s="5" t="b">
@@ -19854,32 +19944,32 @@
       </c>
       <c r="L304" s="5" t="n"/>
       <c r="M304" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N304" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O304" s="5" t="n">
-        <v>13.07</v>
+        <v>27.83</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>open_kg_001</t>
         </is>
       </c>
       <c r="B305" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C305" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D305" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E305" s="5" t="inlineStr">
@@ -19894,12 +19984,12 @@
       </c>
       <c r="G305" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H305" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I305" s="5" t="b">
@@ -19914,33 +20004,29 @@
         </is>
       </c>
       <c r="L305" s="5" t="n"/>
-      <c r="M305" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N305" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M305" s="5" t="n"/>
+      <c r="N305" s="5" t="n"/>
       <c r="O305" s="5" t="n">
-        <v>7.85</v>
+        <v>23.94</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>open_kg_001</t>
         </is>
       </c>
       <c r="B306" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C306" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D306" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E306" s="5" t="inlineStr">
@@ -19955,12 +20041,12 @@
       </c>
       <c r="G306" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H306" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I306" s="5" t="b">
@@ -19975,33 +20061,29 @@
         </is>
       </c>
       <c r="L306" s="5" t="n"/>
-      <c r="M306" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N306" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M306" s="5" t="n"/>
+      <c r="N306" s="5" t="n"/>
       <c r="O306" s="5" t="n">
-        <v>8.73</v>
+        <v>24.11</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>open_kg_001</t>
         </is>
       </c>
       <c r="B307" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C307" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D307" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E307" s="5" t="inlineStr">
@@ -20016,12 +20098,12 @@
       </c>
       <c r="G307" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H307" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I307" s="5" t="b">
@@ -20036,33 +20118,29 @@
         </is>
       </c>
       <c r="L307" s="5" t="n"/>
-      <c r="M307" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N307" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M307" s="5" t="n"/>
+      <c r="N307" s="5" t="n"/>
       <c r="O307" s="5" t="n">
-        <v>4.92</v>
+        <v>24.07</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>open_kg_005</t>
         </is>
       </c>
       <c r="B308" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C308" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D308" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E308" s="5" t="inlineStr">
@@ -20077,53 +20155,53 @@
       </c>
       <c r="G308" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H308" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I308" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J308" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K308" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L308" s="5" t="n"/>
-      <c r="M308" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N308" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>execution_failure</t>
+        </is>
+      </c>
+      <c r="L308" s="5" t="inlineStr">
+        <is>
+          <t>params={'property': 'surface', 'value': 'asphalt', 'limit': 10}</t>
+        </is>
+      </c>
+      <c r="M308" s="5" t="n"/>
+      <c r="N308" s="5" t="n"/>
       <c r="O308" s="5" t="n">
-        <v>18.94</v>
+        <v>12.13</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>open_kg_005</t>
         </is>
       </c>
       <c r="B309" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C309" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D309" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E309" s="5" t="inlineStr">
@@ -20138,53 +20216,53 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I309" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J309" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K309" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L309" s="5" t="n"/>
-      <c r="M309" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N309" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>execution_failure</t>
+        </is>
+      </c>
+      <c r="L309" s="5" t="inlineStr">
+        <is>
+          <t>params={'property': 'surface', 'value': 'asphalt', 'limit': 10}</t>
+        </is>
+      </c>
+      <c r="M309" s="5" t="n"/>
+      <c r="N309" s="5" t="n"/>
       <c r="O309" s="5" t="n">
-        <v>21.38</v>
+        <v>11.86</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>open_kg_005</t>
         </is>
       </c>
       <c r="B310" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C310" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D310" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E310" s="5" t="inlineStr">
@@ -20199,12 +20277,12 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I310" s="5" t="b">
@@ -20215,37 +20293,33 @@
       </c>
       <c r="K310" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>no_results</t>
         </is>
       </c>
       <c r="L310" s="5" t="n"/>
-      <c r="M310" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N310" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="M310" s="5" t="n"/>
+      <c r="N310" s="5" t="n"/>
       <c r="O310" s="5" t="n">
-        <v>14.78</v>
+        <v>32.39</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>open_kg_006</t>
         </is>
       </c>
       <c r="B311" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C311" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D311" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E311" s="5" t="inlineStr">
@@ -20260,12 +20334,12 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I311" s="5" t="b">
@@ -20280,33 +20354,29 @@
         </is>
       </c>
       <c r="L311" s="5" t="n"/>
-      <c r="M311" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N311" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M311" s="5" t="n"/>
+      <c r="N311" s="5" t="n"/>
       <c r="O311" s="5" t="n">
-        <v>7.87</v>
+        <v>22.37</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>open_kg_006</t>
         </is>
       </c>
       <c r="B312" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C312" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D312" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E312" s="5" t="inlineStr">
@@ -20321,12 +20391,12 @@
       </c>
       <c r="G312" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H312" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I312" s="5" t="b">
@@ -20341,33 +20411,29 @@
         </is>
       </c>
       <c r="L312" s="5" t="n"/>
-      <c r="M312" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N312" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M312" s="5" t="n"/>
+      <c r="N312" s="5" t="n"/>
       <c r="O312" s="5" t="n">
-        <v>9.029999999999999</v>
+        <v>22.89</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>open_kg_006</t>
         </is>
       </c>
       <c r="B313" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C313" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E313" s="5" t="inlineStr">
@@ -20382,12 +20448,12 @@
       </c>
       <c r="G313" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H313" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I313" s="5" t="b">
@@ -20402,20 +20468,16 @@
         </is>
       </c>
       <c r="L313" s="5" t="n"/>
-      <c r="M313" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N313" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M313" s="5" t="n"/>
+      <c r="N313" s="5" t="n"/>
       <c r="O313" s="5" t="n">
-        <v>5.17</v>
+        <v>22.82</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>open_kg_003</t>
         </is>
       </c>
       <c r="B314" s="5" t="n">
@@ -20423,12 +20485,12 @@
       </c>
       <c r="C314" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D314" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E314" s="5" t="inlineStr">
@@ -20443,12 +20505,12 @@
       </c>
       <c r="G314" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H314" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I314" s="5" t="b">
@@ -20470,13 +20532,13 @@
         <v>1</v>
       </c>
       <c r="O314" s="5" t="n">
-        <v>19.5</v>
+        <v>47.46</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>open_kg_003</t>
         </is>
       </c>
       <c r="B315" s="5" t="n">
@@ -20484,32 +20546,32 @@
       </c>
       <c r="C315" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D315" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E315" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F315" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G315" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H315" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I315" s="5" t="b">
@@ -20531,13 +20593,13 @@
         <v>1</v>
       </c>
       <c r="O315" s="5" t="n">
-        <v>16.45</v>
+        <v>22.92</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>open_kg_003</t>
         </is>
       </c>
       <c r="B316" s="5" t="n">
@@ -20545,32 +20607,32 @@
       </c>
       <c r="C316" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D316" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E316" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F316" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G316" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H316" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I316" s="5" t="b">
@@ -20592,31 +20654,29 @@
         <v>1</v>
       </c>
       <c r="O316" s="5" t="n">
-        <v>16.76</v>
+        <v>29.16</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B317" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C317" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
-        </is>
-      </c>
-      <c r="D317" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D317" s="5" t="n">
+        <v/>
       </c>
       <c r="E317" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F317" s="5" t="inlineStr">
@@ -20626,19 +20686,19 @@
       </c>
       <c r="G317" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H317" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I317" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J317" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K317" s="5" t="inlineStr">
         <is>
@@ -20646,34 +20706,28 @@
         </is>
       </c>
       <c r="L317" s="5" t="n"/>
-      <c r="M317" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N317" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M317" s="5" t="n"/>
+      <c r="N317" s="5" t="n"/>
       <c r="O317" s="5" t="n">
-        <v>20.52</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B318" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C318" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
-        </is>
-      </c>
-      <c r="D318" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D318" s="5" t="n">
+        <v/>
       </c>
       <c r="E318" s="5" t="inlineStr">
         <is>
@@ -20682,24 +20736,24 @@
       </c>
       <c r="F318" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G318" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H318" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I318" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J318" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K318" s="5" t="inlineStr">
         <is>
@@ -20707,60 +20761,54 @@
         </is>
       </c>
       <c r="L318" s="5" t="n"/>
-      <c r="M318" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N318" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M318" s="5" t="n"/>
+      <c r="N318" s="5" t="n"/>
       <c r="O318" s="5" t="n">
-        <v>18.23</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B319" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C319" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
-        </is>
-      </c>
-      <c r="D319" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D319" s="5" t="n">
+        <v/>
       </c>
       <c r="E319" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F319" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G319" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H319" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I319" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J319" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K319" s="5" t="inlineStr">
         <is>
@@ -20768,38 +20816,32 @@
         </is>
       </c>
       <c r="L319" s="5" t="n"/>
-      <c r="M319" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N319" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M319" s="5" t="n"/>
+      <c r="N319" s="5" t="n"/>
       <c r="O319" s="5" t="n">
-        <v>18.17</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B320" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C320" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
-        </is>
-      </c>
-      <c r="D320" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D320" s="5" t="n">
+        <v/>
       </c>
       <c r="E320" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F320" s="5" t="inlineStr">
@@ -20809,19 +20851,19 @@
       </c>
       <c r="G320" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H320" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I320" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J320" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K320" s="5" t="inlineStr">
         <is>
@@ -20829,60 +20871,54 @@
         </is>
       </c>
       <c r="L320" s="5" t="n"/>
-      <c r="M320" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N320" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M320" s="5" t="n"/>
+      <c r="N320" s="5" t="n"/>
       <c r="O320" s="5" t="n">
-        <v>20.49</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B321" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C321" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
-        </is>
-      </c>
-      <c r="D321" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D321" s="5" t="n">
+        <v/>
       </c>
       <c r="E321" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F321" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G321" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H321" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I321" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J321" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K321" s="5" t="inlineStr">
         <is>
@@ -20890,34 +20926,28 @@
         </is>
       </c>
       <c r="L321" s="5" t="n"/>
-      <c r="M321" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N321" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M321" s="5" t="n"/>
+      <c r="N321" s="5" t="n"/>
       <c r="O321" s="5" t="n">
-        <v>17.83</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B322" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C322" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
-        </is>
-      </c>
-      <c r="D322" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D322" s="5" t="n">
+        <v/>
       </c>
       <c r="E322" s="5" t="inlineStr">
         <is>
@@ -20926,24 +20956,24 @@
       </c>
       <c r="F322" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G322" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H322" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I322" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J322" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K322" s="5" t="inlineStr">
         <is>
@@ -20951,34 +20981,28 @@
         </is>
       </c>
       <c r="L322" s="5" t="n"/>
-      <c r="M322" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N322" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M322" s="5" t="n"/>
+      <c r="N322" s="5" t="n"/>
       <c r="O322" s="5" t="n">
-        <v>17.58</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_001</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B323" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C323" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
-        </is>
-      </c>
-      <c r="D323" s="5" t="inlineStr">
-        <is>
-          <t>flights</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D323" s="5" t="n">
+        <v/>
       </c>
       <c r="E323" s="5" t="inlineStr">
         <is>
@@ -20992,19 +21016,19 @@
       </c>
       <c r="G323" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H323" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I323" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J323" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K323" s="5" t="inlineStr">
         <is>
@@ -21012,34 +21036,28 @@
         </is>
       </c>
       <c r="L323" s="5" t="n"/>
-      <c r="M323" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N323" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M323" s="5" t="n"/>
+      <c r="N323" s="5" t="n"/>
       <c r="O323" s="5" t="n">
-        <v>9.44</v>
+        <v>29.27</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_001</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B324" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C324" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
-        </is>
-      </c>
-      <c r="D324" s="5" t="inlineStr">
-        <is>
-          <t>flights</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D324" s="5" t="n">
+        <v/>
       </c>
       <c r="E324" s="5" t="inlineStr">
         <is>
@@ -21053,19 +21071,19 @@
       </c>
       <c r="G324" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H324" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I324" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J324" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K324" s="5" t="inlineStr">
         <is>
@@ -21073,34 +21091,28 @@
         </is>
       </c>
       <c r="L324" s="5" t="n"/>
-      <c r="M324" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N324" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M324" s="5" t="n"/>
+      <c r="N324" s="5" t="n"/>
       <c r="O324" s="5" t="n">
-        <v>9.07</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_001</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B325" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C325" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
-        </is>
-      </c>
-      <c r="D325" s="5" t="inlineStr">
-        <is>
-          <t>flights</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D325" s="5" t="n">
+        <v/>
       </c>
       <c r="E325" s="5" t="inlineStr">
         <is>
@@ -21114,19 +21126,19 @@
       </c>
       <c r="G325" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H325" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I325" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J325" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K325" s="5" t="inlineStr">
         <is>
@@ -21134,14 +21146,10 @@
         </is>
       </c>
       <c r="L325" s="5" t="n"/>
-      <c r="M325" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N325" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M325" s="5" t="n"/>
+      <c r="N325" s="5" t="n"/>
       <c r="O325" s="5" t="n">
-        <v>8.92</v>
+        <v>17.35</v>
       </c>
     </row>
   </sheetData>

--- a/NL2SPARQL_Evaluation_Results.xlsx
+++ b/NL2SPARQL_Evaluation_Results.xlsx
@@ -17064,7 +17064,7 @@
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B257" s="5" t="n">
@@ -17112,16 +17112,20 @@
         </is>
       </c>
       <c r="L257" s="5" t="n"/>
-      <c r="M257" s="5" t="n"/>
-      <c r="N257" s="5" t="n"/>
+      <c r="M257" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N257" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O257" s="5" t="n">
-        <v>10.68</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B258" s="5" t="n">
@@ -17169,16 +17173,20 @@
         </is>
       </c>
       <c r="L258" s="5" t="n"/>
-      <c r="M258" s="5" t="n"/>
-      <c r="N258" s="5" t="n"/>
+      <c r="M258" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N258" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O258" s="5" t="n">
-        <v>12.47</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_001</t>
+          <t>property_ambiguity_002</t>
         </is>
       </c>
       <c r="B259" s="5" t="n">
@@ -17226,29 +17234,33 @@
         </is>
       </c>
       <c r="L259" s="5" t="n"/>
-      <c r="M259" s="5" t="n"/>
-      <c r="N259" s="5" t="n"/>
+      <c r="M259" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N259" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O259" s="5" t="n">
-        <v>14.34</v>
+        <v>12.83</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>cross_kg_005</t>
         </is>
       </c>
       <c r="B260" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E260" s="5" t="inlineStr">
@@ -17263,12 +17275,12 @@
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H260" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I260" s="5" t="b">
@@ -17290,26 +17302,26 @@
         <v>1</v>
       </c>
       <c r="O260" s="5" t="n">
-        <v>12.05</v>
+        <v>22.65</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>cross_kg_005</t>
         </is>
       </c>
       <c r="B261" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E261" s="5" t="inlineStr">
@@ -17324,12 +17336,12 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I261" s="5" t="b">
@@ -17351,26 +17363,26 @@
         <v>1</v>
       </c>
       <c r="O261" s="5" t="n">
-        <v>12.24</v>
+        <v>23.76</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_002</t>
+          <t>cross_kg_005</t>
         </is>
       </c>
       <c r="B262" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E262" s="5" t="inlineStr">
@@ -17385,12 +17397,12 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I262" s="5" t="b">
@@ -17412,26 +17424,26 @@
         <v>1</v>
       </c>
       <c r="O262" s="5" t="n">
-        <v>12.83</v>
+        <v>22.97</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>cross_kg_009</t>
         </is>
       </c>
       <c r="B263" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C263" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E263" s="5" t="inlineStr">
@@ -17446,12 +17458,12 @@
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H263" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I263" s="5" t="b">
@@ -17466,29 +17478,33 @@
         </is>
       </c>
       <c r="L263" s="5" t="n"/>
-      <c r="M263" s="5" t="n"/>
-      <c r="N263" s="5" t="n"/>
+      <c r="M263" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N263" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O263" s="5" t="n">
-        <v>11.92</v>
+        <v>19.47</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>cross_kg_009</t>
         </is>
       </c>
       <c r="B264" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E264" s="5" t="inlineStr">
@@ -17503,12 +17519,12 @@
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H264" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I264" s="5" t="b">
@@ -17519,33 +17535,37 @@
       </c>
       <c r="K264" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L264" s="5" t="n"/>
-      <c r="M264" s="5" t="n"/>
-      <c r="N264" s="5" t="n"/>
+      <c r="M264" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N264" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O264" s="5" t="n">
-        <v>12.6</v>
+        <v>26.07</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_003</t>
+          <t>cross_kg_009</t>
         </is>
       </c>
       <c r="B265" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E265" s="5" t="inlineStr">
@@ -17560,12 +17580,12 @@
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H265" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I265" s="5" t="b">
@@ -17580,29 +17600,33 @@
         </is>
       </c>
       <c r="L265" s="5" t="n"/>
-      <c r="M265" s="5" t="n"/>
-      <c r="N265" s="5" t="n"/>
+      <c r="M265" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N265" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O265" s="5" t="n">
-        <v>13.69</v>
+        <v>23.25</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B266" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
@@ -17617,12 +17641,12 @@
       </c>
       <c r="G266" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H266" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I266" s="5" t="b">
@@ -17637,29 +17661,33 @@
         </is>
       </c>
       <c r="L266" s="5" t="n"/>
-      <c r="M266" s="5" t="n"/>
-      <c r="N266" s="5" t="n"/>
+      <c r="M266" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N266" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O266" s="5" t="n">
-        <v>13.03</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B267" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E267" s="5" t="inlineStr">
@@ -17674,12 +17702,12 @@
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H267" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I267" s="5" t="b">
@@ -17694,29 +17722,33 @@
         </is>
       </c>
       <c r="L267" s="5" t="n"/>
-      <c r="M267" s="5" t="n"/>
-      <c r="N267" s="5" t="n"/>
+      <c r="M267" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N267" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O267" s="5" t="n">
-        <v>13.16</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B268" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
@@ -17731,12 +17763,12 @@
       </c>
       <c r="G268" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H268" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I268" s="5" t="b">
@@ -17751,29 +17783,33 @@
         </is>
       </c>
       <c r="L268" s="5" t="n"/>
-      <c r="M268" s="5" t="n"/>
-      <c r="N268" s="5" t="n"/>
+      <c r="M268" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N268" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O268" s="5" t="n">
-        <v>13.05</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_005</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B269" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E269" s="5" t="inlineStr">
@@ -17788,12 +17824,12 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I269" s="5" t="b">
@@ -17815,26 +17851,26 @@
         <v>1</v>
       </c>
       <c r="O269" s="5" t="n">
-        <v>22.65</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_005</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B270" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
@@ -17849,12 +17885,12 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I270" s="5" t="b">
@@ -17876,26 +17912,26 @@
         <v>1</v>
       </c>
       <c r="O270" s="5" t="n">
-        <v>23.76</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_005</t>
+          <t>compare_two_airports_002</t>
         </is>
       </c>
       <c r="B271" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
@@ -17910,12 +17946,12 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I271" s="5" t="b">
@@ -17931,32 +17967,32 @@
       </c>
       <c r="L271" s="5" t="n"/>
       <c r="M271" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N271" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O271" s="5" t="n">
-        <v>22.97</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_009</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B272" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
@@ -17971,12 +18007,12 @@
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H272" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I272" s="5" t="b">
@@ -17998,26 +18034,26 @@
         <v>1</v>
       </c>
       <c r="O272" s="5" t="n">
-        <v>19.47</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_009</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B273" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C273" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E273" s="5" t="inlineStr">
@@ -18032,12 +18068,12 @@
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H273" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I273" s="5" t="b">
@@ -18059,26 +18095,26 @@
         <v>1</v>
       </c>
       <c r="O273" s="5" t="n">
-        <v>26.07</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_009</t>
+          <t>ask_query_002</t>
         </is>
       </c>
       <c r="B274" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C274" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E274" s="5" t="inlineStr">
@@ -18093,12 +18129,12 @@
       </c>
       <c r="G274" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H274" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I274" s="5" t="b">
@@ -18120,26 +18156,26 @@
         <v>1</v>
       </c>
       <c r="O274" s="5" t="n">
-        <v>23.25</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B275" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E275" s="5" t="inlineStr">
@@ -18154,12 +18190,12 @@
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H275" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I275" s="5" t="b">
@@ -18181,26 +18217,26 @@
         <v>1</v>
       </c>
       <c r="O275" s="5" t="n">
-        <v>13.57</v>
+        <v>18.94</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B276" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E276" s="5" t="inlineStr">
@@ -18215,12 +18251,12 @@
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H276" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I276" s="5" t="b">
@@ -18242,26 +18278,26 @@
         <v>1</v>
       </c>
       <c r="O276" s="5" t="n">
-        <v>10.24</v>
+        <v>21.38</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>multilingual_edge_002</t>
         </is>
       </c>
       <c r="B277" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C277" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E277" s="5" t="inlineStr">
@@ -18276,7 +18312,7 @@
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H277" s="5" t="inlineStr">
@@ -18297,32 +18333,32 @@
       </c>
       <c r="L277" s="5" t="n"/>
       <c r="M277" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N277" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O277" s="5" t="n">
-        <v>10.42</v>
+        <v>14.78</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B278" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E278" s="5" t="inlineStr">
@@ -18337,12 +18373,12 @@
       </c>
       <c r="G278" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H278" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I278" s="5" t="b">
@@ -18364,26 +18400,26 @@
         <v>1</v>
       </c>
       <c r="O278" s="5" t="n">
-        <v>3.81</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B279" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E279" s="5" t="inlineStr">
@@ -18398,12 +18434,12 @@
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H279" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I279" s="5" t="b">
@@ -18425,26 +18461,26 @@
         <v>1</v>
       </c>
       <c r="O279" s="5" t="n">
-        <v>5.16</v>
+        <v>9.029999999999999</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports_002</t>
+          <t>multilingual_edge_003</t>
         </is>
       </c>
       <c r="B280" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>multilingual_edge</t>
         </is>
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E280" s="5" t="inlineStr">
@@ -18459,12 +18495,12 @@
       </c>
       <c r="G280" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H280" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I280" s="5" t="b">
@@ -18480,32 +18516,32 @@
       </c>
       <c r="L280" s="5" t="n"/>
       <c r="M280" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N280" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O280" s="5" t="n">
-        <v>13.07</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B281" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C281" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E281" s="5" t="inlineStr">
@@ -18520,12 +18556,12 @@
       </c>
       <c r="G281" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H281" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I281" s="5" t="b">
@@ -18547,46 +18583,46 @@
         <v>1</v>
       </c>
       <c r="O281" s="5" t="n">
-        <v>7.85</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B282" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E282" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F282" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H282" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I282" s="5" t="b">
@@ -18608,46 +18644,46 @@
         <v>1</v>
       </c>
       <c r="O282" s="5" t="n">
-        <v>8.73</v>
+        <v>16.45</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
         <is>
-          <t>ask_query_002</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B283" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C283" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E283" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F283" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H283" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I283" s="5" t="b">
@@ -18669,31 +18705,31 @@
         <v>1</v>
       </c>
       <c r="O283" s="5" t="n">
-        <v>4.92</v>
+        <v>16.76</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B284" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C284" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E284" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F284" s="5" t="inlineStr">
@@ -18703,7 +18739,7 @@
       </c>
       <c r="G284" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H284" s="5" t="inlineStr">
@@ -18730,26 +18766,26 @@
         <v>1</v>
       </c>
       <c r="O284" s="5" t="n">
-        <v>18.94</v>
+        <v>20.52</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B285" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C285" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E285" s="5" t="inlineStr">
@@ -18759,12 +18795,12 @@
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H285" s="5" t="inlineStr">
@@ -18791,46 +18827,46 @@
         <v>1</v>
       </c>
       <c r="O285" s="5" t="n">
-        <v>21.38</v>
+        <v>18.23</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_002</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B286" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E286" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H286" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I286" s="5" t="b">
@@ -18846,37 +18882,37 @@
       </c>
       <c r="L286" s="5" t="n"/>
       <c r="M286" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N286" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O286" s="5" t="n">
-        <v>14.78</v>
+        <v>18.17</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B287" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E287" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F287" s="5" t="inlineStr">
@@ -18886,12 +18922,12 @@
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H287" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I287" s="5" t="b">
@@ -18913,46 +18949,46 @@
         <v>1</v>
       </c>
       <c r="O287" s="5" t="n">
-        <v>7.87</v>
+        <v>20.49</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B288" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E288" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H288" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I288" s="5" t="b">
@@ -18974,26 +19010,26 @@
         <v>1</v>
       </c>
       <c r="O288" s="5" t="n">
-        <v>9.029999999999999</v>
+        <v>17.83</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge_003</t>
+          <t>single_kg2_004</t>
         </is>
       </c>
       <c r="B289" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E289" s="5" t="inlineStr">
@@ -19003,17 +19039,17 @@
       </c>
       <c r="F289" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H289" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I289" s="5" t="b">
@@ -19035,26 +19071,26 @@
         <v>1</v>
       </c>
       <c r="O289" s="5" t="n">
-        <v>5.17</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>count_kg1_001</t>
         </is>
       </c>
       <c r="B290" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E290" s="5" t="inlineStr">
@@ -19069,12 +19105,12 @@
       </c>
       <c r="G290" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H290" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I290" s="5" t="b">
@@ -19096,46 +19132,46 @@
         <v>1</v>
       </c>
       <c r="O290" s="5" t="n">
-        <v>19.5</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>count_kg1_001</t>
         </is>
       </c>
       <c r="B291" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E291" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F291" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H291" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I291" s="5" t="b">
@@ -19157,46 +19193,46 @@
         <v>1</v>
       </c>
       <c r="O291" s="5" t="n">
-        <v>16.45</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>count_kg1_001</t>
         </is>
       </c>
       <c r="B292" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>count_kg1</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E292" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F292" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H292" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I292" s="5" t="b">
@@ -19218,13 +19254,13 @@
         <v>1</v>
       </c>
       <c r="O292" s="5" t="n">
-        <v>16.76</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>open_kg_004</t>
         </is>
       </c>
       <c r="B293" s="5" t="n">
@@ -19232,17 +19268,17 @@
       </c>
       <c r="C293" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E293" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F293" s="5" t="inlineStr">
@@ -19252,12 +19288,12 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I293" s="5" t="b">
@@ -19279,13 +19315,13 @@
         <v>1</v>
       </c>
       <c r="O293" s="5" t="n">
-        <v>20.52</v>
+        <v>30.85</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>open_kg_004</t>
         </is>
       </c>
       <c r="B294" s="5" t="n">
@@ -19293,12 +19329,12 @@
       </c>
       <c r="C294" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E294" s="5" t="inlineStr">
@@ -19308,17 +19344,17 @@
       </c>
       <c r="F294" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H294" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I294" s="5" t="b">
@@ -19340,13 +19376,13 @@
         <v>1</v>
       </c>
       <c r="O294" s="5" t="n">
-        <v>18.23</v>
+        <v>30.75</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>open_kg_004</t>
         </is>
       </c>
       <c r="B295" s="5" t="n">
@@ -19354,32 +19390,32 @@
       </c>
       <c r="C295" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E295" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F295" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I295" s="5" t="b">
@@ -19401,13 +19437,13 @@
         <v>1</v>
       </c>
       <c r="O295" s="5" t="n">
-        <v>18.17</v>
+        <v>27.83</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>open_kg_001</t>
         </is>
       </c>
       <c r="B296" s="5" t="n">
@@ -19415,17 +19451,17 @@
       </c>
       <c r="C296" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E296" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F296" s="5" t="inlineStr">
@@ -19435,12 +19471,12 @@
       </c>
       <c r="G296" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H296" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I296" s="5" t="b">
@@ -19455,20 +19491,16 @@
         </is>
       </c>
       <c r="L296" s="5" t="n"/>
-      <c r="M296" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N296" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M296" s="5" t="n"/>
+      <c r="N296" s="5" t="n"/>
       <c r="O296" s="5" t="n">
-        <v>20.49</v>
+        <v>23.94</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>open_kg_001</t>
         </is>
       </c>
       <c r="B297" s="5" t="n">
@@ -19476,32 +19508,32 @@
       </c>
       <c r="C297" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E297" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F297" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I297" s="5" t="b">
@@ -19516,20 +19548,16 @@
         </is>
       </c>
       <c r="L297" s="5" t="n"/>
-      <c r="M297" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N297" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M297" s="5" t="n"/>
+      <c r="N297" s="5" t="n"/>
       <c r="O297" s="5" t="n">
-        <v>17.83</v>
+        <v>24.11</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_004</t>
+          <t>open_kg_001</t>
         </is>
       </c>
       <c r="B298" s="5" t="n">
@@ -19537,12 +19565,12 @@
       </c>
       <c r="C298" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D298" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E298" s="5" t="inlineStr">
@@ -19552,17 +19580,17 @@
       </c>
       <c r="F298" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G298" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H298" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I298" s="5" t="b">
@@ -19577,33 +19605,29 @@
         </is>
       </c>
       <c r="L298" s="5" t="n"/>
-      <c r="M298" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N298" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M298" s="5" t="n"/>
+      <c r="N298" s="5" t="n"/>
       <c r="O298" s="5" t="n">
-        <v>17.58</v>
+        <v>24.07</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_001</t>
+          <t>open_kg_006</t>
         </is>
       </c>
       <c r="B299" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C299" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D299" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E299" s="5" t="inlineStr">
@@ -19618,12 +19642,12 @@
       </c>
       <c r="G299" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H299" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I299" s="5" t="b">
@@ -19638,33 +19662,29 @@
         </is>
       </c>
       <c r="L299" s="5" t="n"/>
-      <c r="M299" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N299" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M299" s="5" t="n"/>
+      <c r="N299" s="5" t="n"/>
       <c r="O299" s="5" t="n">
-        <v>9.44</v>
+        <v>22.37</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_001</t>
+          <t>open_kg_006</t>
         </is>
       </c>
       <c r="B300" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C300" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D300" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E300" s="5" t="inlineStr">
@@ -19679,12 +19699,12 @@
       </c>
       <c r="G300" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H300" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I300" s="5" t="b">
@@ -19699,33 +19719,29 @@
         </is>
       </c>
       <c r="L300" s="5" t="n"/>
-      <c r="M300" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N300" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M300" s="5" t="n"/>
+      <c r="N300" s="5" t="n"/>
       <c r="O300" s="5" t="n">
-        <v>9.07</v>
+        <v>22.89</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
         <is>
-          <t>count_kg1_001</t>
+          <t>open_kg_006</t>
         </is>
       </c>
       <c r="B301" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
-          <t>count_kg1</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D301" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E301" s="5" t="inlineStr">
@@ -19740,12 +19756,12 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I301" s="5" t="b">
@@ -19760,20 +19776,16 @@
         </is>
       </c>
       <c r="L301" s="5" t="n"/>
-      <c r="M301" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N301" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M301" s="5" t="n"/>
+      <c r="N301" s="5" t="n"/>
       <c r="O301" s="5" t="n">
-        <v>8.92</v>
+        <v>22.82</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="5" t="inlineStr">
         <is>
-          <t>open_kg_004</t>
+          <t>open_kg_003</t>
         </is>
       </c>
       <c r="B302" s="5" t="n">
@@ -19828,13 +19840,13 @@
         <v>1</v>
       </c>
       <c r="O302" s="5" t="n">
-        <v>30.85</v>
+        <v>47.46</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="5" t="inlineStr">
         <is>
-          <t>open_kg_004</t>
+          <t>open_kg_003</t>
         </is>
       </c>
       <c r="B303" s="5" t="n">
@@ -19889,13 +19901,13 @@
         <v>1</v>
       </c>
       <c r="O303" s="5" t="n">
-        <v>30.75</v>
+        <v>22.92</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="5" t="inlineStr">
         <is>
-          <t>open_kg_004</t>
+          <t>open_kg_003</t>
         </is>
       </c>
       <c r="B304" s="5" t="n">
@@ -19950,27 +19962,25 @@
         <v>1</v>
       </c>
       <c r="O304" s="5" t="n">
-        <v>27.83</v>
+        <v>29.16</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="5" t="inlineStr">
         <is>
-          <t>open_kg_001</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B305" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C305" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
-        </is>
-      </c>
-      <c r="D305" s="5" t="inlineStr">
-        <is>
-          <t>cross</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D305" s="5" t="n">
+        <v/>
       </c>
       <c r="E305" s="5" t="inlineStr">
         <is>
@@ -19984,19 +19994,19 @@
       </c>
       <c r="G305" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H305" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I305" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J305" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K305" s="5" t="inlineStr">
         <is>
@@ -20007,27 +20017,25 @@
       <c r="M305" s="5" t="n"/>
       <c r="N305" s="5" t="n"/>
       <c r="O305" s="5" t="n">
-        <v>23.94</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="5" t="inlineStr">
         <is>
-          <t>open_kg_001</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B306" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C306" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
-        </is>
-      </c>
-      <c r="D306" s="5" t="inlineStr">
-        <is>
-          <t>cross</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D306" s="5" t="n">
+        <v/>
       </c>
       <c r="E306" s="5" t="inlineStr">
         <is>
@@ -20041,19 +20049,19 @@
       </c>
       <c r="G306" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H306" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I306" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J306" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K306" s="5" t="inlineStr">
         <is>
@@ -20064,27 +20072,25 @@
       <c r="M306" s="5" t="n"/>
       <c r="N306" s="5" t="n"/>
       <c r="O306" s="5" t="n">
-        <v>24.11</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="5" t="inlineStr">
         <is>
-          <t>open_kg_001</t>
+          <t>out_of_scope_001</t>
         </is>
       </c>
       <c r="B307" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C307" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
-        </is>
-      </c>
-      <c r="D307" s="5" t="inlineStr">
-        <is>
-          <t>cross</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D307" s="5" t="n">
+        <v/>
       </c>
       <c r="E307" s="5" t="inlineStr">
         <is>
@@ -20098,19 +20104,19 @@
       </c>
       <c r="G307" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H307" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I307" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J307" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K307" s="5" t="inlineStr">
         <is>
@@ -20121,27 +20127,25 @@
       <c r="M307" s="5" t="n"/>
       <c r="N307" s="5" t="n"/>
       <c r="O307" s="5" t="n">
-        <v>24.07</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="5" t="inlineStr">
         <is>
-          <t>open_kg_005</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B308" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C308" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
-        </is>
-      </c>
-      <c r="D308" s="5" t="inlineStr">
-        <is>
-          <t>cross</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D308" s="5" t="n">
+        <v/>
       </c>
       <c r="E308" s="5" t="inlineStr">
         <is>
@@ -20155,54 +20159,48 @@
       </c>
       <c r="G308" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H308" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I308" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J308" s="5" t="b">
         <v>0</v>
       </c>
       <c r="K308" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L308" s="5" t="inlineStr">
-        <is>
-          <t>params={'property': 'surface', 'value': 'asphalt', 'limit': 10}</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L308" s="5" t="n"/>
       <c r="M308" s="5" t="n"/>
       <c r="N308" s="5" t="n"/>
       <c r="O308" s="5" t="n">
-        <v>12.13</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="5" t="inlineStr">
         <is>
-          <t>open_kg_005</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B309" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C309" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
-        </is>
-      </c>
-      <c r="D309" s="5" t="inlineStr">
-        <is>
-          <t>cross</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D309" s="5" t="n">
+        <v/>
       </c>
       <c r="E309" s="5" t="inlineStr">
         <is>
@@ -20216,54 +20214,48 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I309" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J309" s="5" t="b">
         <v>0</v>
       </c>
       <c r="K309" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L309" s="5" t="inlineStr">
-        <is>
-          <t>params={'property': 'surface', 'value': 'asphalt', 'limit': 10}</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L309" s="5" t="n"/>
       <c r="M309" s="5" t="n"/>
       <c r="N309" s="5" t="n"/>
       <c r="O309" s="5" t="n">
-        <v>11.86</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="5" t="inlineStr">
         <is>
-          <t>open_kg_005</t>
+          <t>out_of_scope_003</t>
         </is>
       </c>
       <c r="B310" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C310" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
-        </is>
-      </c>
-      <c r="D310" s="5" t="inlineStr">
-        <is>
-          <t>cross</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D310" s="5" t="n">
+        <v/>
       </c>
       <c r="E310" s="5" t="inlineStr">
         <is>
@@ -20277,36 +20269,36 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I310" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J310" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K310" s="5" t="inlineStr">
         <is>
-          <t>no_results</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L310" s="5" t="n"/>
       <c r="M310" s="5" t="n"/>
       <c r="N310" s="5" t="n"/>
       <c r="O310" s="5" t="n">
-        <v>32.39</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="5" t="inlineStr">
         <is>
-          <t>open_kg_006</t>
+          <t>open_kg_005</t>
         </is>
       </c>
       <c r="B311" s="5" t="n">
@@ -20346,24 +20338,24 @@
         <v>1</v>
       </c>
       <c r="J311" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K311" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>generation_failure</t>
         </is>
       </c>
       <c r="L311" s="5" t="n"/>
       <c r="M311" s="5" t="n"/>
       <c r="N311" s="5" t="n"/>
       <c r="O311" s="5" t="n">
-        <v>22.37</v>
+        <v>55.57</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="5" t="inlineStr">
         <is>
-          <t>open_kg_006</t>
+          <t>open_kg_005</t>
         </is>
       </c>
       <c r="B312" s="5" t="n">
@@ -20403,24 +20395,24 @@
         <v>1</v>
       </c>
       <c r="J312" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K312" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>generation_failure</t>
         </is>
       </c>
       <c r="L312" s="5" t="n"/>
       <c r="M312" s="5" t="n"/>
       <c r="N312" s="5" t="n"/>
       <c r="O312" s="5" t="n">
-        <v>22.89</v>
+        <v>41.77</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="5" t="inlineStr">
         <is>
-          <t>open_kg_006</t>
+          <t>open_kg_005</t>
         </is>
       </c>
       <c r="B313" s="5" t="n">
@@ -20460,38 +20452,36 @@
         <v>1</v>
       </c>
       <c r="J313" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K313" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>generation_failure</t>
         </is>
       </c>
       <c r="L313" s="5" t="n"/>
       <c r="M313" s="5" t="n"/>
       <c r="N313" s="5" t="n"/>
       <c r="O313" s="5" t="n">
-        <v>22.82</v>
+        <v>37.66</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="5" t="inlineStr">
         <is>
-          <t>open_kg_003</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B314" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C314" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
-        </is>
-      </c>
-      <c r="D314" s="5" t="inlineStr">
-        <is>
-          <t>cross</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D314" s="5" t="n">
+        <v/>
       </c>
       <c r="E314" s="5" t="inlineStr">
         <is>
@@ -20505,19 +20495,19 @@
       </c>
       <c r="G314" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H314" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I314" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J314" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K314" s="5" t="inlineStr">
         <is>
@@ -20525,34 +20515,28 @@
         </is>
       </c>
       <c r="L314" s="5" t="n"/>
-      <c r="M314" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N314" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M314" s="5" t="n"/>
+      <c r="N314" s="5" t="n"/>
       <c r="O314" s="5" t="n">
-        <v>47.46</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="5" t="inlineStr">
         <is>
-          <t>open_kg_003</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B315" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C315" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
-        </is>
-      </c>
-      <c r="D315" s="5" t="inlineStr">
-        <is>
-          <t>cross</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D315" s="5" t="n">
+        <v/>
       </c>
       <c r="E315" s="5" t="inlineStr">
         <is>
@@ -20566,19 +20550,19 @@
       </c>
       <c r="G315" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H315" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I315" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J315" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K315" s="5" t="inlineStr">
         <is>
@@ -20586,34 +20570,28 @@
         </is>
       </c>
       <c r="L315" s="5" t="n"/>
-      <c r="M315" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N315" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M315" s="5" t="n"/>
+      <c r="N315" s="5" t="n"/>
       <c r="O315" s="5" t="n">
-        <v>22.92</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="5" t="inlineStr">
         <is>
-          <t>open_kg_003</t>
+          <t>out_of_scope_002</t>
         </is>
       </c>
       <c r="B316" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C316" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
-        </is>
-      </c>
-      <c r="D316" s="5" t="inlineStr">
-        <is>
-          <t>cross</t>
-        </is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="D316" s="5" t="n">
+        <v/>
       </c>
       <c r="E316" s="5" t="inlineStr">
         <is>
@@ -20627,19 +20605,19 @@
       </c>
       <c r="G316" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="H316" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I316" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J316" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K316" s="5" t="inlineStr">
         <is>
@@ -20647,20 +20625,16 @@
         </is>
       </c>
       <c r="L316" s="5" t="n"/>
-      <c r="M316" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N316" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M316" s="5" t="n"/>
+      <c r="N316" s="5" t="n"/>
       <c r="O316" s="5" t="n">
-        <v>29.16</v>
+        <v>18.64</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B317" s="5" t="n">
@@ -20668,11 +20642,13 @@
       </c>
       <c r="C317" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D317" s="5" t="n">
-        <v/>
+          <t>property_ambiguity</t>
+        </is>
+      </c>
+      <c r="D317" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E317" s="5" t="inlineStr">
         <is>
@@ -20686,19 +20662,19 @@
       </c>
       <c r="G317" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H317" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I317" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J317" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K317" s="5" t="inlineStr">
         <is>
@@ -20706,16 +20682,20 @@
         </is>
       </c>
       <c r="L317" s="5" t="n"/>
-      <c r="M317" s="5" t="n"/>
-      <c r="N317" s="5" t="n"/>
+      <c r="M317" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N317" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O317" s="5" t="n">
-        <v>4.83</v>
+        <v>26.56</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B318" s="5" t="n">
@@ -20723,11 +20703,13 @@
       </c>
       <c r="C318" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D318" s="5" t="n">
-        <v/>
+          <t>property_ambiguity</t>
+        </is>
+      </c>
+      <c r="D318" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E318" s="5" t="inlineStr">
         <is>
@@ -20741,19 +20723,19 @@
       </c>
       <c r="G318" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H318" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I318" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J318" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K318" s="5" t="inlineStr">
         <is>
@@ -20761,16 +20743,20 @@
         </is>
       </c>
       <c r="L318" s="5" t="n"/>
-      <c r="M318" s="5" t="n"/>
-      <c r="N318" s="5" t="n"/>
+      <c r="M318" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N318" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O318" s="5" t="n">
-        <v>4.58</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_001</t>
+          <t>property_ambiguity_001</t>
         </is>
       </c>
       <c r="B319" s="5" t="n">
@@ -20778,11 +20764,13 @@
       </c>
       <c r="C319" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D319" s="5" t="n">
-        <v/>
+          <t>property_ambiguity</t>
+        </is>
+      </c>
+      <c r="D319" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E319" s="5" t="inlineStr">
         <is>
@@ -20796,19 +20784,19 @@
       </c>
       <c r="G319" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H319" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I319" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J319" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K319" s="5" t="inlineStr">
         <is>
@@ -20816,16 +20804,20 @@
         </is>
       </c>
       <c r="L319" s="5" t="n"/>
-      <c r="M319" s="5" t="n"/>
-      <c r="N319" s="5" t="n"/>
+      <c r="M319" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N319" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O319" s="5" t="n">
-        <v>4.08</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B320" s="5" t="n">
@@ -20833,11 +20825,13 @@
       </c>
       <c r="C320" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D320" s="5" t="n">
-        <v/>
+          <t>property_ambiguity</t>
+        </is>
+      </c>
+      <c r="D320" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E320" s="5" t="inlineStr">
         <is>
@@ -20851,19 +20845,19 @@
       </c>
       <c r="G320" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H320" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I320" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J320" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K320" s="5" t="inlineStr">
         <is>
@@ -20871,16 +20865,20 @@
         </is>
       </c>
       <c r="L320" s="5" t="n"/>
-      <c r="M320" s="5" t="n"/>
-      <c r="N320" s="5" t="n"/>
+      <c r="M320" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N320" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O320" s="5" t="n">
-        <v>4.66</v>
+        <v>12.37</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B321" s="5" t="n">
@@ -20888,11 +20886,13 @@
       </c>
       <c r="C321" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D321" s="5" t="n">
-        <v/>
+          <t>property_ambiguity</t>
+        </is>
+      </c>
+      <c r="D321" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E321" s="5" t="inlineStr">
         <is>
@@ -20906,19 +20906,19 @@
       </c>
       <c r="G321" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H321" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I321" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J321" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K321" s="5" t="inlineStr">
         <is>
@@ -20926,16 +20926,20 @@
         </is>
       </c>
       <c r="L321" s="5" t="n"/>
-      <c r="M321" s="5" t="n"/>
-      <c r="N321" s="5" t="n"/>
+      <c r="M321" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N321" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O321" s="5" t="n">
-        <v>3.85</v>
+        <v>12.88</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_003</t>
+          <t>property_ambiguity_003</t>
         </is>
       </c>
       <c r="B322" s="5" t="n">
@@ -20943,11 +20947,13 @@
       </c>
       <c r="C322" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D322" s="5" t="n">
-        <v/>
+          <t>property_ambiguity</t>
+        </is>
+      </c>
+      <c r="D322" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E322" s="5" t="inlineStr">
         <is>
@@ -20961,19 +20967,19 @@
       </c>
       <c r="G322" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H322" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I322" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J322" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K322" s="5" t="inlineStr">
         <is>
@@ -20981,16 +20987,20 @@
         </is>
       </c>
       <c r="L322" s="5" t="n"/>
-      <c r="M322" s="5" t="n"/>
-      <c r="N322" s="5" t="n"/>
+      <c r="M322" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N322" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O322" s="5" t="n">
-        <v>3.85</v>
+        <v>26.08</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B323" s="5" t="n">
@@ -20998,11 +21008,13 @@
       </c>
       <c r="C323" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D323" s="5" t="n">
-        <v/>
+          <t>property_ambiguity</t>
+        </is>
+      </c>
+      <c r="D323" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E323" s="5" t="inlineStr">
         <is>
@@ -21016,19 +21028,19 @@
       </c>
       <c r="G323" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H323" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I323" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J323" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K323" s="5" t="inlineStr">
         <is>
@@ -21036,16 +21048,20 @@
         </is>
       </c>
       <c r="L323" s="5" t="n"/>
-      <c r="M323" s="5" t="n"/>
-      <c r="N323" s="5" t="n"/>
+      <c r="M323" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N323" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O323" s="5" t="n">
-        <v>29.27</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B324" s="5" t="n">
@@ -21053,11 +21069,13 @@
       </c>
       <c r="C324" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D324" s="5" t="n">
-        <v/>
+          <t>property_ambiguity</t>
+        </is>
+      </c>
+      <c r="D324" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E324" s="5" t="inlineStr">
         <is>
@@ -21071,36 +21089,40 @@
       </c>
       <c r="G324" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H324" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I324" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J324" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K324" s="5" t="inlineStr">
+        <is>
+          <t>no_results</t>
+        </is>
+      </c>
+      <c r="L324" s="5" t="n"/>
+      <c r="M324" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="K324" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L324" s="5" t="n"/>
-      <c r="M324" s="5" t="n"/>
-      <c r="N324" s="5" t="n"/>
+      <c r="N324" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O324" s="5" t="n">
-        <v>13.5</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope_002</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B325" s="5" t="n">
@@ -21108,11 +21130,13 @@
       </c>
       <c r="C325" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="D325" s="5" t="n">
-        <v/>
+          <t>property_ambiguity</t>
+        </is>
+      </c>
+      <c r="D325" s="5" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
       </c>
       <c r="E325" s="5" t="inlineStr">
         <is>
@@ -21126,19 +21150,19 @@
       </c>
       <c r="G325" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H325" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I325" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J325" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K325" s="5" t="inlineStr">
         <is>
@@ -21146,10 +21170,14 @@
         </is>
       </c>
       <c r="L325" s="5" t="n"/>
-      <c r="M325" s="5" t="n"/>
-      <c r="N325" s="5" t="n"/>
+      <c r="M325" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N325" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O325" s="5" t="n">
-        <v>17.35</v>
+        <v>12.13</v>
       </c>
     </row>
   </sheetData>
